--- a/Financial Analysis/RBLX.xlsx
+++ b/Financial Analysis/RBLX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD210C7B-85C5-46A0-B0E5-E8D18B59D1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F17B5E-E6C4-494A-B61B-AFC99A2AF171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{20A32264-496F-49BA-BE16-734192C30A81}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="97">
   <si>
     <t>RBLX</t>
   </si>
@@ -268,7 +268,55 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+  </si>
+  <si>
+    <t>SBC</t>
+  </si>
+  <si>
+    <t>Leases</t>
+  </si>
+  <si>
+    <t>Securities</t>
+  </si>
+  <si>
+    <t>Impairment</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>Prepaids</t>
+  </si>
+  <si>
+    <t>D/R</t>
+  </si>
+  <si>
+    <t>Other assets</t>
+  </si>
+  <si>
+    <t>A/P</t>
+  </si>
+  <si>
+    <t>A/L</t>
+  </si>
+  <si>
+    <t>Other liabilities</t>
+  </si>
+  <si>
+    <t>ONCL</t>
+  </si>
+  <si>
+    <t>CFFO</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>FCF</t>
   </si>
 </sst>
 </file>
@@ -368,16 +416,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -392,8 +440,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19179540" y="0"/>
-          <a:ext cx="0" cy="6499860"/>
+          <a:off x="20406360" y="0"/>
+          <a:ext cx="0" cy="10896600"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -426,8 +474,8 @@
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -443,7 +491,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="27111960" y="0"/>
-          <a:ext cx="0" cy="6492240"/>
+          <a:ext cx="0" cy="10896600"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -791,17 +839,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>74.09</v>
+        <v>128.47</v>
       </c>
       <c r="E3" s="3">
-        <v>45781</v>
+        <v>45909</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="3">
-        <v>45784</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -809,11 +857,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>630+48.3</f>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,7 +870,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>50255.246999999996</v>
+        <v>82863.149999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -830,11 +878,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>1158.7+1585.8+1766</f>
-        <v>4510.5</v>
+        <f>994.6+1632.6+2111.3</f>
+        <v>4738.5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -842,11 +890,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>1006.7</f>
-        <v>1006.7</v>
+        <f>992.4</f>
+        <v>992.4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -855,7 +903,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>3503.8</v>
+        <v>3746.1</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -864,7 +912,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>46751.446999999993</v>
+        <v>79117.049999999988</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA5E306-D0AF-4AEC-99D7-81A5EBC23309}">
-  <dimension ref="B2:FK34"/>
+  <dimension ref="B2:FK61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -1131,16 +1179,14 @@
         <v>1035.2</v>
       </c>
       <c r="AF3" s="9">
-        <f>AB3*1.28</f>
-        <v>1143.68</v>
+        <v>1080.7</v>
       </c>
       <c r="AG3" s="9">
-        <f t="shared" ref="AG3" si="0">AC3*1.28</f>
-        <v>1176.32</v>
+        <v>1135</v>
       </c>
       <c r="AH3" s="9">
-        <f>AD3*1.23</f>
-        <v>1215.4860000000001</v>
+        <f>AD3*1.22</f>
+        <v>1205.604</v>
       </c>
       <c r="AI3" s="10"/>
       <c r="AK3" s="9">
@@ -1172,47 +1218,47 @@
       </c>
       <c r="AR3" s="9">
         <f>SUM(AE3:AH3)</f>
-        <v>4570.6859999999997</v>
+        <v>4456.5039999999999</v>
       </c>
       <c r="AS3" s="9">
         <f>AR3*1.22</f>
-        <v>5576.2369199999994</v>
+        <v>5436.9348799999998</v>
       </c>
       <c r="AT3" s="9">
         <f>AS3*1.18</f>
-        <v>6579.9595655999992</v>
+        <v>6415.5831583999998</v>
       </c>
       <c r="AU3" s="9">
         <f>AT3*1.15</f>
-        <v>7566.9535004399986</v>
+        <v>7377.9206321599995</v>
       </c>
       <c r="AV3" s="9">
         <f>AU3*1.12</f>
-        <v>8474.9879204927984</v>
+        <v>8263.2711080192003</v>
       </c>
       <c r="AW3" s="9">
         <f>AV3*1.09</f>
-        <v>9237.7368333371505</v>
+        <v>9006.9655077409298</v>
       </c>
       <c r="AX3" s="9">
         <f>AW3*1.07</f>
-        <v>9884.378411670752</v>
+        <v>9637.4530932827947</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.06</f>
-        <v>10477.441116370997</v>
+        <v>10215.700278879764</v>
       </c>
       <c r="AZ3" s="9">
-        <f t="shared" ref="AZ3:BB3" si="1">AY3*1.05</f>
-        <v>11001.313172189548</v>
+        <f t="shared" ref="AZ3:BB3" si="0">AY3*1.05</f>
+        <v>10726.485292823752</v>
       </c>
       <c r="BA3" s="9">
-        <f t="shared" si="1"/>
-        <v>11551.378830799025</v>
+        <f t="shared" si="0"/>
+        <v>11262.80955746494</v>
       </c>
       <c r="BB3" s="9">
-        <f t="shared" si="1"/>
-        <v>12128.947772338977</v>
+        <f t="shared" si="0"/>
+        <v>11825.950035338186</v>
       </c>
       <c r="BC3" s="9"/>
     </row>
@@ -1309,16 +1355,15 @@
         <v>224.7</v>
       </c>
       <c r="AF4" s="5">
-        <f t="shared" ref="AF4:AH4" si="2">AF3*0.22</f>
-        <v>251.60960000000003</v>
+        <v>236.1</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" si="2"/>
-        <v>258.79039999999998</v>
+        <f t="shared" ref="AG4:AH4" si="1">AG3*0.22</f>
+        <v>249.7</v>
       </c>
       <c r="AH4" s="5">
-        <f t="shared" si="2"/>
-        <v>267.40692000000001</v>
+        <f t="shared" si="1"/>
+        <v>265.23288000000002</v>
       </c>
       <c r="AK4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1349,47 +1394,47 @@
       </c>
       <c r="AR4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>1002.50692</v>
+        <v>975.73288000000002</v>
       </c>
       <c r="AS4" s="5">
         <f>AS3*0.22</f>
-        <v>1226.7721223999999</v>
+        <v>1196.1256736</v>
       </c>
       <c r="AT4" s="5">
-        <f t="shared" ref="AT4:BB4" si="3">AT3*0.22</f>
-        <v>1447.5911044319998</v>
+        <f t="shared" ref="AT4:BB4" si="2">AT3*0.22</f>
+        <v>1411.428294848</v>
       </c>
       <c r="AU4" s="5">
-        <f t="shared" si="3"/>
-        <v>1664.7297700967997</v>
+        <f t="shared" si="2"/>
+        <v>1623.1425390751999</v>
       </c>
       <c r="AV4" s="5">
-        <f t="shared" si="3"/>
-        <v>1864.4973425084156</v>
+        <f t="shared" si="2"/>
+        <v>1817.919643764224</v>
       </c>
       <c r="AW4" s="5">
-        <f t="shared" si="3"/>
-        <v>2032.3021033341731</v>
+        <f t="shared" si="2"/>
+        <v>1981.5324117030045</v>
       </c>
       <c r="AX4" s="5">
-        <f t="shared" si="3"/>
-        <v>2174.5632505675653</v>
+        <f t="shared" si="2"/>
+        <v>2120.2396805222147</v>
       </c>
       <c r="AY4" s="5">
-        <f t="shared" si="3"/>
-        <v>2305.0370456016194</v>
+        <f t="shared" si="2"/>
+        <v>2247.4540613535478</v>
       </c>
       <c r="AZ4" s="5">
-        <f t="shared" si="3"/>
-        <v>2420.2888978817004</v>
+        <f t="shared" si="2"/>
+        <v>2359.8267644212256</v>
       </c>
       <c r="BA4" s="5">
-        <f t="shared" si="3"/>
-        <v>2541.3033427757855</v>
+        <f t="shared" si="2"/>
+        <v>2477.8181026422867</v>
       </c>
       <c r="BB4" s="5">
-        <f t="shared" si="3"/>
-        <v>2668.368509914575</v>
+        <f t="shared" si="2"/>
+        <v>2601.709007774401</v>
       </c>
     </row>
     <row r="5" spans="2:55" x14ac:dyDescent="0.3">
@@ -1485,16 +1530,15 @@
         <v>281.60000000000002</v>
       </c>
       <c r="AF5" s="5">
-        <f>AF3*0.25</f>
-        <v>285.92</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="AG5" s="5">
-        <f>AG3*0.25</f>
-        <v>294.08</v>
+        <f>AG3*0.28</f>
+        <v>317.8</v>
       </c>
       <c r="AH5" s="5">
-        <f>AH3*0.28</f>
-        <v>340.33608000000004</v>
+        <f>AH3*0.3</f>
+        <v>361.68119999999999</v>
       </c>
       <c r="AK5" s="5">
         <f>SUM(C5:F5)</f>
@@ -1525,47 +1569,47 @@
       </c>
       <c r="AR5" s="5">
         <f>SUM(AE5:AH5)</f>
-        <v>1201.9360799999999</v>
+        <v>1277.4811999999999</v>
       </c>
       <c r="AS5" s="5">
-        <f>AS3*0.24</f>
-        <v>1338.2968607999999</v>
+        <f>AS3*0.28</f>
+        <v>1522.3417664000001</v>
       </c>
       <c r="AT5" s="5">
-        <f>AT3*0.23</f>
-        <v>1513.3907000879999</v>
+        <f t="shared" ref="AT5:BB5" si="3">AT3*0.28</f>
+        <v>1796.3632843520002</v>
       </c>
       <c r="AU5" s="5">
-        <f>AU3*0.22</f>
-        <v>1664.7297700967997</v>
+        <f t="shared" si="3"/>
+        <v>2065.8177770048001</v>
       </c>
       <c r="AV5" s="5">
-        <f>AV3*0.21</f>
-        <v>1779.7474633034876</v>
+        <f t="shared" si="3"/>
+        <v>2313.7159102453761</v>
       </c>
       <c r="AW5" s="5">
-        <f t="shared" ref="AW5:BB5" si="4">AW3*0.21</f>
-        <v>1939.9247350008015</v>
+        <f t="shared" si="3"/>
+        <v>2521.9503421674603</v>
       </c>
       <c r="AX5" s="5">
-        <f t="shared" si="4"/>
-        <v>2075.7194664508579</v>
+        <f t="shared" si="3"/>
+        <v>2698.4868661191827</v>
       </c>
       <c r="AY5" s="5">
-        <f t="shared" si="4"/>
-        <v>2200.2626344379096</v>
+        <f t="shared" si="3"/>
+        <v>2860.396078086334</v>
       </c>
       <c r="AZ5" s="5">
-        <f t="shared" si="4"/>
-        <v>2310.2757661598048</v>
+        <f t="shared" si="3"/>
+        <v>3003.4158819906511</v>
       </c>
       <c r="BA5" s="5">
-        <f t="shared" si="4"/>
-        <v>2425.7895544677954</v>
+        <f t="shared" si="3"/>
+        <v>3153.5866760901836</v>
       </c>
       <c r="BB5" s="5">
-        <f t="shared" si="4"/>
-        <v>2547.079032191185</v>
+        <f t="shared" si="3"/>
+        <v>3311.2660098946926</v>
       </c>
     </row>
     <row r="6" spans="2:55" x14ac:dyDescent="0.3">
@@ -1661,16 +1705,15 @@
         <v>242.1</v>
       </c>
       <c r="AF6" s="5">
-        <f>AB6*1.08</f>
-        <v>238.78800000000001</v>
+        <v>260.7</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" ref="AG6:AH6" si="5">AC6*1.04</f>
-        <v>254.38400000000001</v>
+        <f>AC6*1.12</f>
+        <v>273.952</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="5"/>
-        <v>231.71200000000002</v>
+        <f>AD6*1.15</f>
+        <v>256.21999999999997</v>
       </c>
       <c r="AK6" s="5">
         <f>SUM(C6:F6)</f>
@@ -1701,47 +1744,47 @@
       </c>
       <c r="AR6" s="5">
         <f>SUM(AE6:AH6)</f>
-        <v>966.98400000000004</v>
+        <v>1032.972</v>
       </c>
       <c r="AS6" s="5">
         <f>AR6*1.03</f>
-        <v>995.9935200000001</v>
+        <v>1063.9611600000001</v>
       </c>
       <c r="AT6" s="5">
         <f>AS6*1.02</f>
-        <v>1015.9133904000001</v>
+        <v>1085.2403832</v>
       </c>
       <c r="AU6" s="5">
         <f>AT6*1.02</f>
-        <v>1036.2316582080002</v>
+        <v>1106.9451908640001</v>
       </c>
       <c r="AV6" s="5">
         <f>AU6*1.02</f>
-        <v>1056.9562913721602</v>
+        <v>1129.08409468128</v>
       </c>
       <c r="AW6" s="5">
         <f>AV6*1.02</f>
-        <v>1078.0954171996034</v>
+        <v>1151.6657765749057</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" ref="AX6:BB6" si="6">AW6*1.01</f>
-        <v>1088.8763713715994</v>
+        <f t="shared" ref="AX6:BB6" si="4">AW6*1.01</f>
+        <v>1163.1824343406547</v>
       </c>
       <c r="AY6" s="5">
-        <f t="shared" si="6"/>
-        <v>1099.7651350853155</v>
+        <f t="shared" si="4"/>
+        <v>1174.8142586840613</v>
       </c>
       <c r="AZ6" s="5">
-        <f t="shared" si="6"/>
-        <v>1110.7627864361687</v>
+        <f t="shared" si="4"/>
+        <v>1186.562401270902</v>
       </c>
       <c r="BA6" s="5">
-        <f t="shared" si="6"/>
-        <v>1121.8704143005305</v>
+        <f t="shared" si="4"/>
+        <v>1198.4280252836111</v>
       </c>
       <c r="BB6" s="5">
-        <f t="shared" si="6"/>
-        <v>1133.0891184435359</v>
+        <f t="shared" si="4"/>
+        <v>1210.4123055364471</v>
       </c>
     </row>
     <row r="7" spans="2:55" x14ac:dyDescent="0.3">
@@ -1749,111 +1792,111 @@
         <v>74</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:AC7" si="7">SUM(C4:C6)</f>
+        <f t="shared" ref="C7:AC7" si="5">SUM(C4:C6)</f>
         <v>48.900000000000006</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>66.7</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>73.8</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>82.1</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>88.2</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>98.8</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>122</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>138.9</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>200.70000000000002</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>222.70000000000002</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>270.5</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>310.89999999999998</v>
       </c>
       <c r="P7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>355.6</v>
       </c>
       <c r="Q7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>377.4</v>
       </c>
       <c r="R7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>447.7</v>
       </c>
       <c r="S7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>424.1</v>
       </c>
       <c r="T7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>444.49999999999994</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>468.9</v>
       </c>
       <c r="V7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>523</v>
       </c>
       <c r="W7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>545.20000000000005</v>
       </c>
       <c r="X7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>552.79999999999995</v>
       </c>
       <c r="Y7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>553.29999999999995</v>
       </c>
       <c r="Z7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>616.79999999999995</v>
       </c>
       <c r="AA7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>608.20000000000005</v>
       </c>
       <c r="AB7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>628</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>681.1</v>
       </c>
       <c r="AD7" s="5">
@@ -1861,92 +1904,92 @@
         <v>722.1</v>
       </c>
       <c r="AE7" s="5">
-        <f t="shared" ref="AE7:AH7" si="8">SUM(AE4:AE6)</f>
+        <f t="shared" ref="AE7:AH7" si="6">SUM(AE4:AE6)</f>
         <v>748.4</v>
       </c>
       <c r="AF7" s="5">
-        <f t="shared" si="8"/>
-        <v>776.31760000000008</v>
+        <f t="shared" si="6"/>
+        <v>813.2</v>
       </c>
       <c r="AG7" s="5">
-        <f t="shared" si="8"/>
-        <v>807.25440000000003</v>
+        <f t="shared" si="6"/>
+        <v>841.452</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" si="8"/>
-        <v>839.45500000000004</v>
+        <f t="shared" si="6"/>
+        <v>883.13408000000004</v>
       </c>
       <c r="AK7" s="5">
-        <f t="shared" ref="AK7:BB7" si="9">SUM(AK4:AK6)</f>
+        <f t="shared" ref="AK7:BB7" si="7">SUM(AK4:AK6)</f>
         <v>250.4</v>
       </c>
       <c r="AL7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>391.09999999999997</v>
       </c>
       <c r="AM7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>832.8</v>
       </c>
       <c r="AN7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1491.6</v>
       </c>
       <c r="AO7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1860.5</v>
       </c>
       <c r="AP7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2268.1</v>
       </c>
       <c r="AQ7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2639.4</v>
       </c>
       <c r="AR7" s="5">
-        <f t="shared" si="9"/>
-        <v>3171.4270000000001</v>
+        <f t="shared" si="7"/>
+        <v>3286.1860799999995</v>
       </c>
       <c r="AS7" s="5">
-        <f t="shared" si="9"/>
-        <v>3561.0625031999998</v>
+        <f t="shared" si="7"/>
+        <v>3782.4286000000002</v>
       </c>
       <c r="AT7" s="5">
-        <f t="shared" si="9"/>
-        <v>3976.89519492</v>
+        <f t="shared" si="7"/>
+        <v>4293.0319624000003</v>
       </c>
       <c r="AU7" s="5">
-        <f t="shared" si="9"/>
-        <v>4365.6911984015996</v>
+        <f t="shared" si="7"/>
+        <v>4795.9055069440001</v>
       </c>
       <c r="AV7" s="5">
-        <f t="shared" si="9"/>
-        <v>4701.2010971840637</v>
+        <f t="shared" si="7"/>
+        <v>5260.7196486908797</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" si="9"/>
-        <v>5050.3222555345783</v>
+        <f t="shared" si="7"/>
+        <v>5655.1485304453709</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" si="9"/>
-        <v>5339.1590883900226</v>
+        <f t="shared" si="7"/>
+        <v>5981.9089809820525</v>
       </c>
       <c r="AY7" s="5">
-        <f t="shared" si="9"/>
-        <v>5605.0648151248442</v>
+        <f t="shared" si="7"/>
+        <v>6282.6643981239431</v>
       </c>
       <c r="AZ7" s="5">
-        <f t="shared" si="9"/>
-        <v>5841.3274504776737</v>
+        <f t="shared" si="7"/>
+        <v>6549.8050476827784</v>
       </c>
       <c r="BA7" s="5">
-        <f t="shared" si="9"/>
-        <v>6088.963311544112</v>
+        <f t="shared" si="7"/>
+        <v>6829.8328040160814</v>
       </c>
       <c r="BB7" s="5">
-        <f t="shared" si="9"/>
-        <v>6348.5366605492954</v>
+        <f t="shared" si="7"/>
+        <v>7123.3873232055412</v>
       </c>
     </row>
     <row r="8" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1958,200 +2001,200 @@
         <v>14.499999999999993</v>
       </c>
       <c r="D8" s="9">
-        <f t="shared" ref="D8:AD8" si="10">D3-D7</f>
+        <f t="shared" ref="D8:AD8" si="8">D3-D7</f>
         <v>14.400000000000006</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>19.899999999999991</v>
       </c>
       <c r="F8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>25.799999999999997</v>
       </c>
       <c r="G8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>28.400000000000006</v>
       </c>
       <c r="H8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>32.299999999999997</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>25.599999999999994</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>22.699999999999989</v>
       </c>
       <c r="L8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>-0.30000000000001137</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>29.199999999999989</v>
       </c>
       <c r="N8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>39.5</v>
       </c>
       <c r="O8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>76.100000000000023</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>98.5</v>
       </c>
       <c r="Q8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>131.90000000000003</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>121.09999999999997</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>113</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>146.7000000000001</v>
       </c>
       <c r="U8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>48.800000000000068</v>
       </c>
       <c r="V8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="W8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>110.09999999999991</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>128</v>
       </c>
       <c r="Y8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>159.90000000000009</v>
       </c>
       <c r="Z8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>133.10000000000002</v>
       </c>
       <c r="AA8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>193.09999999999991</v>
       </c>
       <c r="AB8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>265.5</v>
       </c>
       <c r="AC8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>237.89999999999998</v>
       </c>
       <c r="AD8" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>266.10000000000002</v>
       </c>
       <c r="AE8" s="9">
-        <f t="shared" ref="AE8:AH8" si="11">AE3-AE7</f>
+        <f t="shared" ref="AE8:AH8" si="9">AE3-AE7</f>
         <v>286.80000000000007</v>
       </c>
       <c r="AF8" s="9">
-        <f t="shared" si="11"/>
-        <v>367.36239999999998</v>
+        <f t="shared" si="9"/>
+        <v>267.5</v>
       </c>
       <c r="AG8" s="9">
-        <f t="shared" si="11"/>
-        <v>369.0655999999999</v>
+        <f t="shared" si="9"/>
+        <v>293.548</v>
       </c>
       <c r="AH8" s="9">
-        <f t="shared" si="11"/>
-        <v>376.03100000000006</v>
+        <f t="shared" si="9"/>
+        <v>322.46992</v>
       </c>
       <c r="AK8" s="9">
-        <f t="shared" ref="AK8" si="12">AK3-AK7</f>
+        <f t="shared" ref="AK8" si="10">AK3-AK7</f>
         <v>74.599999999999994</v>
       </c>
       <c r="AL8" s="9">
-        <f t="shared" ref="AL8" si="13">AL3-AL7</f>
+        <f t="shared" ref="AL8" si="11">AL3-AL7</f>
         <v>117.30000000000001</v>
       </c>
       <c r="AM8" s="9">
-        <f t="shared" ref="AM8" si="14">AM3-AM7</f>
+        <f t="shared" ref="AM8" si="12">AM3-AM7</f>
         <v>91.100000000000023</v>
       </c>
       <c r="AN8" s="9">
-        <f t="shared" ref="AN8" si="15">AN3-AN7</f>
+        <f t="shared" ref="AN8" si="13">AN3-AN7</f>
         <v>427.60000000000014</v>
       </c>
       <c r="AO8" s="9">
-        <f t="shared" ref="AO8" si="16">AO3-AO7</f>
+        <f t="shared" ref="AO8" si="14">AO3-AO7</f>
         <v>364.5</v>
       </c>
       <c r="AP8" s="9">
-        <f t="shared" ref="AP8" si="17">AP3-AP7</f>
+        <f t="shared" ref="AP8" si="15">AP3-AP7</f>
         <v>531.10000000000036</v>
       </c>
       <c r="AQ8" s="9">
-        <f t="shared" ref="AQ8" si="18">AQ3-AQ7</f>
+        <f t="shared" ref="AQ8" si="16">AQ3-AQ7</f>
         <v>962.59999999999991</v>
       </c>
       <c r="AR8" s="9">
-        <f t="shared" ref="AR8" si="19">AR3-AR7</f>
-        <v>1399.2589999999996</v>
+        <f t="shared" ref="AR8" si="17">AR3-AR7</f>
+        <v>1170.3179200000004</v>
       </c>
       <c r="AS8" s="9">
-        <f t="shared" ref="AS8" si="20">AS3-AS7</f>
-        <v>2015.1744167999996</v>
+        <f t="shared" ref="AS8" si="18">AS3-AS7</f>
+        <v>1654.5062799999996</v>
       </c>
       <c r="AT8" s="9">
-        <f t="shared" ref="AT8" si="21">AT3-AT7</f>
-        <v>2603.0643706799992</v>
+        <f t="shared" ref="AT8" si="19">AT3-AT7</f>
+        <v>2122.5511959999994</v>
       </c>
       <c r="AU8" s="9">
-        <f t="shared" ref="AU8" si="22">AU3-AU7</f>
-        <v>3201.262302038399</v>
+        <f t="shared" ref="AU8" si="20">AU3-AU7</f>
+        <v>2582.0151252159994</v>
       </c>
       <c r="AV8" s="9">
-        <f t="shared" ref="AV8" si="23">AV3-AV7</f>
-        <v>3773.7868233087347</v>
+        <f t="shared" ref="AV8" si="21">AV3-AV7</f>
+        <v>3002.5514593283206</v>
       </c>
       <c r="AW8" s="9">
-        <f t="shared" ref="AW8" si="24">AW3-AW7</f>
-        <v>4187.4145778025722</v>
+        <f t="shared" ref="AW8" si="22">AW3-AW7</f>
+        <v>3351.8169772955589</v>
       </c>
       <c r="AX8" s="9">
-        <f t="shared" ref="AX8" si="25">AX3-AX7</f>
-        <v>4545.2193232807294</v>
+        <f t="shared" ref="AX8" si="23">AX3-AX7</f>
+        <v>3655.5441123007422</v>
       </c>
       <c r="AY8" s="9">
-        <f t="shared" ref="AY8" si="26">AY3-AY7</f>
-        <v>4872.3763012461532</v>
+        <f t="shared" ref="AY8" si="24">AY3-AY7</f>
+        <v>3933.0358807558205</v>
       </c>
       <c r="AZ8" s="9">
-        <f t="shared" ref="AZ8" si="27">AZ3-AZ7</f>
-        <v>5159.9857217118742</v>
+        <f t="shared" ref="AZ8" si="25">AZ3-AZ7</f>
+        <v>4176.680245140974</v>
       </c>
       <c r="BA8" s="9">
-        <f t="shared" ref="BA8" si="28">BA3-BA7</f>
-        <v>5462.4155192549133</v>
+        <f t="shared" ref="BA8" si="26">BA3-BA7</f>
+        <v>4432.9767534488583</v>
       </c>
       <c r="BB8" s="9">
-        <f t="shared" ref="BB8" si="29">BB3-BB7</f>
-        <v>5780.4111117896819</v>
+        <f t="shared" ref="BB8" si="27">BB3-BB7</f>
+        <v>4702.5627121326452</v>
       </c>
     </row>
     <row r="9" spans="2:55" x14ac:dyDescent="0.3">
@@ -2247,11 +2290,10 @@
         <v>374.6</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" ref="AF9:AG9" si="30">AB9*1.03</f>
-        <v>372.55099999999999</v>
+        <v>385</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="AG9" si="28">AC9*1.03</f>
         <v>376.36199999999997</v>
       </c>
       <c r="AH9" s="5">
@@ -2287,47 +2329,47 @@
       </c>
       <c r="AR9" s="5">
         <f>SUM(AE9:AH9)</f>
-        <v>1503.3629999999998</v>
+        <v>1515.8119999999999</v>
       </c>
       <c r="AS9" s="5">
         <f>AR9*1.03</f>
-        <v>1548.4638899999998</v>
+        <v>1561.2863599999998</v>
       </c>
       <c r="AT9" s="5">
         <f>AS9*1.02</f>
-        <v>1579.4331677999999</v>
+        <v>1592.5120871999998</v>
       </c>
       <c r="AU9" s="5">
         <f>AT9*1.02</f>
-        <v>1611.021831156</v>
+        <v>1624.3623289439997</v>
       </c>
       <c r="AV9" s="5">
-        <f t="shared" ref="AV9:AW10" si="31">AU9*1.02</f>
-        <v>1643.2422677791201</v>
+        <f t="shared" ref="AV9:AW10" si="29">AU9*1.02</f>
+        <v>1656.8495755228798</v>
       </c>
       <c r="AW9" s="5">
         <f>AV9*1.01</f>
-        <v>1659.6746904569113</v>
+        <v>1673.4180712781088</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" ref="AX9:BB9" si="32">AW9*1.01</f>
-        <v>1676.2714373614804</v>
+        <f t="shared" ref="AX9:BB9" si="30">AW9*1.01</f>
+        <v>1690.1522519908899</v>
       </c>
       <c r="AY9" s="5">
-        <f t="shared" si="32"/>
-        <v>1693.0341517350953</v>
+        <f t="shared" si="30"/>
+        <v>1707.0537745107988</v>
       </c>
       <c r="AZ9" s="5">
-        <f t="shared" si="32"/>
-        <v>1709.9644932524463</v>
+        <f t="shared" si="30"/>
+        <v>1724.1243122559067</v>
       </c>
       <c r="BA9" s="5">
-        <f t="shared" si="32"/>
-        <v>1727.0641381849707</v>
+        <f t="shared" si="30"/>
+        <v>1741.3655553784658</v>
       </c>
       <c r="BB9" s="5">
-        <f t="shared" si="32"/>
-        <v>1744.3347795668205</v>
+        <f t="shared" si="30"/>
+        <v>1758.7792109322504</v>
       </c>
     </row>
     <row r="10" spans="2:55" x14ac:dyDescent="0.3">
@@ -2423,16 +2465,15 @@
         <v>119.1</v>
       </c>
       <c r="AF10" s="5">
-        <f>AB10*1.15</f>
-        <v>121.43999999999998</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="AG10" s="5">
-        <f>AC10*1.2</f>
-        <v>118.44</v>
+        <f>AC10*1.6</f>
+        <v>157.92000000000002</v>
       </c>
       <c r="AH10" s="5">
-        <f>AD10*1.17</f>
-        <v>123.20099999999999</v>
+        <f>AD10*1.55</f>
+        <v>163.215</v>
       </c>
       <c r="AK10" s="5">
         <f>SUM(C10:F10)</f>
@@ -2463,47 +2504,47 @@
       </c>
       <c r="AR10" s="5">
         <f>SUM(AE10:AH10)</f>
-        <v>482.18099999999993</v>
+        <v>592.43499999999995</v>
       </c>
       <c r="AS10" s="5">
         <f>AR10*1.09</f>
-        <v>525.57728999999995</v>
+        <v>645.75414999999998</v>
       </c>
       <c r="AT10" s="5">
         <f>AS10*1.05</f>
-        <v>551.8561545</v>
+        <v>678.04185749999999</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10*1.04</f>
-        <v>573.93040068000005</v>
+        <v>705.16353179999999</v>
       </c>
       <c r="AV10" s="5">
         <f>AU10*1.03</f>
-        <v>591.14831270040008</v>
+        <v>726.318437754</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="31"/>
-        <v>602.97127895440815</v>
+        <f t="shared" si="29"/>
+        <v>740.84480650908006</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" ref="AX10" si="33">AW10*1.02</f>
-        <v>615.0307045334963</v>
+        <f t="shared" ref="AX10" si="31">AW10*1.02</f>
+        <v>755.66170263926165</v>
       </c>
       <c r="AY10" s="5">
-        <f t="shared" ref="AY10" si="34">AX10*1.02</f>
-        <v>627.33131862416622</v>
+        <f t="shared" ref="AY10" si="32">AX10*1.02</f>
+        <v>770.77493669204694</v>
       </c>
       <c r="AZ10" s="5">
-        <f t="shared" ref="AZ10" si="35">AY10*1.02</f>
-        <v>639.8779449966496</v>
+        <f t="shared" ref="AZ10" si="33">AY10*1.02</f>
+        <v>786.19043542588793</v>
       </c>
       <c r="BA10" s="5">
-        <f t="shared" ref="BA10" si="36">AZ10*1.02</f>
-        <v>652.67550389658265</v>
+        <f t="shared" ref="BA10" si="34">AZ10*1.02</f>
+        <v>801.91424413440575</v>
       </c>
       <c r="BB10" s="5">
-        <f t="shared" ref="BB10" si="37">BA10*1.02</f>
-        <v>665.72901397451437</v>
+        <f t="shared" ref="BB10" si="35">BA10*1.02</f>
+        <v>817.95252901709387</v>
       </c>
     </row>
     <row r="11" spans="2:55" x14ac:dyDescent="0.3">
@@ -2599,16 +2640,15 @@
         <v>47.8</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11" si="38">AF3*0.04</f>
-        <v>45.747200000000007</v>
+        <v>52.8</v>
       </c>
       <c r="AG11" s="5">
         <f>AG3*0.05</f>
-        <v>58.816000000000003</v>
+        <v>56.75</v>
       </c>
       <c r="AH11" s="5">
         <f>AH3*0.05</f>
-        <v>60.774300000000011</v>
+        <v>60.280200000000008</v>
       </c>
       <c r="AK11" s="5">
         <f>SUM(C11:F11)</f>
@@ -2639,47 +2679,47 @@
       </c>
       <c r="AR11" s="5">
         <f>SUM(AE11:AH11)</f>
-        <v>213.13750000000002</v>
+        <v>217.6302</v>
       </c>
       <c r="AS11" s="5">
-        <f t="shared" ref="AS11:BB11" si="39">AS3*0.05</f>
-        <v>278.811846</v>
+        <f t="shared" ref="AS11:BB11" si="36">AS3*0.05</f>
+        <v>271.846744</v>
       </c>
       <c r="AT11" s="5">
-        <f t="shared" si="39"/>
-        <v>328.99797827999998</v>
+        <f t="shared" si="36"/>
+        <v>320.77915791999999</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" si="39"/>
-        <v>378.34767502199998</v>
+        <f t="shared" si="36"/>
+        <v>368.89603160799999</v>
       </c>
       <c r="AV11" s="5">
-        <f t="shared" si="39"/>
-        <v>423.74939602463996</v>
+        <f t="shared" si="36"/>
+        <v>413.16355540096004</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="39"/>
-        <v>461.88684166685755</v>
+        <f t="shared" si="36"/>
+        <v>450.3482753870465</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="39"/>
-        <v>494.21892058353762</v>
+        <f t="shared" si="36"/>
+        <v>481.87265466413976</v>
       </c>
       <c r="AY11" s="5">
-        <f t="shared" si="39"/>
-        <v>523.87205581854994</v>
+        <f t="shared" si="36"/>
+        <v>510.78501394398819</v>
       </c>
       <c r="AZ11" s="5">
-        <f t="shared" si="39"/>
-        <v>550.0656586094774</v>
+        <f t="shared" si="36"/>
+        <v>536.3242646411876</v>
       </c>
       <c r="BA11" s="5">
-        <f t="shared" si="39"/>
-        <v>577.56894153995131</v>
+        <f t="shared" si="36"/>
+        <v>563.14047787324705</v>
       </c>
       <c r="BB11" s="5">
-        <f t="shared" si="39"/>
-        <v>606.44738861694884</v>
+        <f t="shared" si="36"/>
+        <v>591.29750176690936</v>
       </c>
     </row>
     <row r="12" spans="2:55" x14ac:dyDescent="0.3">
@@ -2687,204 +2727,204 @@
         <v>23</v>
       </c>
       <c r="C12" s="5">
-        <f t="shared" ref="C12:O12" si="40">SUM(C9:C11)</f>
+        <f t="shared" ref="C12:O12" si="37">SUM(C9:C11)</f>
         <v>28.9</v>
       </c>
       <c r="D12" s="5">
+        <f t="shared" si="37"/>
+        <v>34.599999999999994</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="37"/>
+        <v>60.7</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="37"/>
+        <v>38</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="37"/>
+        <v>38.800000000000004</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="37"/>
+        <v>44.8</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="37"/>
+        <v>51</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="37"/>
+        <v>59.2</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="37"/>
+        <v>95.7</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="37"/>
+        <v>72.800000000000011</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="37"/>
+        <v>80.800000000000011</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="37"/>
+        <v>107.79999999999998</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" si="37"/>
+        <v>211</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" ref="P12:AC12" si="38">SUM(P9:P11)</f>
+        <v>241.4</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="38"/>
+        <v>209.39999999999998</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="38"/>
+        <v>260.8</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="38"/>
+        <v>264.70000000000005</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="38"/>
+        <v>317</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="38"/>
+        <v>348.90000000000003</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="38"/>
+        <v>357.8</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" si="38"/>
+        <v>399.90000000000003</v>
+      </c>
+      <c r="X12" s="5">
+        <f t="shared" si="38"/>
+        <v>441.8</v>
+      </c>
+      <c r="Y12" s="5">
+        <f t="shared" si="38"/>
+        <v>460</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="38"/>
+        <v>488.40000000000003</v>
+      </c>
+      <c r="AA12" s="5">
+        <f t="shared" si="38"/>
+        <v>495.40000000000003</v>
+      </c>
+      <c r="AB12" s="5">
+        <f t="shared" si="38"/>
+        <v>503.59999999999997</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="38"/>
+        <v>516.69999999999993</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" ref="AD12:AH12" si="39">SUM(AD9:AD11)</f>
+        <v>510.1</v>
+      </c>
+      <c r="AE12" s="5">
+        <f t="shared" si="39"/>
+        <v>541.5</v>
+      </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="39"/>
+        <v>590</v>
+      </c>
+      <c r="AG12" s="5">
+        <f t="shared" si="39"/>
+        <v>591.03199999999993</v>
+      </c>
+      <c r="AH12" s="5">
+        <f t="shared" si="39"/>
+        <v>603.34520000000009</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" ref="AK12:AN12" si="40">SUM(AK9:AK11)</f>
+        <v>162.19999999999999</v>
+      </c>
+      <c r="AL12" s="5">
         <f t="shared" si="40"/>
-        <v>34.599999999999994</v>
-      </c>
-      <c r="E12" s="5">
+        <v>193.8</v>
+      </c>
+      <c r="AM12" s="5">
         <f t="shared" si="40"/>
-        <v>60.7</v>
-      </c>
-      <c r="F12" s="5">
+        <v>357.09999999999997</v>
+      </c>
+      <c r="AN12" s="5">
         <f t="shared" si="40"/>
-        <v>38</v>
-      </c>
-      <c r="G12" s="5">
-        <f t="shared" si="40"/>
-        <v>38.800000000000004</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="40"/>
-        <v>44.8</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="40"/>
-        <v>51</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="40"/>
-        <v>59.2</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="40"/>
-        <v>95.7</v>
-      </c>
-      <c r="L12" s="5">
-        <f t="shared" si="40"/>
-        <v>72.800000000000011</v>
-      </c>
-      <c r="M12" s="5">
-        <f t="shared" si="40"/>
-        <v>80.800000000000011</v>
-      </c>
-      <c r="N12" s="5">
-        <f t="shared" si="40"/>
-        <v>107.79999999999998</v>
-      </c>
-      <c r="O12" s="5">
-        <f t="shared" si="40"/>
-        <v>211</v>
-      </c>
-      <c r="P12" s="5">
-        <f t="shared" ref="P12:AC12" si="41">SUM(P9:P11)</f>
-        <v>241.4</v>
-      </c>
-      <c r="Q12" s="5">
-        <f t="shared" si="41"/>
-        <v>209.39999999999998</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="41"/>
-        <v>260.8</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="41"/>
-        <v>264.70000000000005</v>
-      </c>
-      <c r="T12" s="5">
-        <f t="shared" si="41"/>
-        <v>317</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="41"/>
-        <v>348.90000000000003</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="41"/>
-        <v>357.8</v>
-      </c>
-      <c r="W12" s="5">
-        <f t="shared" si="41"/>
-        <v>399.90000000000003</v>
-      </c>
-      <c r="X12" s="5">
-        <f t="shared" si="41"/>
-        <v>441.8</v>
-      </c>
-      <c r="Y12" s="5">
-        <f t="shared" si="41"/>
-        <v>460</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="41"/>
-        <v>488.40000000000003</v>
-      </c>
-      <c r="AA12" s="5">
-        <f t="shared" si="41"/>
-        <v>495.40000000000003</v>
-      </c>
-      <c r="AB12" s="5">
-        <f t="shared" si="41"/>
-        <v>503.59999999999997</v>
-      </c>
-      <c r="AC12" s="5">
-        <f t="shared" si="41"/>
-        <v>516.69999999999993</v>
-      </c>
-      <c r="AD12" s="5">
-        <f t="shared" ref="AD12:AH12" si="42">SUM(AD9:AD11)</f>
-        <v>510.1</v>
-      </c>
-      <c r="AE12" s="5">
-        <f t="shared" si="42"/>
-        <v>541.5</v>
-      </c>
-      <c r="AF12" s="5">
-        <f t="shared" si="42"/>
-        <v>539.73820000000001</v>
-      </c>
-      <c r="AG12" s="5">
-        <f t="shared" si="42"/>
-        <v>553.61799999999994</v>
-      </c>
-      <c r="AH12" s="5">
-        <f t="shared" si="42"/>
-        <v>563.82530000000008</v>
-      </c>
-      <c r="AK12" s="5">
-        <f t="shared" ref="AK12:AN12" si="43">SUM(AK9:AK11)</f>
-        <v>162.19999999999999</v>
-      </c>
-      <c r="AL12" s="5">
-        <f t="shared" si="43"/>
-        <v>193.8</v>
-      </c>
-      <c r="AM12" s="5">
-        <f t="shared" si="43"/>
-        <v>357.09999999999997</v>
-      </c>
-      <c r="AN12" s="5">
-        <f t="shared" si="43"/>
         <v>922.6</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" ref="AO12" si="44">SUM(AO9:AO11)</f>
+        <f t="shared" ref="AO12" si="41">SUM(AO9:AO11)</f>
         <v>1288.4000000000001</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" ref="AP12" si="45">SUM(AP9:AP11)</f>
+        <f t="shared" ref="AP12" si="42">SUM(AP9:AP11)</f>
         <v>1790.1</v>
       </c>
       <c r="AQ12" s="5">
-        <f t="shared" ref="AQ12" si="46">SUM(AQ9:AQ11)</f>
+        <f t="shared" ref="AQ12" si="43">SUM(AQ9:AQ11)</f>
         <v>2025.8</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" ref="AR12" si="47">SUM(AR9:AR11)</f>
-        <v>2198.6814999999997</v>
+        <f t="shared" ref="AR12" si="44">SUM(AR9:AR11)</f>
+        <v>2325.8771999999999</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" ref="AS12" si="48">SUM(AS9:AS11)</f>
-        <v>2352.8530259999998</v>
+        <f t="shared" ref="AS12" si="45">SUM(AS9:AS11)</f>
+        <v>2478.8872539999998</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" ref="AT12" si="49">SUM(AT9:AT11)</f>
-        <v>2460.2873005800002</v>
+        <f t="shared" ref="AT12" si="46">SUM(AT9:AT11)</f>
+        <v>2591.3331026199994</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" ref="AU12" si="50">SUM(AU9:AU11)</f>
-        <v>2563.2999068580002</v>
+        <f t="shared" ref="AU12" si="47">SUM(AU9:AU11)</f>
+        <v>2698.4218923519998</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="51">SUM(AV9:AV11)</f>
-        <v>2658.1399765041606</v>
+        <f t="shared" ref="AV12" si="48">SUM(AV9:AV11)</f>
+        <v>2796.3315686778396</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" ref="AW12" si="52">SUM(AW9:AW11)</f>
-        <v>2724.532811078177</v>
+        <f t="shared" ref="AW12" si="49">SUM(AW9:AW11)</f>
+        <v>2864.6111531742354</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" ref="AX12" si="53">SUM(AX9:AX11)</f>
-        <v>2785.5210624785141</v>
+        <f t="shared" ref="AX12" si="50">SUM(AX9:AX11)</f>
+        <v>2927.6866092942914</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" ref="AY12" si="54">SUM(AY9:AY11)</f>
-        <v>2844.2375261778116</v>
+        <f t="shared" ref="AY12" si="51">SUM(AY9:AY11)</f>
+        <v>2988.613725146834</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" ref="AZ12" si="55">SUM(AZ9:AZ11)</f>
-        <v>2899.9080968585731</v>
+        <f t="shared" ref="AZ12" si="52">SUM(AZ9:AZ11)</f>
+        <v>3046.6390123229826</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="56">SUM(BA9:BA11)</f>
-        <v>2957.308583621505</v>
+        <f t="shared" ref="BA12" si="53">SUM(BA9:BA11)</f>
+        <v>3106.4202773861189</v>
       </c>
       <c r="BB12" s="5">
-        <f t="shared" ref="BB12" si="57">SUM(BB9:BB11)</f>
-        <v>3016.5111821582841</v>
+        <f t="shared" ref="BB12" si="54">SUM(BB9:BB11)</f>
+        <v>3168.0292417162536</v>
       </c>
     </row>
     <row r="13" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2892,204 +2932,204 @@
         <v>25</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:O13" si="58">C8-C12</f>
+        <f t="shared" ref="C13:O13" si="55">C8-C12</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D13" s="9">
+        <f t="shared" si="55"/>
+        <v>-20.199999999999989</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="55"/>
+        <v>-40.800000000000011</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="55"/>
+        <v>-12.200000000000003</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="55"/>
+        <v>-10.399999999999999</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="55"/>
+        <v>-13.799999999999997</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="55"/>
+        <v>-18.700000000000003</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="55"/>
+        <v>-33.600000000000009</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="55"/>
+        <v>-73.000000000000014</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="55"/>
+        <v>-73.100000000000023</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="55"/>
+        <v>-51.600000000000023</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="55"/>
+        <v>-68.299999999999983</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="55"/>
+        <v>-134.89999999999998</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" ref="P13:AC13" si="56">P8-P12</f>
+        <v>-142.9</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="56"/>
+        <v>-77.499999999999943</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="56"/>
+        <v>-139.70000000000005</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="56"/>
+        <v>-151.70000000000005</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" si="56"/>
+        <v>-170.2999999999999</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" si="56"/>
+        <v>-300.09999999999997</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" si="56"/>
+        <v>-301.8</v>
+      </c>
+      <c r="W13" s="9">
+        <f t="shared" si="56"/>
+        <v>-289.80000000000013</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" si="56"/>
+        <v>-313.8</v>
+      </c>
+      <c r="Y13" s="9">
+        <f t="shared" si="56"/>
+        <v>-300.09999999999991</v>
+      </c>
+      <c r="Z13" s="9">
+        <f t="shared" si="56"/>
+        <v>-355.3</v>
+      </c>
+      <c r="AA13" s="9">
+        <f t="shared" si="56"/>
+        <v>-302.30000000000013</v>
+      </c>
+      <c r="AB13" s="9">
+        <f t="shared" si="56"/>
+        <v>-238.09999999999997</v>
+      </c>
+      <c r="AC13" s="9">
+        <f t="shared" si="56"/>
+        <v>-278.79999999999995</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" ref="AD13:AH13" si="57">AD8-AD12</f>
+        <v>-244</v>
+      </c>
+      <c r="AE13" s="9">
+        <f t="shared" si="57"/>
+        <v>-254.69999999999993</v>
+      </c>
+      <c r="AF13" s="9">
+        <f t="shared" si="57"/>
+        <v>-322.5</v>
+      </c>
+      <c r="AG13" s="9">
+        <f t="shared" si="57"/>
+        <v>-297.48399999999992</v>
+      </c>
+      <c r="AH13" s="9">
+        <f t="shared" si="57"/>
+        <v>-280.87528000000009</v>
+      </c>
+      <c r="AK13" s="9">
+        <f t="shared" ref="AK13:AN13" si="58">AK8-AK12</f>
+        <v>-87.6</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="58"/>
-        <v>-20.199999999999989</v>
-      </c>
-      <c r="E13" s="9">
+        <v>-76.5</v>
+      </c>
+      <c r="AM13" s="9">
         <f t="shared" si="58"/>
-        <v>-40.800000000000011</v>
-      </c>
-      <c r="F13" s="9">
+        <v>-265.99999999999994</v>
+      </c>
+      <c r="AN13" s="9">
         <f t="shared" si="58"/>
-        <v>-12.200000000000003</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="58"/>
-        <v>-10.399999999999999</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="58"/>
-        <v>-13.799999999999997</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="58"/>
-        <v>-18.700000000000003</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="58"/>
-        <v>-33.600000000000009</v>
-      </c>
-      <c r="K13" s="9">
-        <f t="shared" si="58"/>
-        <v>-73.000000000000014</v>
-      </c>
-      <c r="L13" s="9">
-        <f t="shared" si="58"/>
-        <v>-73.100000000000023</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="58"/>
-        <v>-51.600000000000023</v>
-      </c>
-      <c r="N13" s="9">
-        <f t="shared" si="58"/>
-        <v>-68.299999999999983</v>
-      </c>
-      <c r="O13" s="9">
-        <f t="shared" si="58"/>
-        <v>-134.89999999999998</v>
-      </c>
-      <c r="P13" s="9">
-        <f t="shared" ref="P13:AC13" si="59">P8-P12</f>
-        <v>-142.9</v>
-      </c>
-      <c r="Q13" s="9">
-        <f t="shared" si="59"/>
-        <v>-77.499999999999943</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="59"/>
-        <v>-139.70000000000005</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="59"/>
-        <v>-151.70000000000005</v>
-      </c>
-      <c r="T13" s="9">
-        <f t="shared" si="59"/>
-        <v>-170.2999999999999</v>
-      </c>
-      <c r="U13" s="9">
-        <f t="shared" si="59"/>
-        <v>-300.09999999999997</v>
-      </c>
-      <c r="V13" s="9">
-        <f t="shared" si="59"/>
-        <v>-301.8</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="59"/>
-        <v>-289.80000000000013</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" si="59"/>
-        <v>-313.8</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="59"/>
-        <v>-300.09999999999991</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="59"/>
-        <v>-355.3</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" si="59"/>
-        <v>-302.30000000000013</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="59"/>
-        <v>-238.09999999999997</v>
-      </c>
-      <c r="AC13" s="9">
-        <f t="shared" si="59"/>
-        <v>-278.79999999999995</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" ref="AD13:AH13" si="60">AD8-AD12</f>
-        <v>-244</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" si="60"/>
-        <v>-254.69999999999993</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="60"/>
-        <v>-172.37580000000003</v>
-      </c>
-      <c r="AG13" s="9">
-        <f t="shared" si="60"/>
-        <v>-184.55240000000003</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" si="60"/>
-        <v>-187.79430000000002</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" ref="AK13:AN13" si="61">AK8-AK12</f>
-        <v>-87.6</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="61"/>
-        <v>-76.5</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" si="61"/>
-        <v>-265.99999999999994</v>
-      </c>
-      <c r="AN13" s="9">
-        <f t="shared" si="61"/>
         <v>-494.99999999999989</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" ref="AO13" si="62">AO8-AO12</f>
+        <f t="shared" ref="AO13" si="59">AO8-AO12</f>
         <v>-923.90000000000009</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" ref="AP13" si="63">AP8-AP12</f>
+        <f t="shared" ref="AP13" si="60">AP8-AP12</f>
         <v>-1258.9999999999995</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13" si="64">AQ8-AQ12</f>
+        <f t="shared" ref="AQ13" si="61">AQ8-AQ12</f>
         <v>-1063.2</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="65">AR8-AR12</f>
-        <v>-799.42250000000013</v>
+        <f t="shared" ref="AR13" si="62">AR8-AR12</f>
+        <v>-1155.5592799999995</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="66">AS8-AS12</f>
-        <v>-337.67860920000021</v>
+        <f t="shared" ref="AS13" si="63">AS8-AS12</f>
+        <v>-824.38097400000015</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="67">AT8-AT12</f>
-        <v>142.77707009999904</v>
+        <f t="shared" ref="AT13" si="64">AT8-AT12</f>
+        <v>-468.78190661999997</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="68">AU8-AU12</f>
-        <v>637.96239518039874</v>
+        <f t="shared" ref="AU13" si="65">AU8-AU12</f>
+        <v>-116.40676713600033</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" ref="AV13" si="69">AV8-AV12</f>
-        <v>1115.6468468045741</v>
+        <f t="shared" ref="AV13" si="66">AV8-AV12</f>
+        <v>206.21989065048092</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" ref="AW13" si="70">AW8-AW12</f>
-        <v>1462.8817667243952</v>
+        <f t="shared" ref="AW13" si="67">AW8-AW12</f>
+        <v>487.20582412132353</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" ref="AX13" si="71">AX8-AX12</f>
-        <v>1759.6982608022154</v>
+        <f t="shared" ref="AX13" si="68">AX8-AX12</f>
+        <v>727.85750300645077</v>
       </c>
       <c r="AY13" s="9">
-        <f t="shared" ref="AY13" si="72">AY8-AY12</f>
-        <v>2028.1387750683416</v>
+        <f t="shared" ref="AY13" si="69">AY8-AY12</f>
+        <v>944.42215560898649</v>
       </c>
       <c r="AZ13" s="9">
-        <f t="shared" ref="AZ13" si="73">AZ8-AZ12</f>
-        <v>2260.0776248533011</v>
+        <f t="shared" ref="AZ13" si="70">AZ8-AZ12</f>
+        <v>1130.0412328179914</v>
       </c>
       <c r="BA13" s="9">
-        <f t="shared" ref="BA13" si="74">BA8-BA12</f>
-        <v>2505.1069356334083</v>
+        <f t="shared" ref="BA13" si="71">BA8-BA12</f>
+        <v>1326.5564760627394</v>
       </c>
       <c r="BB13" s="9">
-        <f t="shared" ref="BB13" si="75">BB8-BB12</f>
-        <v>2763.8999296313978</v>
+        <f t="shared" ref="BB13" si="72">BB8-BB12</f>
+        <v>1534.5334704163915</v>
       </c>
     </row>
     <row r="14" spans="2:55" x14ac:dyDescent="0.3">
@@ -3185,15 +3225,14 @@
         <v>-46.3</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" ref="AF14:AH15" si="76">AB14*1.1</f>
-        <v>-48.84</v>
+        <v>-48.8</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="AG14:AH15" si="73">AC14*1.1</f>
         <v>-51.370000000000005</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>-50.93</v>
       </c>
       <c r="AK14" s="5">
@@ -3225,47 +3264,47 @@
       </c>
       <c r="AR14" s="5">
         <f>SUM(AE14:AH14)</f>
-        <v>-197.44</v>
+        <v>-197.4</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" ref="AS14:AW15" si="77">AR14*1.01</f>
-        <v>-199.4144</v>
+        <f t="shared" ref="AS14:AW15" si="74">AR14*1.01</f>
+        <v>-199.374</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" si="77"/>
-        <v>-201.40854400000001</v>
+        <f t="shared" si="74"/>
+        <v>-201.36774</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="77"/>
-        <v>-203.42262944000001</v>
+        <f t="shared" si="74"/>
+        <v>-203.3814174</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" si="77"/>
-        <v>-205.45685573440002</v>
+        <f t="shared" si="74"/>
+        <v>-205.41523157400002</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" si="77"/>
-        <v>-207.51142429174402</v>
+        <f t="shared" si="74"/>
+        <v>-207.46938388974002</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" ref="AX14:AX15" si="78">AW14*1.01</f>
-        <v>-209.58653853466146</v>
+        <f t="shared" ref="AX14:AX15" si="75">AW14*1.01</f>
+        <v>-209.5440777286374</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" ref="AY14:AY15" si="79">AX14*1.01</f>
-        <v>-211.68240392000808</v>
+        <f t="shared" ref="AY14:AY15" si="76">AX14*1.01</f>
+        <v>-211.63951850592377</v>
       </c>
       <c r="AZ14" s="5">
-        <f t="shared" ref="AZ14:AZ15" si="80">AY14*1.01</f>
-        <v>-213.79922795920817</v>
+        <f t="shared" ref="AZ14:AZ15" si="77">AY14*1.01</f>
+        <v>-213.75591369098302</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" ref="BA14:BA15" si="81">AZ14*1.01</f>
-        <v>-215.93722023880025</v>
+        <f t="shared" ref="BA14:BA15" si="78">AZ14*1.01</f>
+        <v>-215.89347282789285</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" ref="BB14:BB15" si="82">BA14*1.01</f>
-        <v>-218.09659244118825</v>
+        <f t="shared" ref="BB14:BB15" si="79">BA14*1.01</f>
+        <v>-218.05240755617177</v>
       </c>
     </row>
     <row r="15" spans="2:55" x14ac:dyDescent="0.3">
@@ -3374,15 +3413,15 @@
         <v>7.1000000000000005</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="76"/>
-        <v>14.850000000000001</v>
+        <f>10.3-5.1</f>
+        <v>5.2000000000000011</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>8.6900000000000013</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>22.55</v>
       </c>
       <c r="AK15" s="5">
@@ -3414,47 +3453,47 @@
       </c>
       <c r="AR15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>53.190000000000005</v>
+        <v>43.540000000000006</v>
       </c>
       <c r="AS15" s="5">
         <f>AR15*1.01</f>
-        <v>53.721900000000005</v>
+        <v>43.975400000000008</v>
       </c>
       <c r="AT15" s="5">
+        <f t="shared" si="74"/>
+        <v>44.415154000000008</v>
+      </c>
+      <c r="AU15" s="5">
+        <f t="shared" si="74"/>
+        <v>44.859305540000008</v>
+      </c>
+      <c r="AV15" s="5">
+        <f t="shared" si="74"/>
+        <v>45.307898595400012</v>
+      </c>
+      <c r="AW15" s="5">
+        <f t="shared" si="74"/>
+        <v>45.760977581354013</v>
+      </c>
+      <c r="AX15" s="5">
+        <f t="shared" si="75"/>
+        <v>46.21858735716755</v>
+      </c>
+      <c r="AY15" s="5">
+        <f t="shared" si="76"/>
+        <v>46.680773230739227</v>
+      </c>
+      <c r="AZ15" s="5">
         <f t="shared" si="77"/>
-        <v>54.259119000000005</v>
-      </c>
-      <c r="AU15" s="5">
-        <f t="shared" si="77"/>
-        <v>54.801710190000009</v>
-      </c>
-      <c r="AV15" s="5">
-        <f t="shared" si="77"/>
-        <v>55.34972729190001</v>
-      </c>
-      <c r="AW15" s="5">
-        <f t="shared" si="77"/>
-        <v>55.903224564819013</v>
-      </c>
-      <c r="AX15" s="5">
+        <v>47.147580963046622</v>
+      </c>
+      <c r="BA15" s="5">
         <f t="shared" si="78"/>
-        <v>56.462256810467203</v>
-      </c>
-      <c r="AY15" s="5">
+        <v>47.619056772677091</v>
+      </c>
+      <c r="BB15" s="5">
         <f t="shared" si="79"/>
-        <v>57.026879378571877</v>
-      </c>
-      <c r="AZ15" s="5">
-        <f t="shared" si="80"/>
-        <v>57.597148172357599</v>
-      </c>
-      <c r="BA15" s="5">
-        <f t="shared" si="81"/>
-        <v>58.173119654081177</v>
-      </c>
-      <c r="BB15" s="5">
-        <f t="shared" si="82"/>
-        <v>58.754850850621992</v>
+        <v>48.095247340403866</v>
       </c>
     </row>
     <row r="16" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3462,132 +3501,132 @@
         <v>28</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:Q16" si="83">C13-C14-C15</f>
+        <f t="shared" ref="C16:Q16" si="80">C13-C14-C15</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="80"/>
+        <v>-23.599999999999987</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="80"/>
+        <v>-39.600000000000009</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="80"/>
+        <v>-10.600000000000003</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="80"/>
+        <v>-8.8999999999999986</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="80"/>
+        <v>-12.199999999999998</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="80"/>
+        <v>-17.3</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="80"/>
+        <v>-32.800000000000011</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="80"/>
+        <v>-74.90000000000002</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="80"/>
+        <v>-75.000000000000028</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="80"/>
+        <v>-50.100000000000023</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="80"/>
+        <v>-64.199999999999989</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="80"/>
+        <v>-135.99999999999997</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="80"/>
+        <v>-142.9</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="80"/>
+        <v>-78.29999999999994</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" ref="R16:S16" si="81">R13-R14-R15</f>
+        <v>-146.70000000000005</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="81"/>
+        <v>-161.90000000000006</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" ref="T16" si="82">T13-T14-T15</f>
+        <v>-179.09999999999991</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" ref="U16:V16" si="83">U13-U14-U15</f>
+        <v>-301.59999999999997</v>
+      </c>
+      <c r="V16" s="9">
         <f t="shared" si="83"/>
-        <v>-23.599999999999987</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="83"/>
-        <v>-39.600000000000009</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="83"/>
-        <v>-10.600000000000003</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="83"/>
-        <v>-8.8999999999999986</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="83"/>
-        <v>-12.199999999999998</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="83"/>
-        <v>-17.3</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="83"/>
-        <v>-32.800000000000011</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="83"/>
-        <v>-74.90000000000002</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="83"/>
-        <v>-75.000000000000028</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="83"/>
-        <v>-50.100000000000023</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="83"/>
-        <v>-64.199999999999989</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="83"/>
-        <v>-135.99999999999997</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="83"/>
-        <v>-142.9</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="83"/>
-        <v>-78.29999999999994</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" ref="R16:S16" si="84">R13-R14-R15</f>
-        <v>-146.70000000000005</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="84"/>
-        <v>-161.90000000000006</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" ref="T16" si="85">T13-T14-T15</f>
-        <v>-179.09999999999991</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" ref="U16:V16" si="86">U13-U14-U15</f>
-        <v>-301.59999999999997</v>
-      </c>
-      <c r="V16" s="9">
+        <v>-288.2</v>
+      </c>
+      <c r="W16" s="9">
+        <f t="shared" ref="W16" si="84">W13-W14-W15</f>
+        <v>-269.10000000000008</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" ref="X16" si="85">X13-X14-X15</f>
+        <v>-285.8</v>
+      </c>
+      <c r="Y16" s="9">
+        <f t="shared" ref="Y16:Z16" si="86">Y13-Y14-Y15</f>
+        <v>-278.29999999999995</v>
+      </c>
+      <c r="Z16" s="9">
         <f t="shared" si="86"/>
-        <v>-288.2</v>
-      </c>
-      <c r="W16" s="9">
-        <f t="shared" ref="W16" si="87">W13-W14-W15</f>
-        <v>-269.10000000000008</v>
-      </c>
-      <c r="X16" s="9">
-        <f t="shared" ref="X16" si="88">X13-X14-X15</f>
-        <v>-285.8</v>
-      </c>
-      <c r="Y16" s="9">
-        <f t="shared" ref="Y16:Z16" si="89">Y13-Y14-Y15</f>
-        <v>-278.29999999999995</v>
-      </c>
-      <c r="Z16" s="9">
+        <v>-325.2</v>
+      </c>
+      <c r="AA16" s="9">
+        <f t="shared" ref="AA16" si="87">AA13-AA14-AA15</f>
+        <v>-270.80000000000013</v>
+      </c>
+      <c r="AB16" s="9">
+        <f t="shared" ref="AB16" si="88">AB13-AB14-AB15</f>
+        <v>-207.19999999999996</v>
+      </c>
+      <c r="AC16" s="9">
+        <f t="shared" ref="AC16:AH16" si="89">AC13-AC14-AC15</f>
+        <v>-239.99999999999997</v>
+      </c>
+      <c r="AD16" s="9">
         <f t="shared" si="89"/>
-        <v>-325.2</v>
-      </c>
-      <c r="AA16" s="9">
-        <f t="shared" ref="AA16" si="90">AA13-AA14-AA15</f>
-        <v>-270.80000000000013</v>
-      </c>
-      <c r="AB16" s="9">
-        <f t="shared" ref="AB16" si="91">AB13-AB14-AB15</f>
-        <v>-207.19999999999996</v>
-      </c>
-      <c r="AC16" s="9">
-        <f t="shared" ref="AC16:AH16" si="92">AC13-AC14-AC15</f>
-        <v>-239.99999999999997</v>
-      </c>
-      <c r="AD16" s="9">
-        <f t="shared" si="92"/>
         <v>-218.2</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="89"/>
         <v>-215.49999999999991</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="92"/>
-        <v>-138.38580000000002</v>
+        <f t="shared" si="89"/>
+        <v>-278.89999999999998</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="92"/>
-        <v>-141.87240000000003</v>
+        <f t="shared" si="89"/>
+        <v>-254.80399999999992</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="92"/>
-        <v>-159.41430000000003</v>
+        <f t="shared" si="89"/>
+        <v>-252.49528000000009</v>
       </c>
       <c r="AK16" s="9">
         <f>AK13-AK14-AK15</f>
@@ -3602,64 +3641,64 @@
         <v>-264.19999999999993</v>
       </c>
       <c r="AN16" s="9">
-        <f t="shared" ref="AN16:AW16" si="93">AN13-AN14-AN15</f>
+        <f t="shared" ref="AN16:AW16" si="90">AN13-AN14-AN15</f>
         <v>-503.89999999999986</v>
       </c>
       <c r="AO16" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-930.80000000000018</v>
       </c>
       <c r="AP16" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-1158.3999999999996</v>
       </c>
       <c r="AQ16" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-936.2</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" si="93"/>
-        <v>-655.17250000000013</v>
+        <f t="shared" si="90"/>
+        <v>-1001.6992799999995</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" si="93"/>
-        <v>-191.98610920000021</v>
+        <f t="shared" si="90"/>
+        <v>-668.98237400000016</v>
       </c>
       <c r="AT16" s="9">
-        <f t="shared" si="93"/>
-        <v>289.92649509999904</v>
+        <f t="shared" si="90"/>
+        <v>-311.82932061999998</v>
       </c>
       <c r="AU16" s="9">
-        <f t="shared" si="93"/>
-        <v>786.58331443039879</v>
+        <f t="shared" si="90"/>
+        <v>42.115344723999669</v>
       </c>
       <c r="AV16" s="9">
-        <f t="shared" si="93"/>
-        <v>1265.7539752470741</v>
+        <f t="shared" si="90"/>
+        <v>366.32722362908095</v>
       </c>
       <c r="AW16" s="9">
-        <f t="shared" si="93"/>
-        <v>1614.4899664513202</v>
+        <f t="shared" si="90"/>
+        <v>648.91423042970951</v>
       </c>
       <c r="AX16" s="9">
-        <f t="shared" ref="AX16:BB16" si="94">AX13-AX14-AX15</f>
-        <v>1912.8225425264097</v>
+        <f t="shared" ref="AX16:BB16" si="91">AX13-AX14-AX15</f>
+        <v>891.18299337792064</v>
       </c>
       <c r="AY16" s="9">
-        <f t="shared" si="94"/>
-        <v>2182.7942996097781</v>
+        <f t="shared" si="91"/>
+        <v>1109.3809008841708</v>
       </c>
       <c r="AZ16" s="9">
-        <f t="shared" si="94"/>
-        <v>2416.2797046401515</v>
+        <f t="shared" si="91"/>
+        <v>1296.6495655459278</v>
       </c>
       <c r="BA16" s="9">
-        <f t="shared" si="94"/>
-        <v>2662.8710362181273</v>
+        <f t="shared" si="91"/>
+        <v>1494.830892117955</v>
       </c>
       <c r="BB16" s="9">
-        <f t="shared" si="94"/>
-        <v>2923.2416712219642</v>
+        <f t="shared" si="91"/>
+        <v>1704.4906306321595</v>
       </c>
     </row>
     <row r="17" spans="2:167" x14ac:dyDescent="0.3">
@@ -3755,16 +3794,15 @@
         <v>0.9</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" ref="AF17:AH17" si="95">AF16*0.01</f>
-        <v>-1.3838580000000003</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" si="95"/>
-        <v>-1.4187240000000003</v>
+        <f t="shared" ref="AG17:AH17" si="92">AG16*0.01</f>
+        <v>-2.5480399999999994</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="95"/>
-        <v>-1.5941430000000003</v>
+        <f t="shared" si="92"/>
+        <v>-2.5249528000000008</v>
       </c>
       <c r="AK17" s="5">
         <f>SUM(C17:F17)</f>
@@ -3795,7 +3833,7 @@
       </c>
       <c r="AR17" s="5">
         <f>SUM(AE17:AH17)</f>
-        <v>-3.496725000000001</v>
+        <v>-3.1729928000000003</v>
       </c>
       <c r="AS17" s="5">
         <v>0</v>
@@ -3921,16 +3959,15 @@
         <v>-1.3</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" ref="AF18:AH18" si="96">AF16*0.01</f>
-        <v>-1.3838580000000003</v>
+        <v>-1.4</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="96"/>
-        <v>-1.4187240000000003</v>
+        <f t="shared" ref="AG18:AH18" si="93">AG16*0.01</f>
+        <v>-2.5480399999999994</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="96"/>
-        <v>-1.5941430000000003</v>
+        <f t="shared" si="93"/>
+        <v>-2.5249528000000008</v>
       </c>
       <c r="AK18" s="5">
         <f>SUM(C18:F18)</f>
@@ -3961,47 +3998,47 @@
       </c>
       <c r="AR18" s="5">
         <f>SUM(AE18:AH18)</f>
-        <v>-5.6967250000000007</v>
+        <v>-7.7729928000000008</v>
       </c>
       <c r="AS18" s="5">
-        <f t="shared" ref="AS18:BB18" si="97">AS16*0.01</f>
-        <v>-1.9198610920000021</v>
+        <f t="shared" ref="AS18:BB18" si="94">AS16*0.01</f>
+        <v>-6.6898237400000014</v>
       </c>
       <c r="AT18" s="5">
-        <f t="shared" si="97"/>
-        <v>2.8992649509999904</v>
+        <f t="shared" si="94"/>
+        <v>-3.1182932061999997</v>
       </c>
       <c r="AU18" s="5">
-        <f t="shared" si="97"/>
-        <v>7.8658331443039877</v>
+        <f t="shared" si="94"/>
+        <v>0.4211534472399967</v>
       </c>
       <c r="AV18" s="5">
-        <f t="shared" si="97"/>
-        <v>12.657539752470742</v>
+        <f t="shared" si="94"/>
+        <v>3.6632722362908097</v>
       </c>
       <c r="AW18" s="5">
-        <f t="shared" si="97"/>
-        <v>16.144899664513204</v>
+        <f t="shared" si="94"/>
+        <v>6.4891423042970953</v>
       </c>
       <c r="AX18" s="5">
-        <f t="shared" si="97"/>
-        <v>19.128225425264098</v>
+        <f t="shared" si="94"/>
+        <v>8.911829933779206</v>
       </c>
       <c r="AY18" s="5">
-        <f t="shared" si="97"/>
-        <v>21.827942996097782</v>
+        <f t="shared" si="94"/>
+        <v>11.093809008841708</v>
       </c>
       <c r="AZ18" s="5">
-        <f t="shared" si="97"/>
-        <v>24.162797046401515</v>
+        <f t="shared" si="94"/>
+        <v>12.966495655459278</v>
       </c>
       <c r="BA18" s="5">
-        <f t="shared" si="97"/>
-        <v>26.628710362181273</v>
+        <f t="shared" si="94"/>
+        <v>14.948308921179551</v>
       </c>
       <c r="BB18" s="5">
-        <f t="shared" si="97"/>
-        <v>29.232416712219642</v>
+        <f t="shared" si="94"/>
+        <v>17.044906306321597</v>
       </c>
     </row>
     <row r="19" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4009,132 +4046,132 @@
         <v>31</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:N19" si="98">C16-C17-C18</f>
+        <f t="shared" ref="C19:N19" si="95">C16-C17-C18</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-23.599999999999987</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-10.600000000000003</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-8.8999999999999986</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-12.199999999999998</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-17.400000000000002</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-32.600000000000009</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-74.40000000000002</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-74.300000000000026</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-48.700000000000024</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-55.699999999999989</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" ref="O19:Q19" si="99">O16-O17-O18</f>
+        <f t="shared" ref="O19:Q19" si="96">O16-O17-O18</f>
         <v>-134.09999999999997</v>
       </c>
       <c r="P19" s="9">
+        <f t="shared" si="96"/>
+        <v>-140.1</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="96"/>
+        <v>-74.099999999999937</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" ref="R19:S19" si="97">R16-R17-R18</f>
+        <v>-143.40000000000003</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" si="97"/>
+        <v>-160.40000000000006</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" ref="T19" si="98">T16-T17-T18</f>
+        <v>-176.49999999999989</v>
+      </c>
+      <c r="U19" s="9">
+        <f t="shared" ref="U19:V19" si="99">U16-U17-U18</f>
+        <v>-297.89999999999992</v>
+      </c>
+      <c r="V19" s="9">
         <f t="shared" si="99"/>
-        <v>-140.1</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="99"/>
-        <v>-74.099999999999937</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" ref="R19:S19" si="100">R16-R17-R18</f>
-        <v>-143.40000000000003</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" si="100"/>
-        <v>-160.40000000000006</v>
-      </c>
-      <c r="T19" s="9">
-        <f t="shared" ref="T19" si="101">T16-T17-T18</f>
-        <v>-176.49999999999989</v>
-      </c>
-      <c r="U19" s="9">
-        <f t="shared" ref="U19:V19" si="102">U16-U17-U18</f>
-        <v>-297.89999999999992</v>
-      </c>
-      <c r="V19" s="9">
+        <v>-289.79999999999995</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" ref="W19" si="100">W16-W17-W18</f>
+        <v>-268.20000000000005</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" ref="X19" si="101">X16-X17-X18</f>
+        <v>-282.5</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" ref="Y19:Z19" si="102">Y16-Y17-Y18</f>
+        <v>-277.29999999999995</v>
+      </c>
+      <c r="Z19" s="9">
         <f t="shared" si="102"/>
-        <v>-289.79999999999995</v>
-      </c>
-      <c r="W19" s="9">
-        <f t="shared" ref="W19" si="103">W16-W17-W18</f>
-        <v>-268.20000000000005</v>
-      </c>
-      <c r="X19" s="9">
-        <f t="shared" ref="X19" si="104">X16-X17-X18</f>
-        <v>-282.5</v>
-      </c>
-      <c r="Y19" s="9">
-        <f t="shared" ref="Y19:Z19" si="105">Y16-Y17-Y18</f>
-        <v>-277.29999999999995</v>
-      </c>
-      <c r="Z19" s="9">
+        <v>-323.89999999999998</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" ref="AA19" si="103">AA16-AA17-AA18</f>
+        <v>-270.60000000000014</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" ref="AB19" si="104">AB16-AB17-AB18</f>
+        <v>-205.99999999999994</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" ref="AC19:AD19" si="105">AC16-AC17-AC18</f>
+        <v>-239.2</v>
+      </c>
+      <c r="AD19" s="9">
         <f t="shared" si="105"/>
-        <v>-323.89999999999998</v>
-      </c>
-      <c r="AA19" s="9">
-        <f t="shared" ref="AA19" si="106">AA16-AA17-AA18</f>
-        <v>-270.60000000000014</v>
-      </c>
-      <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="107">AB16-AB17-AB18</f>
-        <v>-205.99999999999994</v>
-      </c>
-      <c r="AC19" s="9">
-        <f t="shared" ref="AC19:AD19" si="108">AC16-AC17-AC18</f>
-        <v>-239.2</v>
-      </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="108"/>
         <v>-219.29999999999998</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" ref="AE19:AH19" si="109">AE16-AE17-AE18</f>
+        <f t="shared" ref="AE19:AH19" si="106">AE16-AE17-AE18</f>
         <v>-215.09999999999991</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="109"/>
-        <v>-135.61808400000001</v>
+        <f t="shared" si="106"/>
+        <v>-278.5</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="109"/>
-        <v>-139.03495200000003</v>
+        <f t="shared" si="106"/>
+        <v>-249.70791999999994</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="109"/>
-        <v>-156.22601400000002</v>
+        <f t="shared" si="106"/>
+        <v>-247.44537440000011</v>
       </c>
       <c r="AK19" s="9">
         <f>AK16-AK17-AK18</f>
@@ -4149,516 +4186,516 @@
         <v>-253.09999999999994</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19:AW19" si="110">AN16-AN17-AN18</f>
+        <f t="shared" ref="AN19:AW19" si="107">AN16-AN17-AN18</f>
         <v>-491.69999999999987</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-924.60000000000025</v>
       </c>
       <c r="AP19" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-1151.8999999999996</v>
       </c>
       <c r="AQ19" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>-935.1</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" si="110"/>
-        <v>-645.97905000000014</v>
+        <f t="shared" si="107"/>
+        <v>-990.7532943999995</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="110"/>
-        <v>-190.06624810800022</v>
+        <f t="shared" si="107"/>
+        <v>-662.29255026000021</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="110"/>
-        <v>287.02723014899908</v>
+        <f t="shared" si="107"/>
+        <v>-308.71102741379997</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="110"/>
-        <v>778.71748128609477</v>
+        <f t="shared" si="107"/>
+        <v>41.694191276759675</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="110"/>
-        <v>1253.0964354946034</v>
+        <f t="shared" si="107"/>
+        <v>362.66395139279012</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" si="110"/>
-        <v>1598.3450667868071</v>
+        <f t="shared" si="107"/>
+        <v>642.42508812541246</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" ref="AX19:BB19" si="111">AX16-AX17-AX18</f>
-        <v>1893.6943171011455</v>
+        <f t="shared" ref="AX19:BB19" si="108">AX16-AX17-AX18</f>
+        <v>882.27116344414139</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" si="111"/>
-        <v>2160.9663566136805</v>
+        <f t="shared" si="108"/>
+        <v>1098.2870918753292</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" si="111"/>
-        <v>2392.1169075937501</v>
+        <f t="shared" si="108"/>
+        <v>1283.6830698904685</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" si="111"/>
-        <v>2636.2423258559461</v>
+        <f t="shared" si="108"/>
+        <v>1479.8825831967754</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" si="111"/>
-        <v>2894.0092545097446</v>
+        <f t="shared" si="108"/>
+        <v>1687.445724325838</v>
       </c>
       <c r="BC19" s="1">
         <f>BB19*(1+$BE$26)</f>
-        <v>2865.0691619646473</v>
+        <v>1670.5712670825797</v>
       </c>
       <c r="BD19" s="1">
-        <f t="shared" ref="BD19:DO19" si="112">BC19*(1+$BE$26)</f>
-        <v>2836.418470345001</v>
+        <f t="shared" ref="BD19:DO19" si="109">BC19*(1+$BE$26)</f>
+        <v>1653.8655544117539</v>
       </c>
       <c r="BE19" s="1">
-        <f t="shared" si="112"/>
-        <v>2808.0542856415509</v>
+        <f t="shared" si="109"/>
+        <v>1637.3268988676364</v>
       </c>
       <c r="BF19" s="1">
-        <f t="shared" si="112"/>
-        <v>2779.9737427851355</v>
+        <f t="shared" si="109"/>
+        <v>1620.9536298789601</v>
       </c>
       <c r="BG19" s="1">
-        <f t="shared" si="112"/>
-        <v>2752.1740053572839</v>
+        <f t="shared" si="109"/>
+        <v>1604.7440935801706</v>
       </c>
       <c r="BH19" s="1">
-        <f t="shared" si="112"/>
-        <v>2724.6522653037109</v>
+        <f t="shared" si="109"/>
+        <v>1588.6966526443689</v>
       </c>
       <c r="BI19" s="1">
-        <f t="shared" si="112"/>
-        <v>2697.4057426506738</v>
+        <f t="shared" si="109"/>
+        <v>1572.8096861179251</v>
       </c>
       <c r="BJ19" s="1">
-        <f t="shared" si="112"/>
-        <v>2670.4316852241668</v>
+        <f t="shared" si="109"/>
+        <v>1557.0815892567459</v>
       </c>
       <c r="BK19" s="1">
-        <f t="shared" si="112"/>
-        <v>2643.727368371925</v>
+        <f t="shared" si="109"/>
+        <v>1541.5107733641785</v>
       </c>
       <c r="BL19" s="1">
-        <f t="shared" si="112"/>
-        <v>2617.2900946882055</v>
+        <f t="shared" si="109"/>
+        <v>1526.0956656305366</v>
       </c>
       <c r="BM19" s="1">
-        <f t="shared" si="112"/>
-        <v>2591.1171937413233</v>
+        <f t="shared" si="109"/>
+        <v>1510.8347089742313</v>
       </c>
       <c r="BN19" s="1">
-        <f t="shared" si="112"/>
-        <v>2565.2060218039101</v>
+        <f t="shared" si="109"/>
+        <v>1495.7263618844888</v>
       </c>
       <c r="BO19" s="1">
-        <f t="shared" si="112"/>
-        <v>2539.5539615858711</v>
+        <f t="shared" si="109"/>
+        <v>1480.7690982656438</v>
       </c>
       <c r="BP19" s="1">
-        <f t="shared" si="112"/>
-        <v>2514.1584219700126</v>
+        <f t="shared" si="109"/>
+        <v>1465.9614072829875</v>
       </c>
       <c r="BQ19" s="1">
-        <f t="shared" si="112"/>
-        <v>2489.0168377503123</v>
+        <f t="shared" si="109"/>
+        <v>1451.3017932101575</v>
       </c>
       <c r="BR19" s="1">
-        <f t="shared" si="112"/>
-        <v>2464.1266693728094</v>
+        <f t="shared" si="109"/>
+        <v>1436.7887752780559</v>
       </c>
       <c r="BS19" s="1">
-        <f t="shared" si="112"/>
-        <v>2439.4854026790813</v>
+        <f t="shared" si="109"/>
+        <v>1422.4208875252755</v>
       </c>
       <c r="BT19" s="1">
-        <f t="shared" si="112"/>
-        <v>2415.0905486522906</v>
+        <f t="shared" si="109"/>
+        <v>1408.1966786500227</v>
       </c>
       <c r="BU19" s="1">
-        <f t="shared" si="112"/>
-        <v>2390.9396431657678</v>
+        <f t="shared" si="109"/>
+        <v>1394.1147118635224</v>
       </c>
       <c r="BV19" s="1">
-        <f t="shared" si="112"/>
-        <v>2367.0302467341103</v>
+        <f t="shared" si="109"/>
+        <v>1380.1735647448872</v>
       </c>
       <c r="BW19" s="1">
-        <f t="shared" si="112"/>
-        <v>2343.3599442667692</v>
+        <f t="shared" si="109"/>
+        <v>1366.3718290974384</v>
       </c>
       <c r="BX19" s="1">
-        <f t="shared" si="112"/>
-        <v>2319.9263448241013</v>
+        <f t="shared" si="109"/>
+        <v>1352.708110806464</v>
       </c>
       <c r="BY19" s="1">
-        <f t="shared" si="112"/>
-        <v>2296.7270813758601</v>
+        <f t="shared" si="109"/>
+        <v>1339.1810296983992</v>
       </c>
       <c r="BZ19" s="1">
-        <f t="shared" si="112"/>
-        <v>2273.7598105621014</v>
+        <f t="shared" si="109"/>
+        <v>1325.7892194014153</v>
       </c>
       <c r="CA19" s="1">
-        <f t="shared" si="112"/>
-        <v>2251.0222124564802</v>
+        <f t="shared" si="109"/>
+        <v>1312.5313272074011</v>
       </c>
       <c r="CB19" s="1">
-        <f t="shared" si="112"/>
-        <v>2228.5119903319155</v>
+        <f t="shared" si="109"/>
+        <v>1299.4060139353271</v>
       </c>
       <c r="CC19" s="1">
-        <f t="shared" si="112"/>
-        <v>2206.2268704285962</v>
+        <f t="shared" si="109"/>
+        <v>1286.4119537959739</v>
       </c>
       <c r="CD19" s="1">
-        <f t="shared" si="112"/>
-        <v>2184.1646017243102</v>
+        <f t="shared" si="109"/>
+        <v>1273.5478342580141</v>
       </c>
       <c r="CE19" s="1">
-        <f t="shared" si="112"/>
-        <v>2162.3229557070672</v>
+        <f t="shared" si="109"/>
+        <v>1260.812355915434</v>
       </c>
       <c r="CF19" s="1">
-        <f t="shared" si="112"/>
-        <v>2140.6997261499964</v>
+        <f t="shared" si="109"/>
+        <v>1248.2042323562796</v>
       </c>
       <c r="CG19" s="1">
-        <f t="shared" si="112"/>
-        <v>2119.2927288884966</v>
+        <f t="shared" si="109"/>
+        <v>1235.7221900327168</v>
       </c>
       <c r="CH19" s="1">
-        <f t="shared" si="112"/>
-        <v>2098.0998015996115</v>
+        <f t="shared" si="109"/>
+        <v>1223.3649681323895</v>
       </c>
       <c r="CI19" s="1">
-        <f t="shared" si="112"/>
-        <v>2077.1188035836153</v>
+        <f t="shared" si="109"/>
+        <v>1211.1313184510657</v>
       </c>
       <c r="CJ19" s="1">
-        <f t="shared" si="112"/>
-        <v>2056.3476155477792</v>
+        <f t="shared" si="109"/>
+        <v>1199.020005266555</v>
       </c>
       <c r="CK19" s="1">
-        <f t="shared" si="112"/>
-        <v>2035.7841393923015</v>
+        <f t="shared" si="109"/>
+        <v>1187.0298052138894</v>
       </c>
       <c r="CL19" s="1">
-        <f t="shared" si="112"/>
-        <v>2015.4262979983785</v>
+        <f t="shared" si="109"/>
+        <v>1175.1595071617505</v>
       </c>
       <c r="CM19" s="1">
-        <f t="shared" si="112"/>
-        <v>1995.2720350183947</v>
+        <f t="shared" si="109"/>
+        <v>1163.4079120901331</v>
       </c>
       <c r="CN19" s="1">
-        <f t="shared" si="112"/>
-        <v>1975.3193146682108</v>
+        <f t="shared" si="109"/>
+        <v>1151.7738329692318</v>
       </c>
       <c r="CO19" s="1">
-        <f t="shared" si="112"/>
-        <v>1955.5661215215287</v>
+        <f t="shared" si="109"/>
+        <v>1140.2560946395395</v>
       </c>
       <c r="CP19" s="1">
-        <f t="shared" si="112"/>
-        <v>1936.0104603063135</v>
+        <f t="shared" si="109"/>
+        <v>1128.8535336931441</v>
       </c>
       <c r="CQ19" s="1">
-        <f t="shared" si="112"/>
-        <v>1916.6503557032504</v>
+        <f t="shared" si="109"/>
+        <v>1117.5649983562125</v>
       </c>
       <c r="CR19" s="1">
-        <f t="shared" si="112"/>
-        <v>1897.4838521462179</v>
+        <f t="shared" si="109"/>
+        <v>1106.3893483726504</v>
       </c>
       <c r="CS19" s="1">
-        <f t="shared" si="112"/>
-        <v>1878.5090136247557</v>
+        <f t="shared" si="109"/>
+        <v>1095.3254548889238</v>
       </c>
       <c r="CT19" s="1">
-        <f t="shared" si="112"/>
-        <v>1859.723923488508</v>
+        <f t="shared" si="109"/>
+        <v>1084.3722003400346</v>
       </c>
       <c r="CU19" s="1">
-        <f t="shared" si="112"/>
-        <v>1841.1266842536229</v>
+        <f t="shared" si="109"/>
+        <v>1073.5284783366342</v>
       </c>
       <c r="CV19" s="1">
-        <f t="shared" si="112"/>
-        <v>1822.7154174110867</v>
+        <f t="shared" si="109"/>
+        <v>1062.7931935532679</v>
       </c>
       <c r="CW19" s="1">
-        <f t="shared" si="112"/>
-        <v>1804.4882632369759</v>
+        <f t="shared" si="109"/>
+        <v>1052.1652616177353</v>
       </c>
       <c r="CX19" s="1">
-        <f t="shared" si="112"/>
-        <v>1786.4433806046061</v>
+        <f t="shared" si="109"/>
+        <v>1041.6436090015579</v>
       </c>
       <c r="CY19" s="1">
-        <f t="shared" si="112"/>
-        <v>1768.5789467985601</v>
+        <f t="shared" si="109"/>
+        <v>1031.2271729115423</v>
       </c>
       <c r="CZ19" s="1">
-        <f t="shared" si="112"/>
-        <v>1750.8931573305745</v>
+        <f t="shared" si="109"/>
+        <v>1020.9149011824269</v>
       </c>
       <c r="DA19" s="1">
-        <f t="shared" si="112"/>
-        <v>1733.3842257572687</v>
+        <f t="shared" si="109"/>
+        <v>1010.7057521706026</v>
       </c>
       <c r="DB19" s="1">
-        <f t="shared" si="112"/>
-        <v>1716.050383499696</v>
+        <f t="shared" si="109"/>
+        <v>1000.5986946488966</v>
       </c>
       <c r="DC19" s="1">
-        <f t="shared" si="112"/>
-        <v>1698.889879664699</v>
+        <f t="shared" si="109"/>
+        <v>990.59270770240767</v>
       </c>
       <c r="DD19" s="1">
-        <f t="shared" si="112"/>
-        <v>1681.9009808680521</v>
+        <f t="shared" si="109"/>
+        <v>980.68678062538356</v>
       </c>
       <c r="DE19" s="1">
-        <f t="shared" si="112"/>
-        <v>1665.0819710593717</v>
+        <f t="shared" si="109"/>
+        <v>970.87991281912969</v>
       </c>
       <c r="DF19" s="1">
-        <f t="shared" si="112"/>
-        <v>1648.431151348778</v>
+        <f t="shared" si="109"/>
+        <v>961.17111369093834</v>
       </c>
       <c r="DG19" s="1">
-        <f t="shared" si="112"/>
-        <v>1631.9468398352903</v>
+        <f t="shared" si="109"/>
+        <v>951.55940255402891</v>
       </c>
       <c r="DH19" s="1">
-        <f t="shared" si="112"/>
-        <v>1615.6273714369374</v>
+        <f t="shared" si="109"/>
+        <v>942.04380852848863</v>
       </c>
       <c r="DI19" s="1">
-        <f t="shared" si="112"/>
-        <v>1599.4710977225679</v>
+        <f t="shared" si="109"/>
+        <v>932.62337044320373</v>
       </c>
       <c r="DJ19" s="1">
-        <f t="shared" si="112"/>
-        <v>1583.4763867453423</v>
+        <f t="shared" si="109"/>
+        <v>923.29713673877166</v>
       </c>
       <c r="DK19" s="1">
-        <f t="shared" si="112"/>
-        <v>1567.6416228778889</v>
+        <f t="shared" si="109"/>
+        <v>914.06416537138398</v>
       </c>
       <c r="DL19" s="1">
-        <f t="shared" si="112"/>
-        <v>1551.9652066491101</v>
+        <f t="shared" si="109"/>
+        <v>904.92352371767015</v>
       </c>
       <c r="DM19" s="1">
-        <f t="shared" si="112"/>
-        <v>1536.445554582619</v>
+        <f t="shared" si="109"/>
+        <v>895.87428848049342</v>
       </c>
       <c r="DN19" s="1">
-        <f t="shared" si="112"/>
-        <v>1521.0810990367929</v>
+        <f t="shared" si="109"/>
+        <v>886.91554559568851</v>
       </c>
       <c r="DO19" s="1">
-        <f t="shared" si="112"/>
-        <v>1505.870288046425</v>
+        <f t="shared" si="109"/>
+        <v>878.04639013973167</v>
       </c>
       <c r="DP19" s="1">
-        <f t="shared" ref="DP19:FK19" si="113">DO19*(1+$BE$26)</f>
-        <v>1490.8115851659607</v>
+        <f t="shared" ref="DP19:FK19" si="110">DO19*(1+$BE$26)</f>
+        <v>869.26592623833437</v>
       </c>
       <c r="DQ19" s="1">
-        <f t="shared" si="113"/>
-        <v>1475.903469314301</v>
+        <f t="shared" si="110"/>
+        <v>860.57326697595101</v>
       </c>
       <c r="DR19" s="1">
-        <f t="shared" si="113"/>
-        <v>1461.1444346211579</v>
+        <f t="shared" si="110"/>
+        <v>851.96753430619151</v>
       </c>
       <c r="DS19" s="1">
-        <f t="shared" si="113"/>
-        <v>1446.5329902749463</v>
+        <f t="shared" si="110"/>
+        <v>843.44785896312953</v>
       </c>
       <c r="DT19" s="1">
-        <f t="shared" si="113"/>
-        <v>1432.0676603721968</v>
+        <f t="shared" si="110"/>
+        <v>835.01338037349819</v>
       </c>
       <c r="DU19" s="1">
-        <f t="shared" si="113"/>
-        <v>1417.7469837684748</v>
+        <f t="shared" si="110"/>
+        <v>826.66324656976326</v>
       </c>
       <c r="DV19" s="1">
-        <f t="shared" si="113"/>
-        <v>1403.56951393079</v>
+        <f t="shared" si="110"/>
+        <v>818.39661410406563</v>
       </c>
       <c r="DW19" s="1">
-        <f t="shared" si="113"/>
-        <v>1389.533818791482</v>
+        <f t="shared" si="110"/>
+        <v>810.21264796302501</v>
       </c>
       <c r="DX19" s="1">
-        <f t="shared" si="113"/>
-        <v>1375.6384806035671</v>
+        <f t="shared" si="110"/>
+        <v>802.11052148339479</v>
       </c>
       <c r="DY19" s="1">
-        <f t="shared" si="113"/>
-        <v>1361.8820957975315</v>
+        <f t="shared" si="110"/>
+        <v>794.08941626856085</v>
       </c>
       <c r="DZ19" s="1">
-        <f t="shared" si="113"/>
-        <v>1348.2632748395563</v>
+        <f t="shared" si="110"/>
+        <v>786.14852210587526</v>
       </c>
       <c r="EA19" s="1">
-        <f t="shared" si="113"/>
-        <v>1334.7806420911606</v>
+        <f t="shared" si="110"/>
+        <v>778.28703688481653</v>
       </c>
       <c r="EB19" s="1">
-        <f t="shared" si="113"/>
-        <v>1321.432835670249</v>
+        <f t="shared" si="110"/>
+        <v>770.50416651596834</v>
       </c>
       <c r="EC19" s="1">
-        <f t="shared" si="113"/>
-        <v>1308.2185073135465</v>
+        <f t="shared" si="110"/>
+        <v>762.79912485080865</v>
       </c>
       <c r="ED19" s="1">
-        <f t="shared" si="113"/>
-        <v>1295.1363222404111</v>
+        <f t="shared" si="110"/>
+        <v>755.17113360230053</v>
       </c>
       <c r="EE19" s="1">
-        <f t="shared" si="113"/>
-        <v>1282.184959018007</v>
+        <f t="shared" si="110"/>
+        <v>747.61942226627752</v>
       </c>
       <c r="EF19" s="1">
-        <f t="shared" si="113"/>
-        <v>1269.3631094278269</v>
+        <f t="shared" si="110"/>
+        <v>740.14322804361473</v>
       </c>
       <c r="EG19" s="1">
-        <f t="shared" si="113"/>
-        <v>1256.6694783335486</v>
+        <f t="shared" si="110"/>
+        <v>732.74179576317863</v>
       </c>
       <c r="EH19" s="1">
-        <f t="shared" si="113"/>
-        <v>1244.102783550213</v>
+        <f t="shared" si="110"/>
+        <v>725.41437780554679</v>
       </c>
       <c r="EI19" s="1">
-        <f t="shared" si="113"/>
-        <v>1231.6617557147108</v>
+        <f t="shared" si="110"/>
+        <v>718.16023402749136</v>
       </c>
       <c r="EJ19" s="1">
-        <f t="shared" si="113"/>
-        <v>1219.3451381575637</v>
+        <f t="shared" si="110"/>
+        <v>710.97863168721642</v>
       </c>
       <c r="EK19" s="1">
-        <f t="shared" si="113"/>
-        <v>1207.1516867759881</v>
+        <f t="shared" si="110"/>
+        <v>703.86884537034427</v>
       </c>
       <c r="EL19" s="1">
-        <f t="shared" si="113"/>
-        <v>1195.0801699082283</v>
+        <f t="shared" si="110"/>
+        <v>696.83015691664082</v>
       </c>
       <c r="EM19" s="1">
-        <f t="shared" si="113"/>
-        <v>1183.1293682091459</v>
+        <f t="shared" si="110"/>
+        <v>689.86185534747437</v>
       </c>
       <c r="EN19" s="1">
-        <f t="shared" si="113"/>
-        <v>1171.2980745270545</v>
+        <f t="shared" si="110"/>
+        <v>682.96323679399961</v>
       </c>
       <c r="EO19" s="1">
-        <f t="shared" si="113"/>
-        <v>1159.5850937817841</v>
+        <f t="shared" si="110"/>
+        <v>676.13360442605961</v>
       </c>
       <c r="EP19" s="1">
-        <f t="shared" si="113"/>
-        <v>1147.9892428439662</v>
+        <f t="shared" si="110"/>
+        <v>669.37226838179902</v>
       </c>
       <c r="EQ19" s="1">
-        <f t="shared" si="113"/>
-        <v>1136.5093504155266</v>
+        <f t="shared" si="110"/>
+        <v>662.67854569798101</v>
       </c>
       <c r="ER19" s="1">
-        <f t="shared" si="113"/>
-        <v>1125.1442569113713</v>
+        <f t="shared" si="110"/>
+        <v>656.05176024100115</v>
       </c>
       <c r="ES19" s="1">
-        <f t="shared" si="113"/>
-        <v>1113.8928143422575</v>
+        <f t="shared" si="110"/>
+        <v>649.49124263859107</v>
       </c>
       <c r="ET19" s="1">
-        <f t="shared" si="113"/>
-        <v>1102.7538861988348</v>
+        <f t="shared" si="110"/>
+        <v>642.99633021220518</v>
       </c>
       <c r="EU19" s="1">
-        <f t="shared" si="113"/>
-        <v>1091.7263473368464</v>
+        <f t="shared" si="110"/>
+        <v>636.56636691008316</v>
       </c>
       <c r="EV19" s="1">
-        <f t="shared" si="113"/>
-        <v>1080.809083863478</v>
+        <f t="shared" si="110"/>
+        <v>630.20070324098231</v>
       </c>
       <c r="EW19" s="1">
-        <f t="shared" si="113"/>
-        <v>1070.0009930248432</v>
+        <f t="shared" si="110"/>
+        <v>623.89869620857246</v>
       </c>
       <c r="EX19" s="1">
-        <f t="shared" si="113"/>
-        <v>1059.3009830945948</v>
+        <f t="shared" si="110"/>
+        <v>617.65970924648673</v>
       </c>
       <c r="EY19" s="1">
-        <f t="shared" si="113"/>
-        <v>1048.7079732636489</v>
+        <f t="shared" si="110"/>
+        <v>611.48311215402191</v>
       </c>
       <c r="EZ19" s="1">
-        <f t="shared" si="113"/>
-        <v>1038.2208935310125</v>
+        <f t="shared" si="110"/>
+        <v>605.36828103248172</v>
       </c>
       <c r="FA19" s="1">
-        <f t="shared" si="113"/>
-        <v>1027.8386845957023</v>
+        <f t="shared" si="110"/>
+        <v>599.31459822215686</v>
       </c>
       <c r="FB19" s="1">
-        <f t="shared" si="113"/>
-        <v>1017.5602977497452</v>
+        <f t="shared" si="110"/>
+        <v>593.3214522399353</v>
       </c>
       <c r="FC19" s="1">
-        <f t="shared" si="113"/>
-        <v>1007.3846947722478</v>
+        <f t="shared" si="110"/>
+        <v>587.38823771753596</v>
       </c>
       <c r="FD19" s="1">
-        <f t="shared" si="113"/>
-        <v>997.31084782452535</v>
+        <f t="shared" si="110"/>
+        <v>581.51435534036057</v>
       </c>
       <c r="FE19" s="1">
-        <f t="shared" si="113"/>
-        <v>987.33773934628005</v>
+        <f t="shared" si="110"/>
+        <v>575.69921178695699</v>
       </c>
       <c r="FF19" s="1">
-        <f t="shared" si="113"/>
-        <v>977.46436195281728</v>
+        <f t="shared" si="110"/>
+        <v>569.94221966908742</v>
       </c>
       <c r="FG19" s="1">
-        <f t="shared" si="113"/>
-        <v>967.68971833328908</v>
+        <f t="shared" si="110"/>
+        <v>564.24279747239655</v>
       </c>
       <c r="FH19" s="1">
-        <f t="shared" si="113"/>
-        <v>958.01282114995615</v>
+        <f t="shared" si="110"/>
+        <v>558.60036949767255</v>
       </c>
       <c r="FI19" s="1">
-        <f t="shared" si="113"/>
-        <v>948.43269293845663</v>
+        <f t="shared" si="110"/>
+        <v>553.01436580269581</v>
       </c>
       <c r="FJ19" s="1">
-        <f t="shared" si="113"/>
-        <v>938.94836600907206</v>
+        <f t="shared" si="110"/>
+        <v>547.48422214466882</v>
       </c>
       <c r="FK19" s="1">
-        <f t="shared" si="113"/>
-        <v>929.55888234898134</v>
+        <f t="shared" si="110"/>
+        <v>542.00937992322213</v>
       </c>
     </row>
     <row r="20" spans="2:167" x14ac:dyDescent="0.3">
@@ -4756,16 +4793,16 @@
         <v>678.3</v>
       </c>
       <c r="AF20" s="5">
-        <f>630+48.3</f>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AG20" s="5">
-        <f>630+48.3</f>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AH20" s="5">
-        <f>630+48.3</f>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AK20" s="5">
         <v>147.30000000000001</v>
@@ -4786,52 +4823,52 @@
         <v>489</v>
       </c>
       <c r="AQ20" s="5">
-        <f t="shared" ref="AQ20" si="114">619+48.3</f>
+        <f t="shared" ref="AQ20" si="111">619+48.3</f>
         <v>667.3</v>
       </c>
       <c r="AR20" s="5">
-        <f t="shared" ref="AR20:BB20" si="115">630+48.3</f>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AS20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AT20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AU20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AV20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AW20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AX20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AY20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="AZ20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="BA20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
       <c r="BB20" s="5">
-        <f t="shared" si="115"/>
-        <v>678.3</v>
+        <f>645</f>
+        <v>645</v>
       </c>
     </row>
     <row r="21" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4839,132 +4876,132 @@
         <v>32</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:N21" si="116">C19/C20</f>
+        <f t="shared" ref="C21:N21" si="112">C19/C20</f>
         <v>-9.7759674134419577E-2</v>
       </c>
       <c r="D21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.16021724372029861</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.26883910386965382</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="112"/>
+        <v>-7.1961982348947739E-2</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="112"/>
+        <v>-6.0420909708078736E-2</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="112"/>
+        <v>-8.2824168363883205E-2</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.11812627291242363</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.22131704005431097</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.50509164969450115</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.50441276306856764</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.33061778682959958</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="112"/>
+        <v>-0.30587589236683138</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" ref="O21:Q21" si="113">O19/O20</f>
+        <v>-0.27423312883435574</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="113"/>
+        <v>-0.28650306748466259</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="113"/>
+        <v>-0.15153374233128822</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" ref="R21:S21" si="114">R19/R20</f>
+        <v>-0.29325153374233137</v>
+      </c>
+      <c r="S21" s="8">
+        <f t="shared" si="114"/>
+        <v>-0.32801635991820055</v>
+      </c>
+      <c r="T21" s="8">
+        <f t="shared" ref="T21" si="115">T19/T20</f>
+        <v>-0.36094069529652328</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" ref="U21:V21" si="116">U19/U20</f>
+        <v>-0.60920245398772987</v>
+      </c>
+      <c r="V21" s="8">
         <f t="shared" si="116"/>
-        <v>-0.16021724372029861</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.26883910386965382</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="116"/>
-        <v>-7.1961982348947739E-2</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="116"/>
-        <v>-6.0420909708078736E-2</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="116"/>
-        <v>-8.2824168363883205E-2</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.11812627291242363</v>
-      </c>
-      <c r="J21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.22131704005431097</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.50509164969450115</v>
-      </c>
-      <c r="L21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.50441276306856764</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.33061778682959958</v>
-      </c>
-      <c r="N21" s="8">
-        <f t="shared" si="116"/>
-        <v>-0.30587589236683138</v>
-      </c>
-      <c r="O21" s="8">
-        <f t="shared" ref="O21:Q21" si="117">O19/O20</f>
-        <v>-0.27423312883435574</v>
-      </c>
-      <c r="P21" s="8">
-        <f t="shared" si="117"/>
-        <v>-0.28650306748466259</v>
-      </c>
-      <c r="Q21" s="8">
-        <f t="shared" si="117"/>
-        <v>-0.15153374233128822</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" ref="R21:S21" si="118">R19/R20</f>
-        <v>-0.29325153374233137</v>
-      </c>
-      <c r="S21" s="8">
-        <f t="shared" si="118"/>
-        <v>-0.32801635991820055</v>
-      </c>
-      <c r="T21" s="8">
-        <f t="shared" ref="T21" si="119">T19/T20</f>
-        <v>-0.36094069529652328</v>
-      </c>
-      <c r="U21" s="8">
-        <f t="shared" ref="U21:V21" si="120">U19/U20</f>
-        <v>-0.60920245398772987</v>
-      </c>
-      <c r="V21" s="8">
-        <f t="shared" si="120"/>
         <v>-0.59263803680981586</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" ref="W21" si="121">W19/W20</f>
+        <f t="shared" ref="W21" si="117">W19/W20</f>
         <v>-0.54846625766871171</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" ref="X21" si="122">X19/X20</f>
+        <f t="shared" ref="X21" si="118">X19/X20</f>
         <v>-0.57770961145194277</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21:Z21" si="123">Y19/Y20</f>
+        <f t="shared" ref="Y21:Z21" si="119">Y19/Y20</f>
         <v>-0.5670756646216768</v>
       </c>
       <c r="Z21" s="8">
+        <f t="shared" si="119"/>
+        <v>-0.66237218813905929</v>
+      </c>
+      <c r="AA21" s="8">
+        <f t="shared" ref="AA21" si="120">AA19/AA20</f>
+        <v>-0.5533742331288346</v>
+      </c>
+      <c r="AB21" s="8">
+        <f t="shared" ref="AB21" si="121">AB19/AB20</f>
+        <v>-0.42126789366053158</v>
+      </c>
+      <c r="AC21" s="8">
+        <f t="shared" ref="AC21:AD21" si="122">AC19/AC20</f>
+        <v>-0.36452301127704961</v>
+      </c>
+      <c r="AD21" s="8">
+        <f t="shared" si="122"/>
+        <v>-0.32863779409560917</v>
+      </c>
+      <c r="AE21" s="8">
+        <f t="shared" ref="AE21:AH21" si="123">AE19/AE20</f>
+        <v>-0.31711632021229536</v>
+      </c>
+      <c r="AF21" s="8">
         <f t="shared" si="123"/>
-        <v>-0.66237218813905929</v>
-      </c>
-      <c r="AA21" s="8">
-        <f t="shared" ref="AA21" si="124">AA19/AA20</f>
-        <v>-0.5533742331288346</v>
-      </c>
-      <c r="AB21" s="8">
-        <f t="shared" ref="AB21" si="125">AB19/AB20</f>
-        <v>-0.42126789366053158</v>
-      </c>
-      <c r="AC21" s="8">
-        <f t="shared" ref="AC21:AD21" si="126">AC19/AC20</f>
-        <v>-0.36452301127704961</v>
-      </c>
-      <c r="AD21" s="8">
-        <f t="shared" si="126"/>
-        <v>-0.32863779409560917</v>
-      </c>
-      <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AH21" si="127">AE19/AE20</f>
-        <v>-0.31711632021229536</v>
-      </c>
-      <c r="AF21" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.19993820433436535</v>
+        <v>-0.43178294573643411</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.20497560371517035</v>
+        <f t="shared" si="123"/>
+        <v>-0.38714406201550378</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.23031993808049539</v>
+        <f t="shared" si="123"/>
+        <v>-0.38363623937984515</v>
       </c>
       <c r="AK21" s="8">
         <f>AK19/AK20</f>
@@ -4979,64 +5016,64 @@
         <v>-1.4235095613048365</v>
       </c>
       <c r="AN21" s="8">
-        <f t="shared" ref="AN21:AW21" si="128">AN19/AN20</f>
+        <f t="shared" ref="AN21:AW21" si="124">AN19/AN20</f>
         <v>-2.4720965309200595</v>
       </c>
       <c r="AO21" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-1.8907975460122703</v>
       </c>
       <c r="AP21" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-2.3556237218813898</v>
       </c>
       <c r="AQ21" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-1.4013187471901696</v>
       </c>
       <c r="AR21" s="8">
-        <f t="shared" si="128"/>
-        <v>-0.95235006634232666</v>
+        <f t="shared" si="124"/>
+        <v>-1.5360516192248055</v>
       </c>
       <c r="AS21" s="8">
-        <f t="shared" si="128"/>
-        <v>-0.28020971267580752</v>
+        <f t="shared" si="124"/>
+        <v>-1.0268101554418607</v>
       </c>
       <c r="AT21" s="8">
-        <f t="shared" si="128"/>
-        <v>0.42315675976558914</v>
+        <f t="shared" si="124"/>
+        <v>-0.47862174792837203</v>
       </c>
       <c r="AU21" s="8">
-        <f t="shared" si="128"/>
-        <v>1.1480428737816524</v>
+        <f t="shared" si="124"/>
+        <v>6.464215701823206E-2</v>
       </c>
       <c r="AV21" s="8">
-        <f t="shared" si="128"/>
-        <v>1.8474073942128904</v>
+        <f t="shared" si="124"/>
+        <v>0.56226969208184518</v>
       </c>
       <c r="AW21" s="8">
-        <f t="shared" si="128"/>
-        <v>2.3563984472752577</v>
+        <f t="shared" si="124"/>
+        <v>0.996007888566531</v>
       </c>
       <c r="AX21" s="8">
-        <f t="shared" ref="AX21:BB21" si="129">AX19/AX20</f>
-        <v>2.791824144333106</v>
+        <f t="shared" ref="AX21:BB21" si="125">AX19/AX20</f>
+        <v>1.3678622689056457</v>
       </c>
       <c r="AY21" s="8">
-        <f t="shared" si="129"/>
-        <v>3.1858563417568639</v>
+        <f t="shared" si="125"/>
+        <v>1.7027706850780298</v>
       </c>
       <c r="AZ21" s="8">
-        <f t="shared" si="129"/>
-        <v>3.5266355706822208</v>
+        <f t="shared" si="125"/>
+        <v>1.990206309907703</v>
       </c>
       <c r="BA21" s="8">
-        <f t="shared" si="129"/>
-        <v>3.8865433080583021</v>
+        <f t="shared" si="125"/>
+        <v>2.2943916018554655</v>
       </c>
       <c r="BB21" s="8">
-        <f t="shared" si="129"/>
-        <v>4.2665623684354195</v>
+        <f t="shared" si="125"/>
+        <v>2.6161949214354077</v>
       </c>
     </row>
     <row r="23" spans="2:167" x14ac:dyDescent="0.3">
@@ -5048,183 +5085,183 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7">
-        <f t="shared" ref="G23:R23" si="130">G3/C3-1</f>
+        <f t="shared" ref="G23:R23" si="126">G3/C3-1</f>
         <v>0.74290220820189279</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.58090185676392569</v>
       </c>
       <c r="I23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.51385681293302543</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.48192771084337349</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.46244343891402706</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.68120805369127524</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.92143401983218931</v>
       </c>
       <c r="N23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>1.1002710027100271</v>
       </c>
       <c r="O23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>1.3948019801980198</v>
       </c>
       <c r="P23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>1.2659680638722555</v>
       </c>
       <c r="Q23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>1.0218340611353711</v>
       </c>
       <c r="R23" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="126"/>
         <v>0.83483870967741924</v>
       </c>
       <c r="S23" s="7">
-        <f t="shared" ref="S23:AD23" si="131">S3/O3-1</f>
+        <f t="shared" ref="S23:AD23" si="127">S3/O3-1</f>
         <v>0.38785529715762279</v>
       </c>
       <c r="T23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.30191587756000882</v>
       </c>
       <c r="U23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>1.6493225996465855E-2</v>
       </c>
       <c r="V23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>1.7932489451476963E-2</v>
       </c>
       <c r="W23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.22007075032582368</v>
       </c>
       <c r="X23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.15155615696887659</v>
       </c>
       <c r="Y23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.37763183310797754</v>
       </c>
       <c r="Z23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.29516407599309158</v>
       </c>
       <c r="AA23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.22279871814436136</v>
       </c>
       <c r="AB23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.31242655699177457</v>
       </c>
       <c r="AC23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.28855860908581032</v>
       </c>
       <c r="AD23" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.3177757034271238</v>
       </c>
       <c r="AE23" s="7">
-        <f t="shared" ref="AE23" si="132">AE3/AA3-1</f>
+        <f t="shared" ref="AE23" si="128">AE3/AA3-1</f>
         <v>0.29190066142518423</v>
       </c>
       <c r="AF23" s="7">
-        <f t="shared" ref="AF23" si="133">AF3/AB3-1</f>
-        <v>0.28000000000000003</v>
+        <f t="shared" ref="AF23" si="129">AF3/AB3-1</f>
+        <v>0.20951315053161723</v>
       </c>
       <c r="AG23" s="7">
-        <f t="shared" ref="AG23" si="134">AG3/AC3-1</f>
-        <v>0.28000000000000003</v>
+        <f t="shared" ref="AG23" si="130">AG3/AC3-1</f>
+        <v>0.23503808487486388</v>
       </c>
       <c r="AH23" s="7">
-        <f t="shared" ref="AH23" si="135">AH3/AD3-1</f>
-        <v>0.22999999999999998</v>
+        <f t="shared" ref="AH23" si="131">AH3/AD3-1</f>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AL23" s="7">
-        <f t="shared" ref="AL23:AX23" si="136">AL3/AK3-1</f>
+        <f t="shared" ref="AL23:AX23" si="132">AL3/AK3-1</f>
         <v>0.56430769230769218</v>
       </c>
       <c r="AM23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.81726986624704967</v>
       </c>
       <c r="AN23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.0772810910271677</v>
       </c>
       <c r="AO23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.15933722384326798</v>
       </c>
       <c r="AP23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.25806741573033709</v>
       </c>
       <c r="AQ23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.28679622749356937</v>
       </c>
       <c r="AR23" s="7">
-        <f t="shared" si="136"/>
-        <v>0.26893003886729594</v>
+        <f t="shared" si="132"/>
+        <v>0.23723042754025547</v>
       </c>
       <c r="AS23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AT23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="AU23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AV23" s="7">
-        <f t="shared" si="136"/>
-        <v>0.11999999999999988</v>
+        <f t="shared" si="132"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AW23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AX23" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AY23" s="7">
-        <f t="shared" ref="AY23:BB23" si="137">AY3/AX3-1</f>
+        <f t="shared" ref="AY23:BB23" si="133">AY3/AX3-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AZ23" s="7">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA23" s="7">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB23" s="7">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -5233,204 +5270,204 @@
         <v>73</v>
       </c>
       <c r="C24" s="7">
-        <f t="shared" ref="C24:AC24" si="138">C4/C3</f>
-        <v>0.21766561514195584</v>
+        <f>(C3-C4)/C3</f>
+        <v>0.78233438485804407</v>
       </c>
       <c r="D24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22148541114058354</v>
+        <f t="shared" ref="D24:AH24" si="134">(D3-D4)/D3</f>
+        <v>0.77851458885941638</v>
       </c>
       <c r="E24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.2263279445727483</v>
+        <f t="shared" si="134"/>
+        <v>0.77367205542725181</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22991967871485944</v>
+        <f t="shared" si="134"/>
+        <v>0.77008032128514048</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.23438914027149321</v>
+        <f t="shared" si="134"/>
+        <v>0.76561085972850673</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.23238255033557045</v>
+        <f t="shared" si="134"/>
+        <v>0.76761744966442946</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.24103737604881773</v>
+        <f t="shared" si="134"/>
+        <v>0.7589626239511823</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25203252032520329</v>
+        <f t="shared" si="134"/>
+        <v>0.74796747967479671</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25866336633663367</v>
+        <f t="shared" si="134"/>
+        <v>0.74133663366336633</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.26796407185628746</v>
+        <f t="shared" si="134"/>
+        <v>0.73203592814371254</v>
       </c>
       <c r="M24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.26121476776498609</v>
+        <f t="shared" si="134"/>
+        <v>0.73878523223501402</v>
       </c>
       <c r="N24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25354838709677424</v>
+        <f t="shared" si="134"/>
+        <v>0.7464516129032257</v>
       </c>
       <c r="O24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25297157622739019</v>
+        <f t="shared" si="134"/>
+        <v>0.74702842377260992</v>
       </c>
       <c r="P24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25743228363796522</v>
+        <f t="shared" si="134"/>
+        <v>0.74256771636203489</v>
       </c>
       <c r="Q24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25525230708816021</v>
+        <f t="shared" si="134"/>
+        <v>0.74474769291183973</v>
       </c>
       <c r="R24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.26722925457102675</v>
+        <f t="shared" si="134"/>
+        <v>0.73277074542897325</v>
       </c>
       <c r="S24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.25246695215043752</v>
+        <f t="shared" si="134"/>
+        <v>0.74753304784956243</v>
       </c>
       <c r="T24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.24221921515561565</v>
+        <f t="shared" si="134"/>
+        <v>0.75778078484438438</v>
       </c>
       <c r="U24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.24415684759513231</v>
+        <f t="shared" si="134"/>
+        <v>0.75584315240486777</v>
       </c>
       <c r="V24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.2459412780656304</v>
+        <f t="shared" si="134"/>
+        <v>0.75405872193436962</v>
       </c>
       <c r="W24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.23164962612543877</v>
+        <f t="shared" si="134"/>
+        <v>0.76835037387456129</v>
       </c>
       <c r="X24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.23795534665099885</v>
+        <f t="shared" si="134"/>
+        <v>0.76204465334900118</v>
       </c>
       <c r="Y24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22938867077958494</v>
+        <f t="shared" si="134"/>
+        <v>0.77061132922041498</v>
       </c>
       <c r="Z24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22896386184824644</v>
+        <f t="shared" si="134"/>
+        <v>0.77103613815175365</v>
       </c>
       <c r="AA24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22326219892674407</v>
+        <f t="shared" si="134"/>
+        <v>0.77673780107325596</v>
       </c>
       <c r="AB24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22227196418578624</v>
+        <f t="shared" si="134"/>
+        <v>0.77772803581421379</v>
       </c>
       <c r="AC24" s="7">
-        <f t="shared" si="138"/>
-        <v>0.22306855277475518</v>
+        <f t="shared" si="134"/>
+        <v>0.77693144722524488</v>
       </c>
       <c r="AD24" s="7">
-        <f>AD4/AD3</f>
-        <v>0.22131147540983603</v>
+        <f t="shared" si="134"/>
+        <v>0.77868852459016391</v>
       </c>
       <c r="AE24" s="7">
-        <f t="shared" ref="AE24:AH24" si="139">AE4/AE3</f>
-        <v>0.21705950540958266</v>
+        <f t="shared" si="134"/>
+        <v>0.78294049459041726</v>
       </c>
       <c r="AF24" s="7">
-        <f t="shared" si="139"/>
-        <v>0.22</v>
+        <f t="shared" si="134"/>
+        <v>0.78153048949754789</v>
       </c>
       <c r="AG24" s="7">
-        <f t="shared" si="139"/>
-        <v>0.22</v>
+        <f t="shared" si="134"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AH24" s="7">
-        <f t="shared" si="139"/>
-        <v>0.22</v>
+        <f t="shared" si="134"/>
+        <v>0.78</v>
       </c>
       <c r="AK24" s="7">
-        <f t="shared" ref="AK24:AQ24" si="140">AK4/AK3</f>
-        <v>0.22461538461538461</v>
+        <f t="shared" ref="AK24:BB24" si="135">(AK3-AK4)/AK3</f>
+        <v>0.77538461538461534</v>
       </c>
       <c r="AL24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.24075531077891424</v>
+        <f t="shared" si="135"/>
+        <v>0.75924468922108579</v>
       </c>
       <c r="AM24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.25966013637839597</v>
+        <f t="shared" si="135"/>
+        <v>0.74033986362160409</v>
       </c>
       <c r="AN24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.25885785744060025</v>
+        <f t="shared" si="135"/>
+        <v>0.74114214255939981</v>
       </c>
       <c r="AO24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.24611235955056177</v>
+        <f t="shared" si="135"/>
+        <v>0.75388764044943823</v>
       </c>
       <c r="AP24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.23188768219491276</v>
+        <f t="shared" si="135"/>
+        <v>0.76811231780508726</v>
       </c>
       <c r="AQ24" s="7">
-        <f t="shared" si="140"/>
-        <v>0.22243198223209329</v>
+        <f t="shared" si="135"/>
+        <v>0.77756801776790674</v>
       </c>
       <c r="AR24" s="7">
-        <f t="shared" ref="AR24:BB24" si="141">AR4/AR3</f>
-        <v>0.21933401681935713</v>
+        <f t="shared" si="135"/>
+        <v>0.78105418956204231</v>
       </c>
       <c r="AS24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AT24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AU24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AV24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.78</v>
       </c>
       <c r="AW24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AX24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="135"/>
+        <v>0.78</v>
       </c>
       <c r="AY24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.78</v>
       </c>
       <c r="AZ24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.78</v>
       </c>
       <c r="BA24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.78</v>
       </c>
       <c r="BB24" s="7">
-        <f t="shared" si="141"/>
-        <v>0.22</v>
+        <f t="shared" si="135"/>
+        <v>0.77999999999999992</v>
       </c>
     </row>
     <row r="25" spans="2:167" x14ac:dyDescent="0.3">
@@ -5438,204 +5475,204 @@
         <v>39</v>
       </c>
       <c r="C25" s="7">
-        <f t="shared" ref="C25:AD25" si="142">C5/C3</f>
-        <v>0.25709779179810727</v>
+        <f>(C3-C5)/C3</f>
+        <v>0.74290220820189268</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.21883289124668434</v>
+        <f t="shared" ref="D25:AH25" si="136">(D3-D5)/D3</f>
+        <v>0.78116710875331563</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.20785219399538107</v>
+        <f t="shared" si="136"/>
+        <v>0.79214780600461887</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.21184738955823296</v>
+        <f t="shared" si="136"/>
+        <v>0.7881526104417671</v>
       </c>
       <c r="G25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.20542986425339366</v>
+        <f t="shared" si="136"/>
+        <v>0.79457013574660629</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.19546979865771813</v>
+        <f t="shared" si="136"/>
+        <v>0.80453020134228193</v>
       </c>
       <c r="I25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.19984744469870327</v>
+        <f t="shared" si="136"/>
+        <v>0.8001525553012967</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.26964769647696474</v>
+        <f t="shared" si="136"/>
+        <v>0.73035230352303526</v>
       </c>
       <c r="K25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.27537128712871289</v>
+        <f t="shared" si="136"/>
+        <v>0.72462871287128716</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.42465069860279436</v>
+        <f t="shared" si="136"/>
+        <v>0.57534930139720564</v>
       </c>
       <c r="M25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.33942040492258835</v>
+        <f t="shared" si="136"/>
+        <v>0.66057959507741171</v>
       </c>
       <c r="N25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.36645161290322581</v>
+        <f t="shared" si="136"/>
+        <v>0.63354838709677419</v>
       </c>
       <c r="O25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.30723514211886305</v>
+        <f t="shared" si="136"/>
+        <v>0.69276485788113706</v>
       </c>
       <c r="P25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.28561990750935912</v>
+        <f t="shared" si="136"/>
+        <v>0.71438009249064083</v>
       </c>
       <c r="Q25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.25525230708816021</v>
+        <f t="shared" si="136"/>
+        <v>0.74474769291183973</v>
       </c>
       <c r="R25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.2807665260196906</v>
+        <f t="shared" si="136"/>
+        <v>0.71923347398030946</v>
       </c>
       <c r="S25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.27387823496555574</v>
+        <f t="shared" si="136"/>
+        <v>0.72612176503444426</v>
       </c>
       <c r="T25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.24205006765899861</v>
+        <f t="shared" si="136"/>
+        <v>0.75794993234100139</v>
       </c>
       <c r="U25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.29264052540081126</v>
+        <f t="shared" si="136"/>
+        <v>0.7073594745991888</v>
       </c>
       <c r="V25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.31450777202072538</v>
+        <f t="shared" si="136"/>
+        <v>0.68549222797927456</v>
       </c>
       <c r="W25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.278345795818709</v>
+        <f t="shared" si="136"/>
+        <v>0.721654204181291</v>
       </c>
       <c r="X25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.24353701527614574</v>
+        <f t="shared" si="136"/>
+        <v>0.75646298472385431</v>
       </c>
       <c r="Y25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.23934380257992144</v>
+        <f t="shared" si="136"/>
+        <v>0.76065619742007851</v>
       </c>
       <c r="Z25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.29577276970262706</v>
+        <f t="shared" si="136"/>
+        <v>0.70422723029737289</v>
       </c>
       <c r="AA25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.25258954199425937</v>
+        <f t="shared" si="136"/>
+        <v>0.74741045800574069</v>
       </c>
       <c r="AB25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.2331281477336318</v>
+        <f t="shared" si="136"/>
+        <v>0.76687185226636823</v>
       </c>
       <c r="AC25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.25190424374319914</v>
+        <f t="shared" si="136"/>
+        <v>0.74809575625680091</v>
       </c>
       <c r="AD25" s="7">
-        <f t="shared" si="142"/>
-        <v>0.2839506172839506</v>
+        <f t="shared" si="136"/>
+        <v>0.71604938271604934</v>
       </c>
       <c r="AE25" s="7">
-        <f t="shared" ref="AE25:AH25" si="143">AE5/AE3</f>
-        <v>0.27202472952086554</v>
+        <f t="shared" si="136"/>
+        <v>0.72797527047913446</v>
       </c>
       <c r="AF25" s="7">
-        <f t="shared" si="143"/>
-        <v>0.25</v>
+        <f t="shared" si="136"/>
+        <v>0.70722679744609973</v>
       </c>
       <c r="AG25" s="7">
-        <f t="shared" si="143"/>
-        <v>0.25</v>
+        <f t="shared" si="136"/>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AH25" s="7">
-        <f t="shared" si="143"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="136"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="AK25" s="7">
-        <f t="shared" ref="AK25:AQ25" si="144">AK5/AK3</f>
-        <v>0.22123076923076926</v>
+        <f t="shared" ref="AK25:BB25" si="137">(AK3-AK5)/AK3</f>
+        <v>0.77876923076923077</v>
       </c>
       <c r="AL25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.22029897718332023</v>
+        <f t="shared" si="137"/>
+        <v>0.77970102281667975</v>
       </c>
       <c r="AM25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.35577443446260415</v>
+        <f t="shared" si="137"/>
+        <v>0.64422556553739585</v>
       </c>
       <c r="AN25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.28048145060441848</v>
+        <f t="shared" si="137"/>
+        <v>0.71951854939558157</v>
       </c>
       <c r="AO25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.28035955056179773</v>
+        <f t="shared" si="137"/>
+        <v>0.71964044943820227</v>
       </c>
       <c r="AP25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.26461131751929123</v>
+        <f t="shared" si="137"/>
+        <v>0.73538868248070866</v>
       </c>
       <c r="AQ25" s="7">
-        <f t="shared" si="144"/>
-        <v>0.2561910049972238</v>
+        <f t="shared" si="137"/>
+        <v>0.7438089950027762</v>
       </c>
       <c r="AR25" s="7">
-        <f t="shared" ref="AR25:BB25" si="145">AR5/AR3</f>
-        <v>0.26296623307748551</v>
+        <f t="shared" si="137"/>
+        <v>0.71334454092266042</v>
       </c>
       <c r="AS25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.24</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="AT25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.23</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="AU25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.22</v>
+        <f t="shared" si="137"/>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AV25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="AW25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21</v>
+        <f t="shared" si="137"/>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AX25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="AY25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21000000000000002</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="AZ25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.20999999999999996</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="BA25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
       <c r="BB25" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21</v>
+        <f t="shared" si="137"/>
+        <v>0.72</v>
       </c>
     </row>
     <row r="26" spans="2:167" x14ac:dyDescent="0.3">
@@ -5647,184 +5684,184 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7">
-        <f t="shared" ref="G26:AD26" si="146">G6/C6-1</f>
+        <f t="shared" ref="G26:AD26" si="138">G6/C6-1</f>
         <v>0.78191489361702127</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.33812949640287782</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.40893470790377995</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.51006711409395966</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.57014925373134329</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.66397849462365577</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.74146341463414656</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.73999999999999955</v>
       </c>
       <c r="O26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.78897338403041806</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.76090468497576746</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.64425770308123242</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.73690932311622004</v>
       </c>
       <c r="S26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.50265674814027639</v>
       </c>
       <c r="T26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.45137614678899074</v>
       </c>
       <c r="U26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.62691652470187376</v>
       </c>
       <c r="V26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.45955882352941169</v>
       </c>
       <c r="W26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.49222065063649212</v>
       </c>
       <c r="X26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.42225031605562591</v>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.14659685863874339</v>
       </c>
       <c r="Z26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.12493702770780857</v>
       </c>
       <c r="AA26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>7.5355450236966881E-2</v>
       </c>
       <c r="AB26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>-1.7333333333333312E-2</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>0.11689497716894981</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="138"/>
         <v>-2.2391401701746805E-3</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" ref="AE26" si="147">AE6/AA6-1</f>
+        <f t="shared" ref="AE26" si="139">AE6/AA6-1</f>
         <v>6.6989863375936487E-2</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" ref="AF26" si="148">AF6/AB6-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="AF26" si="140">AF6/AB6-1</f>
+        <v>0.17910447761194037</v>
       </c>
       <c r="AG26" s="7">
-        <f t="shared" ref="AG26" si="149">AG6/AC6-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AG26" si="141">AG6/AC6-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" ref="AH26" si="150">AH6/AD6-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AH26" si="142">AH6/AD6-1</f>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AK26" s="7"/>
       <c r="AL26" s="7">
-        <f t="shared" ref="AL26:AQ26" si="151">AL6/AK6-1</f>
+        <f t="shared" ref="AL26:AQ26" si="143">AL6/AK6-1</f>
         <v>0.48530805687203782</v>
       </c>
       <c r="AM26" s="7">
-        <f t="shared" si="151"/>
+        <f t="shared" si="143"/>
         <v>0.68602425015954061</v>
       </c>
       <c r="AN26" s="7">
-        <f t="shared" si="151"/>
+        <f t="shared" si="143"/>
         <v>0.72785768357305081</v>
       </c>
       <c r="AO26" s="7">
-        <f t="shared" si="151"/>
+        <f t="shared" si="143"/>
         <v>0.50952902519167576</v>
       </c>
       <c r="AP26" s="7">
-        <f t="shared" si="151"/>
+        <f t="shared" si="143"/>
         <v>0.27456102162240592</v>
       </c>
       <c r="AQ26" s="7">
-        <f t="shared" si="151"/>
+        <f t="shared" si="143"/>
         <v>4.2240692246385159E-2</v>
       </c>
       <c r="AR26" s="7">
-        <f t="shared" ref="AR26:BB26" si="152">AR6/AQ6-1</f>
-        <v>5.6351321826523915E-2</v>
+        <f t="shared" ref="AR26:BB26" si="144">AR6/AQ6-1</f>
+        <v>0.12843784138081693</v>
       </c>
       <c r="AS26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB26" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="144"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD26" t="s">
@@ -5839,210 +5876,210 @@
         <v>36</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:AD27" si="153">C8/C3</f>
+        <f t="shared" ref="C27:AD27" si="145">C8/C3</f>
         <v>0.22870662460567812</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.19098143236074278</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.22979214780600454</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.25903614457831325</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.25701357466063351</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.26006711409395972</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.24637681159420288</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.17344173441734415</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.1404702970297029</v>
       </c>
       <c r="L27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>-1.4970059880240088E-3</v>
       </c>
       <c r="M27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.11591901548233421</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.12741935483870967</v>
       </c>
       <c r="O27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.19664082687338508</v>
       </c>
       <c r="P27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.21691257432283637</v>
       </c>
       <c r="Q27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.25898291773021803</v>
       </c>
       <c r="R27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.21290436005625873</v>
       </c>
       <c r="S27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.21038912679203128</v>
       </c>
       <c r="T27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.2481393775372126</v>
       </c>
       <c r="U27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>9.4263086729766396E-2</v>
       </c>
       <c r="V27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>9.6718480138169263E-2</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.16801464977872718</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.18801410105757932</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.22420078519349423</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.17749033204427261</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.24098340197179574</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.29714605484051482</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.25886833514689878</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="145"/>
         <v>0.26927747419550702</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" ref="AE27:AH27" si="154">AE8/AE3</f>
+        <f t="shared" ref="AE27:AH27" si="146">AE8/AE3</f>
         <v>0.27704791344667701</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="154"/>
-        <v>0.32121082820369329</v>
+        <f t="shared" si="146"/>
+        <v>0.24752475247524752</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="154"/>
-        <v>0.31374591947769309</v>
+        <f t="shared" si="146"/>
+        <v>0.25863259911894271</v>
       </c>
       <c r="AH27" s="7">
-        <f t="shared" si="154"/>
-        <v>0.30936678826411823</v>
+        <f t="shared" si="146"/>
+        <v>0.26747582124810465</v>
       </c>
       <c r="AK27" s="7">
-        <f t="shared" ref="AK27:AX27" si="155">AK8/AK3</f>
+        <f t="shared" ref="AK27:AX27" si="147">AK8/AK3</f>
         <v>0.22953846153846152</v>
       </c>
       <c r="AL27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>0.23072383949645953</v>
       </c>
       <c r="AM27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>9.8603744994047005E-2</v>
       </c>
       <c r="AN27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>0.22280116715298048</v>
       </c>
       <c r="AO27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>0.16382022471910113</v>
       </c>
       <c r="AP27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>0.18973278079451283</v>
       </c>
       <c r="AQ27" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="147"/>
         <v>0.26724042198778453</v>
       </c>
       <c r="AR27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.3061376344820011</v>
+        <f t="shared" si="147"/>
+        <v>0.26260896882399309</v>
       </c>
       <c r="AS27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.36138608271328609</v>
+        <f t="shared" si="147"/>
+        <v>0.30430864384382689</v>
       </c>
       <c r="AT27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.39560491895555239</v>
+        <f t="shared" si="147"/>
+        <v>0.33084306501754523</v>
       </c>
       <c r="AU27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.42305827594318557</v>
+        <f t="shared" si="147"/>
+        <v>0.34996515331990974</v>
       </c>
       <c r="AV27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.44528521559111545</v>
+        <f t="shared" si="147"/>
+        <v>0.36336112177348934</v>
       </c>
       <c r="AW27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.45329442192930069</v>
+        <f t="shared" si="147"/>
+        <v>0.37213609560454958</v>
       </c>
       <c r="AX27" s="7">
-        <f t="shared" si="155"/>
-        <v>0.45983865995195677</v>
+        <f t="shared" si="147"/>
+        <v>0.37930603416878039</v>
       </c>
       <c r="AY27" s="7">
-        <f t="shared" ref="AY27:BB27" si="156">AY8/AY3</f>
-        <v>0.46503494957686448</v>
+        <f t="shared" ref="AY27:BB27" si="148">AY8/AY3</f>
+        <v>0.38499914576459271</v>
       </c>
       <c r="AZ27" s="7">
-        <f t="shared" si="156"/>
-        <v>0.46903361816441252</v>
+        <f t="shared" si="148"/>
+        <v>0.38938013068784627</v>
       </c>
       <c r="BA27" s="7">
-        <f t="shared" si="156"/>
-        <v>0.47287995652005382</v>
+        <f t="shared" si="148"/>
+        <v>0.39359422094735691</v>
       </c>
       <c r="BB27" s="7">
-        <f t="shared" si="156"/>
-        <v>0.47657976770024235</v>
+        <f t="shared" si="148"/>
+        <v>0.3976477744350766</v>
       </c>
       <c r="BD27" t="s">
         <v>41</v>
       </c>
       <c r="BE27" s="7">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="28" spans="2:167" x14ac:dyDescent="0.3">
@@ -6050,211 +6087,211 @@
         <v>37</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28:R28" si="157">C13/C3</f>
+        <f t="shared" ref="C28:R28" si="149">C13/C3</f>
         <v>-0.22712933753943226</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.26790450928381948</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.47113163972286393</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.12248995983935747</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-9.4117647058823514E-2</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.11577181208053688</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.1426392067124333</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.2276422764227643</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.45173267326732686</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.36477045908183642</v>
       </c>
       <c r="M28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.20484319174275514</v>
       </c>
       <c r="N28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.22032258064516125</v>
       </c>
       <c r="O28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.34857881136950897</v>
       </c>
       <c r="P28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.3146883946267342</v>
       </c>
       <c r="Q28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.15216964461024926</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="149"/>
         <v>-0.24560478199718716</v>
       </c>
       <c r="S28" s="7">
-        <f t="shared" ref="S28:AD28" si="158">S13/S3</f>
+        <f t="shared" ref="S28:AD28" si="150">S13/S3</f>
         <v>-0.28244274809160314</v>
       </c>
       <c r="T28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.2880581867388361</v>
       </c>
       <c r="U28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.5796793509754683</v>
       </c>
       <c r="V28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.52124352331606216</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.44224019533038328</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.46092831962397185</v>
       </c>
       <c r="Y28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.42077958496915296</v>
       </c>
       <c r="Z28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.47379650620082681</v>
       </c>
       <c r="AA28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.37726194933233514</v>
       </c>
       <c r="AB28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.26648013430330159</v>
       </c>
       <c r="AC28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.30337323177366698</v>
       </c>
       <c r="AD28" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="150"/>
         <v>-0.24691358024691357</v>
       </c>
       <c r="AE28" s="7">
-        <f t="shared" ref="AE28:AH28" si="159">AE13/AE3</f>
+        <f t="shared" ref="AE28:AH28" si="151">AE13/AE3</f>
         <v>-0.24603941267387935</v>
       </c>
       <c r="AF28" s="7">
-        <f t="shared" si="159"/>
-        <v>-0.15072030637940684</v>
+        <f t="shared" si="151"/>
+        <v>-0.29841769223651338</v>
       </c>
       <c r="AG28" s="7">
-        <f t="shared" si="159"/>
-        <v>-0.1568896218715996</v>
+        <f t="shared" si="151"/>
+        <v>-0.26210044052863429</v>
       </c>
       <c r="AH28" s="7">
-        <f t="shared" si="159"/>
-        <v>-0.15450140931281808</v>
+        <f t="shared" si="151"/>
+        <v>-0.23297474129150209</v>
       </c>
       <c r="AK28" s="7">
-        <f t="shared" ref="AK28:AX28" si="160">AK13/AK3</f>
+        <f t="shared" ref="AK28:AX28" si="152">AK13/AK3</f>
         <v>-0.2695384615384615</v>
       </c>
       <c r="AL28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.15047206923682141</v>
       </c>
       <c r="AM28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.28790994696395711</v>
       </c>
       <c r="AN28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.25791996665277195</v>
       </c>
       <c r="AO28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.41523595505617983</v>
       </c>
       <c r="AP28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.44977136324664169</v>
       </c>
       <c r="AQ28" s="7">
-        <f t="shared" si="160"/>
+        <f t="shared" si="152"/>
         <v>-0.29516935036091063</v>
       </c>
       <c r="AR28" s="7">
-        <f t="shared" si="160"/>
-        <v>-0.17490208253203135</v>
+        <f t="shared" si="152"/>
+        <v>-0.2592972608125112</v>
       </c>
       <c r="AS28" s="7">
-        <f t="shared" si="160"/>
-        <v>-6.0556718454494979E-2</v>
+        <f t="shared" si="152"/>
+        <v>-0.15162605258203868</v>
       </c>
       <c r="AT28" s="7">
-        <f t="shared" si="160"/>
-        <v>2.1698776212309413E-2</v>
+        <f t="shared" si="152"/>
+        <v>-7.306925887262769E-2</v>
       </c>
       <c r="AU28" s="7">
-        <f t="shared" si="160"/>
-        <v>8.4309014868837628E-2</v>
+        <f t="shared" si="152"/>
+        <v>-1.577772016529818E-2</v>
       </c>
       <c r="AV28" s="7">
-        <f t="shared" si="160"/>
-        <v>0.13163993356343359</v>
+        <f t="shared" si="152"/>
+        <v>2.4956205351940118E-2</v>
       </c>
       <c r="AW28" s="7">
-        <f t="shared" si="160"/>
-        <v>0.15835932470441749</v>
+        <f t="shared" si="152"/>
+        <v>5.4092116118641766E-2</v>
       </c>
       <c r="AX28" s="7">
-        <f t="shared" si="160"/>
-        <v>0.17802821659726142</v>
+        <f t="shared" si="152"/>
+        <v>7.5523843899563042E-2</v>
       </c>
       <c r="AY28" s="7">
-        <f t="shared" ref="AY28:BB28" si="161">AY13/AY3</f>
-        <v>0.19357195641017497</v>
+        <f t="shared" ref="AY28:BB28" si="153">AY13/AY3</f>
+        <v>9.2448107308072888E-2</v>
       </c>
       <c r="AZ28" s="7">
-        <f t="shared" si="161"/>
-        <v>0.20543707732696848</v>
+        <f t="shared" si="153"/>
+        <v>0.10535056003610177</v>
       </c>
       <c r="BA28" s="7">
-        <f t="shared" si="161"/>
-        <v>0.21686648601239983</v>
+        <f t="shared" si="153"/>
+        <v>0.11778202137702877</v>
       </c>
       <c r="BB28" s="7">
-        <f t="shared" si="161"/>
-        <v>0.22787631553123591</v>
+        <f t="shared" si="153"/>
+        <v>0.12975984727069825</v>
       </c>
       <c r="BD28" t="s">
         <v>42</v>
       </c>
       <c r="BE28" s="5">
         <f>NPV(BE27,AR19:FK19)</f>
-        <v>21482.975188473243</v>
+        <v>12322.354963311001</v>
       </c>
     </row>
     <row r="29" spans="2:167" x14ac:dyDescent="0.3">
@@ -6266,184 +6303,184 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G30" si="162">G9/C9-1</f>
+        <f t="shared" ref="G29:G30" si="154">G9/C9-1</f>
         <v>0.56521739130434789</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" ref="H29:H30" si="163">H9/D9-1</f>
+        <f t="shared" ref="H29:H30" si="155">H9/D9-1</f>
         <v>0.51219512195121975</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" ref="I29:I30" si="164">I9/E9-1</f>
+        <f t="shared" ref="I29:I30" si="156">I9/E9-1</f>
         <v>-0.22005571030640669</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" ref="J29:J30" si="165">J9/F9-1</f>
+        <f t="shared" ref="J29:J30" si="157">J9/F9-1</f>
         <v>0.55714285714285738</v>
       </c>
       <c r="K29" s="7">
-        <f t="shared" ref="K29:K30" si="166">K9/G9-1</f>
+        <f t="shared" ref="K29:K30" si="158">K9/G9-1</f>
         <v>1.2870370370370368</v>
       </c>
       <c r="L29" s="7">
-        <f t="shared" ref="L29:L30" si="167">L9/H9-1</f>
+        <f t="shared" ref="L29:L30" si="159">L9/H9-1</f>
         <v>0.62096774193548399</v>
       </c>
       <c r="M29" s="7">
-        <f t="shared" ref="M29:M30" si="168">M9/I9-1</f>
+        <f t="shared" ref="M29:M30" si="160">M9/I9-1</f>
         <v>0.84642857142857153</v>
       </c>
       <c r="N29" s="7">
-        <f t="shared" ref="N29:N30" si="169">N9/J9-1</f>
+        <f t="shared" ref="N29:N30" si="161">N9/J9-1</f>
         <v>0.83792048929663543</v>
       </c>
       <c r="O29" s="7">
-        <f t="shared" ref="O29:O30" si="170">O9/K9-1</f>
+        <f t="shared" ref="O29:O30" si="162">O9/K9-1</f>
         <v>0.95546558704453433</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" ref="P29:P30" si="171">P9/L9-1</f>
+        <f t="shared" ref="P29:P30" si="163">P9/L9-1</f>
         <v>2.1019900497512438</v>
       </c>
       <c r="Q29" s="7">
-        <f t="shared" ref="Q29:Q30" si="172">Q9/M9-1</f>
+        <f t="shared" ref="Q29:Q30" si="164">Q9/M9-1</f>
         <v>1.67311411992263</v>
       </c>
       <c r="R29" s="7">
-        <f t="shared" ref="R29:R30" si="173">R9/N9-1</f>
+        <f t="shared" ref="R29:R30" si="165">R9/N9-1</f>
         <v>1.8885191347753749</v>
       </c>
       <c r="S29" s="7">
-        <f t="shared" ref="S29:S30" si="174">S9/O9-1</f>
+        <f t="shared" ref="S29:S30" si="166">S9/O9-1</f>
         <v>0.84057971014492772</v>
       </c>
       <c r="T29" s="7">
-        <f t="shared" ref="T29:T30" si="175">T9/P9-1</f>
+        <f t="shared" ref="T29:T30" si="167">T9/P9-1</f>
         <v>0.69847634322373708</v>
       </c>
       <c r="U29" s="7">
-        <f t="shared" ref="U29:U30" si="176">U9/Q9-1</f>
+        <f t="shared" ref="U29:U30" si="168">U9/Q9-1</f>
         <v>0.70477568740955143</v>
       </c>
       <c r="V29" s="7">
-        <f t="shared" ref="V29:V30" si="177">V9/R9-1</f>
+        <f t="shared" ref="V29:V30" si="169">V9/R9-1</f>
         <v>0.43087557603686655</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" ref="W29:W30" si="178">W9/S9-1</f>
+        <f t="shared" ref="W29:W30" si="170">W9/S9-1</f>
         <v>0.54949381327334068</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" ref="X29:X30" si="179">X9/T9-1</f>
+        <f t="shared" ref="X29:X30" si="171">X9/T9-1</f>
         <v>0.48866855524079322</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" ref="Y29:Y30" si="180">Y9/U9-1</f>
+        <f t="shared" ref="Y29:Y30" si="172">Y9/U9-1</f>
         <v>0.36502546689303927</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" ref="Z29:Z30" si="181">Z9/V9-1</f>
+        <f t="shared" ref="Z29:Z30" si="173">Z9/V9-1</f>
         <v>0.37318840579710155</v>
       </c>
       <c r="AA29" s="7">
-        <f t="shared" ref="AA29:AA30" si="182">AA9/W9-1</f>
+        <f t="shared" ref="AA29:AA30" si="174">AA9/W9-1</f>
         <v>0.31433756805807622</v>
       </c>
       <c r="AB29" s="7">
-        <f t="shared" ref="AB29:AB30" si="183">AB9/X9-1</f>
+        <f t="shared" ref="AB29:AB30" si="175">AB9/X9-1</f>
         <v>0.14716143355534395</v>
       </c>
       <c r="AC29" s="7">
-        <f t="shared" ref="AC29:AC30" si="184">AC9/Y9-1</f>
+        <f t="shared" ref="AC29:AC30" si="176">AC9/Y9-1</f>
         <v>0.13619402985074602</v>
       </c>
       <c r="AD29" s="7">
-        <f t="shared" ref="AD29:AD30" si="185">AD9/Z9-1</f>
+        <f t="shared" ref="AD29:AD30" si="177">AD9/Z9-1</f>
         <v>4.0750513046027503E-2</v>
       </c>
       <c r="AE29" s="7">
-        <f t="shared" ref="AE29:AE30" si="186">AE9/AA9-1</f>
+        <f t="shared" ref="AE29:AE30" si="178">AE9/AA9-1</f>
         <v>3.4520850593758645E-2</v>
       </c>
       <c r="AF29" s="7">
-        <f t="shared" ref="AF29:AF30" si="187">AF9/AB9-1</f>
+        <f t="shared" ref="AF29:AF30" si="179">AF9/AB9-1</f>
+        <v>6.4418025988388194E-2</v>
+      </c>
+      <c r="AG29" s="7">
+        <f t="shared" ref="AG29:AG30" si="180">AG9/AC9-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG29" s="7">
-        <f t="shared" ref="AG29:AG30" si="188">AG9/AC9-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AH29" s="7">
-        <f t="shared" ref="AH29:AH30" si="189">AH9/AD9-1</f>
+        <f t="shared" ref="AH29:AH30" si="181">AH9/AD9-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AK29" s="7"/>
       <c r="AL29" s="7">
-        <f t="shared" ref="AL29:AW29" si="190">AL9/AK9-1</f>
+        <f t="shared" ref="AL29:AW29" si="182">AL9/AK9-1</f>
         <v>0.2296211251435134</v>
       </c>
       <c r="AM29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>0.88048552754435105</v>
       </c>
       <c r="AN29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>1.6469712015888778</v>
       </c>
       <c r="AO29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>0.63871693866066392</v>
       </c>
       <c r="AP29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>0.43486721611721602</v>
       </c>
       <c r="AQ29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>0.15213402473075366</v>
       </c>
       <c r="AR29" s="7">
-        <f t="shared" si="190"/>
-        <v>4.0965932696302554E-2</v>
+        <f t="shared" si="182"/>
+        <v>4.9585929926603045E-2</v>
       </c>
       <c r="AS29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW29" s="7">
-        <f t="shared" si="190"/>
+        <f t="shared" si="182"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="7">
-        <f t="shared" ref="AX29:AX30" si="191">AX9/AW9-1</f>
+        <f t="shared" ref="AX29:AX30" si="183">AX9/AW9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="7">
-        <f t="shared" ref="AY29:AY30" si="192">AY9/AX9-1</f>
+        <f t="shared" ref="AY29:AY30" si="184">AY9/AX9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="7">
-        <f t="shared" ref="AZ29:AZ30" si="193">AZ9/AY9-1</f>
+        <f t="shared" ref="AZ29:AZ30" si="185">AZ9/AY9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="7">
-        <f t="shared" ref="BA29:BA30" si="194">BA9/AZ9-1</f>
+        <f t="shared" ref="BA29:BA30" si="186">BA9/AZ9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB29" s="7">
-        <f t="shared" ref="BB29:BB30" si="195">BB9/BA9-1</f>
+        <f t="shared" ref="BB29:BB30" si="187">BB9/BA9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD29" t="s">
@@ -6451,7 +6488,7 @@
       </c>
       <c r="BE29" s="5">
         <f>Main!D8</f>
-        <v>3503.8</v>
+        <v>3746.1</v>
       </c>
       <c r="BG29" t="s">
         <v>75</v>
@@ -6466,184 +6503,184 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7">
+        <f t="shared" si="154"/>
+        <v>0.54385964912280715</v>
+      </c>
+      <c r="H30" s="7">
+        <f t="shared" si="155"/>
+        <v>0.36111111111111116</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="156"/>
+        <v>-0.23703703703703694</v>
+      </c>
+      <c r="J30" s="7">
+        <f t="shared" si="157"/>
+        <v>0.60493827160493829</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="158"/>
+        <v>2.4772727272727271</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="159"/>
+        <v>0.90816326530612224</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="160"/>
+        <v>0.57281553398058227</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="161"/>
+        <v>1.4461538461538455</v>
+      </c>
+      <c r="O30" s="7">
         <f t="shared" si="162"/>
-        <v>0.54385964912280715</v>
-      </c>
-      <c r="H30" s="7">
+        <v>2.0849673202614381</v>
+      </c>
+      <c r="P30" s="7">
         <f t="shared" si="163"/>
-        <v>0.36111111111111116</v>
-      </c>
-      <c r="I30" s="7">
+        <v>4.2245989304812834</v>
+      </c>
+      <c r="Q30" s="7">
         <f t="shared" si="164"/>
-        <v>-0.23703703703703694</v>
-      </c>
-      <c r="J30" s="7">
+        <v>2.1851851851851856</v>
+      </c>
+      <c r="R30" s="7">
         <f t="shared" si="165"/>
-        <v>0.60493827160493829</v>
-      </c>
-      <c r="K30" s="7">
+        <v>0.86792452830188727</v>
+      </c>
+      <c r="S30" s="7">
         <f t="shared" si="166"/>
-        <v>2.4772727272727271</v>
-      </c>
-      <c r="L30" s="7">
+        <v>-0.38771186440677974</v>
+      </c>
+      <c r="T30" s="7">
         <f t="shared" si="167"/>
-        <v>0.90816326530612224</v>
-      </c>
-      <c r="M30" s="7">
+        <v>-0.19447287615148412</v>
+      </c>
+      <c r="U30" s="7">
         <f t="shared" si="168"/>
-        <v>0.57281553398058227</v>
-      </c>
-      <c r="N30" s="7">
+        <v>0.57364341085271309</v>
+      </c>
+      <c r="V30" s="7">
         <f t="shared" si="169"/>
-        <v>1.4461538461538455</v>
-      </c>
-      <c r="O30" s="7">
+        <v>0.34175084175084192</v>
+      </c>
+      <c r="W30" s="7">
         <f t="shared" si="170"/>
-        <v>2.0849673202614381</v>
-      </c>
-      <c r="P30" s="7">
+        <v>0.68858131487889263</v>
+      </c>
+      <c r="X30" s="7">
         <f t="shared" si="171"/>
-        <v>4.2245989304812834</v>
-      </c>
-      <c r="Q30" s="7">
+        <v>0.22236340533672183</v>
+      </c>
+      <c r="Y30" s="7">
         <f t="shared" si="172"/>
-        <v>2.1851851851851856</v>
-      </c>
-      <c r="R30" s="7">
+        <v>0.2007389162561577</v>
+      </c>
+      <c r="Z30" s="7">
         <f t="shared" si="173"/>
-        <v>0.86792452830188727</v>
-      </c>
-      <c r="S30" s="7">
+        <v>0.23964868255959848</v>
+      </c>
+      <c r="AA30" s="7">
         <f t="shared" si="174"/>
-        <v>-0.38771186440677974</v>
-      </c>
-      <c r="T30" s="7">
+        <v>2.049180327868827E-3</v>
+      </c>
+      <c r="AB30" s="7">
         <f t="shared" si="175"/>
-        <v>-0.19447287615148412</v>
-      </c>
-      <c r="U30" s="7">
+        <v>9.7713097713097552E-2</v>
+      </c>
+      <c r="AC30" s="7">
         <f t="shared" si="176"/>
-        <v>0.57364341085271309</v>
-      </c>
-      <c r="V30" s="7">
+        <v>1.2307692307692353E-2</v>
+      </c>
+      <c r="AD30" s="7">
         <f t="shared" si="177"/>
-        <v>0.34175084175084192</v>
-      </c>
-      <c r="W30" s="7">
+        <v>6.578947368421062E-2</v>
+      </c>
+      <c r="AE30" s="7">
         <f t="shared" si="178"/>
-        <v>0.68858131487889263</v>
-      </c>
-      <c r="X30" s="7">
+        <v>0.21779141104294486</v>
+      </c>
+      <c r="AF30" s="7">
         <f t="shared" si="179"/>
-        <v>0.22236340533672183</v>
-      </c>
-      <c r="Y30" s="7">
+        <v>0.44128787878787867</v>
+      </c>
+      <c r="AG30" s="7">
         <f t="shared" si="180"/>
-        <v>0.2007389162561577</v>
-      </c>
-      <c r="Z30" s="7">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AH30" s="7">
         <f t="shared" si="181"/>
-        <v>0.23964868255959848</v>
-      </c>
-      <c r="AA30" s="7">
-        <f t="shared" si="182"/>
-        <v>2.049180327868827E-3</v>
-      </c>
-      <c r="AB30" s="7">
-        <f t="shared" si="183"/>
-        <v>9.7713097713097552E-2</v>
-      </c>
-      <c r="AC30" s="7">
-        <f t="shared" si="184"/>
-        <v>1.2307692307692353E-2</v>
-      </c>
-      <c r="AD30" s="7">
-        <f t="shared" si="185"/>
-        <v>6.578947368421062E-2</v>
-      </c>
-      <c r="AE30" s="7">
-        <f t="shared" si="186"/>
-        <v>0.21779141104294486</v>
-      </c>
-      <c r="AF30" s="7">
-        <f t="shared" si="187"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AG30" s="7">
-        <f t="shared" si="188"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AH30" s="7">
-        <f t="shared" si="189"/>
-        <v>0.16999999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AK30" s="7"/>
       <c r="AL30" s="7">
-        <f t="shared" ref="AL30:AW30" si="196">AL10/AK10-1</f>
+        <f t="shared" ref="AL30:AW30" si="188">AL10/AK10-1</f>
         <v>0.21449275362318865</v>
       </c>
       <c r="AM30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>1.3221957040572789</v>
       </c>
       <c r="AN30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>2.1151079136690649</v>
       </c>
       <c r="AO30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>-1.8805674694820307E-2</v>
       </c>
       <c r="AP30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>0.31170141223940839</v>
       </c>
       <c r="AQ30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>4.4347603178672035E-2</v>
       </c>
       <c r="AR30" s="7">
-        <f t="shared" si="196"/>
-        <v>0.1835567010309278</v>
+        <f t="shared" si="188"/>
+        <v>0.45418507609229253</v>
       </c>
       <c r="AS30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AT30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AU30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AV30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW30" s="7">
-        <f t="shared" si="196"/>
+        <f t="shared" si="188"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX30" s="7">
-        <f t="shared" si="191"/>
+        <f t="shared" si="183"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY30" s="7">
-        <f t="shared" si="192"/>
+        <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ30" s="7">
-        <f t="shared" si="193"/>
+        <f t="shared" si="185"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA30" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="186"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB30" s="7">
-        <f t="shared" si="195"/>
+        <f t="shared" si="187"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD30" t="s">
@@ -6651,7 +6688,7 @@
       </c>
       <c r="BE30" s="5">
         <f>BE28+BE29</f>
-        <v>24986.775188473242</v>
+        <v>16068.454963311002</v>
       </c>
     </row>
     <row r="31" spans="2:167" x14ac:dyDescent="0.3">
@@ -6659,211 +6696,211 @@
         <v>38</v>
       </c>
       <c r="C31" s="7">
-        <f t="shared" ref="C31:R31" si="197">C11/C3</f>
+        <f t="shared" ref="C31:R31" si="189">C11/C3</f>
         <v>0.14826498422712936</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>0.14588859416445621</v>
       </c>
       <c r="E31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>0.13048498845265591</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>8.9357429718875517E-2</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>7.601809954751132E-2</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>8.5570469798657706E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>9.6872616323417232E-2</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>9.1463414634146339E-2</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>9.7153465346534656E-2</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>6.9361277445109781E-2</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>5.1210797935688765E-2</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>5.129032258064517E-2</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>5.1679586563307491E-2</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>4.1841004184100417E-2</v>
       </c>
       <c r="Q31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>3.8484193991753388E-2</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" si="197"/>
+        <f t="shared" si="189"/>
         <v>4.8874824191279892E-2</v>
       </c>
       <c r="S31" s="7">
-        <f t="shared" ref="S31:AD31" si="198">S11/S3</f>
+        <f t="shared" ref="S31:AD31" si="190">S11/S3</f>
         <v>5.4179854775646991E-2</v>
       </c>
       <c r="T31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>4.4824086603518262E-2</v>
       </c>
       <c r="U31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>6.200502221363724E-2</v>
       </c>
       <c r="V31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>5.1295336787564767E-2</v>
       </c>
       <c r="W31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>4.0897298947047155E-2</v>
       </c>
       <c r="X31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>4.4506462984723862E-2</v>
       </c>
       <c r="Y31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>5.7347167694896235E-2</v>
       </c>
       <c r="Z31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>6.4675290038671826E-2</v>
       </c>
       <c r="AA31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>4.430300761262948E-2</v>
       </c>
       <c r="AB31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>4.0626748740906542E-2</v>
       </c>
       <c r="AC31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>5.7236126224156691E-2</v>
       </c>
       <c r="AD31" s="7">
-        <f t="shared" si="198"/>
+        <f t="shared" si="190"/>
         <v>5.0394656952033996E-2</v>
       </c>
       <c r="AE31" s="7">
-        <f t="shared" ref="AE31:AH31" si="199">AE11/AE3</f>
+        <f t="shared" ref="AE31:AH31" si="191">AE11/AE3</f>
         <v>4.6174652241112821E-2</v>
       </c>
       <c r="AF31" s="7">
-        <f t="shared" si="199"/>
-        <v>0.04</v>
+        <f t="shared" si="191"/>
+        <v>4.8857222170815208E-2</v>
       </c>
       <c r="AG31" s="7">
-        <f t="shared" si="199"/>
+        <f t="shared" si="191"/>
         <v>0.05</v>
       </c>
       <c r="AH31" s="7">
-        <f t="shared" si="199"/>
+        <f t="shared" si="191"/>
         <v>0.05</v>
       </c>
       <c r="AK31" s="7">
-        <f t="shared" ref="AK31:AX31" si="200">AK11/AK3</f>
+        <f t="shared" ref="AK31:AX31" si="192">AK11/AK3</f>
         <v>0.12492307692307693</v>
       </c>
       <c r="AL31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>8.8119590873328088E-2</v>
       </c>
       <c r="AM31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>6.3210304145470284E-2</v>
       </c>
       <c r="AN31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>4.5018757815756566E-2</v>
       </c>
       <c r="AO31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>5.2764044943820226E-2</v>
       </c>
       <c r="AP31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>5.2336381823378103E-2</v>
       </c>
       <c r="AQ31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>4.8362021099389224E-2</v>
       </c>
       <c r="AR31" s="7">
-        <f t="shared" si="200"/>
-        <v>4.6631402813494524E-2</v>
+        <f t="shared" si="192"/>
+        <v>4.8834288042824602E-2</v>
       </c>
       <c r="AS31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AT31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AU31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AV31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AW31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AX31" s="7">
-        <f t="shared" si="200"/>
+        <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
       <c r="AY31" s="7">
-        <f t="shared" ref="AY31:BB31" si="201">AY11/AY3</f>
-        <v>5.000000000000001E-2</v>
+        <f t="shared" ref="AY31:BB31" si="193">AY11/AY3</f>
+        <v>0.05</v>
       </c>
       <c r="AZ31" s="7">
-        <f t="shared" si="201"/>
+        <f t="shared" si="193"/>
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="BA31" s="7">
+        <f t="shared" si="193"/>
         <v>0.05</v>
       </c>
-      <c r="BA31" s="7">
-        <f t="shared" si="201"/>
+      <c r="BB31" s="7">
+        <f t="shared" si="193"/>
         <v>0.05</v>
-      </c>
-      <c r="BB31" s="7">
-        <f t="shared" si="201"/>
-        <v>4.9999999999999996E-2</v>
       </c>
       <c r="BD31" t="s">
         <v>45</v>
       </c>
       <c r="BE31" s="4">
         <f>BE30/AW20</f>
-        <v>36.837351007626779</v>
+        <v>24.912333276451164</v>
       </c>
     </row>
     <row r="32" spans="2:167" x14ac:dyDescent="0.3">
@@ -6871,43 +6908,43 @@
         <v>29</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32:L32" si="202">C17/C16</f>
+        <f t="shared" ref="C32:L32" si="194">C17/C16</f>
         <v>0</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="202"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="M32" s="7">
@@ -6915,159 +6952,159 @@
         <v>0</v>
       </c>
       <c r="N32" s="7">
-        <f t="shared" ref="N32:R32" si="203">N17/N16</f>
+        <f t="shared" ref="N32:R32" si="195">N17/N16</f>
         <v>0.10436137071651093</v>
       </c>
       <c r="O32" s="7">
-        <f t="shared" si="203"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="P32" s="7">
-        <f t="shared" si="203"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="Q32" s="7">
-        <f t="shared" si="203"/>
+        <f t="shared" si="195"/>
         <v>1.2771392081736919E-2</v>
       </c>
       <c r="R32" s="7">
-        <f t="shared" si="203"/>
+        <f t="shared" si="195"/>
         <v>-4.771642808452623E-3</v>
       </c>
       <c r="S32" s="7">
-        <f t="shared" ref="S32:AD32" si="204">S17/S16</f>
+        <f t="shared" ref="S32:AD32" si="196">S17/S16</f>
         <v>-1.852995676343421E-3</v>
       </c>
       <c r="T32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>1.6750418760469021E-3</v>
       </c>
       <c r="U32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-1.3262599469496023E-3</v>
       </c>
       <c r="V32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-1.1103400416377517E-2</v>
       </c>
       <c r="W32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-2.6012634708286872E-3</v>
       </c>
       <c r="X32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>4.1987403778866337E-3</v>
       </c>
       <c r="Y32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-2.5152712899748474E-3</v>
       </c>
       <c r="Z32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-9.225092250922509E-4</v>
       </c>
       <c r="AA32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-4.0620384047267344E-3</v>
       </c>
       <c r="AB32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-4.8262548262548275E-4</v>
       </c>
       <c r="AC32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-1.25E-3</v>
       </c>
       <c r="AD32" s="7">
-        <f t="shared" si="204"/>
+        <f t="shared" si="196"/>
         <v>-1.1915673693858845E-2</v>
       </c>
       <c r="AE32" s="7">
-        <f t="shared" ref="AE32:AH32" si="205">AE17/AE16</f>
+        <f t="shared" ref="AE32:AH32" si="197">AE17/AE16</f>
         <v>-4.1763341067285404E-3</v>
       </c>
       <c r="AF32" s="7">
-        <f t="shared" si="205"/>
+        <f t="shared" si="197"/>
+        <v>-3.5855145213338118E-3</v>
+      </c>
+      <c r="AG32" s="7">
+        <f t="shared" si="197"/>
         <v>0.01</v>
       </c>
-      <c r="AG32" s="7">
-        <f t="shared" si="205"/>
+      <c r="AH32" s="7">
+        <f t="shared" si="197"/>
         <v>0.01</v>
       </c>
-      <c r="AH32" s="7">
-        <f t="shared" si="205"/>
-        <v>0.01</v>
-      </c>
       <c r="AK32" s="7">
-        <f t="shared" ref="AK32:AM32" si="206">AK17/AK16</f>
+        <f t="shared" ref="AK32:AM32" si="198">AK17/AK16</f>
         <v>0</v>
       </c>
       <c r="AL32" s="7">
-        <f t="shared" si="206"/>
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AM32" s="7">
-        <f t="shared" si="206"/>
+        <f t="shared" si="198"/>
         <v>2.5359576078728244E-2</v>
       </c>
       <c r="AN32" s="7">
-        <f t="shared" ref="AN32:AW32" si="207">AN17/AN16</f>
+        <f t="shared" ref="AN32:AW32" si="199">AN17/AN16</f>
         <v>5.953562214725146E-4</v>
       </c>
       <c r="AO32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>-3.8676407391491185E-3</v>
       </c>
       <c r="AP32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>-4.3162983425414374E-4</v>
       </c>
       <c r="AQ32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>-4.3794061098055975E-3</v>
       </c>
       <c r="AR32" s="7">
-        <f t="shared" si="207"/>
-        <v>5.3371058766965955E-3</v>
+        <f t="shared" si="199"/>
+        <v>3.1676101434354649E-3</v>
       </c>
       <c r="AS32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AT32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AU32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AV32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AW32" s="7">
-        <f t="shared" si="207"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AX32" s="7">
-        <f t="shared" ref="AX32:BB32" si="208">AX17/AX16</f>
+        <f t="shared" ref="AX32:BB32" si="200">AX17/AX16</f>
         <v>0</v>
       </c>
       <c r="AY32" s="7">
-        <f t="shared" si="208"/>
+        <f t="shared" si="200"/>
         <v>0</v>
       </c>
       <c r="AZ32" s="7">
-        <f t="shared" si="208"/>
+        <f t="shared" si="200"/>
         <v>0</v>
       </c>
       <c r="BA32" s="7">
-        <f t="shared" si="208"/>
+        <f t="shared" si="200"/>
         <v>0</v>
       </c>
       <c r="BB32" s="7">
-        <f t="shared" si="208"/>
+        <f t="shared" si="200"/>
         <v>0</v>
       </c>
       <c r="BD32" t="s">
@@ -7075,24 +7112,1455 @@
       </c>
       <c r="BE32" s="4">
         <f>Main!D3</f>
-        <v>74.09</v>
+        <v>128.47</v>
       </c>
     </row>
-    <row r="33" spans="56:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:57" x14ac:dyDescent="0.3">
       <c r="BD33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="BE33" s="10">
         <f>BE31/BE32-1</f>
-        <v>-0.5028026588253911</v>
+        <v>-0.80608443001127761</v>
       </c>
     </row>
-    <row r="34" spans="56:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:57" x14ac:dyDescent="0.3">
       <c r="BD34" t="s">
         <v>48</v>
       </c>
       <c r="BE34" s="6" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:57" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO35" s="9">
+        <f t="shared" ref="AO35:AP35" si="201">AO19</f>
+        <v>-924.60000000000025</v>
+      </c>
+      <c r="AP35" s="9">
+        <f t="shared" si="201"/>
+        <v>-1151.8999999999996</v>
+      </c>
+      <c r="AQ35" s="9">
+        <f>AQ19</f>
+        <v>-935.1</v>
+      </c>
+      <c r="AR35" s="9">
+        <f t="shared" ref="AR35:BB35" si="202">AR19</f>
+        <v>-990.7532943999995</v>
+      </c>
+      <c r="AS35" s="9">
+        <f t="shared" si="202"/>
+        <v>-662.29255026000021</v>
+      </c>
+      <c r="AT35" s="9">
+        <f t="shared" si="202"/>
+        <v>-308.71102741379997</v>
+      </c>
+      <c r="AU35" s="9">
+        <f t="shared" si="202"/>
+        <v>41.694191276759675</v>
+      </c>
+      <c r="AV35" s="9">
+        <f t="shared" si="202"/>
+        <v>362.66395139279012</v>
+      </c>
+      <c r="AW35" s="9">
+        <f t="shared" si="202"/>
+        <v>642.42508812541246</v>
+      </c>
+      <c r="AX35" s="9">
+        <f t="shared" si="202"/>
+        <v>882.27116344414139</v>
+      </c>
+      <c r="AY35" s="9">
+        <f t="shared" si="202"/>
+        <v>1098.2870918753292</v>
+      </c>
+      <c r="AZ35" s="9">
+        <f t="shared" si="202"/>
+        <v>1283.6830698904685</v>
+      </c>
+      <c r="BA35" s="9">
+        <f t="shared" si="202"/>
+        <v>1479.8825831967754</v>
+      </c>
+      <c r="BB35" s="9">
+        <f t="shared" si="202"/>
+        <v>1687.445724325838</v>
+      </c>
+    </row>
+    <row r="36" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO36" s="5">
+        <v>130.1</v>
+      </c>
+      <c r="AP36" s="5">
+        <v>208.1</v>
+      </c>
+      <c r="AQ36" s="5">
+        <v>226.4</v>
+      </c>
+      <c r="AR36" s="5">
+        <f>AQ36*1.05</f>
+        <v>237.72000000000003</v>
+      </c>
+      <c r="AS36" s="5">
+        <f t="shared" ref="AS36:BB36" si="203">AR36*1.05</f>
+        <v>249.60600000000005</v>
+      </c>
+      <c r="AT36" s="5">
+        <f t="shared" si="203"/>
+        <v>262.08630000000005</v>
+      </c>
+      <c r="AU36" s="5">
+        <f t="shared" si="203"/>
+        <v>275.19061500000009</v>
+      </c>
+      <c r="AV36" s="5">
+        <f t="shared" si="203"/>
+        <v>288.9501457500001</v>
+      </c>
+      <c r="AW36" s="5">
+        <f t="shared" si="203"/>
+        <v>303.39765303750011</v>
+      </c>
+      <c r="AX36" s="5">
+        <f t="shared" si="203"/>
+        <v>318.56753568937512</v>
+      </c>
+      <c r="AY36" s="5">
+        <f t="shared" si="203"/>
+        <v>334.49591247384387</v>
+      </c>
+      <c r="AZ36" s="5">
+        <f t="shared" si="203"/>
+        <v>351.22070809753609</v>
+      </c>
+      <c r="BA36" s="5">
+        <f t="shared" si="203"/>
+        <v>368.78174350241289</v>
+      </c>
+      <c r="BB36" s="5">
+        <f t="shared" si="203"/>
+        <v>387.22083067753357</v>
+      </c>
+    </row>
+    <row r="37" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO37" s="5">
+        <v>589.5</v>
+      </c>
+      <c r="AP37" s="5">
+        <v>868</v>
+      </c>
+      <c r="AQ37" s="5">
+        <v>1015.8</v>
+      </c>
+      <c r="AR37" s="5">
+        <f>AQ37*1.2</f>
+        <v>1218.9599999999998</v>
+      </c>
+      <c r="AS37" s="5">
+        <f>AR37*1.1</f>
+        <v>1340.856</v>
+      </c>
+      <c r="AT37" s="5">
+        <f>AS37*1.05</f>
+        <v>1407.8988000000002</v>
+      </c>
+      <c r="AU37" s="5">
+        <f>AT37*0.95</f>
+        <v>1337.50386</v>
+      </c>
+      <c r="AV37" s="5">
+        <f>AU37*0.9</f>
+        <v>1203.7534740000001</v>
+      </c>
+      <c r="AW37" s="5">
+        <f t="shared" ref="AW37" si="204">AV37*0.9</f>
+        <v>1083.3781266000001</v>
+      </c>
+      <c r="AX37" s="5">
+        <f>AW37*0.8</f>
+        <v>866.70250128000009</v>
+      </c>
+      <c r="AY37" s="5">
+        <f t="shared" ref="AY37:BB37" si="205">AX37*0.8</f>
+        <v>693.36200102400016</v>
+      </c>
+      <c r="AZ37" s="5">
+        <f t="shared" si="205"/>
+        <v>554.68960081920011</v>
+      </c>
+      <c r="BA37" s="5">
+        <f t="shared" si="205"/>
+        <v>443.75168065536013</v>
+      </c>
+      <c r="BB37" s="5">
+        <f t="shared" si="205"/>
+        <v>355.00134452428813</v>
+      </c>
+    </row>
+    <row r="38" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO38" s="5">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="AP38" s="5">
+        <v>97.1</v>
+      </c>
+      <c r="AQ38" s="5">
+        <v>118.1</v>
+      </c>
+      <c r="AR38" s="5">
+        <f>AQ38*1.03</f>
+        <v>121.643</v>
+      </c>
+      <c r="AS38" s="5">
+        <f t="shared" ref="AS38:BB38" si="206">AR38*1.03</f>
+        <v>125.29229000000001</v>
+      </c>
+      <c r="AT38" s="5">
+        <f t="shared" si="206"/>
+        <v>129.0510587</v>
+      </c>
+      <c r="AU38" s="5">
+        <f t="shared" si="206"/>
+        <v>132.922590461</v>
+      </c>
+      <c r="AV38" s="5">
+        <f t="shared" si="206"/>
+        <v>136.91026817483001</v>
+      </c>
+      <c r="AW38" s="5">
+        <f t="shared" si="206"/>
+        <v>141.01757622007491</v>
+      </c>
+      <c r="AX38" s="5">
+        <f t="shared" si="206"/>
+        <v>145.24810350667715</v>
+      </c>
+      <c r="AY38" s="5">
+        <f t="shared" si="206"/>
+        <v>149.60554661187749</v>
+      </c>
+      <c r="AZ38" s="5">
+        <f t="shared" si="206"/>
+        <v>154.09371301023381</v>
+      </c>
+      <c r="BA38" s="5">
+        <f t="shared" si="206"/>
+        <v>158.71652440054083</v>
+      </c>
+      <c r="BB38" s="5">
+        <f t="shared" si="206"/>
+        <v>163.47802013255708</v>
+      </c>
+    </row>
+    <row r="39" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="5">
+        <v>-73.2</v>
+      </c>
+      <c r="AQ39" s="5">
+        <v>-82.8</v>
+      </c>
+      <c r="AR39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA39" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO40" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AP40" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AQ40" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AR40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA40" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO41" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="AP41" s="5">
+        <v>9</v>
+      </c>
+      <c r="AQ41" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="AR41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA41" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO42" s="5">
+        <v>-72.5</v>
+      </c>
+      <c r="AP42" s="5">
+        <v>-126.2</v>
+      </c>
+      <c r="AQ42" s="5">
+        <v>-110.5</v>
+      </c>
+      <c r="AR42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA42" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB42" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO43" s="5">
+        <v>-33.799999999999997</v>
+      </c>
+      <c r="AP43" s="5">
+        <v>-12.8</v>
+      </c>
+      <c r="AQ43" s="5">
+        <v>-3.1</v>
+      </c>
+      <c r="AR43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA43" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO44" s="5">
+        <v>-101.7</v>
+      </c>
+      <c r="AP44" s="5">
+        <v>-139.9</v>
+      </c>
+      <c r="AQ44" s="5">
+        <v>-165.7</v>
+      </c>
+      <c r="AR44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA44" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB44" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO45" s="5">
+        <v>-1.2</v>
+      </c>
+      <c r="AP45" s="5">
+        <v>-6</v>
+      </c>
+      <c r="AQ45" s="5">
+        <v>-3.4</v>
+      </c>
+      <c r="AR45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA45" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB45" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO46" s="5">
+        <v>10.3</v>
+      </c>
+      <c r="AP46" s="5">
+        <v>-3.5</v>
+      </c>
+      <c r="AQ46" s="5">
+        <v>-7.5</v>
+      </c>
+      <c r="AR46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA46" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO47" s="5">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AP47" s="5">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AQ47" s="5">
+        <v>-2.7</v>
+      </c>
+      <c r="AR47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA47" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO48" s="5">
+        <v>67.8</v>
+      </c>
+      <c r="AP48" s="5">
+        <v>83.2</v>
+      </c>
+      <c r="AQ48" s="5">
+        <v>24.7</v>
+      </c>
+      <c r="AR48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA48" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO49" s="5">
+        <v>662.4</v>
+      </c>
+      <c r="AP49" s="5">
+        <v>742.3</v>
+      </c>
+      <c r="AQ49" s="5">
+        <v>795.4</v>
+      </c>
+      <c r="AR49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA49" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO50" s="5">
+        <v>-47.9</v>
+      </c>
+      <c r="AP50" s="5">
+        <v>-50.5</v>
+      </c>
+      <c r="AQ50" s="5">
+        <v>-77.400000000000006</v>
+      </c>
+      <c r="AR50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA50" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO51" s="5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="AP51" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="AQ51" s="5">
+        <v>31.2</v>
+      </c>
+      <c r="AR51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA51" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB51" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO52" s="9">
+        <f>AO35+SUM(AO36:AO51)</f>
+        <v>378.99999999999943</v>
+      </c>
+      <c r="AP52" s="9">
+        <f>AP35+SUM(AP36:AP51)</f>
+        <v>465.10000000000036</v>
+      </c>
+      <c r="AQ52" s="9">
+        <f>AQ35+SUM(AQ36:AQ51)</f>
+        <v>827.9</v>
+      </c>
+      <c r="AR52" s="9">
+        <f>AR35+SUM(AR36:AR51)</f>
+        <v>587.56970560000036</v>
+      </c>
+      <c r="AS52" s="9">
+        <f t="shared" ref="AS52:BB52" si="207">AS35+SUM(AS36:AS51)</f>
+        <v>1053.4617397399998</v>
+      </c>
+      <c r="AT52" s="9">
+        <f t="shared" si="207"/>
+        <v>1490.3251312862003</v>
+      </c>
+      <c r="AU52" s="9">
+        <f t="shared" si="207"/>
+        <v>1787.31125673776</v>
+      </c>
+      <c r="AV52" s="9">
+        <f t="shared" si="207"/>
+        <v>1992.2778393176202</v>
+      </c>
+      <c r="AW52" s="9">
+        <f t="shared" si="207"/>
+        <v>2170.2184439829875</v>
+      </c>
+      <c r="AX52" s="9">
+        <f t="shared" si="207"/>
+        <v>2212.7893039201936</v>
+      </c>
+      <c r="AY52" s="9">
+        <f t="shared" si="207"/>
+        <v>2275.7505519850511</v>
+      </c>
+      <c r="AZ52" s="9">
+        <f t="shared" si="207"/>
+        <v>2343.6870918174382</v>
+      </c>
+      <c r="BA52" s="9">
+        <f t="shared" si="207"/>
+        <v>2451.1325317550891</v>
+      </c>
+      <c r="BB52" s="9">
+        <f t="shared" si="207"/>
+        <v>2593.1459196602168</v>
+      </c>
+    </row>
+    <row r="53" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO53" s="5">
+        <v>426.2</v>
+      </c>
+      <c r="AP53" s="5">
+        <v>320.7</v>
+      </c>
+      <c r="AQ53" s="5">
+        <f>179.6</f>
+        <v>179.6</v>
+      </c>
+      <c r="AR53" s="5">
+        <f>AQ53*1.1</f>
+        <v>197.56</v>
+      </c>
+      <c r="AS53" s="5">
+        <f t="shared" ref="AS53:BB53" si="208">AR53*1.1</f>
+        <v>217.31600000000003</v>
+      </c>
+      <c r="AT53" s="5">
+        <f t="shared" si="208"/>
+        <v>239.04760000000005</v>
+      </c>
+      <c r="AU53" s="5">
+        <f t="shared" si="208"/>
+        <v>262.95236000000006</v>
+      </c>
+      <c r="AV53" s="5">
+        <f t="shared" si="208"/>
+        <v>289.2475960000001</v>
+      </c>
+      <c r="AW53" s="5">
+        <f t="shared" si="208"/>
+        <v>318.17235560000012</v>
+      </c>
+      <c r="AX53" s="5">
+        <f t="shared" si="208"/>
+        <v>349.98959116000015</v>
+      </c>
+      <c r="AY53" s="5">
+        <f t="shared" si="208"/>
+        <v>384.98855027600018</v>
+      </c>
+      <c r="AZ53" s="5">
+        <f t="shared" si="208"/>
+        <v>423.48740530360021</v>
+      </c>
+      <c r="BA53" s="5">
+        <f t="shared" si="208"/>
+        <v>465.83614583396024</v>
+      </c>
+      <c r="BB53" s="5">
+        <f t="shared" si="208"/>
+        <v>512.41976041735631</v>
+      </c>
+    </row>
+    <row r="54" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO54" s="9">
+        <f>AO52-AO53</f>
+        <v>-47.200000000000557</v>
+      </c>
+      <c r="AP54" s="9">
+        <f>AP52-AP53</f>
+        <v>144.40000000000038</v>
+      </c>
+      <c r="AQ54" s="9">
+        <f>AQ52-AQ53</f>
+        <v>648.29999999999995</v>
+      </c>
+      <c r="AR54" s="9">
+        <f>AR52-AR53</f>
+        <v>390.00970560000036</v>
+      </c>
+      <c r="AS54" s="9">
+        <f t="shared" ref="AS54:BB54" si="209">AS52-AS53</f>
+        <v>836.14573973999973</v>
+      </c>
+      <c r="AT54" s="9">
+        <f t="shared" si="209"/>
+        <v>1251.2775312862002</v>
+      </c>
+      <c r="AU54" s="9">
+        <f t="shared" si="209"/>
+        <v>1524.35889673776</v>
+      </c>
+      <c r="AV54" s="9">
+        <f t="shared" si="209"/>
+        <v>1703.03024331762</v>
+      </c>
+      <c r="AW54" s="9">
+        <f t="shared" si="209"/>
+        <v>1852.0460883829874</v>
+      </c>
+      <c r="AX54" s="9">
+        <f t="shared" si="209"/>
+        <v>1862.7997127601934</v>
+      </c>
+      <c r="AY54" s="9">
+        <f t="shared" si="209"/>
+        <v>1890.7620017090508</v>
+      </c>
+      <c r="AZ54" s="9">
+        <f t="shared" si="209"/>
+        <v>1920.1996865138381</v>
+      </c>
+      <c r="BA54" s="9">
+        <f t="shared" si="209"/>
+        <v>1985.2963859211288</v>
+      </c>
+      <c r="BB54" s="9">
+        <f t="shared" si="209"/>
+        <v>2080.7261592428604</v>
+      </c>
+      <c r="BC54" s="1">
+        <f>BB54*(1+$BE$26)</f>
+        <v>2059.918897650432</v>
+      </c>
+      <c r="BD54" s="1">
+        <f t="shared" ref="BD54:DO54" si="210">BC54*(1+$BE$26)</f>
+        <v>2039.3197086739276</v>
+      </c>
+      <c r="BE54" s="1">
+        <f t="shared" si="210"/>
+        <v>2018.9265115871883</v>
+      </c>
+      <c r="BF54" s="1">
+        <f t="shared" si="210"/>
+        <v>1998.7372464713164</v>
+      </c>
+      <c r="BG54" s="1">
+        <f t="shared" si="210"/>
+        <v>1978.7498740066032</v>
+      </c>
+      <c r="BH54" s="1">
+        <f t="shared" si="210"/>
+        <v>1958.9623752665373</v>
+      </c>
+      <c r="BI54" s="1">
+        <f t="shared" si="210"/>
+        <v>1939.3727515138719</v>
+      </c>
+      <c r="BJ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1919.9790239987331</v>
+      </c>
+      <c r="BK54" s="1">
+        <f t="shared" si="210"/>
+        <v>1900.7792337587457</v>
+      </c>
+      <c r="BL54" s="1">
+        <f t="shared" si="210"/>
+        <v>1881.7714414211582</v>
+      </c>
+      <c r="BM54" s="1">
+        <f t="shared" si="210"/>
+        <v>1862.9537270069466</v>
+      </c>
+      <c r="BN54" s="1">
+        <f t="shared" si="210"/>
+        <v>1844.3241897368771</v>
+      </c>
+      <c r="BO54" s="1">
+        <f t="shared" si="210"/>
+        <v>1825.8809478395083</v>
+      </c>
+      <c r="BP54" s="1">
+        <f t="shared" si="210"/>
+        <v>1807.6221383611132</v>
+      </c>
+      <c r="BQ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1789.545916977502</v>
+      </c>
+      <c r="BR54" s="1">
+        <f t="shared" si="210"/>
+        <v>1771.650457807727</v>
+      </c>
+      <c r="BS54" s="1">
+        <f t="shared" si="210"/>
+        <v>1753.9339532296497</v>
+      </c>
+      <c r="BT54" s="1">
+        <f t="shared" si="210"/>
+        <v>1736.3946136973532</v>
+      </c>
+      <c r="BU54" s="1">
+        <f t="shared" si="210"/>
+        <v>1719.0306675603797</v>
+      </c>
+      <c r="BV54" s="1">
+        <f t="shared" si="210"/>
+        <v>1701.8403608847759</v>
+      </c>
+      <c r="BW54" s="1">
+        <f t="shared" si="210"/>
+        <v>1684.8219572759281</v>
+      </c>
+      <c r="BX54" s="1">
+        <f t="shared" si="210"/>
+        <v>1667.9737377031688</v>
+      </c>
+      <c r="BY54" s="1">
+        <f t="shared" si="210"/>
+        <v>1651.2940003261372</v>
+      </c>
+      <c r="BZ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1634.7810603228759</v>
+      </c>
+      <c r="CA54" s="1">
+        <f t="shared" si="210"/>
+        <v>1618.4332497196472</v>
+      </c>
+      <c r="CB54" s="1">
+        <f t="shared" si="210"/>
+        <v>1602.2489172224507</v>
+      </c>
+      <c r="CC54" s="1">
+        <f t="shared" si="210"/>
+        <v>1586.2264280502261</v>
+      </c>
+      <c r="CD54" s="1">
+        <f t="shared" si="210"/>
+        <v>1570.3641637697237</v>
+      </c>
+      <c r="CE54" s="1">
+        <f t="shared" si="210"/>
+        <v>1554.6605221320265</v>
+      </c>
+      <c r="CF54" s="1">
+        <f t="shared" si="210"/>
+        <v>1539.1139169107062</v>
+      </c>
+      <c r="CG54" s="1">
+        <f t="shared" si="210"/>
+        <v>1523.7227777415992</v>
+      </c>
+      <c r="CH54" s="1">
+        <f t="shared" si="210"/>
+        <v>1508.4855499641833</v>
+      </c>
+      <c r="CI54" s="1">
+        <f t="shared" si="210"/>
+        <v>1493.4006944645414</v>
+      </c>
+      <c r="CJ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1478.4666875198959</v>
+      </c>
+      <c r="CK54" s="1">
+        <f t="shared" si="210"/>
+        <v>1463.6820206446969</v>
+      </c>
+      <c r="CL54" s="1">
+        <f t="shared" si="210"/>
+        <v>1449.0452004382498</v>
+      </c>
+      <c r="CM54" s="1">
+        <f t="shared" si="210"/>
+        <v>1434.5547484338674</v>
+      </c>
+      <c r="CN54" s="1">
+        <f t="shared" si="210"/>
+        <v>1420.2092009495286</v>
+      </c>
+      <c r="CO54" s="1">
+        <f t="shared" si="210"/>
+        <v>1406.0071089400333</v>
+      </c>
+      <c r="CP54" s="1">
+        <f t="shared" si="210"/>
+        <v>1391.947037850633</v>
+      </c>
+      <c r="CQ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1378.0275674721267</v>
+      </c>
+      <c r="CR54" s="1">
+        <f t="shared" si="210"/>
+        <v>1364.2472917974055</v>
+      </c>
+      <c r="CS54" s="1">
+        <f t="shared" si="210"/>
+        <v>1350.6048188794314</v>
+      </c>
+      <c r="CT54" s="1">
+        <f t="shared" si="210"/>
+        <v>1337.0987706906371</v>
+      </c>
+      <c r="CU54" s="1">
+        <f t="shared" si="210"/>
+        <v>1323.7277829837308</v>
+      </c>
+      <c r="CV54" s="1">
+        <f t="shared" si="210"/>
+        <v>1310.4905051538935</v>
+      </c>
+      <c r="CW54" s="1">
+        <f t="shared" si="210"/>
+        <v>1297.3856001023546</v>
+      </c>
+      <c r="CX54" s="1">
+        <f t="shared" si="210"/>
+        <v>1284.4117441013311</v>
+      </c>
+      <c r="CY54" s="1">
+        <f t="shared" si="210"/>
+        <v>1271.5676266603177</v>
+      </c>
+      <c r="CZ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1258.8519503937146</v>
+      </c>
+      <c r="DA54" s="1">
+        <f t="shared" si="210"/>
+        <v>1246.2634308897775</v>
+      </c>
+      <c r="DB54" s="1">
+        <f t="shared" si="210"/>
+        <v>1233.8007965808797</v>
+      </c>
+      <c r="DC54" s="1">
+        <f t="shared" si="210"/>
+        <v>1221.4627886150708</v>
+      </c>
+      <c r="DD54" s="1">
+        <f t="shared" si="210"/>
+        <v>1209.2481607289201</v>
+      </c>
+      <c r="DE54" s="1">
+        <f t="shared" si="210"/>
+        <v>1197.1556791216308</v>
+      </c>
+      <c r="DF54" s="1">
+        <f t="shared" si="210"/>
+        <v>1185.1841223304145</v>
+      </c>
+      <c r="DG54" s="1">
+        <f t="shared" si="210"/>
+        <v>1173.3322811071105</v>
+      </c>
+      <c r="DH54" s="1">
+        <f t="shared" si="210"/>
+        <v>1161.5989582960394</v>
+      </c>
+      <c r="DI54" s="1">
+        <f t="shared" si="210"/>
+        <v>1149.9829687130791</v>
+      </c>
+      <c r="DJ54" s="1">
+        <f t="shared" si="210"/>
+        <v>1138.4831390259483</v>
+      </c>
+      <c r="DK54" s="1">
+        <f t="shared" si="210"/>
+        <v>1127.0983076356888</v>
+      </c>
+      <c r="DL54" s="1">
+        <f t="shared" si="210"/>
+        <v>1115.8273245593318</v>
+      </c>
+      <c r="DM54" s="1">
+        <f t="shared" si="210"/>
+        <v>1104.6690513137385</v>
+      </c>
+      <c r="DN54" s="1">
+        <f t="shared" si="210"/>
+        <v>1093.622360800601</v>
+      </c>
+      <c r="DO54" s="1">
+        <f t="shared" si="210"/>
+        <v>1082.686137192595</v>
+      </c>
+      <c r="DP54" s="1">
+        <f t="shared" ref="DP54:EP54" si="211">DO54*(1+$BE$26)</f>
+        <v>1071.8592758206689</v>
+      </c>
+      <c r="DQ54" s="1">
+        <f t="shared" si="211"/>
+        <v>1061.1406830624621</v>
+      </c>
+      <c r="DR54" s="1">
+        <f t="shared" si="211"/>
+        <v>1050.5292762318375</v>
+      </c>
+      <c r="DS54" s="1">
+        <f t="shared" si="211"/>
+        <v>1040.0239834695192</v>
+      </c>
+      <c r="DT54" s="1">
+        <f t="shared" si="211"/>
+        <v>1029.623743634824</v>
+      </c>
+      <c r="DU54" s="1">
+        <f t="shared" si="211"/>
+        <v>1019.3275061984757</v>
+      </c>
+      <c r="DV54" s="1">
+        <f t="shared" si="211"/>
+        <v>1009.1342311364909</v>
+      </c>
+      <c r="DW54" s="1">
+        <f t="shared" si="211"/>
+        <v>999.04288882512606</v>
+      </c>
+      <c r="DX54" s="1">
+        <f t="shared" si="211"/>
+        <v>989.05245993687481</v>
+      </c>
+      <c r="DY54" s="1">
+        <f t="shared" si="211"/>
+        <v>979.16193533750607</v>
+      </c>
+      <c r="DZ54" s="1">
+        <f t="shared" si="211"/>
+        <v>969.37031598413103</v>
+      </c>
+      <c r="EA54" s="1">
+        <f t="shared" si="211"/>
+        <v>959.67661282428969</v>
+      </c>
+      <c r="EB54" s="1">
+        <f t="shared" si="211"/>
+        <v>950.07984669604673</v>
+      </c>
+      <c r="EC54" s="1">
+        <f t="shared" si="211"/>
+        <v>940.5790482290862</v>
+      </c>
+      <c r="ED54" s="1">
+        <f t="shared" si="211"/>
+        <v>931.17325774679534</v>
+      </c>
+      <c r="EE54" s="1">
+        <f t="shared" si="211"/>
+        <v>921.86152516932736</v>
+      </c>
+      <c r="EF54" s="1">
+        <f t="shared" si="211"/>
+        <v>912.64290991763403</v>
+      </c>
+      <c r="EG54" s="1">
+        <f t="shared" si="211"/>
+        <v>903.51648081845769</v>
+      </c>
+      <c r="EH54" s="1">
+        <f t="shared" si="211"/>
+        <v>894.48131601027308</v>
+      </c>
+      <c r="EI54" s="1">
+        <f t="shared" si="211"/>
+        <v>885.53650285017034</v>
+      </c>
+      <c r="EJ54" s="1">
+        <f t="shared" si="211"/>
+        <v>876.68113782166859</v>
+      </c>
+      <c r="EK54" s="1">
+        <f t="shared" si="211"/>
+        <v>867.91432644345184</v>
+      </c>
+      <c r="EL54" s="1">
+        <f t="shared" si="211"/>
+        <v>859.23518317901733</v>
+      </c>
+      <c r="EM54" s="1">
+        <f t="shared" si="211"/>
+        <v>850.64283134722712</v>
+      </c>
+      <c r="EN54" s="1">
+        <f t="shared" si="211"/>
+        <v>842.13640303375485</v>
+      </c>
+      <c r="EO54" s="1">
+        <f t="shared" si="211"/>
+        <v>833.71503900341725</v>
+      </c>
+      <c r="EP54" s="1">
+        <f t="shared" si="211"/>
+        <v>825.37788861338311</v>
+      </c>
+    </row>
+    <row r="56" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE56" s="5">
+        <f>NPV(BE27,AR54:EP54)</f>
+        <v>23253.763191710452</v>
+      </c>
+    </row>
+    <row r="57" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE57" s="5">
+        <f>Main!D8</f>
+        <v>3746.1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE58" s="5">
+        <f>BE56+BE57</f>
+        <v>26999.86319171045</v>
+      </c>
+    </row>
+    <row r="59" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE59" s="4">
+        <f>BE58/BB20</f>
+        <v>41.860253010403802</v>
+      </c>
+    </row>
+    <row r="60" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE60" s="4">
+        <f>Main!D3</f>
+        <v>128.47</v>
+      </c>
+    </row>
+    <row r="61" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="BE61" s="10">
+        <f>BE59/BE60-1</f>
+        <v>-0.67416320533662488</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RBLX.xlsx
+++ b/Financial Analysis/RBLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F17B5E-E6C4-494A-B61B-AFC99A2AF171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EB8740-6F35-4CF3-BF94-B92B84E80C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{20A32264-496F-49BA-BE16-734192C30A81}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="98">
   <si>
     <t>RBLX</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
   </si>
 </sst>
 </file>
@@ -416,13 +419,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -440,7 +443,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20406360" y="0"/>
+          <a:off x="21015960" y="0"/>
           <a:ext cx="0" cy="10896600"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -839,17 +842,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>128.47</v>
+        <v>116.53</v>
       </c>
       <c r="E3" s="3">
-        <v>45909</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="3">
-        <v>45966</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,11 +860,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -870,7 +873,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>82863.149999999994</v>
+        <v>81804.06</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -878,11 +881,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>994.6+1632.6+2111.3</f>
-        <v>4738.5</v>
+        <f>1016.8+1843.7+2360.6</f>
+        <v>5221.1000000000004</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,11 +893,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>992.4</f>
-        <v>992.4</v>
+        <f>992.7</f>
+        <v>992.7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -903,7 +906,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>3746.1</v>
+        <v>4228.4000000000005</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -912,7 +915,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>79117.049999999988</v>
+        <v>77575.66</v>
       </c>
     </row>
   </sheetData>
@@ -1182,11 +1185,11 @@
         <v>1080.7</v>
       </c>
       <c r="AG3" s="9">
-        <v>1135</v>
+        <v>1359.6</v>
       </c>
       <c r="AH3" s="9">
-        <f>AD3*1.22</f>
-        <v>1205.604</v>
+        <f>AD3*1.4</f>
+        <v>1383.48</v>
       </c>
       <c r="AI3" s="10"/>
       <c r="AK3" s="9">
@@ -1218,47 +1221,47 @@
       </c>
       <c r="AR3" s="9">
         <f>SUM(AE3:AH3)</f>
-        <v>4456.5039999999999</v>
+        <v>4858.9799999999996</v>
       </c>
       <c r="AS3" s="9">
         <f>AR3*1.22</f>
-        <v>5436.9348799999998</v>
+        <v>5927.9555999999993</v>
       </c>
       <c r="AT3" s="9">
         <f>AS3*1.18</f>
-        <v>6415.5831583999998</v>
+        <v>6994.9876079999985</v>
       </c>
       <c r="AU3" s="9">
         <f>AT3*1.15</f>
-        <v>7377.9206321599995</v>
+        <v>8044.2357491999974</v>
       </c>
       <c r="AV3" s="9">
         <f>AU3*1.12</f>
-        <v>8263.2711080192003</v>
+        <v>9009.5440391039974</v>
       </c>
       <c r="AW3" s="9">
         <f>AV3*1.09</f>
-        <v>9006.9655077409298</v>
+        <v>9820.4030026233577</v>
       </c>
       <c r="AX3" s="9">
         <f>AW3*1.07</f>
-        <v>9637.4530932827947</v>
+        <v>10507.831212806994</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.06</f>
-        <v>10215.700278879764</v>
+        <v>11138.301085575415</v>
       </c>
       <c r="AZ3" s="9">
         <f t="shared" ref="AZ3:BB3" si="0">AY3*1.05</f>
-        <v>10726.485292823752</v>
+        <v>11695.216139854187</v>
       </c>
       <c r="BA3" s="9">
         <f t="shared" si="0"/>
-        <v>11262.80955746494</v>
+        <v>12279.976946846897</v>
       </c>
       <c r="BB3" s="9">
         <f t="shared" si="0"/>
-        <v>11825.950035338186</v>
+        <v>12893.975794189242</v>
       </c>
       <c r="BC3" s="9"/>
     </row>
@@ -1358,12 +1361,11 @@
         <v>236.1</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" ref="AG4:AH4" si="1">AG3*0.22</f>
-        <v>249.7</v>
+        <v>296.5</v>
       </c>
       <c r="AH4" s="5">
-        <f t="shared" si="1"/>
-        <v>265.23288000000002</v>
+        <f t="shared" ref="AG4:AH4" si="1">AH3*0.22</f>
+        <v>304.36560000000003</v>
       </c>
       <c r="AK4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1394,47 +1396,47 @@
       </c>
       <c r="AR4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>975.73288000000002</v>
+        <v>1061.6656</v>
       </c>
       <c r="AS4" s="5">
         <f>AS3*0.22</f>
-        <v>1196.1256736</v>
+        <v>1304.150232</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" ref="AT4:BB4" si="2">AT3*0.22</f>
-        <v>1411.428294848</v>
+        <v>1538.8972737599997</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="2"/>
-        <v>1623.1425390751999</v>
+        <v>1769.7318648239993</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="2"/>
-        <v>1817.919643764224</v>
+        <v>1982.0996886028795</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="2"/>
-        <v>1981.5324117030045</v>
+        <v>2160.4886605771385</v>
       </c>
       <c r="AX4" s="5">
         <f t="shared" si="2"/>
-        <v>2120.2396805222147</v>
+        <v>2311.7228668175385</v>
       </c>
       <c r="AY4" s="5">
         <f t="shared" si="2"/>
-        <v>2247.4540613535478</v>
+        <v>2450.4262388265911</v>
       </c>
       <c r="AZ4" s="5">
         <f t="shared" si="2"/>
-        <v>2359.8267644212256</v>
+        <v>2572.9475507679213</v>
       </c>
       <c r="BA4" s="5">
         <f t="shared" si="2"/>
-        <v>2477.8181026422867</v>
+        <v>2701.5949283063173</v>
       </c>
       <c r="BB4" s="5">
         <f t="shared" si="2"/>
-        <v>2601.709007774401</v>
+        <v>2836.6746747216334</v>
       </c>
     </row>
     <row r="5" spans="2:55" x14ac:dyDescent="0.3">
@@ -1533,12 +1535,11 @@
         <v>316.39999999999998</v>
       </c>
       <c r="AG5" s="5">
-        <f>AG3*0.28</f>
-        <v>317.8</v>
+        <v>427.9</v>
       </c>
       <c r="AH5" s="5">
-        <f>AH3*0.3</f>
-        <v>361.68119999999999</v>
+        <f>AH3*0.32</f>
+        <v>442.71360000000004</v>
       </c>
       <c r="AK5" s="5">
         <f>SUM(C5:F5)</f>
@@ -1569,47 +1570,47 @@
       </c>
       <c r="AR5" s="5">
         <f>SUM(AE5:AH5)</f>
-        <v>1277.4811999999999</v>
+        <v>1468.6136000000001</v>
       </c>
       <c r="AS5" s="5">
         <f>AS3*0.28</f>
-        <v>1522.3417664000001</v>
+        <v>1659.8275679999999</v>
       </c>
       <c r="AT5" s="5">
         <f t="shared" ref="AT5:BB5" si="3">AT3*0.28</f>
-        <v>1796.3632843520002</v>
+        <v>1958.5965302399998</v>
       </c>
       <c r="AU5" s="5">
         <f t="shared" si="3"/>
-        <v>2065.8177770048001</v>
+        <v>2252.3860097759994</v>
       </c>
       <c r="AV5" s="5">
         <f t="shared" si="3"/>
-        <v>2313.7159102453761</v>
+        <v>2522.6723309491194</v>
       </c>
       <c r="AW5" s="5">
         <f t="shared" si="3"/>
-        <v>2521.9503421674603</v>
+        <v>2749.7128407345404</v>
       </c>
       <c r="AX5" s="5">
         <f t="shared" si="3"/>
-        <v>2698.4868661191827</v>
+        <v>2942.1927395859584</v>
       </c>
       <c r="AY5" s="5">
         <f t="shared" si="3"/>
-        <v>2860.396078086334</v>
+        <v>3118.7243039611162</v>
       </c>
       <c r="AZ5" s="5">
         <f t="shared" si="3"/>
-        <v>3003.4158819906511</v>
+        <v>3274.6605191591725</v>
       </c>
       <c r="BA5" s="5">
         <f t="shared" si="3"/>
-        <v>3153.5866760901836</v>
+        <v>3438.3935451171315</v>
       </c>
       <c r="BB5" s="5">
         <f t="shared" si="3"/>
-        <v>3311.2660098946926</v>
+        <v>3610.3132223729881</v>
       </c>
     </row>
     <row r="6" spans="2:55" x14ac:dyDescent="0.3">
@@ -1708,12 +1709,11 @@
         <v>260.7</v>
       </c>
       <c r="AG6" s="5">
-        <f>AC6*1.12</f>
-        <v>273.952</v>
+        <v>321.39999999999998</v>
       </c>
       <c r="AH6" s="5">
-        <f>AD6*1.15</f>
-        <v>256.21999999999997</v>
+        <f>AD6*1.5</f>
+        <v>334.20000000000005</v>
       </c>
       <c r="AK6" s="5">
         <f>SUM(C6:F6)</f>
@@ -1744,47 +1744,47 @@
       </c>
       <c r="AR6" s="5">
         <f>SUM(AE6:AH6)</f>
-        <v>1032.972</v>
+        <v>1158.4000000000001</v>
       </c>
       <c r="AS6" s="5">
         <f>AR6*1.03</f>
-        <v>1063.9611600000001</v>
+        <v>1193.152</v>
       </c>
       <c r="AT6" s="5">
         <f>AS6*1.02</f>
-        <v>1085.2403832</v>
+        <v>1217.01504</v>
       </c>
       <c r="AU6" s="5">
         <f>AT6*1.02</f>
-        <v>1106.9451908640001</v>
+        <v>1241.3553408</v>
       </c>
       <c r="AV6" s="5">
         <f>AU6*1.02</f>
-        <v>1129.08409468128</v>
+        <v>1266.182447616</v>
       </c>
       <c r="AW6" s="5">
         <f>AV6*1.02</f>
-        <v>1151.6657765749057</v>
+        <v>1291.5060965683201</v>
       </c>
       <c r="AX6" s="5">
         <f t="shared" ref="AX6:BB6" si="4">AW6*1.01</f>
-        <v>1163.1824343406547</v>
+        <v>1304.4211575340034</v>
       </c>
       <c r="AY6" s="5">
         <f t="shared" si="4"/>
-        <v>1174.8142586840613</v>
+        <v>1317.4653691093436</v>
       </c>
       <c r="AZ6" s="5">
         <f t="shared" si="4"/>
-        <v>1186.562401270902</v>
+        <v>1330.640022800437</v>
       </c>
       <c r="BA6" s="5">
         <f t="shared" si="4"/>
-        <v>1198.4280252836111</v>
+        <v>1343.9464230284414</v>
       </c>
       <c r="BB6" s="5">
         <f t="shared" si="4"/>
-        <v>1210.4123055364471</v>
+        <v>1357.3858872587257</v>
       </c>
     </row>
     <row r="7" spans="2:55" x14ac:dyDescent="0.3">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="AG7" s="5">
         <f t="shared" si="6"/>
-        <v>841.452</v>
+        <v>1045.8</v>
       </c>
       <c r="AH7" s="5">
         <f t="shared" si="6"/>
-        <v>883.13408000000004</v>
+        <v>1081.2792000000002</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" ref="AK7:BB7" si="7">SUM(AK4:AK6)</f>
@@ -1949,47 +1949,47 @@
       </c>
       <c r="AR7" s="5">
         <f t="shared" si="7"/>
-        <v>3286.1860799999995</v>
+        <v>3688.6792</v>
       </c>
       <c r="AS7" s="5">
         <f t="shared" si="7"/>
-        <v>3782.4286000000002</v>
+        <v>4157.1297999999997</v>
       </c>
       <c r="AT7" s="5">
         <f t="shared" si="7"/>
-        <v>4293.0319624000003</v>
+        <v>4714.508844</v>
       </c>
       <c r="AU7" s="5">
         <f t="shared" si="7"/>
-        <v>4795.9055069440001</v>
+        <v>5263.4732153999985</v>
       </c>
       <c r="AV7" s="5">
         <f t="shared" si="7"/>
-        <v>5260.7196486908797</v>
+        <v>5770.9544671679987</v>
       </c>
       <c r="AW7" s="5">
         <f t="shared" si="7"/>
-        <v>5655.1485304453709</v>
+        <v>6201.7075978799985</v>
       </c>
       <c r="AX7" s="5">
         <f t="shared" si="7"/>
-        <v>5981.9089809820525</v>
+        <v>6558.3367639375001</v>
       </c>
       <c r="AY7" s="5">
         <f t="shared" si="7"/>
-        <v>6282.6643981239431</v>
+        <v>6886.6159118970509</v>
       </c>
       <c r="AZ7" s="5">
         <f t="shared" si="7"/>
-        <v>6549.8050476827784</v>
+        <v>7178.2480927275301</v>
       </c>
       <c r="BA7" s="5">
         <f t="shared" si="7"/>
-        <v>6829.8328040160814</v>
+        <v>7483.9348964518904</v>
       </c>
       <c r="BB7" s="5">
         <f t="shared" si="7"/>
-        <v>7123.3873232055412</v>
+        <v>7804.3737843533472</v>
       </c>
     </row>
     <row r="8" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2118,11 +2118,11 @@
       </c>
       <c r="AG8" s="9">
         <f t="shared" si="9"/>
-        <v>293.548</v>
+        <v>313.79999999999995</v>
       </c>
       <c r="AH8" s="9">
         <f t="shared" si="9"/>
-        <v>322.46992</v>
+        <v>302.20079999999984</v>
       </c>
       <c r="AK8" s="9">
         <f t="shared" ref="AK8" si="10">AK3-AK7</f>
@@ -2154,47 +2154,47 @@
       </c>
       <c r="AR8" s="9">
         <f t="shared" ref="AR8" si="17">AR3-AR7</f>
-        <v>1170.3179200000004</v>
+        <v>1170.3007999999995</v>
       </c>
       <c r="AS8" s="9">
         <f t="shared" ref="AS8" si="18">AS3-AS7</f>
-        <v>1654.5062799999996</v>
+        <v>1770.8257999999996</v>
       </c>
       <c r="AT8" s="9">
         <f t="shared" ref="AT8" si="19">AT3-AT7</f>
-        <v>2122.5511959999994</v>
+        <v>2280.4787639999986</v>
       </c>
       <c r="AU8" s="9">
         <f t="shared" ref="AU8" si="20">AU3-AU7</f>
-        <v>2582.0151252159994</v>
+        <v>2780.7625337999989</v>
       </c>
       <c r="AV8" s="9">
         <f t="shared" ref="AV8" si="21">AV3-AV7</f>
-        <v>3002.5514593283206</v>
+        <v>3238.5895719359987</v>
       </c>
       <c r="AW8" s="9">
         <f t="shared" ref="AW8" si="22">AW3-AW7</f>
-        <v>3351.8169772955589</v>
+        <v>3618.6954047433592</v>
       </c>
       <c r="AX8" s="9">
         <f t="shared" ref="AX8" si="23">AX3-AX7</f>
-        <v>3655.5441123007422</v>
+        <v>3949.4944488694937</v>
       </c>
       <c r="AY8" s="9">
         <f t="shared" ref="AY8" si="24">AY3-AY7</f>
-        <v>3933.0358807558205</v>
+        <v>4251.6851736783638</v>
       </c>
       <c r="AZ8" s="9">
         <f t="shared" ref="AZ8" si="25">AZ3-AZ7</f>
-        <v>4176.680245140974</v>
+        <v>4516.9680471266565</v>
       </c>
       <c r="BA8" s="9">
         <f t="shared" ref="BA8" si="26">BA3-BA7</f>
-        <v>4432.9767534488583</v>
+        <v>4796.0420503950063</v>
       </c>
       <c r="BB8" s="9">
         <f t="shared" ref="BB8" si="27">BB3-BB7</f>
-        <v>4702.5627121326452</v>
+        <v>5089.6020098358949</v>
       </c>
     </row>
     <row r="9" spans="2:55" x14ac:dyDescent="0.3">
@@ -2293,12 +2293,11 @@
         <v>385</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" ref="AG9" si="28">AC9*1.03</f>
-        <v>376.36199999999997</v>
+        <v>398.3</v>
       </c>
       <c r="AH9" s="5">
-        <f>AD9*1.07</f>
-        <v>379.85</v>
+        <f>AD9*1.14</f>
+        <v>404.7</v>
       </c>
       <c r="AK9" s="5">
         <f>SUM(C9:F9)</f>
@@ -2329,47 +2328,47 @@
       </c>
       <c r="AR9" s="5">
         <f>SUM(AE9:AH9)</f>
-        <v>1515.8119999999999</v>
+        <v>1562.6000000000001</v>
       </c>
       <c r="AS9" s="5">
         <f>AR9*1.03</f>
-        <v>1561.2863599999998</v>
+        <v>1609.4780000000003</v>
       </c>
       <c r="AT9" s="5">
         <f>AS9*1.02</f>
-        <v>1592.5120871999998</v>
+        <v>1641.6675600000003</v>
       </c>
       <c r="AU9" s="5">
         <f>AT9*1.02</f>
-        <v>1624.3623289439997</v>
+        <v>1674.5009112000002</v>
       </c>
       <c r="AV9" s="5">
-        <f t="shared" ref="AV9:AW10" si="29">AU9*1.02</f>
-        <v>1656.8495755228798</v>
+        <f t="shared" ref="AV9:AW10" si="28">AU9*1.02</f>
+        <v>1707.9909294240003</v>
       </c>
       <c r="AW9" s="5">
         <f>AV9*1.01</f>
-        <v>1673.4180712781088</v>
+        <v>1725.0708387182403</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" ref="AX9:BB9" si="30">AW9*1.01</f>
-        <v>1690.1522519908899</v>
+        <f t="shared" ref="AX9:BB9" si="29">AW9*1.01</f>
+        <v>1742.3215471054227</v>
       </c>
       <c r="AY9" s="5">
-        <f t="shared" si="30"/>
-        <v>1707.0537745107988</v>
+        <f t="shared" si="29"/>
+        <v>1759.7447625764769</v>
       </c>
       <c r="AZ9" s="5">
-        <f t="shared" si="30"/>
-        <v>1724.1243122559067</v>
+        <f t="shared" si="29"/>
+        <v>1777.3422102022416</v>
       </c>
       <c r="BA9" s="5">
-        <f t="shared" si="30"/>
-        <v>1741.3655553784658</v>
+        <f t="shared" si="29"/>
+        <v>1795.115632304264</v>
       </c>
       <c r="BB9" s="5">
-        <f t="shared" si="30"/>
-        <v>1758.7792109322504</v>
+        <f t="shared" si="29"/>
+        <v>1813.0667886273066</v>
       </c>
     </row>
     <row r="10" spans="2:55" x14ac:dyDescent="0.3">
@@ -2468,12 +2467,11 @@
         <v>152.19999999999999</v>
       </c>
       <c r="AG10" s="5">
-        <f>AC10*1.6</f>
-        <v>157.92000000000002</v>
+        <v>145</v>
       </c>
       <c r="AH10" s="5">
-        <f>AD10*1.55</f>
-        <v>163.215</v>
+        <f>AD10*1.47</f>
+        <v>154.791</v>
       </c>
       <c r="AK10" s="5">
         <f>SUM(C10:F10)</f>
@@ -2504,47 +2502,47 @@
       </c>
       <c r="AR10" s="5">
         <f>SUM(AE10:AH10)</f>
-        <v>592.43499999999995</v>
+        <v>571.09099999999989</v>
       </c>
       <c r="AS10" s="5">
         <f>AR10*1.09</f>
-        <v>645.75414999999998</v>
+        <v>622.48918999999989</v>
       </c>
       <c r="AT10" s="5">
         <f>AS10*1.05</f>
-        <v>678.04185749999999</v>
+        <v>653.61364949999995</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10*1.04</f>
-        <v>705.16353179999999</v>
+        <v>679.75819547999993</v>
       </c>
       <c r="AV10" s="5">
         <f>AU10*1.03</f>
-        <v>726.318437754</v>
+        <v>700.15094134439994</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="29"/>
-        <v>740.84480650908006</v>
+        <f t="shared" si="28"/>
+        <v>714.15396017128796</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" ref="AX10" si="31">AW10*1.02</f>
-        <v>755.66170263926165</v>
+        <f t="shared" ref="AX10" si="30">AW10*1.02</f>
+        <v>728.43703937471378</v>
       </c>
       <c r="AY10" s="5">
-        <f t="shared" ref="AY10" si="32">AX10*1.02</f>
-        <v>770.77493669204694</v>
+        <f t="shared" ref="AY10" si="31">AX10*1.02</f>
+        <v>743.00578016220811</v>
       </c>
       <c r="AZ10" s="5">
-        <f t="shared" ref="AZ10" si="33">AY10*1.02</f>
-        <v>786.19043542588793</v>
+        <f t="shared" ref="AZ10" si="32">AY10*1.02</f>
+        <v>757.86589576545225</v>
       </c>
       <c r="BA10" s="5">
-        <f t="shared" ref="BA10" si="34">AZ10*1.02</f>
-        <v>801.91424413440575</v>
+        <f t="shared" ref="BA10" si="33">AZ10*1.02</f>
+        <v>773.02321368076127</v>
       </c>
       <c r="BB10" s="5">
-        <f t="shared" ref="BB10" si="35">BA10*1.02</f>
-        <v>817.95252901709387</v>
+        <f t="shared" ref="BB10" si="34">BA10*1.02</f>
+        <v>788.4836779543765</v>
       </c>
     </row>
     <row r="11" spans="2:55" x14ac:dyDescent="0.3">
@@ -2643,12 +2641,11 @@
         <v>52.8</v>
       </c>
       <c r="AG11" s="5">
-        <f>AG3*0.05</f>
-        <v>56.75</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="AH11" s="5">
         <f>AH3*0.05</f>
-        <v>60.280200000000008</v>
+        <v>69.174000000000007</v>
       </c>
       <c r="AK11" s="5">
         <f>SUM(C11:F11)</f>
@@ -2679,47 +2676,47 @@
       </c>
       <c r="AR11" s="5">
         <f>SUM(AE11:AH11)</f>
-        <v>217.6302</v>
+        <v>236.874</v>
       </c>
       <c r="AS11" s="5">
-        <f t="shared" ref="AS11:BB11" si="36">AS3*0.05</f>
-        <v>271.846744</v>
+        <f t="shared" ref="AS11:BB11" si="35">AS3*0.05</f>
+        <v>296.39777999999995</v>
       </c>
       <c r="AT11" s="5">
-        <f t="shared" si="36"/>
-        <v>320.77915791999999</v>
+        <f t="shared" si="35"/>
+        <v>349.74938039999995</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" si="36"/>
-        <v>368.89603160799999</v>
+        <f t="shared" si="35"/>
+        <v>402.21178745999987</v>
       </c>
       <c r="AV11" s="5">
-        <f t="shared" si="36"/>
-        <v>413.16355540096004</v>
+        <f t="shared" si="35"/>
+        <v>450.47720195519992</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="36"/>
-        <v>450.3482753870465</v>
+        <f t="shared" si="35"/>
+        <v>491.0201501311679</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="36"/>
-        <v>481.87265466413976</v>
+        <f t="shared" si="35"/>
+        <v>525.39156064034967</v>
       </c>
       <c r="AY11" s="5">
-        <f t="shared" si="36"/>
-        <v>510.78501394398819</v>
+        <f t="shared" si="35"/>
+        <v>556.91505427877075</v>
       </c>
       <c r="AZ11" s="5">
-        <f t="shared" si="36"/>
-        <v>536.3242646411876</v>
+        <f t="shared" si="35"/>
+        <v>584.76080699270938</v>
       </c>
       <c r="BA11" s="5">
-        <f t="shared" si="36"/>
-        <v>563.14047787324705</v>
+        <f t="shared" si="35"/>
+        <v>613.9988473423449</v>
       </c>
       <c r="BB11" s="5">
-        <f t="shared" si="36"/>
-        <v>591.29750176690936</v>
+        <f t="shared" si="35"/>
+        <v>644.69878970946218</v>
       </c>
     </row>
     <row r="12" spans="2:55" x14ac:dyDescent="0.3">
@@ -2727,204 +2724,204 @@
         <v>23</v>
       </c>
       <c r="C12" s="5">
-        <f t="shared" ref="C12:O12" si="37">SUM(C9:C11)</f>
+        <f t="shared" ref="C12:O12" si="36">SUM(C9:C11)</f>
         <v>28.9</v>
       </c>
       <c r="D12" s="5">
+        <f t="shared" si="36"/>
+        <v>34.599999999999994</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="36"/>
+        <v>60.7</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="36"/>
+        <v>38</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="36"/>
+        <v>38.800000000000004</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="36"/>
+        <v>44.8</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="36"/>
+        <v>51</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="36"/>
+        <v>59.2</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="36"/>
+        <v>95.7</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="36"/>
+        <v>72.800000000000011</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="36"/>
+        <v>80.800000000000011</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="36"/>
+        <v>107.79999999999998</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" si="36"/>
+        <v>211</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" ref="P12:AC12" si="37">SUM(P9:P11)</f>
+        <v>241.4</v>
+      </c>
+      <c r="Q12" s="5">
         <f t="shared" si="37"/>
-        <v>34.599999999999994</v>
-      </c>
-      <c r="E12" s="5">
+        <v>209.39999999999998</v>
+      </c>
+      <c r="R12" s="5">
         <f t="shared" si="37"/>
-        <v>60.7</v>
-      </c>
-      <c r="F12" s="5">
+        <v>260.8</v>
+      </c>
+      <c r="S12" s="5">
         <f t="shared" si="37"/>
-        <v>38</v>
-      </c>
-      <c r="G12" s="5">
+        <v>264.70000000000005</v>
+      </c>
+      <c r="T12" s="5">
         <f t="shared" si="37"/>
-        <v>38.800000000000004</v>
-      </c>
-      <c r="H12" s="5">
+        <v>317</v>
+      </c>
+      <c r="U12" s="5">
         <f t="shared" si="37"/>
-        <v>44.8</v>
-      </c>
-      <c r="I12" s="5">
+        <v>348.90000000000003</v>
+      </c>
+      <c r="V12" s="5">
         <f t="shared" si="37"/>
-        <v>51</v>
-      </c>
-      <c r="J12" s="5">
+        <v>357.8</v>
+      </c>
+      <c r="W12" s="5">
         <f t="shared" si="37"/>
-        <v>59.2</v>
-      </c>
-      <c r="K12" s="5">
+        <v>399.90000000000003</v>
+      </c>
+      <c r="X12" s="5">
         <f t="shared" si="37"/>
-        <v>95.7</v>
-      </c>
-      <c r="L12" s="5">
+        <v>441.8</v>
+      </c>
+      <c r="Y12" s="5">
         <f t="shared" si="37"/>
-        <v>72.800000000000011</v>
-      </c>
-      <c r="M12" s="5">
+        <v>460</v>
+      </c>
+      <c r="Z12" s="5">
         <f t="shared" si="37"/>
-        <v>80.800000000000011</v>
-      </c>
-      <c r="N12" s="5">
+        <v>488.40000000000003</v>
+      </c>
+      <c r="AA12" s="5">
         <f t="shared" si="37"/>
-        <v>107.79999999999998</v>
-      </c>
-      <c r="O12" s="5">
+        <v>495.40000000000003</v>
+      </c>
+      <c r="AB12" s="5">
         <f t="shared" si="37"/>
-        <v>211</v>
-      </c>
-      <c r="P12" s="5">
-        <f t="shared" ref="P12:AC12" si="38">SUM(P9:P11)</f>
-        <v>241.4</v>
-      </c>
-      <c r="Q12" s="5">
+        <v>503.59999999999997</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="37"/>
+        <v>516.69999999999993</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" ref="AD12:AH12" si="38">SUM(AD9:AD11)</f>
+        <v>510.1</v>
+      </c>
+      <c r="AE12" s="5">
         <f t="shared" si="38"/>
-        <v>209.39999999999998</v>
-      </c>
-      <c r="R12" s="5">
+        <v>541.5</v>
+      </c>
+      <c r="AF12" s="5">
         <f t="shared" si="38"/>
-        <v>260.8</v>
-      </c>
-      <c r="S12" s="5">
+        <v>590</v>
+      </c>
+      <c r="AG12" s="5">
         <f t="shared" si="38"/>
-        <v>264.70000000000005</v>
-      </c>
-      <c r="T12" s="5">
+        <v>610.4</v>
+      </c>
+      <c r="AH12" s="5">
         <f t="shared" si="38"/>
-        <v>317</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="38"/>
-        <v>348.90000000000003</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="38"/>
-        <v>357.8</v>
-      </c>
-      <c r="W12" s="5">
-        <f t="shared" si="38"/>
-        <v>399.90000000000003</v>
-      </c>
-      <c r="X12" s="5">
-        <f t="shared" si="38"/>
-        <v>441.8</v>
-      </c>
-      <c r="Y12" s="5">
-        <f t="shared" si="38"/>
-        <v>460</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="38"/>
-        <v>488.40000000000003</v>
-      </c>
-      <c r="AA12" s="5">
-        <f t="shared" si="38"/>
-        <v>495.40000000000003</v>
-      </c>
-      <c r="AB12" s="5">
-        <f t="shared" si="38"/>
-        <v>503.59999999999997</v>
-      </c>
-      <c r="AC12" s="5">
-        <f t="shared" si="38"/>
-        <v>516.69999999999993</v>
-      </c>
-      <c r="AD12" s="5">
-        <f t="shared" ref="AD12:AH12" si="39">SUM(AD9:AD11)</f>
-        <v>510.1</v>
-      </c>
-      <c r="AE12" s="5">
+        <v>628.66499999999996</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" ref="AK12:AN12" si="39">SUM(AK9:AK11)</f>
+        <v>162.19999999999999</v>
+      </c>
+      <c r="AL12" s="5">
         <f t="shared" si="39"/>
-        <v>541.5</v>
-      </c>
-      <c r="AF12" s="5">
+        <v>193.8</v>
+      </c>
+      <c r="AM12" s="5">
         <f t="shared" si="39"/>
-        <v>590</v>
-      </c>
-      <c r="AG12" s="5">
+        <v>357.09999999999997</v>
+      </c>
+      <c r="AN12" s="5">
         <f t="shared" si="39"/>
-        <v>591.03199999999993</v>
-      </c>
-      <c r="AH12" s="5">
-        <f t="shared" si="39"/>
-        <v>603.34520000000009</v>
-      </c>
-      <c r="AK12" s="5">
-        <f t="shared" ref="AK12:AN12" si="40">SUM(AK9:AK11)</f>
-        <v>162.19999999999999</v>
-      </c>
-      <c r="AL12" s="5">
-        <f t="shared" si="40"/>
-        <v>193.8</v>
-      </c>
-      <c r="AM12" s="5">
-        <f t="shared" si="40"/>
-        <v>357.09999999999997</v>
-      </c>
-      <c r="AN12" s="5">
-        <f t="shared" si="40"/>
         <v>922.6</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" ref="AO12" si="41">SUM(AO9:AO11)</f>
+        <f t="shared" ref="AO12" si="40">SUM(AO9:AO11)</f>
         <v>1288.4000000000001</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" ref="AP12" si="42">SUM(AP9:AP11)</f>
+        <f t="shared" ref="AP12" si="41">SUM(AP9:AP11)</f>
         <v>1790.1</v>
       </c>
       <c r="AQ12" s="5">
-        <f t="shared" ref="AQ12" si="43">SUM(AQ9:AQ11)</f>
+        <f t="shared" ref="AQ12" si="42">SUM(AQ9:AQ11)</f>
         <v>2025.8</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" ref="AR12" si="44">SUM(AR9:AR11)</f>
-        <v>2325.8771999999999</v>
+        <f t="shared" ref="AR12" si="43">SUM(AR9:AR11)</f>
+        <v>2370.5649999999996</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" ref="AS12" si="45">SUM(AS9:AS11)</f>
-        <v>2478.8872539999998</v>
+        <f t="shared" ref="AS12" si="44">SUM(AS9:AS11)</f>
+        <v>2528.3649700000001</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" ref="AT12" si="46">SUM(AT9:AT11)</f>
-        <v>2591.3331026199994</v>
+        <f t="shared" ref="AT12" si="45">SUM(AT9:AT11)</f>
+        <v>2645.0305899000005</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" ref="AU12" si="47">SUM(AU9:AU11)</f>
-        <v>2698.4218923519998</v>
+        <f t="shared" ref="AU12" si="46">SUM(AU9:AU11)</f>
+        <v>2756.4708941399999</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="48">SUM(AV9:AV11)</f>
-        <v>2796.3315686778396</v>
+        <f t="shared" ref="AV12" si="47">SUM(AV9:AV11)</f>
+        <v>2858.6190727235999</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" ref="AW12" si="49">SUM(AW9:AW11)</f>
-        <v>2864.6111531742354</v>
+        <f t="shared" ref="AW12" si="48">SUM(AW9:AW11)</f>
+        <v>2930.2449490206964</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" ref="AX12" si="50">SUM(AX9:AX11)</f>
-        <v>2927.6866092942914</v>
+        <f t="shared" ref="AX12" si="49">SUM(AX9:AX11)</f>
+        <v>2996.1501471204865</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" ref="AY12" si="51">SUM(AY9:AY11)</f>
-        <v>2988.613725146834</v>
+        <f t="shared" ref="AY12" si="50">SUM(AY9:AY11)</f>
+        <v>3059.6655970174556</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" ref="AZ12" si="52">SUM(AZ9:AZ11)</f>
-        <v>3046.6390123229826</v>
+        <f t="shared" ref="AZ12" si="51">SUM(AZ9:AZ11)</f>
+        <v>3119.968912960403</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="53">SUM(BA9:BA11)</f>
-        <v>3106.4202773861189</v>
+        <f t="shared" ref="BA12" si="52">SUM(BA9:BA11)</f>
+        <v>3182.13769332737</v>
       </c>
       <c r="BB12" s="5">
-        <f t="shared" ref="BB12" si="54">SUM(BB9:BB11)</f>
-        <v>3168.0292417162536</v>
+        <f t="shared" ref="BB12" si="53">SUM(BB9:BB11)</f>
+        <v>3246.2492562911452</v>
       </c>
     </row>
     <row r="13" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2932,204 +2929,204 @@
         <v>25</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:O13" si="55">C8-C12</f>
+        <f t="shared" ref="C13:O13" si="54">C8-C12</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D13" s="9">
+        <f t="shared" si="54"/>
+        <v>-20.199999999999989</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="54"/>
+        <v>-40.800000000000011</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="54"/>
+        <v>-12.200000000000003</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="54"/>
+        <v>-10.399999999999999</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="54"/>
+        <v>-13.799999999999997</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="54"/>
+        <v>-18.700000000000003</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="54"/>
+        <v>-33.600000000000009</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="54"/>
+        <v>-73.000000000000014</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="54"/>
+        <v>-73.100000000000023</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="54"/>
+        <v>-51.600000000000023</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="54"/>
+        <v>-68.299999999999983</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="54"/>
+        <v>-134.89999999999998</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" ref="P13:AC13" si="55">P8-P12</f>
+        <v>-142.9</v>
+      </c>
+      <c r="Q13" s="9">
         <f t="shared" si="55"/>
-        <v>-20.199999999999989</v>
-      </c>
-      <c r="E13" s="9">
+        <v>-77.499999999999943</v>
+      </c>
+      <c r="R13" s="9">
         <f t="shared" si="55"/>
-        <v>-40.800000000000011</v>
-      </c>
-      <c r="F13" s="9">
+        <v>-139.70000000000005</v>
+      </c>
+      <c r="S13" s="9">
         <f t="shared" si="55"/>
-        <v>-12.200000000000003</v>
-      </c>
-      <c r="G13" s="9">
+        <v>-151.70000000000005</v>
+      </c>
+      <c r="T13" s="9">
         <f t="shared" si="55"/>
-        <v>-10.399999999999999</v>
-      </c>
-      <c r="H13" s="9">
+        <v>-170.2999999999999</v>
+      </c>
+      <c r="U13" s="9">
         <f t="shared" si="55"/>
-        <v>-13.799999999999997</v>
-      </c>
-      <c r="I13" s="9">
+        <v>-300.09999999999997</v>
+      </c>
+      <c r="V13" s="9">
         <f t="shared" si="55"/>
-        <v>-18.700000000000003</v>
-      </c>
-      <c r="J13" s="9">
+        <v>-301.8</v>
+      </c>
+      <c r="W13" s="9">
         <f t="shared" si="55"/>
-        <v>-33.600000000000009</v>
-      </c>
-      <c r="K13" s="9">
+        <v>-289.80000000000013</v>
+      </c>
+      <c r="X13" s="9">
         <f t="shared" si="55"/>
-        <v>-73.000000000000014</v>
-      </c>
-      <c r="L13" s="9">
+        <v>-313.8</v>
+      </c>
+      <c r="Y13" s="9">
         <f t="shared" si="55"/>
-        <v>-73.100000000000023</v>
-      </c>
-      <c r="M13" s="9">
+        <v>-300.09999999999991</v>
+      </c>
+      <c r="Z13" s="9">
         <f t="shared" si="55"/>
-        <v>-51.600000000000023</v>
-      </c>
-      <c r="N13" s="9">
+        <v>-355.3</v>
+      </c>
+      <c r="AA13" s="9">
         <f t="shared" si="55"/>
-        <v>-68.299999999999983</v>
-      </c>
-      <c r="O13" s="9">
+        <v>-302.30000000000013</v>
+      </c>
+      <c r="AB13" s="9">
         <f t="shared" si="55"/>
-        <v>-134.89999999999998</v>
-      </c>
-      <c r="P13" s="9">
-        <f t="shared" ref="P13:AC13" si="56">P8-P12</f>
-        <v>-142.9</v>
-      </c>
-      <c r="Q13" s="9">
+        <v>-238.09999999999997</v>
+      </c>
+      <c r="AC13" s="9">
+        <f t="shared" si="55"/>
+        <v>-278.79999999999995</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" ref="AD13:AH13" si="56">AD8-AD12</f>
+        <v>-244</v>
+      </c>
+      <c r="AE13" s="9">
         <f t="shared" si="56"/>
-        <v>-77.499999999999943</v>
-      </c>
-      <c r="R13" s="9">
+        <v>-254.69999999999993</v>
+      </c>
+      <c r="AF13" s="9">
         <f t="shared" si="56"/>
-        <v>-139.70000000000005</v>
-      </c>
-      <c r="S13" s="9">
+        <v>-322.5</v>
+      </c>
+      <c r="AG13" s="9">
         <f t="shared" si="56"/>
-        <v>-151.70000000000005</v>
-      </c>
-      <c r="T13" s="9">
+        <v>-296.60000000000002</v>
+      </c>
+      <c r="AH13" s="9">
         <f t="shared" si="56"/>
-        <v>-170.2999999999999</v>
-      </c>
-      <c r="U13" s="9">
-        <f t="shared" si="56"/>
-        <v>-300.09999999999997</v>
-      </c>
-      <c r="V13" s="9">
-        <f t="shared" si="56"/>
-        <v>-301.8</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="56"/>
-        <v>-289.80000000000013</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" si="56"/>
-        <v>-313.8</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="56"/>
-        <v>-300.09999999999991</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="56"/>
-        <v>-355.3</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" si="56"/>
-        <v>-302.30000000000013</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="56"/>
-        <v>-238.09999999999997</v>
-      </c>
-      <c r="AC13" s="9">
-        <f t="shared" si="56"/>
-        <v>-278.79999999999995</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" ref="AD13:AH13" si="57">AD8-AD12</f>
-        <v>-244</v>
-      </c>
-      <c r="AE13" s="9">
+        <v>-326.46420000000012</v>
+      </c>
+      <c r="AK13" s="9">
+        <f t="shared" ref="AK13:AN13" si="57">AK8-AK12</f>
+        <v>-87.6</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="57"/>
-        <v>-254.69999999999993</v>
-      </c>
-      <c r="AF13" s="9">
+        <v>-76.5</v>
+      </c>
+      <c r="AM13" s="9">
         <f t="shared" si="57"/>
-        <v>-322.5</v>
-      </c>
-      <c r="AG13" s="9">
+        <v>-265.99999999999994</v>
+      </c>
+      <c r="AN13" s="9">
         <f t="shared" si="57"/>
-        <v>-297.48399999999992</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" si="57"/>
-        <v>-280.87528000000009</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" ref="AK13:AN13" si="58">AK8-AK12</f>
-        <v>-87.6</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="58"/>
-        <v>-76.5</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" si="58"/>
-        <v>-265.99999999999994</v>
-      </c>
-      <c r="AN13" s="9">
-        <f t="shared" si="58"/>
         <v>-494.99999999999989</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" ref="AO13" si="59">AO8-AO12</f>
+        <f t="shared" ref="AO13" si="58">AO8-AO12</f>
         <v>-923.90000000000009</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" ref="AP13" si="60">AP8-AP12</f>
+        <f t="shared" ref="AP13" si="59">AP8-AP12</f>
         <v>-1258.9999999999995</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13" si="61">AQ8-AQ12</f>
+        <f t="shared" ref="AQ13" si="60">AQ8-AQ12</f>
         <v>-1063.2</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="62">AR8-AR12</f>
-        <v>-1155.5592799999995</v>
+        <f t="shared" ref="AR13" si="61">AR8-AR12</f>
+        <v>-1200.2642000000001</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="63">AS8-AS12</f>
-        <v>-824.38097400000015</v>
+        <f t="shared" ref="AS13" si="62">AS8-AS12</f>
+        <v>-757.53917000000047</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="64">AT8-AT12</f>
-        <v>-468.78190661999997</v>
+        <f t="shared" ref="AT13" si="63">AT8-AT12</f>
+        <v>-364.55182590000186</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="65">AU8-AU12</f>
-        <v>-116.40676713600033</v>
+        <f t="shared" ref="AU13" si="64">AU8-AU12</f>
+        <v>24.291639659998964</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" ref="AV13" si="66">AV8-AV12</f>
-        <v>206.21989065048092</v>
+        <f t="shared" ref="AV13" si="65">AV8-AV12</f>
+        <v>379.97049921239886</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" ref="AW13" si="67">AW8-AW12</f>
-        <v>487.20582412132353</v>
+        <f t="shared" ref="AW13" si="66">AW8-AW12</f>
+        <v>688.45045572266281</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" ref="AX13" si="68">AX8-AX12</f>
-        <v>727.85750300645077</v>
+        <f t="shared" ref="AX13" si="67">AX8-AX12</f>
+        <v>953.34430174900717</v>
       </c>
       <c r="AY13" s="9">
-        <f t="shared" ref="AY13" si="69">AY8-AY12</f>
-        <v>944.42215560898649</v>
+        <f t="shared" ref="AY13" si="68">AY8-AY12</f>
+        <v>1192.0195766609081</v>
       </c>
       <c r="AZ13" s="9">
-        <f t="shared" ref="AZ13" si="70">AZ8-AZ12</f>
-        <v>1130.0412328179914</v>
+        <f t="shared" ref="AZ13" si="69">AZ8-AZ12</f>
+        <v>1396.9991341662535</v>
       </c>
       <c r="BA13" s="9">
-        <f t="shared" ref="BA13" si="71">BA8-BA12</f>
-        <v>1326.5564760627394</v>
+        <f t="shared" ref="BA13" si="70">BA8-BA12</f>
+        <v>1613.9043570676363</v>
       </c>
       <c r="BB13" s="9">
-        <f t="shared" ref="BB13" si="72">BB8-BB12</f>
-        <v>1534.5334704163915</v>
+        <f t="shared" ref="BB13" si="71">BB8-BB12</f>
+        <v>1843.3527535447497</v>
       </c>
     </row>
     <row r="14" spans="2:55" x14ac:dyDescent="0.3">
@@ -3228,11 +3225,10 @@
         <v>-48.8</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" ref="AG14:AH15" si="73">AC14*1.1</f>
-        <v>-51.370000000000005</v>
+        <v>-52.1</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="AG14:AH15" si="72">AD14*1.1</f>
         <v>-50.93</v>
       </c>
       <c r="AK14" s="5">
@@ -3264,47 +3260,47 @@
       </c>
       <c r="AR14" s="5">
         <f>SUM(AE14:AH14)</f>
-        <v>-197.4</v>
+        <v>-198.13</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" ref="AS14:AW15" si="74">AR14*1.01</f>
-        <v>-199.374</v>
+        <f t="shared" ref="AS14:AW15" si="73">AR14*1.01</f>
+        <v>-200.1113</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" si="74"/>
-        <v>-201.36774</v>
+        <f t="shared" si="73"/>
+        <v>-202.112413</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="74"/>
-        <v>-203.3814174</v>
+        <f t="shared" si="73"/>
+        <v>-204.13353713000001</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" si="74"/>
-        <v>-205.41523157400002</v>
+        <f t="shared" si="73"/>
+        <v>-206.1748725013</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" si="74"/>
-        <v>-207.46938388974002</v>
+        <f t="shared" si="73"/>
+        <v>-208.23662122631299</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" ref="AX14:AX15" si="75">AW14*1.01</f>
-        <v>-209.5440777286374</v>
+        <f t="shared" ref="AX14:AX15" si="74">AW14*1.01</f>
+        <v>-210.31898743857613</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" ref="AY14:AY15" si="76">AX14*1.01</f>
-        <v>-211.63951850592377</v>
+        <f t="shared" ref="AY14:AY15" si="75">AX14*1.01</f>
+        <v>-212.42217731296191</v>
       </c>
       <c r="AZ14" s="5">
-        <f t="shared" ref="AZ14:AZ15" si="77">AY14*1.01</f>
-        <v>-213.75591369098302</v>
+        <f t="shared" ref="AZ14:AZ15" si="76">AY14*1.01</f>
+        <v>-214.54639908609153</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" ref="BA14:BA15" si="78">AZ14*1.01</f>
-        <v>-215.89347282789285</v>
+        <f t="shared" ref="BA14:BA15" si="77">AZ14*1.01</f>
+        <v>-216.69186307695244</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" ref="BB14:BB15" si="79">BA14*1.01</f>
-        <v>-218.05240755617177</v>
+        <f t="shared" ref="BB14:BB15" si="78">BA14*1.01</f>
+        <v>-218.85878170772196</v>
       </c>
     </row>
     <row r="15" spans="2:55" x14ac:dyDescent="0.3">
@@ -3417,11 +3413,11 @@
         <v>5.2000000000000011</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="73"/>
-        <v>8.6900000000000013</v>
+        <f>10.4+1.8</f>
+        <v>12.200000000000001</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>22.55</v>
       </c>
       <c r="AK15" s="5">
@@ -3453,47 +3449,47 @@
       </c>
       <c r="AR15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>43.540000000000006</v>
+        <v>47.05</v>
       </c>
       <c r="AS15" s="5">
         <f>AR15*1.01</f>
-        <v>43.975400000000008</v>
+        <v>47.520499999999998</v>
       </c>
       <c r="AT15" s="5">
+        <f t="shared" si="73"/>
+        <v>47.995705000000001</v>
+      </c>
+      <c r="AU15" s="5">
+        <f t="shared" si="73"/>
+        <v>48.475662050000004</v>
+      </c>
+      <c r="AV15" s="5">
+        <f t="shared" si="73"/>
+        <v>48.960418670500005</v>
+      </c>
+      <c r="AW15" s="5">
+        <f t="shared" si="73"/>
+        <v>49.450022857205006</v>
+      </c>
+      <c r="AX15" s="5">
         <f t="shared" si="74"/>
-        <v>44.415154000000008</v>
-      </c>
-      <c r="AU15" s="5">
-        <f t="shared" si="74"/>
-        <v>44.859305540000008</v>
-      </c>
-      <c r="AV15" s="5">
-        <f t="shared" si="74"/>
-        <v>45.307898595400012</v>
-      </c>
-      <c r="AW15" s="5">
-        <f t="shared" si="74"/>
-        <v>45.760977581354013</v>
-      </c>
-      <c r="AX15" s="5">
+        <v>49.944523085777057</v>
+      </c>
+      <c r="AY15" s="5">
         <f t="shared" si="75"/>
-        <v>46.21858735716755</v>
-      </c>
-      <c r="AY15" s="5">
+        <v>50.44396831663483</v>
+      </c>
+      <c r="AZ15" s="5">
         <f t="shared" si="76"/>
-        <v>46.680773230739227</v>
-      </c>
-      <c r="AZ15" s="5">
+        <v>50.948407999801177</v>
+      </c>
+      <c r="BA15" s="5">
         <f t="shared" si="77"/>
-        <v>47.147580963046622</v>
-      </c>
-      <c r="BA15" s="5">
+        <v>51.457892079799187</v>
+      </c>
+      <c r="BB15" s="5">
         <f t="shared" si="78"/>
-        <v>47.619056772677091</v>
-      </c>
-      <c r="BB15" s="5">
-        <f t="shared" si="79"/>
-        <v>48.095247340403866</v>
+        <v>51.972471000597182</v>
       </c>
     </row>
     <row r="16" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3501,132 +3497,132 @@
         <v>28</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:Q16" si="80">C13-C14-C15</f>
+        <f t="shared" ref="C16:Q16" si="79">C13-C14-C15</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="79"/>
+        <v>-23.599999999999987</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="79"/>
+        <v>-39.600000000000009</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="79"/>
+        <v>-10.600000000000003</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="79"/>
+        <v>-8.8999999999999986</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="79"/>
+        <v>-12.199999999999998</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="79"/>
+        <v>-17.3</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="79"/>
+        <v>-32.800000000000011</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="79"/>
+        <v>-74.90000000000002</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="79"/>
+        <v>-75.000000000000028</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="79"/>
+        <v>-50.100000000000023</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="79"/>
+        <v>-64.199999999999989</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="79"/>
+        <v>-135.99999999999997</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="79"/>
+        <v>-142.9</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="79"/>
+        <v>-78.29999999999994</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" ref="R16:S16" si="80">R13-R14-R15</f>
+        <v>-146.70000000000005</v>
+      </c>
+      <c r="S16" s="9">
         <f t="shared" si="80"/>
-        <v>-23.599999999999987</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="80"/>
-        <v>-39.600000000000009</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="80"/>
-        <v>-10.600000000000003</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="80"/>
-        <v>-8.8999999999999986</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="80"/>
-        <v>-12.199999999999998</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="80"/>
-        <v>-17.3</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="80"/>
-        <v>-32.800000000000011</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="80"/>
-        <v>-74.90000000000002</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="80"/>
-        <v>-75.000000000000028</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="80"/>
-        <v>-50.100000000000023</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="80"/>
-        <v>-64.199999999999989</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="80"/>
-        <v>-135.99999999999997</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="80"/>
-        <v>-142.9</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="80"/>
-        <v>-78.29999999999994</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" ref="R16:S16" si="81">R13-R14-R15</f>
-        <v>-146.70000000000005</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="81"/>
         <v>-161.90000000000006</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" ref="T16" si="82">T13-T14-T15</f>
+        <f t="shared" ref="T16" si="81">T13-T14-T15</f>
         <v>-179.09999999999991</v>
       </c>
       <c r="U16" s="9">
-        <f t="shared" ref="U16:V16" si="83">U13-U14-U15</f>
+        <f t="shared" ref="U16:V16" si="82">U13-U14-U15</f>
         <v>-301.59999999999997</v>
       </c>
       <c r="V16" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>-288.2</v>
       </c>
       <c r="W16" s="9">
-        <f t="shared" ref="W16" si="84">W13-W14-W15</f>
+        <f t="shared" ref="W16" si="83">W13-W14-W15</f>
         <v>-269.10000000000008</v>
       </c>
       <c r="X16" s="9">
-        <f t="shared" ref="X16" si="85">X13-X14-X15</f>
+        <f t="shared" ref="X16" si="84">X13-X14-X15</f>
         <v>-285.8</v>
       </c>
       <c r="Y16" s="9">
-        <f t="shared" ref="Y16:Z16" si="86">Y13-Y14-Y15</f>
+        <f t="shared" ref="Y16:Z16" si="85">Y13-Y14-Y15</f>
         <v>-278.29999999999995</v>
       </c>
       <c r="Z16" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>-325.2</v>
       </c>
       <c r="AA16" s="9">
-        <f t="shared" ref="AA16" si="87">AA13-AA14-AA15</f>
+        <f t="shared" ref="AA16" si="86">AA13-AA14-AA15</f>
         <v>-270.80000000000013</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" ref="AB16" si="88">AB13-AB14-AB15</f>
+        <f t="shared" ref="AB16" si="87">AB13-AB14-AB15</f>
         <v>-207.19999999999996</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" ref="AC16:AH16" si="89">AC13-AC14-AC15</f>
+        <f t="shared" ref="AC16:AH16" si="88">AC13-AC14-AC15</f>
         <v>-239.99999999999997</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>-218.2</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>-215.49999999999991</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>-278.89999999999998</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="89"/>
-        <v>-254.80399999999992</v>
+        <f t="shared" si="88"/>
+        <v>-256.70000000000005</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="89"/>
-        <v>-252.49528000000009</v>
+        <f t="shared" si="88"/>
+        <v>-298.08420000000012</v>
       </c>
       <c r="AK16" s="9">
         <f>AK13-AK14-AK15</f>
@@ -3641,64 +3637,64 @@
         <v>-264.19999999999993</v>
       </c>
       <c r="AN16" s="9">
-        <f t="shared" ref="AN16:AW16" si="90">AN13-AN14-AN15</f>
+        <f t="shared" ref="AN16:AW16" si="89">AN13-AN14-AN15</f>
         <v>-503.89999999999986</v>
       </c>
       <c r="AO16" s="9">
+        <f t="shared" si="89"/>
+        <v>-930.80000000000018</v>
+      </c>
+      <c r="AP16" s="9">
+        <f t="shared" si="89"/>
+        <v>-1158.3999999999996</v>
+      </c>
+      <c r="AQ16" s="9">
+        <f t="shared" si="89"/>
+        <v>-936.2</v>
+      </c>
+      <c r="AR16" s="9">
+        <f t="shared" si="89"/>
+        <v>-1049.1842000000001</v>
+      </c>
+      <c r="AS16" s="9">
+        <f t="shared" si="89"/>
+        <v>-604.94837000000041</v>
+      </c>
+      <c r="AT16" s="9">
+        <f t="shared" si="89"/>
+        <v>-210.43511790000184</v>
+      </c>
+      <c r="AU16" s="9">
+        <f t="shared" si="89"/>
+        <v>179.94951473999896</v>
+      </c>
+      <c r="AV16" s="9">
+        <f t="shared" si="89"/>
+        <v>537.1849530431989</v>
+      </c>
+      <c r="AW16" s="9">
+        <f t="shared" si="89"/>
+        <v>847.2370540917708</v>
+      </c>
+      <c r="AX16" s="9">
+        <f t="shared" ref="AX16:BB16" si="90">AX13-AX14-AX15</f>
+        <v>1113.7187661018063</v>
+      </c>
+      <c r="AY16" s="9">
         <f t="shared" si="90"/>
-        <v>-930.80000000000018</v>
-      </c>
-      <c r="AP16" s="9">
+        <v>1353.997785657235</v>
+      </c>
+      <c r="AZ16" s="9">
         <f t="shared" si="90"/>
-        <v>-1158.3999999999996</v>
-      </c>
-      <c r="AQ16" s="9">
+        <v>1560.5971252525437</v>
+      </c>
+      <c r="BA16" s="9">
         <f t="shared" si="90"/>
-        <v>-936.2</v>
-      </c>
-      <c r="AR16" s="9">
+        <v>1779.1383280647894</v>
+      </c>
+      <c r="BB16" s="9">
         <f t="shared" si="90"/>
-        <v>-1001.6992799999995</v>
-      </c>
-      <c r="AS16" s="9">
-        <f t="shared" si="90"/>
-        <v>-668.98237400000016</v>
-      </c>
-      <c r="AT16" s="9">
-        <f t="shared" si="90"/>
-        <v>-311.82932061999998</v>
-      </c>
-      <c r="AU16" s="9">
-        <f t="shared" si="90"/>
-        <v>42.115344723999669</v>
-      </c>
-      <c r="AV16" s="9">
-        <f t="shared" si="90"/>
-        <v>366.32722362908095</v>
-      </c>
-      <c r="AW16" s="9">
-        <f t="shared" si="90"/>
-        <v>648.91423042970951</v>
-      </c>
-      <c r="AX16" s="9">
-        <f t="shared" ref="AX16:BB16" si="91">AX13-AX14-AX15</f>
-        <v>891.18299337792064</v>
-      </c>
-      <c r="AY16" s="9">
-        <f t="shared" si="91"/>
-        <v>1109.3809008841708</v>
-      </c>
-      <c r="AZ16" s="9">
-        <f t="shared" si="91"/>
-        <v>1296.6495655459278</v>
-      </c>
-      <c r="BA16" s="9">
-        <f t="shared" si="91"/>
-        <v>1494.830892117955</v>
-      </c>
-      <c r="BB16" s="9">
-        <f t="shared" si="91"/>
-        <v>1704.4906306321595</v>
+        <v>2010.2390642518744</v>
       </c>
     </row>
     <row r="17" spans="2:167" x14ac:dyDescent="0.3">
@@ -3797,12 +3793,11 @@
         <v>1</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" ref="AG17:AH17" si="92">AG16*0.01</f>
-        <v>-2.5480399999999994</v>
+        <v>0.8</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="92"/>
-        <v>-2.5249528000000008</v>
+        <f t="shared" ref="AG17:AH17" si="91">AH16*0.01</f>
+        <v>-2.9808420000000013</v>
       </c>
       <c r="AK17" s="5">
         <f>SUM(C17:F17)</f>
@@ -3833,7 +3828,7 @@
       </c>
       <c r="AR17" s="5">
         <f>SUM(AE17:AH17)</f>
-        <v>-3.1729928000000003</v>
+        <v>-0.28084200000000115</v>
       </c>
       <c r="AS17" s="5">
         <v>0</v>
@@ -3962,12 +3957,11 @@
         <v>-1.4</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" ref="AG18:AH18" si="93">AG16*0.01</f>
-        <v>-2.5480399999999994</v>
+        <v>-1.7</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="93"/>
-        <v>-2.5249528000000008</v>
+        <f t="shared" ref="AG18:AH18" si="92">AH16*0.01</f>
+        <v>-2.9808420000000013</v>
       </c>
       <c r="AK18" s="5">
         <f>SUM(C18:F18)</f>
@@ -3998,47 +3992,47 @@
       </c>
       <c r="AR18" s="5">
         <f>SUM(AE18:AH18)</f>
-        <v>-7.7729928000000008</v>
+        <v>-7.3808420000000012</v>
       </c>
       <c r="AS18" s="5">
-        <f t="shared" ref="AS18:BB18" si="94">AS16*0.01</f>
-        <v>-6.6898237400000014</v>
+        <f t="shared" ref="AS18:BB18" si="93">AS16*0.01</f>
+        <v>-6.0494837000000041</v>
       </c>
       <c r="AT18" s="5">
-        <f t="shared" si="94"/>
-        <v>-3.1182932061999997</v>
+        <f t="shared" si="93"/>
+        <v>-2.1043511790000187</v>
       </c>
       <c r="AU18" s="5">
-        <f t="shared" si="94"/>
-        <v>0.4211534472399967</v>
+        <f t="shared" si="93"/>
+        <v>1.7994951473999896</v>
       </c>
       <c r="AV18" s="5">
-        <f t="shared" si="94"/>
-        <v>3.6632722362908097</v>
+        <f t="shared" si="93"/>
+        <v>5.3718495304319891</v>
       </c>
       <c r="AW18" s="5">
-        <f t="shared" si="94"/>
-        <v>6.4891423042970953</v>
+        <f t="shared" si="93"/>
+        <v>8.4723705409177086</v>
       </c>
       <c r="AX18" s="5">
-        <f t="shared" si="94"/>
-        <v>8.911829933779206</v>
+        <f t="shared" si="93"/>
+        <v>11.137187661018062</v>
       </c>
       <c r="AY18" s="5">
-        <f t="shared" si="94"/>
-        <v>11.093809008841708</v>
+        <f t="shared" si="93"/>
+        <v>13.539977856572349</v>
       </c>
       <c r="AZ18" s="5">
-        <f t="shared" si="94"/>
-        <v>12.966495655459278</v>
+        <f t="shared" si="93"/>
+        <v>15.605971252525437</v>
       </c>
       <c r="BA18" s="5">
-        <f t="shared" si="94"/>
-        <v>14.948308921179551</v>
+        <f t="shared" si="93"/>
+        <v>17.791383280647896</v>
       </c>
       <c r="BB18" s="5">
-        <f t="shared" si="94"/>
-        <v>17.044906306321597</v>
+        <f t="shared" si="93"/>
+        <v>20.102390642518746</v>
       </c>
     </row>
     <row r="19" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4046,132 +4040,132 @@
         <v>31</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:N19" si="95">C16-C17-C18</f>
+        <f t="shared" ref="C19:N19" si="94">C16-C17-C18</f>
         <v>-14.400000000000006</v>
       </c>
       <c r="D19" s="9">
+        <f t="shared" si="94"/>
+        <v>-23.599999999999987</v>
+      </c>
+      <c r="E19" s="9">
+        <f t="shared" si="94"/>
+        <v>-39.600000000000009</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="94"/>
+        <v>-10.600000000000003</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="94"/>
+        <v>-8.8999999999999986</v>
+      </c>
+      <c r="H19" s="9">
+        <f t="shared" si="94"/>
+        <v>-12.199999999999998</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="94"/>
+        <v>-17.400000000000002</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="94"/>
+        <v>-32.600000000000009</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="94"/>
+        <v>-74.40000000000002</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="94"/>
+        <v>-74.300000000000026</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="94"/>
+        <v>-48.700000000000024</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="94"/>
+        <v>-55.699999999999989</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" ref="O19:Q19" si="95">O16-O17-O18</f>
+        <v>-134.09999999999997</v>
+      </c>
+      <c r="P19" s="9">
         <f t="shared" si="95"/>
-        <v>-23.599999999999987</v>
-      </c>
-      <c r="E19" s="9">
+        <v>-140.1</v>
+      </c>
+      <c r="Q19" s="9">
         <f t="shared" si="95"/>
-        <v>-39.600000000000009</v>
-      </c>
-      <c r="F19" s="9">
-        <f t="shared" si="95"/>
-        <v>-10.600000000000003</v>
-      </c>
-      <c r="G19" s="9">
-        <f t="shared" si="95"/>
-        <v>-8.8999999999999986</v>
-      </c>
-      <c r="H19" s="9">
-        <f t="shared" si="95"/>
-        <v>-12.199999999999998</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="95"/>
-        <v>-17.400000000000002</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="95"/>
-        <v>-32.600000000000009</v>
-      </c>
-      <c r="K19" s="9">
-        <f t="shared" si="95"/>
-        <v>-74.40000000000002</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="95"/>
-        <v>-74.300000000000026</v>
-      </c>
-      <c r="M19" s="9">
-        <f t="shared" si="95"/>
-        <v>-48.700000000000024</v>
-      </c>
-      <c r="N19" s="9">
-        <f t="shared" si="95"/>
-        <v>-55.699999999999989</v>
-      </c>
-      <c r="O19" s="9">
-        <f t="shared" ref="O19:Q19" si="96">O16-O17-O18</f>
-        <v>-134.09999999999997</v>
-      </c>
-      <c r="P19" s="9">
+        <v>-74.099999999999937</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" ref="R19:S19" si="96">R16-R17-R18</f>
+        <v>-143.40000000000003</v>
+      </c>
+      <c r="S19" s="9">
         <f t="shared" si="96"/>
-        <v>-140.1</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="96"/>
-        <v>-74.099999999999937</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" ref="R19:S19" si="97">R16-R17-R18</f>
-        <v>-143.40000000000003</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" si="97"/>
         <v>-160.40000000000006</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" ref="T19" si="98">T16-T17-T18</f>
+        <f t="shared" ref="T19" si="97">T16-T17-T18</f>
         <v>-176.49999999999989</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19:V19" si="99">U16-U17-U18</f>
+        <f t="shared" ref="U19:V19" si="98">U16-U17-U18</f>
         <v>-297.89999999999992</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="98"/>
         <v>-289.79999999999995</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19" si="100">W16-W17-W18</f>
+        <f t="shared" ref="W19" si="99">W16-W17-W18</f>
         <v>-268.20000000000005</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19" si="101">X16-X17-X18</f>
+        <f t="shared" ref="X19" si="100">X16-X17-X18</f>
         <v>-282.5</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19:Z19" si="102">Y16-Y17-Y18</f>
+        <f t="shared" ref="Y19:Z19" si="101">Y16-Y17-Y18</f>
         <v>-277.29999999999995</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>-323.89999999999998</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" ref="AA19" si="103">AA16-AA17-AA18</f>
+        <f t="shared" ref="AA19" si="102">AA16-AA17-AA18</f>
         <v>-270.60000000000014</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="104">AB16-AB17-AB18</f>
+        <f t="shared" ref="AB19" si="103">AB16-AB17-AB18</f>
         <v>-205.99999999999994</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" ref="AC19:AD19" si="105">AC16-AC17-AC18</f>
+        <f t="shared" ref="AC19:AD19" si="104">AC16-AC17-AC18</f>
         <v>-239.2</v>
       </c>
       <c r="AD19" s="9">
+        <f t="shared" si="104"/>
+        <v>-219.29999999999998</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" ref="AE19:AH19" si="105">AE16-AE17-AE18</f>
+        <v>-215.09999999999991</v>
+      </c>
+      <c r="AF19" s="9">
         <f t="shared" si="105"/>
-        <v>-219.29999999999998</v>
-      </c>
-      <c r="AE19" s="9">
-        <f t="shared" ref="AE19:AH19" si="106">AE16-AE17-AE18</f>
-        <v>-215.09999999999991</v>
-      </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="106"/>
         <v>-278.5</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="106"/>
-        <v>-249.70791999999994</v>
+        <f t="shared" si="105"/>
+        <v>-255.80000000000007</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="106"/>
-        <v>-247.44537440000011</v>
+        <f t="shared" si="105"/>
+        <v>-292.12251600000013</v>
       </c>
       <c r="AK19" s="9">
         <f>AK16-AK17-AK18</f>
@@ -4186,516 +4180,516 @@
         <v>-253.09999999999994</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19:AW19" si="107">AN16-AN17-AN18</f>
+        <f t="shared" ref="AN19:AW19" si="106">AN16-AN17-AN18</f>
         <v>-491.69999999999987</v>
       </c>
       <c r="AO19" s="9">
+        <f t="shared" si="106"/>
+        <v>-924.60000000000025</v>
+      </c>
+      <c r="AP19" s="9">
+        <f t="shared" si="106"/>
+        <v>-1151.8999999999996</v>
+      </c>
+      <c r="AQ19" s="9">
+        <f t="shared" si="106"/>
+        <v>-935.1</v>
+      </c>
+      <c r="AR19" s="9">
+        <f t="shared" si="106"/>
+        <v>-1041.5225160000002</v>
+      </c>
+      <c r="AS19" s="9">
+        <f t="shared" si="106"/>
+        <v>-598.89888630000041</v>
+      </c>
+      <c r="AT19" s="9">
+        <f t="shared" si="106"/>
+        <v>-208.33076672100182</v>
+      </c>
+      <c r="AU19" s="9">
+        <f t="shared" si="106"/>
+        <v>178.15001959259897</v>
+      </c>
+      <c r="AV19" s="9">
+        <f t="shared" si="106"/>
+        <v>531.81310351276693</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" si="106"/>
+        <v>838.76468355085308</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" ref="AX19:BB19" si="107">AX16-AX17-AX18</f>
+        <v>1102.5815784407882</v>
+      </c>
+      <c r="AY19" s="9">
         <f t="shared" si="107"/>
-        <v>-924.60000000000025</v>
-      </c>
-      <c r="AP19" s="9">
+        <v>1340.4578078006627</v>
+      </c>
+      <c r="AZ19" s="9">
         <f t="shared" si="107"/>
-        <v>-1151.8999999999996</v>
-      </c>
-      <c r="AQ19" s="9">
+        <v>1544.9911540000182</v>
+      </c>
+      <c r="BA19" s="9">
         <f t="shared" si="107"/>
-        <v>-935.1</v>
-      </c>
-      <c r="AR19" s="9">
+        <v>1761.3469447841414</v>
+      </c>
+      <c r="BB19" s="9">
         <f t="shared" si="107"/>
-        <v>-990.7532943999995</v>
-      </c>
-      <c r="AS19" s="9">
-        <f t="shared" si="107"/>
-        <v>-662.29255026000021</v>
-      </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="107"/>
-        <v>-308.71102741379997</v>
-      </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="107"/>
-        <v>41.694191276759675</v>
-      </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="107"/>
-        <v>362.66395139279012</v>
-      </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="107"/>
-        <v>642.42508812541246</v>
-      </c>
-      <c r="AX19" s="9">
-        <f t="shared" ref="AX19:BB19" si="108">AX16-AX17-AX18</f>
-        <v>882.27116344414139</v>
-      </c>
-      <c r="AY19" s="9">
-        <f t="shared" si="108"/>
-        <v>1098.2870918753292</v>
-      </c>
-      <c r="AZ19" s="9">
-        <f t="shared" si="108"/>
-        <v>1283.6830698904685</v>
-      </c>
-      <c r="BA19" s="9">
-        <f t="shared" si="108"/>
-        <v>1479.8825831967754</v>
-      </c>
-      <c r="BB19" s="9">
-        <f t="shared" si="108"/>
-        <v>1687.445724325838</v>
+        <v>1990.1366736093557</v>
       </c>
       <c r="BC19" s="1">
         <f>BB19*(1+$BE$26)</f>
-        <v>1670.5712670825797</v>
+        <v>1970.2353068732621</v>
       </c>
       <c r="BD19" s="1">
-        <f t="shared" ref="BD19:DO19" si="109">BC19*(1+$BE$26)</f>
-        <v>1653.8655544117539</v>
+        <f t="shared" ref="BD19:DO19" si="108">BC19*(1+$BE$26)</f>
+        <v>1950.5329538045294</v>
       </c>
       <c r="BE19" s="1">
+        <f t="shared" si="108"/>
+        <v>1931.0276242664841</v>
+      </c>
+      <c r="BF19" s="1">
+        <f t="shared" si="108"/>
+        <v>1911.7173480238191</v>
+      </c>
+      <c r="BG19" s="1">
+        <f t="shared" si="108"/>
+        <v>1892.6001745435808</v>
+      </c>
+      <c r="BH19" s="1">
+        <f t="shared" si="108"/>
+        <v>1873.674172798145</v>
+      </c>
+      <c r="BI19" s="1">
+        <f t="shared" si="108"/>
+        <v>1854.9374310701635</v>
+      </c>
+      <c r="BJ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1836.3880567594617</v>
+      </c>
+      <c r="BK19" s="1">
+        <f t="shared" si="108"/>
+        <v>1818.0241761918671</v>
+      </c>
+      <c r="BL19" s="1">
+        <f t="shared" si="108"/>
+        <v>1799.8439344299484</v>
+      </c>
+      <c r="BM19" s="1">
+        <f t="shared" si="108"/>
+        <v>1781.845495085649</v>
+      </c>
+      <c r="BN19" s="1">
+        <f t="shared" si="108"/>
+        <v>1764.0270401347925</v>
+      </c>
+      <c r="BO19" s="1">
+        <f t="shared" si="108"/>
+        <v>1746.3867697334447</v>
+      </c>
+      <c r="BP19" s="1">
+        <f t="shared" si="108"/>
+        <v>1728.9229020361101</v>
+      </c>
+      <c r="BQ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1711.6336730157491</v>
+      </c>
+      <c r="BR19" s="1">
+        <f t="shared" si="108"/>
+        <v>1694.5173362855917</v>
+      </c>
+      <c r="BS19" s="1">
+        <f t="shared" si="108"/>
+        <v>1677.5721629227357</v>
+      </c>
+      <c r="BT19" s="1">
+        <f t="shared" si="108"/>
+        <v>1660.7964412935085</v>
+      </c>
+      <c r="BU19" s="1">
+        <f t="shared" si="108"/>
+        <v>1644.1884768805733</v>
+      </c>
+      <c r="BV19" s="1">
+        <f t="shared" si="108"/>
+        <v>1627.7465921117675</v>
+      </c>
+      <c r="BW19" s="1">
+        <f t="shared" si="108"/>
+        <v>1611.4691261906498</v>
+      </c>
+      <c r="BX19" s="1">
+        <f t="shared" si="108"/>
+        <v>1595.3544349287433</v>
+      </c>
+      <c r="BY19" s="1">
+        <f t="shared" si="108"/>
+        <v>1579.4008905794558</v>
+      </c>
+      <c r="BZ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1563.6068816736613</v>
+      </c>
+      <c r="CA19" s="1">
+        <f t="shared" si="108"/>
+        <v>1547.9708128569246</v>
+      </c>
+      <c r="CB19" s="1">
+        <f t="shared" si="108"/>
+        <v>1532.4911047283554</v>
+      </c>
+      <c r="CC19" s="1">
+        <f t="shared" si="108"/>
+        <v>1517.1661936810717</v>
+      </c>
+      <c r="CD19" s="1">
+        <f t="shared" si="108"/>
+        <v>1501.9945317442609</v>
+      </c>
+      <c r="CE19" s="1">
+        <f t="shared" si="108"/>
+        <v>1486.9745864268184</v>
+      </c>
+      <c r="CF19" s="1">
+        <f t="shared" si="108"/>
+        <v>1472.1048405625502</v>
+      </c>
+      <c r="CG19" s="1">
+        <f t="shared" si="108"/>
+        <v>1457.3837921569248</v>
+      </c>
+      <c r="CH19" s="1">
+        <f t="shared" si="108"/>
+        <v>1442.8099542353555</v>
+      </c>
+      <c r="CI19" s="1">
+        <f t="shared" si="108"/>
+        <v>1428.381854693002</v>
+      </c>
+      <c r="CJ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1414.098036146072</v>
+      </c>
+      <c r="CK19" s="1">
+        <f t="shared" si="108"/>
+        <v>1399.9570557846112</v>
+      </c>
+      <c r="CL19" s="1">
+        <f t="shared" si="108"/>
+        <v>1385.9574852267651</v>
+      </c>
+      <c r="CM19" s="1">
+        <f t="shared" si="108"/>
+        <v>1372.0979103744974</v>
+      </c>
+      <c r="CN19" s="1">
+        <f t="shared" si="108"/>
+        <v>1358.3769312707523</v>
+      </c>
+      <c r="CO19" s="1">
+        <f t="shared" si="108"/>
+        <v>1344.7931619580447</v>
+      </c>
+      <c r="CP19" s="1">
+        <f t="shared" si="108"/>
+        <v>1331.3452303384643</v>
+      </c>
+      <c r="CQ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1318.0317780350797</v>
+      </c>
+      <c r="CR19" s="1">
+        <f t="shared" si="108"/>
+        <v>1304.8514602547289</v>
+      </c>
+      <c r="CS19" s="1">
+        <f t="shared" si="108"/>
+        <v>1291.8029456521815</v>
+      </c>
+      <c r="CT19" s="1">
+        <f t="shared" si="108"/>
+        <v>1278.8849161956596</v>
+      </c>
+      <c r="CU19" s="1">
+        <f t="shared" si="108"/>
+        <v>1266.0960670337029</v>
+      </c>
+      <c r="CV19" s="1">
+        <f t="shared" si="108"/>
+        <v>1253.4351063633658</v>
+      </c>
+      <c r="CW19" s="1">
+        <f t="shared" si="108"/>
+        <v>1240.9007552997321</v>
+      </c>
+      <c r="CX19" s="1">
+        <f t="shared" si="108"/>
+        <v>1228.4917477467347</v>
+      </c>
+      <c r="CY19" s="1">
+        <f t="shared" si="108"/>
+        <v>1216.2068302692674</v>
+      </c>
+      <c r="CZ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1204.0447619665747</v>
+      </c>
+      <c r="DA19" s="1">
+        <f t="shared" si="108"/>
+        <v>1192.004314346909</v>
+      </c>
+      <c r="DB19" s="1">
+        <f t="shared" si="108"/>
+        <v>1180.08427120344</v>
+      </c>
+      <c r="DC19" s="1">
+        <f t="shared" si="108"/>
+        <v>1168.2834284914056</v>
+      </c>
+      <c r="DD19" s="1">
+        <f t="shared" si="108"/>
+        <v>1156.6005942064915</v>
+      </c>
+      <c r="DE19" s="1">
+        <f t="shared" si="108"/>
+        <v>1145.0345882644265</v>
+      </c>
+      <c r="DF19" s="1">
+        <f t="shared" si="108"/>
+        <v>1133.5842423817821</v>
+      </c>
+      <c r="DG19" s="1">
+        <f t="shared" si="108"/>
+        <v>1122.2483999579642</v>
+      </c>
+      <c r="DH19" s="1">
+        <f t="shared" si="108"/>
+        <v>1111.0259159583845</v>
+      </c>
+      <c r="DI19" s="1">
+        <f t="shared" si="108"/>
+        <v>1099.9156567988007</v>
+      </c>
+      <c r="DJ19" s="1">
+        <f t="shared" si="108"/>
+        <v>1088.9165002308127</v>
+      </c>
+      <c r="DK19" s="1">
+        <f t="shared" si="108"/>
+        <v>1078.0273352285046</v>
+      </c>
+      <c r="DL19" s="1">
+        <f t="shared" si="108"/>
+        <v>1067.2470618762195</v>
+      </c>
+      <c r="DM19" s="1">
+        <f t="shared" si="108"/>
+        <v>1056.5745912574573</v>
+      </c>
+      <c r="DN19" s="1">
+        <f t="shared" si="108"/>
+        <v>1046.0088453448827</v>
+      </c>
+      <c r="DO19" s="1">
+        <f t="shared" si="108"/>
+        <v>1035.5487568914339</v>
+      </c>
+      <c r="DP19" s="1">
+        <f t="shared" ref="DP19:FK19" si="109">DO19*(1+$BE$26)</f>
+        <v>1025.1932693225194</v>
+      </c>
+      <c r="DQ19" s="1">
         <f t="shared" si="109"/>
-        <v>1637.3268988676364</v>
-      </c>
-      <c r="BF19" s="1">
+        <v>1014.9413366292943</v>
+      </c>
+      <c r="DR19" s="1">
         <f t="shared" si="109"/>
-        <v>1620.9536298789601</v>
-      </c>
-      <c r="BG19" s="1">
+        <v>1004.7919232630013</v>
+      </c>
+      <c r="DS19" s="1">
         <f t="shared" si="109"/>
-        <v>1604.7440935801706</v>
-      </c>
-      <c r="BH19" s="1">
+        <v>994.74400403037134</v>
+      </c>
+      <c r="DT19" s="1">
         <f t="shared" si="109"/>
-        <v>1588.6966526443689</v>
-      </c>
-      <c r="BI19" s="1">
+        <v>984.79656399006763</v>
+      </c>
+      <c r="DU19" s="1">
         <f t="shared" si="109"/>
-        <v>1572.8096861179251</v>
-      </c>
-      <c r="BJ19" s="1">
+        <v>974.94859835016689</v>
+      </c>
+      <c r="DV19" s="1">
         <f t="shared" si="109"/>
-        <v>1557.0815892567459</v>
-      </c>
-      <c r="BK19" s="1">
+        <v>965.19911236666519</v>
+      </c>
+      <c r="DW19" s="1">
         <f t="shared" si="109"/>
-        <v>1541.5107733641785</v>
-      </c>
-      <c r="BL19" s="1">
+        <v>955.54712124299851</v>
+      </c>
+      <c r="DX19" s="1">
         <f t="shared" si="109"/>
-        <v>1526.0956656305366</v>
-      </c>
-      <c r="BM19" s="1">
+        <v>945.99165003056851</v>
+      </c>
+      <c r="DY19" s="1">
         <f t="shared" si="109"/>
-        <v>1510.8347089742313</v>
-      </c>
-      <c r="BN19" s="1">
+        <v>936.53173353026284</v>
+      </c>
+      <c r="DZ19" s="1">
         <f t="shared" si="109"/>
-        <v>1495.7263618844888</v>
-      </c>
-      <c r="BO19" s="1">
+        <v>927.16641619496022</v>
+      </c>
+      <c r="EA19" s="1">
         <f t="shared" si="109"/>
-        <v>1480.7690982656438</v>
-      </c>
-      <c r="BP19" s="1">
+        <v>917.8947520330106</v>
+      </c>
+      <c r="EB19" s="1">
         <f t="shared" si="109"/>
-        <v>1465.9614072829875</v>
-      </c>
-      <c r="BQ19" s="1">
+        <v>908.71580451268051</v>
+      </c>
+      <c r="EC19" s="1">
         <f t="shared" si="109"/>
-        <v>1451.3017932101575</v>
-      </c>
-      <c r="BR19" s="1">
+        <v>899.62864646755372</v>
+      </c>
+      <c r="ED19" s="1">
         <f t="shared" si="109"/>
-        <v>1436.7887752780559</v>
-      </c>
-      <c r="BS19" s="1">
+        <v>890.63236000287816</v>
+      </c>
+      <c r="EE19" s="1">
         <f t="shared" si="109"/>
-        <v>1422.4208875252755</v>
-      </c>
-      <c r="BT19" s="1">
+        <v>881.72603640284933</v>
+      </c>
+      <c r="EF19" s="1">
         <f t="shared" si="109"/>
-        <v>1408.1966786500227</v>
-      </c>
-      <c r="BU19" s="1">
+        <v>872.90877603882086</v>
+      </c>
+      <c r="EG19" s="1">
         <f t="shared" si="109"/>
-        <v>1394.1147118635224</v>
-      </c>
-      <c r="BV19" s="1">
+        <v>864.17968827843265</v>
+      </c>
+      <c r="EH19" s="1">
         <f t="shared" si="109"/>
-        <v>1380.1735647448872</v>
-      </c>
-      <c r="BW19" s="1">
+        <v>855.53789139564833</v>
+      </c>
+      <c r="EI19" s="1">
         <f t="shared" si="109"/>
-        <v>1366.3718290974384</v>
-      </c>
-      <c r="BX19" s="1">
+        <v>846.98251248169186</v>
+      </c>
+      <c r="EJ19" s="1">
         <f t="shared" si="109"/>
-        <v>1352.708110806464</v>
-      </c>
-      <c r="BY19" s="1">
+        <v>838.51268735687495</v>
+      </c>
+      <c r="EK19" s="1">
         <f t="shared" si="109"/>
-        <v>1339.1810296983992</v>
-      </c>
-      <c r="BZ19" s="1">
+        <v>830.12756048330618</v>
+      </c>
+      <c r="EL19" s="1">
         <f t="shared" si="109"/>
-        <v>1325.7892194014153</v>
-      </c>
-      <c r="CA19" s="1">
+        <v>821.82628487847307</v>
+      </c>
+      <c r="EM19" s="1">
         <f t="shared" si="109"/>
-        <v>1312.5313272074011</v>
-      </c>
-      <c r="CB19" s="1">
+        <v>813.6080220296883</v>
+      </c>
+      <c r="EN19" s="1">
         <f t="shared" si="109"/>
-        <v>1299.4060139353271</v>
-      </c>
-      <c r="CC19" s="1">
+        <v>805.47194180939141</v>
+      </c>
+      <c r="EO19" s="1">
         <f t="shared" si="109"/>
-        <v>1286.4119537959739</v>
-      </c>
-      <c r="CD19" s="1">
+        <v>797.41722239129751</v>
+      </c>
+      <c r="EP19" s="1">
         <f t="shared" si="109"/>
-        <v>1273.5478342580141</v>
-      </c>
-      <c r="CE19" s="1">
+        <v>789.44305016738451</v>
+      </c>
+      <c r="EQ19" s="1">
         <f t="shared" si="109"/>
-        <v>1260.812355915434</v>
-      </c>
-      <c r="CF19" s="1">
+        <v>781.5486196657107</v>
+      </c>
+      <c r="ER19" s="1">
         <f t="shared" si="109"/>
-        <v>1248.2042323562796</v>
-      </c>
-      <c r="CG19" s="1">
+        <v>773.73313346905354</v>
+      </c>
+      <c r="ES19" s="1">
         <f t="shared" si="109"/>
-        <v>1235.7221900327168</v>
-      </c>
-      <c r="CH19" s="1">
+        <v>765.99580213436298</v>
+      </c>
+      <c r="ET19" s="1">
         <f t="shared" si="109"/>
-        <v>1223.3649681323895</v>
-      </c>
-      <c r="CI19" s="1">
+        <v>758.33584411301933</v>
+      </c>
+      <c r="EU19" s="1">
         <f t="shared" si="109"/>
-        <v>1211.1313184510657</v>
-      </c>
-      <c r="CJ19" s="1">
+        <v>750.75248567188919</v>
+      </c>
+      <c r="EV19" s="1">
         <f t="shared" si="109"/>
-        <v>1199.020005266555</v>
-      </c>
-      <c r="CK19" s="1">
+        <v>743.24496081517032</v>
+      </c>
+      <c r="EW19" s="1">
         <f t="shared" si="109"/>
-        <v>1187.0298052138894</v>
-      </c>
-      <c r="CL19" s="1">
+        <v>735.81251120701859</v>
+      </c>
+      <c r="EX19" s="1">
         <f t="shared" si="109"/>
-        <v>1175.1595071617505</v>
-      </c>
-      <c r="CM19" s="1">
+        <v>728.4543860949484</v>
+      </c>
+      <c r="EY19" s="1">
         <f t="shared" si="109"/>
-        <v>1163.4079120901331</v>
-      </c>
-      <c r="CN19" s="1">
+        <v>721.16984223399891</v>
+      </c>
+      <c r="EZ19" s="1">
         <f t="shared" si="109"/>
-        <v>1151.7738329692318</v>
-      </c>
-      <c r="CO19" s="1">
+        <v>713.95814381165894</v>
+      </c>
+      <c r="FA19" s="1">
         <f t="shared" si="109"/>
-        <v>1140.2560946395395</v>
-      </c>
-      <c r="CP19" s="1">
+        <v>706.81856237354236</v>
+      </c>
+      <c r="FB19" s="1">
         <f t="shared" si="109"/>
-        <v>1128.8535336931441</v>
-      </c>
-      <c r="CQ19" s="1">
+        <v>699.75037674980695</v>
+      </c>
+      <c r="FC19" s="1">
         <f t="shared" si="109"/>
-        <v>1117.5649983562125</v>
-      </c>
-      <c r="CR19" s="1">
+        <v>692.75287298230887</v>
+      </c>
+      <c r="FD19" s="1">
         <f t="shared" si="109"/>
-        <v>1106.3893483726504</v>
-      </c>
-      <c r="CS19" s="1">
+        <v>685.82534425248582</v>
+      </c>
+      <c r="FE19" s="1">
         <f t="shared" si="109"/>
-        <v>1095.3254548889238</v>
-      </c>
-      <c r="CT19" s="1">
+        <v>678.96709080996095</v>
+      </c>
+      <c r="FF19" s="1">
         <f t="shared" si="109"/>
-        <v>1084.3722003400346</v>
-      </c>
-      <c r="CU19" s="1">
+        <v>672.1774199018613</v>
+      </c>
+      <c r="FG19" s="1">
         <f t="shared" si="109"/>
-        <v>1073.5284783366342</v>
-      </c>
-      <c r="CV19" s="1">
+        <v>665.45564570284273</v>
+      </c>
+      <c r="FH19" s="1">
         <f t="shared" si="109"/>
-        <v>1062.7931935532679</v>
-      </c>
-      <c r="CW19" s="1">
+        <v>658.8010892458143</v>
+      </c>
+      <c r="FI19" s="1">
         <f t="shared" si="109"/>
-        <v>1052.1652616177353</v>
-      </c>
-      <c r="CX19" s="1">
+        <v>652.2130783533562</v>
+      </c>
+      <c r="FJ19" s="1">
         <f t="shared" si="109"/>
-        <v>1041.6436090015579</v>
-      </c>
-      <c r="CY19" s="1">
+        <v>645.69094756982258</v>
+      </c>
+      <c r="FK19" s="1">
         <f t="shared" si="109"/>
-        <v>1031.2271729115423</v>
-      </c>
-      <c r="CZ19" s="1">
-        <f t="shared" si="109"/>
-        <v>1020.9149011824269</v>
-      </c>
-      <c r="DA19" s="1">
-        <f t="shared" si="109"/>
-        <v>1010.7057521706026</v>
-      </c>
-      <c r="DB19" s="1">
-        <f t="shared" si="109"/>
-        <v>1000.5986946488966</v>
-      </c>
-      <c r="DC19" s="1">
-        <f t="shared" si="109"/>
-        <v>990.59270770240767</v>
-      </c>
-      <c r="DD19" s="1">
-        <f t="shared" si="109"/>
-        <v>980.68678062538356</v>
-      </c>
-      <c r="DE19" s="1">
-        <f t="shared" si="109"/>
-        <v>970.87991281912969</v>
-      </c>
-      <c r="DF19" s="1">
-        <f t="shared" si="109"/>
-        <v>961.17111369093834</v>
-      </c>
-      <c r="DG19" s="1">
-        <f t="shared" si="109"/>
-        <v>951.55940255402891</v>
-      </c>
-      <c r="DH19" s="1">
-        <f t="shared" si="109"/>
-        <v>942.04380852848863</v>
-      </c>
-      <c r="DI19" s="1">
-        <f t="shared" si="109"/>
-        <v>932.62337044320373</v>
-      </c>
-      <c r="DJ19" s="1">
-        <f t="shared" si="109"/>
-        <v>923.29713673877166</v>
-      </c>
-      <c r="DK19" s="1">
-        <f t="shared" si="109"/>
-        <v>914.06416537138398</v>
-      </c>
-      <c r="DL19" s="1">
-        <f t="shared" si="109"/>
-        <v>904.92352371767015</v>
-      </c>
-      <c r="DM19" s="1">
-        <f t="shared" si="109"/>
-        <v>895.87428848049342</v>
-      </c>
-      <c r="DN19" s="1">
-        <f t="shared" si="109"/>
-        <v>886.91554559568851</v>
-      </c>
-      <c r="DO19" s="1">
-        <f t="shared" si="109"/>
-        <v>878.04639013973167</v>
-      </c>
-      <c r="DP19" s="1">
-        <f t="shared" ref="DP19:FK19" si="110">DO19*(1+$BE$26)</f>
-        <v>869.26592623833437</v>
-      </c>
-      <c r="DQ19" s="1">
-        <f t="shared" si="110"/>
-        <v>860.57326697595101</v>
-      </c>
-      <c r="DR19" s="1">
-        <f t="shared" si="110"/>
-        <v>851.96753430619151</v>
-      </c>
-      <c r="DS19" s="1">
-        <f t="shared" si="110"/>
-        <v>843.44785896312953</v>
-      </c>
-      <c r="DT19" s="1">
-        <f t="shared" si="110"/>
-        <v>835.01338037349819</v>
-      </c>
-      <c r="DU19" s="1">
-        <f t="shared" si="110"/>
-        <v>826.66324656976326</v>
-      </c>
-      <c r="DV19" s="1">
-        <f t="shared" si="110"/>
-        <v>818.39661410406563</v>
-      </c>
-      <c r="DW19" s="1">
-        <f t="shared" si="110"/>
-        <v>810.21264796302501</v>
-      </c>
-      <c r="DX19" s="1">
-        <f t="shared" si="110"/>
-        <v>802.11052148339479</v>
-      </c>
-      <c r="DY19" s="1">
-        <f t="shared" si="110"/>
-        <v>794.08941626856085</v>
-      </c>
-      <c r="DZ19" s="1">
-        <f t="shared" si="110"/>
-        <v>786.14852210587526</v>
-      </c>
-      <c r="EA19" s="1">
-        <f t="shared" si="110"/>
-        <v>778.28703688481653</v>
-      </c>
-      <c r="EB19" s="1">
-        <f t="shared" si="110"/>
-        <v>770.50416651596834</v>
-      </c>
-      <c r="EC19" s="1">
-        <f t="shared" si="110"/>
-        <v>762.79912485080865</v>
-      </c>
-      <c r="ED19" s="1">
-        <f t="shared" si="110"/>
-        <v>755.17113360230053</v>
-      </c>
-      <c r="EE19" s="1">
-        <f t="shared" si="110"/>
-        <v>747.61942226627752</v>
-      </c>
-      <c r="EF19" s="1">
-        <f t="shared" si="110"/>
-        <v>740.14322804361473</v>
-      </c>
-      <c r="EG19" s="1">
-        <f t="shared" si="110"/>
-        <v>732.74179576317863</v>
-      </c>
-      <c r="EH19" s="1">
-        <f t="shared" si="110"/>
-        <v>725.41437780554679</v>
-      </c>
-      <c r="EI19" s="1">
-        <f t="shared" si="110"/>
-        <v>718.16023402749136</v>
-      </c>
-      <c r="EJ19" s="1">
-        <f t="shared" si="110"/>
-        <v>710.97863168721642</v>
-      </c>
-      <c r="EK19" s="1">
-        <f t="shared" si="110"/>
-        <v>703.86884537034427</v>
-      </c>
-      <c r="EL19" s="1">
-        <f t="shared" si="110"/>
-        <v>696.83015691664082</v>
-      </c>
-      <c r="EM19" s="1">
-        <f t="shared" si="110"/>
-        <v>689.86185534747437</v>
-      </c>
-      <c r="EN19" s="1">
-        <f t="shared" si="110"/>
-        <v>682.96323679399961</v>
-      </c>
-      <c r="EO19" s="1">
-        <f t="shared" si="110"/>
-        <v>676.13360442605961</v>
-      </c>
-      <c r="EP19" s="1">
-        <f t="shared" si="110"/>
-        <v>669.37226838179902</v>
-      </c>
-      <c r="EQ19" s="1">
-        <f t="shared" si="110"/>
-        <v>662.67854569798101</v>
-      </c>
-      <c r="ER19" s="1">
-        <f t="shared" si="110"/>
-        <v>656.05176024100115</v>
-      </c>
-      <c r="ES19" s="1">
-        <f t="shared" si="110"/>
-        <v>649.49124263859107</v>
-      </c>
-      <c r="ET19" s="1">
-        <f t="shared" si="110"/>
-        <v>642.99633021220518</v>
-      </c>
-      <c r="EU19" s="1">
-        <f t="shared" si="110"/>
-        <v>636.56636691008316</v>
-      </c>
-      <c r="EV19" s="1">
-        <f t="shared" si="110"/>
-        <v>630.20070324098231</v>
-      </c>
-      <c r="EW19" s="1">
-        <f t="shared" si="110"/>
-        <v>623.89869620857246</v>
-      </c>
-      <c r="EX19" s="1">
-        <f t="shared" si="110"/>
-        <v>617.65970924648673</v>
-      </c>
-      <c r="EY19" s="1">
-        <f t="shared" si="110"/>
-        <v>611.48311215402191</v>
-      </c>
-      <c r="EZ19" s="1">
-        <f t="shared" si="110"/>
-        <v>605.36828103248172</v>
-      </c>
-      <c r="FA19" s="1">
-        <f t="shared" si="110"/>
-        <v>599.31459822215686</v>
-      </c>
-      <c r="FB19" s="1">
-        <f t="shared" si="110"/>
-        <v>593.3214522399353</v>
-      </c>
-      <c r="FC19" s="1">
-        <f t="shared" si="110"/>
-        <v>587.38823771753596</v>
-      </c>
-      <c r="FD19" s="1">
-        <f t="shared" si="110"/>
-        <v>581.51435534036057</v>
-      </c>
-      <c r="FE19" s="1">
-        <f t="shared" si="110"/>
-        <v>575.69921178695699</v>
-      </c>
-      <c r="FF19" s="1">
-        <f t="shared" si="110"/>
-        <v>569.94221966908742</v>
-      </c>
-      <c r="FG19" s="1">
-        <f t="shared" si="110"/>
-        <v>564.24279747239655</v>
-      </c>
-      <c r="FH19" s="1">
-        <f t="shared" si="110"/>
-        <v>558.60036949767255</v>
-      </c>
-      <c r="FI19" s="1">
-        <f t="shared" si="110"/>
-        <v>553.01436580269581</v>
-      </c>
-      <c r="FJ19" s="1">
-        <f t="shared" si="110"/>
-        <v>547.48422214466882</v>
-      </c>
-      <c r="FK19" s="1">
-        <f t="shared" si="110"/>
-        <v>542.00937992322213</v>
+        <v>639.23403809412434</v>
       </c>
     </row>
     <row r="20" spans="2:167" x14ac:dyDescent="0.3">
@@ -4797,12 +4791,12 @@
         <v>645</v>
       </c>
       <c r="AG20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AH20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AK20" s="5">
         <v>147.30000000000001</v>
@@ -4823,52 +4817,52 @@
         <v>489</v>
       </c>
       <c r="AQ20" s="5">
-        <f t="shared" ref="AQ20" si="111">619+48.3</f>
+        <f t="shared" ref="AQ20" si="110">619+48.3</f>
         <v>667.3</v>
       </c>
       <c r="AR20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AS20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AT20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AU20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AV20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AW20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AX20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AY20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="AZ20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="BA20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
       <c r="BB20" s="5">
-        <f>645</f>
-        <v>645</v>
+        <f>654.9+47.1</f>
+        <v>702</v>
       </c>
     </row>
     <row r="21" spans="2:167" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4876,132 +4870,132 @@
         <v>32</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:N21" si="112">C19/C20</f>
+        <f t="shared" ref="C21:N21" si="111">C19/C20</f>
         <v>-9.7759674134419577E-2</v>
       </c>
       <c r="D21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.16021724372029861</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.26883910386965382</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="111"/>
+        <v>-7.1961982348947739E-2</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="111"/>
+        <v>-6.0420909708078736E-2</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="111"/>
+        <v>-8.2824168363883205E-2</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.11812627291242363</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.22131704005431097</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.50509164969450115</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.50441276306856764</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.33061778682959958</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="111"/>
+        <v>-0.30587589236683138</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" ref="O21:Q21" si="112">O19/O20</f>
+        <v>-0.27423312883435574</v>
+      </c>
+      <c r="P21" s="8">
         <f t="shared" si="112"/>
-        <v>-0.16021724372029861</v>
-      </c>
-      <c r="E21" s="8">
+        <v>-0.28650306748466259</v>
+      </c>
+      <c r="Q21" s="8">
         <f t="shared" si="112"/>
-        <v>-0.26883910386965382</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="112"/>
-        <v>-7.1961982348947739E-2</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="112"/>
-        <v>-6.0420909708078736E-2</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="112"/>
-        <v>-8.2824168363883205E-2</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.11812627291242363</v>
-      </c>
-      <c r="J21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.22131704005431097</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.50509164969450115</v>
-      </c>
-      <c r="L21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.50441276306856764</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.33061778682959958</v>
-      </c>
-      <c r="N21" s="8">
-        <f t="shared" si="112"/>
-        <v>-0.30587589236683138</v>
-      </c>
-      <c r="O21" s="8">
-        <f t="shared" ref="O21:Q21" si="113">O19/O20</f>
-        <v>-0.27423312883435574</v>
-      </c>
-      <c r="P21" s="8">
+        <v>-0.15153374233128822</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" ref="R21:S21" si="113">R19/R20</f>
+        <v>-0.29325153374233137</v>
+      </c>
+      <c r="S21" s="8">
         <f t="shared" si="113"/>
-        <v>-0.28650306748466259</v>
-      </c>
-      <c r="Q21" s="8">
-        <f t="shared" si="113"/>
-        <v>-0.15153374233128822</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" ref="R21:S21" si="114">R19/R20</f>
-        <v>-0.29325153374233137</v>
-      </c>
-      <c r="S21" s="8">
-        <f t="shared" si="114"/>
         <v>-0.32801635991820055</v>
       </c>
       <c r="T21" s="8">
-        <f t="shared" ref="T21" si="115">T19/T20</f>
+        <f t="shared" ref="T21" si="114">T19/T20</f>
         <v>-0.36094069529652328</v>
       </c>
       <c r="U21" s="8">
-        <f t="shared" ref="U21:V21" si="116">U19/U20</f>
+        <f t="shared" ref="U21:V21" si="115">U19/U20</f>
         <v>-0.60920245398772987</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>-0.59263803680981586</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" ref="W21" si="117">W19/W20</f>
+        <f t="shared" ref="W21" si="116">W19/W20</f>
         <v>-0.54846625766871171</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" ref="X21" si="118">X19/X20</f>
+        <f t="shared" ref="X21" si="117">X19/X20</f>
         <v>-0.57770961145194277</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21:Z21" si="119">Y19/Y20</f>
+        <f t="shared" ref="Y21:Z21" si="118">Y19/Y20</f>
         <v>-0.5670756646216768</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>-0.66237218813905929</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" ref="AA21" si="120">AA19/AA20</f>
+        <f t="shared" ref="AA21" si="119">AA19/AA20</f>
         <v>-0.5533742331288346</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" ref="AB21" si="121">AB19/AB20</f>
+        <f t="shared" ref="AB21" si="120">AB19/AB20</f>
         <v>-0.42126789366053158</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" ref="AC21:AD21" si="122">AC19/AC20</f>
+        <f t="shared" ref="AC21:AD21" si="121">AC19/AC20</f>
         <v>-0.36452301127704961</v>
       </c>
       <c r="AD21" s="8">
+        <f t="shared" si="121"/>
+        <v>-0.32863779409560917</v>
+      </c>
+      <c r="AE21" s="8">
+        <f t="shared" ref="AE21:AH21" si="122">AE19/AE20</f>
+        <v>-0.31711632021229536</v>
+      </c>
+      <c r="AF21" s="8">
         <f t="shared" si="122"/>
-        <v>-0.32863779409560917</v>
-      </c>
-      <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AH21" si="123">AE19/AE20</f>
-        <v>-0.31711632021229536</v>
-      </c>
-      <c r="AF21" s="8">
-        <f t="shared" si="123"/>
         <v>-0.43178294573643411</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="123"/>
-        <v>-0.38714406201550378</v>
+        <f t="shared" si="122"/>
+        <v>-0.3643874643874645</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="123"/>
-        <v>-0.38363623937984515</v>
+        <f t="shared" si="122"/>
+        <v>-0.41612894017094038</v>
       </c>
       <c r="AK21" s="8">
         <f>AK19/AK20</f>
@@ -5016,64 +5010,64 @@
         <v>-1.4235095613048365</v>
       </c>
       <c r="AN21" s="8">
-        <f t="shared" ref="AN21:AW21" si="124">AN19/AN20</f>
+        <f t="shared" ref="AN21:AW21" si="123">AN19/AN20</f>
         <v>-2.4720965309200595</v>
       </c>
       <c r="AO21" s="8">
+        <f t="shared" si="123"/>
+        <v>-1.8907975460122703</v>
+      </c>
+      <c r="AP21" s="8">
+        <f t="shared" si="123"/>
+        <v>-2.3556237218813898</v>
+      </c>
+      <c r="AQ21" s="8">
+        <f t="shared" si="123"/>
+        <v>-1.4013187471901696</v>
+      </c>
+      <c r="AR21" s="8">
+        <f t="shared" si="123"/>
+        <v>-1.483650307692308</v>
+      </c>
+      <c r="AS21" s="8">
+        <f t="shared" si="123"/>
+        <v>-0.85313231666666722</v>
+      </c>
+      <c r="AT21" s="8">
+        <f t="shared" si="123"/>
+        <v>-0.29676747396154107</v>
+      </c>
+      <c r="AU21" s="8">
+        <f t="shared" si="123"/>
+        <v>0.25377495668461392</v>
+      </c>
+      <c r="AV21" s="8">
+        <f t="shared" si="123"/>
+        <v>0.75756852352245996</v>
+      </c>
+      <c r="AW21" s="8">
+        <f t="shared" si="123"/>
+        <v>1.1948214865396767</v>
+      </c>
+      <c r="AX21" s="8">
+        <f t="shared" ref="AX21:BB21" si="124">AX19/AX20</f>
+        <v>1.5706290291179319</v>
+      </c>
+      <c r="AY21" s="8">
         <f t="shared" si="124"/>
-        <v>-1.8907975460122703</v>
-      </c>
-      <c r="AP21" s="8">
+        <v>1.9094840566961009</v>
+      </c>
+      <c r="AZ21" s="8">
         <f t="shared" si="124"/>
-        <v>-2.3556237218813898</v>
-      </c>
-      <c r="AQ21" s="8">
+        <v>2.2008420997151257</v>
+      </c>
+      <c r="BA21" s="8">
         <f t="shared" si="124"/>
-        <v>-1.4013187471901696</v>
-      </c>
-      <c r="AR21" s="8">
+        <v>2.5090412318862412</v>
+      </c>
+      <c r="BB21" s="8">
         <f t="shared" si="124"/>
-        <v>-1.5360516192248055</v>
-      </c>
-      <c r="AS21" s="8">
-        <f t="shared" si="124"/>
-        <v>-1.0268101554418607</v>
-      </c>
-      <c r="AT21" s="8">
-        <f t="shared" si="124"/>
-        <v>-0.47862174792837203</v>
-      </c>
-      <c r="AU21" s="8">
-        <f t="shared" si="124"/>
-        <v>6.464215701823206E-2</v>
-      </c>
-      <c r="AV21" s="8">
-        <f t="shared" si="124"/>
-        <v>0.56226969208184518</v>
-      </c>
-      <c r="AW21" s="8">
-        <f t="shared" si="124"/>
-        <v>0.996007888566531</v>
-      </c>
-      <c r="AX21" s="8">
-        <f t="shared" ref="AX21:BB21" si="125">AX19/AX20</f>
-        <v>1.3678622689056457</v>
-      </c>
-      <c r="AY21" s="8">
-        <f t="shared" si="125"/>
-        <v>1.7027706850780298</v>
-      </c>
-      <c r="AZ21" s="8">
-        <f t="shared" si="125"/>
-        <v>1.990206309907703</v>
-      </c>
-      <c r="BA21" s="8">
-        <f t="shared" si="125"/>
-        <v>2.2943916018554655</v>
-      </c>
-      <c r="BB21" s="8">
-        <f t="shared" si="125"/>
-        <v>2.6161949214354077</v>
+        <v>2.8349525265090536</v>
       </c>
     </row>
     <row r="23" spans="2:167" x14ac:dyDescent="0.3">
@@ -5085,183 +5079,183 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7">
-        <f t="shared" ref="G23:R23" si="126">G3/C3-1</f>
+        <f t="shared" ref="G23:R23" si="125">G3/C3-1</f>
         <v>0.74290220820189279</v>
       </c>
       <c r="H23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.58090185676392569</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.51385681293302543</v>
+      </c>
+      <c r="J23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.48192771084337349</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.46244343891402706</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.68120805369127524</v>
+      </c>
+      <c r="M23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.92143401983218931</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="125"/>
+        <v>1.1002710027100271</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="125"/>
+        <v>1.3948019801980198</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="125"/>
+        <v>1.2659680638722555</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" si="125"/>
+        <v>1.0218340611353711</v>
+      </c>
+      <c r="R23" s="7">
+        <f t="shared" si="125"/>
+        <v>0.83483870967741924</v>
+      </c>
+      <c r="S23" s="7">
+        <f t="shared" ref="S23:AD23" si="126">S3/O3-1</f>
+        <v>0.38785529715762279</v>
+      </c>
+      <c r="T23" s="7">
         <f t="shared" si="126"/>
-        <v>0.58090185676392569</v>
-      </c>
-      <c r="I23" s="7">
+        <v>0.30191587756000882</v>
+      </c>
+      <c r="U23" s="7">
         <f t="shared" si="126"/>
-        <v>0.51385681293302543</v>
-      </c>
-      <c r="J23" s="7">
+        <v>1.6493225996465855E-2</v>
+      </c>
+      <c r="V23" s="7">
         <f t="shared" si="126"/>
-        <v>0.48192771084337349</v>
-      </c>
-      <c r="K23" s="7">
+        <v>1.7932489451476963E-2</v>
+      </c>
+      <c r="W23" s="7">
         <f t="shared" si="126"/>
-        <v>0.46244343891402706</v>
-      </c>
-      <c r="L23" s="7">
+        <v>0.22007075032582368</v>
+      </c>
+      <c r="X23" s="7">
         <f t="shared" si="126"/>
-        <v>0.68120805369127524</v>
-      </c>
-      <c r="M23" s="7">
+        <v>0.15155615696887659</v>
+      </c>
+      <c r="Y23" s="7">
         <f t="shared" si="126"/>
-        <v>0.92143401983218931</v>
-      </c>
-      <c r="N23" s="7">
+        <v>0.37763183310797754</v>
+      </c>
+      <c r="Z23" s="7">
         <f t="shared" si="126"/>
-        <v>1.1002710027100271</v>
-      </c>
-      <c r="O23" s="7">
+        <v>0.29516407599309158</v>
+      </c>
+      <c r="AA23" s="7">
         <f t="shared" si="126"/>
-        <v>1.3948019801980198</v>
-      </c>
-      <c r="P23" s="7">
+        <v>0.22279871814436136</v>
+      </c>
+      <c r="AB23" s="7">
         <f t="shared" si="126"/>
-        <v>1.2659680638722555</v>
-      </c>
-      <c r="Q23" s="7">
+        <v>0.31242655699177457</v>
+      </c>
+      <c r="AC23" s="7">
         <f t="shared" si="126"/>
-        <v>1.0218340611353711</v>
-      </c>
-      <c r="R23" s="7">
+        <v>0.28855860908581032</v>
+      </c>
+      <c r="AD23" s="7">
         <f t="shared" si="126"/>
-        <v>0.83483870967741924</v>
-      </c>
-      <c r="S23" s="7">
-        <f t="shared" ref="S23:AD23" si="127">S3/O3-1</f>
-        <v>0.38785529715762279</v>
-      </c>
-      <c r="T23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.30191587756000882</v>
-      </c>
-      <c r="U23" s="7">
-        <f t="shared" si="127"/>
-        <v>1.6493225996465855E-2</v>
-      </c>
-      <c r="V23" s="7">
-        <f t="shared" si="127"/>
-        <v>1.7932489451476963E-2</v>
-      </c>
-      <c r="W23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.22007075032582368</v>
-      </c>
-      <c r="X23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.15155615696887659</v>
-      </c>
-      <c r="Y23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.37763183310797754</v>
-      </c>
-      <c r="Z23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.29516407599309158</v>
-      </c>
-      <c r="AA23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.22279871814436136</v>
-      </c>
-      <c r="AB23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.31242655699177457</v>
-      </c>
-      <c r="AC23" s="7">
-        <f t="shared" si="127"/>
-        <v>0.28855860908581032</v>
-      </c>
-      <c r="AD23" s="7">
-        <f t="shared" si="127"/>
         <v>0.3177757034271238</v>
       </c>
       <c r="AE23" s="7">
-        <f t="shared" ref="AE23" si="128">AE3/AA3-1</f>
+        <f t="shared" ref="AE23" si="127">AE3/AA3-1</f>
         <v>0.29190066142518423</v>
       </c>
       <c r="AF23" s="7">
-        <f t="shared" ref="AF23" si="129">AF3/AB3-1</f>
+        <f t="shared" ref="AF23" si="128">AF3/AB3-1</f>
         <v>0.20951315053161723</v>
       </c>
       <c r="AG23" s="7">
-        <f t="shared" ref="AG23" si="130">AG3/AC3-1</f>
-        <v>0.23503808487486388</v>
+        <f t="shared" ref="AG23" si="129">AG3/AC3-1</f>
+        <v>0.47943416757344925</v>
       </c>
       <c r="AH23" s="7">
-        <f t="shared" ref="AH23" si="131">AH3/AD3-1</f>
+        <f t="shared" ref="AH23" si="130">AH3/AD3-1</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="AL23" s="7">
+        <f t="shared" ref="AL23:AX23" si="131">AL3/AK3-1</f>
+        <v>0.56430769230769218</v>
+      </c>
+      <c r="AM23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.81726986624704967</v>
+      </c>
+      <c r="AN23" s="7">
+        <f t="shared" si="131"/>
+        <v>1.0772810910271677</v>
+      </c>
+      <c r="AO23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.15933722384326798</v>
+      </c>
+      <c r="AP23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.25806741573033709</v>
+      </c>
+      <c r="AQ23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.28679622749356937</v>
+      </c>
+      <c r="AR23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.34896724042198768</v>
+      </c>
+      <c r="AS23" s="7">
+        <f t="shared" si="131"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="AL23" s="7">
-        <f t="shared" ref="AL23:AX23" si="132">AL3/AK3-1</f>
-        <v>0.56430769230769218</v>
-      </c>
-      <c r="AM23" s="7">
+      <c r="AT23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="AU23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AV23" s="7">
+        <f t="shared" si="131"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AW23" s="7">
+        <f t="shared" si="131"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AX23" s="7">
+        <f t="shared" si="131"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AY23" s="7">
+        <f t="shared" ref="AY23:BB23" si="132">AY3/AX3-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AZ23" s="7">
         <f t="shared" si="132"/>
-        <v>0.81726986624704967</v>
-      </c>
-      <c r="AN23" s="7">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BA23" s="7">
         <f t="shared" si="132"/>
-        <v>1.0772810910271677</v>
-      </c>
-      <c r="AO23" s="7">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BB23" s="7">
         <f t="shared" si="132"/>
-        <v>0.15933722384326798</v>
-      </c>
-      <c r="AP23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.25806741573033709</v>
-      </c>
-      <c r="AQ23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.28679622749356937</v>
-      </c>
-      <c r="AR23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.23723042754025547</v>
-      </c>
-      <c r="AS23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="AT23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.17999999999999994</v>
-      </c>
-      <c r="AU23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AV23" s="7">
-        <f t="shared" si="132"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AW23" s="7">
-        <f t="shared" si="132"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="AX23" s="7">
-        <f t="shared" si="132"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AY23" s="7">
-        <f t="shared" ref="AY23:BB23" si="133">AY3/AX3-1</f>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AZ23" s="7">
-        <f t="shared" si="133"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="BA23" s="7">
-        <f t="shared" si="133"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="BB23" s="7">
-        <f t="shared" si="133"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -5274,200 +5268,200 @@
         <v>0.78233438485804407</v>
       </c>
       <c r="D24" s="7">
-        <f t="shared" ref="D24:AH24" si="134">(D3-D4)/D3</f>
+        <f t="shared" ref="D24:AH24" si="133">(D3-D4)/D3</f>
         <v>0.77851458885941638</v>
       </c>
       <c r="E24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77367205542725181</v>
+      </c>
+      <c r="F24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77008032128514048</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.76561085972850673</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.76761744966442946</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.7589626239511823</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74796747967479671</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74133663366336633</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.73203592814371254</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.73878523223501402</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.7464516129032257</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74702842377260992</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74256771636203489</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74474769291183973</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.73277074542897325</v>
+      </c>
+      <c r="S24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.74753304784956243</v>
+      </c>
+      <c r="T24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.75778078484438438</v>
+      </c>
+      <c r="U24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.75584315240486777</v>
+      </c>
+      <c r="V24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.75405872193436962</v>
+      </c>
+      <c r="W24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.76835037387456129</v>
+      </c>
+      <c r="X24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.76204465334900118</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77061132922041498</v>
+      </c>
+      <c r="Z24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77103613815175365</v>
+      </c>
+      <c r="AA24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77673780107325596</v>
+      </c>
+      <c r="AB24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77772803581421379</v>
+      </c>
+      <c r="AC24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77693144722524488</v>
+      </c>
+      <c r="AD24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77868852459016391</v>
+      </c>
+      <c r="AE24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.78294049459041726</v>
+      </c>
+      <c r="AF24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.78153048949754789</v>
+      </c>
+      <c r="AG24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.78192115328037659</v>
+      </c>
+      <c r="AH24" s="7">
+        <f t="shared" si="133"/>
+        <v>0.77999999999999992</v>
+      </c>
+      <c r="AK24" s="7">
+        <f t="shared" ref="AK24:BB24" si="134">(AK3-AK4)/AK3</f>
+        <v>0.77538461538461534</v>
+      </c>
+      <c r="AL24" s="7">
         <f t="shared" si="134"/>
-        <v>0.77367205542725181</v>
-      </c>
-      <c r="F24" s="7">
+        <v>0.75924468922108579</v>
+      </c>
+      <c r="AM24" s="7">
         <f t="shared" si="134"/>
-        <v>0.77008032128514048</v>
-      </c>
-      <c r="G24" s="7">
+        <v>0.74033986362160409</v>
+      </c>
+      <c r="AN24" s="7">
         <f t="shared" si="134"/>
-        <v>0.76561085972850673</v>
-      </c>
-      <c r="H24" s="7">
+        <v>0.74114214255939981</v>
+      </c>
+      <c r="AO24" s="7">
         <f t="shared" si="134"/>
-        <v>0.76761744966442946</v>
-      </c>
-      <c r="I24" s="7">
+        <v>0.75388764044943823</v>
+      </c>
+      <c r="AP24" s="7">
         <f t="shared" si="134"/>
-        <v>0.7589626239511823</v>
-      </c>
-      <c r="J24" s="7">
+        <v>0.76811231780508726</v>
+      </c>
+      <c r="AQ24" s="7">
         <f t="shared" si="134"/>
-        <v>0.74796747967479671</v>
-      </c>
-      <c r="K24" s="7">
+        <v>0.77756801776790674</v>
+      </c>
+      <c r="AR24" s="7">
         <f t="shared" si="134"/>
-        <v>0.74133663366336633</v>
-      </c>
-      <c r="L24" s="7">
+        <v>0.78150443097110911</v>
+      </c>
+      <c r="AS24" s="7">
         <f t="shared" si="134"/>
-        <v>0.73203592814371254</v>
-      </c>
-      <c r="M24" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="AT24" s="7">
         <f t="shared" si="134"/>
-        <v>0.73878523223501402</v>
-      </c>
-      <c r="N24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.7464516129032257</v>
-      </c>
-      <c r="O24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.74702842377260992</v>
-      </c>
-      <c r="P24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.74256771636203489</v>
-      </c>
-      <c r="Q24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.74474769291183973</v>
-      </c>
-      <c r="R24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.73277074542897325</v>
-      </c>
-      <c r="S24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.74753304784956243</v>
-      </c>
-      <c r="T24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.75778078484438438</v>
-      </c>
-      <c r="U24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.75584315240486777</v>
-      </c>
-      <c r="V24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.75405872193436962</v>
-      </c>
-      <c r="W24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.76835037387456129</v>
-      </c>
-      <c r="X24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.76204465334900118</v>
-      </c>
-      <c r="Y24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77061132922041498</v>
-      </c>
-      <c r="Z24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77103613815175365</v>
-      </c>
-      <c r="AA24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77673780107325596</v>
-      </c>
-      <c r="AB24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77772803581421379</v>
-      </c>
-      <c r="AC24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77693144722524488</v>
-      </c>
-      <c r="AD24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.77868852459016391</v>
-      </c>
-      <c r="AE24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.78294049459041726</v>
-      </c>
-      <c r="AF24" s="7">
-        <f t="shared" si="134"/>
-        <v>0.78153048949754789</v>
-      </c>
-      <c r="AG24" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="AU24" s="7">
         <f t="shared" si="134"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="AH24" s="7">
+      <c r="AV24" s="7">
+        <f t="shared" si="134"/>
+        <v>0.77999999999999992</v>
+      </c>
+      <c r="AW24" s="7">
         <f t="shared" si="134"/>
         <v>0.78</v>
       </c>
-      <c r="AK24" s="7">
-        <f t="shared" ref="AK24:BB24" si="135">(AK3-AK4)/AK3</f>
-        <v>0.77538461538461534</v>
-      </c>
-      <c r="AL24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.75924468922108579</v>
-      </c>
-      <c r="AM24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.74033986362160409</v>
-      </c>
-      <c r="AN24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.74114214255939981</v>
-      </c>
-      <c r="AO24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.75388764044943823</v>
-      </c>
-      <c r="AP24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.76811231780508726</v>
-      </c>
-      <c r="AQ24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.77756801776790674</v>
-      </c>
-      <c r="AR24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.78105418956204231</v>
-      </c>
-      <c r="AS24" s="7">
-        <f t="shared" si="135"/>
+      <c r="AX24" s="7">
+        <f t="shared" si="134"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="AT24" s="7">
-        <f t="shared" si="135"/>
+      <c r="AY24" s="7">
+        <f t="shared" si="134"/>
+        <v>0.78</v>
+      </c>
+      <c r="AZ24" s="7">
+        <f t="shared" si="134"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="AU24" s="7">
-        <f t="shared" si="135"/>
+      <c r="BA24" s="7">
+        <f t="shared" si="134"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="AV24" s="7">
-        <f t="shared" si="135"/>
+      <c r="BB24" s="7">
+        <f t="shared" si="134"/>
         <v>0.78</v>
-      </c>
-      <c r="AW24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.77999999999999992</v>
-      </c>
-      <c r="AX24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.78</v>
-      </c>
-      <c r="AY24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.78</v>
-      </c>
-      <c r="AZ24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.78</v>
-      </c>
-      <c r="BA24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.78</v>
-      </c>
-      <c r="BB24" s="7">
-        <f t="shared" si="135"/>
-        <v>0.77999999999999992</v>
       </c>
     </row>
     <row r="25" spans="2:167" x14ac:dyDescent="0.3">
@@ -5479,199 +5473,199 @@
         <v>0.74290220820189268</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" ref="D25:AH25" si="136">(D3-D5)/D3</f>
+        <f t="shared" ref="D25:AH25" si="135">(D3-D5)/D3</f>
         <v>0.78116710875331563</v>
       </c>
       <c r="E25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.79214780600461887</v>
+      </c>
+      <c r="F25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.7881526104417671</v>
+      </c>
+      <c r="G25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.79457013574660629</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.80453020134228193</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.8001525553012967</v>
+      </c>
+      <c r="J25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.73035230352303526</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.72462871287128716</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.57534930139720564</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.66057959507741171</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.63354838709677419</v>
+      </c>
+      <c r="O25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.69276485788113706</v>
+      </c>
+      <c r="P25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.71438009249064083</v>
+      </c>
+      <c r="Q25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.74474769291183973</v>
+      </c>
+      <c r="R25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.71923347398030946</v>
+      </c>
+      <c r="S25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.72612176503444426</v>
+      </c>
+      <c r="T25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.75794993234100139</v>
+      </c>
+      <c r="U25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.7073594745991888</v>
+      </c>
+      <c r="V25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.68549222797927456</v>
+      </c>
+      <c r="W25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.721654204181291</v>
+      </c>
+      <c r="X25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.75646298472385431</v>
+      </c>
+      <c r="Y25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.76065619742007851</v>
+      </c>
+      <c r="Z25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.70422723029737289</v>
+      </c>
+      <c r="AA25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.74741045800574069</v>
+      </c>
+      <c r="AB25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.76687185226636823</v>
+      </c>
+      <c r="AC25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.74809575625680091</v>
+      </c>
+      <c r="AD25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.71604938271604934</v>
+      </c>
+      <c r="AE25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.72797527047913446</v>
+      </c>
+      <c r="AF25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.70722679744609973</v>
+      </c>
+      <c r="AG25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.68527508090614886</v>
+      </c>
+      <c r="AH25" s="7">
+        <f t="shared" si="135"/>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="AK25" s="7">
+        <f t="shared" ref="AK25:BB25" si="136">(AK3-AK5)/AK3</f>
+        <v>0.77876923076923077</v>
+      </c>
+      <c r="AL25" s="7">
         <f t="shared" si="136"/>
-        <v>0.79214780600461887</v>
-      </c>
-      <c r="F25" s="7">
+        <v>0.77970102281667975</v>
+      </c>
+      <c r="AM25" s="7">
         <f t="shared" si="136"/>
-        <v>0.7881526104417671</v>
-      </c>
-      <c r="G25" s="7">
+        <v>0.64422556553739585</v>
+      </c>
+      <c r="AN25" s="7">
         <f t="shared" si="136"/>
-        <v>0.79457013574660629</v>
-      </c>
-      <c r="H25" s="7">
+        <v>0.71951854939558157</v>
+      </c>
+      <c r="AO25" s="7">
         <f t="shared" si="136"/>
-        <v>0.80453020134228193</v>
-      </c>
-      <c r="I25" s="7">
+        <v>0.71964044943820227</v>
+      </c>
+      <c r="AP25" s="7">
         <f t="shared" si="136"/>
-        <v>0.8001525553012967</v>
-      </c>
-      <c r="J25" s="7">
+        <v>0.73538868248070866</v>
+      </c>
+      <c r="AQ25" s="7">
         <f t="shared" si="136"/>
-        <v>0.73035230352303526</v>
-      </c>
-      <c r="K25" s="7">
+        <v>0.7438089950027762</v>
+      </c>
+      <c r="AR25" s="7">
         <f t="shared" si="136"/>
-        <v>0.72462871287128716</v>
-      </c>
-      <c r="L25" s="7">
+        <v>0.69775269706810894</v>
+      </c>
+      <c r="AS25" s="7">
         <f t="shared" si="136"/>
-        <v>0.57534930139720564</v>
-      </c>
-      <c r="M25" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AT25" s="7">
         <f t="shared" si="136"/>
-        <v>0.66057959507741171</v>
-      </c>
-      <c r="N25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.63354838709677419</v>
-      </c>
-      <c r="O25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.69276485788113706</v>
-      </c>
-      <c r="P25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.71438009249064083</v>
-      </c>
-      <c r="Q25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.74474769291183973</v>
-      </c>
-      <c r="R25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.71923347398030946</v>
-      </c>
-      <c r="S25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.72612176503444426</v>
-      </c>
-      <c r="T25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.75794993234100139</v>
-      </c>
-      <c r="U25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.7073594745991888</v>
-      </c>
-      <c r="V25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.68549222797927456</v>
-      </c>
-      <c r="W25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.721654204181291</v>
-      </c>
-      <c r="X25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.75646298472385431</v>
-      </c>
-      <c r="Y25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.76065619742007851</v>
-      </c>
-      <c r="Z25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.70422723029737289</v>
-      </c>
-      <c r="AA25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.74741045800574069</v>
-      </c>
-      <c r="AB25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.76687185226636823</v>
-      </c>
-      <c r="AC25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.74809575625680091</v>
-      </c>
-      <c r="AD25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.71604938271604934</v>
-      </c>
-      <c r="AE25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.72797527047913446</v>
-      </c>
-      <c r="AF25" s="7">
-        <f t="shared" si="136"/>
-        <v>0.70722679744609973</v>
-      </c>
-      <c r="AG25" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AU25" s="7">
         <f t="shared" si="136"/>
         <v>0.72000000000000008</v>
       </c>
-      <c r="AH25" s="7">
+      <c r="AV25" s="7">
         <f t="shared" si="136"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="AK25" s="7">
-        <f t="shared" ref="AK25:BB25" si="137">(AK3-AK5)/AK3</f>
-        <v>0.77876923076923077</v>
-      </c>
-      <c r="AL25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.77970102281667975</v>
-      </c>
-      <c r="AM25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.64422556553739585</v>
-      </c>
-      <c r="AN25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.71951854939558157</v>
-      </c>
-      <c r="AO25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.71964044943820227</v>
-      </c>
-      <c r="AP25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.73538868248070866</v>
-      </c>
-      <c r="AQ25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.7438089950027762</v>
-      </c>
-      <c r="AR25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.71334454092266042</v>
-      </c>
-      <c r="AS25" s="7">
-        <f t="shared" si="137"/>
+        <v>0.72000000000000008</v>
+      </c>
+      <c r="AW25" s="7">
+        <f t="shared" si="136"/>
         <v>0.72</v>
       </c>
-      <c r="AT25" s="7">
-        <f t="shared" si="137"/>
+      <c r="AX25" s="7">
+        <f t="shared" si="136"/>
         <v>0.72</v>
       </c>
-      <c r="AU25" s="7">
-        <f t="shared" si="137"/>
+      <c r="AY25" s="7">
+        <f t="shared" si="136"/>
+        <v>0.72</v>
+      </c>
+      <c r="AZ25" s="7">
+        <f t="shared" si="136"/>
         <v>0.71999999999999986</v>
       </c>
-      <c r="AV25" s="7">
-        <f t="shared" si="137"/>
+      <c r="BA25" s="7">
+        <f t="shared" si="136"/>
         <v>0.72</v>
       </c>
-      <c r="AW25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.72000000000000008</v>
-      </c>
-      <c r="AX25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.72</v>
-      </c>
-      <c r="AY25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.72</v>
-      </c>
-      <c r="AZ25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.72</v>
-      </c>
-      <c r="BA25" s="7">
-        <f t="shared" si="137"/>
-        <v>0.72</v>
-      </c>
       <c r="BB25" s="7">
-        <f t="shared" si="137"/>
+        <f t="shared" si="136"/>
         <v>0.72</v>
       </c>
     </row>
@@ -5684,184 +5678,184 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7">
-        <f t="shared" ref="G26:AD26" si="138">G6/C6-1</f>
+        <f t="shared" ref="G26:AD26" si="137">G6/C6-1</f>
         <v>0.78191489361702127</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.33812949640287782</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.40893470790377995</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.51006711409395966</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.57014925373134329</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.66397849462365577</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.74146341463414656</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.73999999999999955</v>
       </c>
       <c r="O26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.78897338403041806</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.76090468497576746</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.64425770308123242</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.73690932311622004</v>
       </c>
       <c r="S26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.50265674814027639</v>
       </c>
       <c r="T26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.45137614678899074</v>
       </c>
       <c r="U26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.62691652470187376</v>
       </c>
       <c r="V26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.45955882352941169</v>
       </c>
       <c r="W26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.49222065063649212</v>
       </c>
       <c r="X26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.42225031605562591</v>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.14659685863874339</v>
       </c>
       <c r="Z26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.12493702770780857</v>
       </c>
       <c r="AA26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>7.5355450236966881E-2</v>
       </c>
       <c r="AB26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>-1.7333333333333312E-2</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.11689497716894981</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>-2.2391401701746805E-3</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" ref="AE26" si="139">AE6/AA6-1</f>
+        <f t="shared" ref="AE26" si="138">AE6/AA6-1</f>
         <v>6.6989863375936487E-2</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" ref="AF26" si="140">AF6/AB6-1</f>
+        <f t="shared" ref="AF26" si="139">AF6/AB6-1</f>
         <v>0.17910447761194037</v>
       </c>
       <c r="AG26" s="7">
-        <f t="shared" ref="AG26" si="141">AG6/AC6-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="AG26" si="140">AG6/AC6-1</f>
+        <v>0.31398201144726068</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" ref="AH26" si="142">AH6/AD6-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AH26" si="141">AH6/AD6-1</f>
+        <v>0.50000000000000022</v>
       </c>
       <c r="AK26" s="7"/>
       <c r="AL26" s="7">
-        <f t="shared" ref="AL26:AQ26" si="143">AL6/AK6-1</f>
+        <f t="shared" ref="AL26:AQ26" si="142">AL6/AK6-1</f>
         <v>0.48530805687203782</v>
       </c>
       <c r="AM26" s="7">
+        <f t="shared" si="142"/>
+        <v>0.68602425015954061</v>
+      </c>
+      <c r="AN26" s="7">
+        <f t="shared" si="142"/>
+        <v>0.72785768357305081</v>
+      </c>
+      <c r="AO26" s="7">
+        <f t="shared" si="142"/>
+        <v>0.50952902519167576</v>
+      </c>
+      <c r="AP26" s="7">
+        <f t="shared" si="142"/>
+        <v>0.27456102162240592</v>
+      </c>
+      <c r="AQ26" s="7">
+        <f t="shared" si="142"/>
+        <v>4.2240692246385159E-2</v>
+      </c>
+      <c r="AR26" s="7">
+        <f t="shared" ref="AR26:BB26" si="143">AR6/AQ6-1</f>
+        <v>0.26545772339960672</v>
+      </c>
+      <c r="AS26" s="7">
         <f t="shared" si="143"/>
-        <v>0.68602425015954061</v>
-      </c>
-      <c r="AN26" s="7">
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AT26" s="7">
         <f t="shared" si="143"/>
-        <v>0.72785768357305081</v>
-      </c>
-      <c r="AO26" s="7">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AU26" s="7">
         <f t="shared" si="143"/>
-        <v>0.50952902519167576</v>
-      </c>
-      <c r="AP26" s="7">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AV26" s="7">
         <f t="shared" si="143"/>
-        <v>0.27456102162240592</v>
-      </c>
-      <c r="AQ26" s="7">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AW26" s="7">
         <f t="shared" si="143"/>
-        <v>4.2240692246385159E-2</v>
-      </c>
-      <c r="AR26" s="7">
-        <f t="shared" ref="AR26:BB26" si="144">AR6/AQ6-1</f>
-        <v>0.12843784138081693</v>
-      </c>
-      <c r="AS26" s="7">
-        <f t="shared" si="144"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AT26" s="7">
-        <f t="shared" si="144"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AU26" s="7">
-        <f t="shared" si="144"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AV26" s="7">
-        <f t="shared" si="144"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AW26" s="7">
-        <f t="shared" si="144"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AX26" s="7">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY26" s="7">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ26" s="7">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA26" s="7">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB26" s="7">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD26" t="s">
@@ -5876,204 +5870,204 @@
         <v>36</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:AD27" si="145">C8/C3</f>
+        <f t="shared" ref="C27:AD27" si="144">C8/C3</f>
         <v>0.22870662460567812</v>
       </c>
       <c r="D27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.19098143236074278</v>
+      </c>
+      <c r="E27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.22979214780600454</v>
+      </c>
+      <c r="F27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.25903614457831325</v>
+      </c>
+      <c r="G27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.25701357466063351</v>
+      </c>
+      <c r="H27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.26006711409395972</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.24637681159420288</v>
+      </c>
+      <c r="J27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.17344173441734415</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.1404702970297029</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="144"/>
+        <v>-1.4970059880240088E-3</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.11591901548233421</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.12741935483870967</v>
+      </c>
+      <c r="O27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.19664082687338508</v>
+      </c>
+      <c r="P27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.21691257432283637</v>
+      </c>
+      <c r="Q27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.25898291773021803</v>
+      </c>
+      <c r="R27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.21290436005625873</v>
+      </c>
+      <c r="S27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.21038912679203128</v>
+      </c>
+      <c r="T27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.2481393775372126</v>
+      </c>
+      <c r="U27" s="7">
+        <f t="shared" si="144"/>
+        <v>9.4263086729766396E-2</v>
+      </c>
+      <c r="V27" s="7">
+        <f t="shared" si="144"/>
+        <v>9.6718480138169263E-2</v>
+      </c>
+      <c r="W27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.16801464977872718</v>
+      </c>
+      <c r="X27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.18801410105757932</v>
+      </c>
+      <c r="Y27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.22420078519349423</v>
+      </c>
+      <c r="Z27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.17749033204427261</v>
+      </c>
+      <c r="AA27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.24098340197179574</v>
+      </c>
+      <c r="AB27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.29714605484051482</v>
+      </c>
+      <c r="AC27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.25886833514689878</v>
+      </c>
+      <c r="AD27" s="7">
+        <f t="shared" si="144"/>
+        <v>0.26927747419550702</v>
+      </c>
+      <c r="AE27" s="7">
+        <f t="shared" ref="AE27:AH27" si="145">AE8/AE3</f>
+        <v>0.27704791344667701</v>
+      </c>
+      <c r="AF27" s="7">
         <f t="shared" si="145"/>
-        <v>0.19098143236074278</v>
-      </c>
-      <c r="E27" s="7">
+        <v>0.24752475247524752</v>
+      </c>
+      <c r="AG27" s="7">
         <f t="shared" si="145"/>
-        <v>0.22979214780600454</v>
-      </c>
-      <c r="F27" s="7">
+        <v>0.23080317740511913</v>
+      </c>
+      <c r="AH27" s="7">
         <f t="shared" si="145"/>
-        <v>0.25903614457831325</v>
-      </c>
-      <c r="G27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.25701357466063351</v>
-      </c>
-      <c r="H27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.26006711409395972</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.24637681159420288</v>
-      </c>
-      <c r="J27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.17344173441734415</v>
-      </c>
-      <c r="K27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.1404702970297029</v>
-      </c>
-      <c r="L27" s="7">
-        <f t="shared" si="145"/>
-        <v>-1.4970059880240088E-3</v>
-      </c>
-      <c r="M27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.11591901548233421</v>
-      </c>
-      <c r="N27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.12741935483870967</v>
-      </c>
-      <c r="O27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.19664082687338508</v>
-      </c>
-      <c r="P27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21691257432283637</v>
-      </c>
-      <c r="Q27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.25898291773021803</v>
-      </c>
-      <c r="R27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21290436005625873</v>
-      </c>
-      <c r="S27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.21038912679203128</v>
-      </c>
-      <c r="T27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.2481393775372126</v>
-      </c>
-      <c r="U27" s="7">
-        <f t="shared" si="145"/>
-        <v>9.4263086729766396E-2</v>
-      </c>
-      <c r="V27" s="7">
-        <f t="shared" si="145"/>
-        <v>9.6718480138169263E-2</v>
-      </c>
-      <c r="W27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.16801464977872718</v>
-      </c>
-      <c r="X27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.18801410105757932</v>
-      </c>
-      <c r="Y27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.22420078519349423</v>
-      </c>
-      <c r="Z27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.17749033204427261</v>
-      </c>
-      <c r="AA27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.24098340197179574</v>
-      </c>
-      <c r="AB27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.29714605484051482</v>
-      </c>
-      <c r="AC27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.25886833514689878</v>
-      </c>
-      <c r="AD27" s="7">
-        <f t="shared" si="145"/>
-        <v>0.26927747419550702</v>
-      </c>
-      <c r="AE27" s="7">
-        <f t="shared" ref="AE27:AH27" si="146">AE8/AE3</f>
-        <v>0.27704791344667701</v>
-      </c>
-      <c r="AF27" s="7">
+        <v>0.21843525023852881</v>
+      </c>
+      <c r="AK27" s="7">
+        <f t="shared" ref="AK27:AX27" si="146">AK8/AK3</f>
+        <v>0.22953846153846152</v>
+      </c>
+      <c r="AL27" s="7">
         <f t="shared" si="146"/>
-        <v>0.24752475247524752</v>
-      </c>
-      <c r="AG27" s="7">
+        <v>0.23072383949645953</v>
+      </c>
+      <c r="AM27" s="7">
         <f t="shared" si="146"/>
-        <v>0.25863259911894271</v>
-      </c>
-      <c r="AH27" s="7">
+        <v>9.8603744994047005E-2</v>
+      </c>
+      <c r="AN27" s="7">
         <f t="shared" si="146"/>
-        <v>0.26747582124810465</v>
-      </c>
-      <c r="AK27" s="7">
-        <f t="shared" ref="AK27:AX27" si="147">AK8/AK3</f>
-        <v>0.22953846153846152</v>
-      </c>
-      <c r="AL27" s="7">
+        <v>0.22280116715298048</v>
+      </c>
+      <c r="AO27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.16382022471910113</v>
+      </c>
+      <c r="AP27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.18973278079451283</v>
+      </c>
+      <c r="AQ27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.26724042198778453</v>
+      </c>
+      <c r="AR27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.24085318317836246</v>
+      </c>
+      <c r="AS27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.29872453835517926</v>
+      </c>
+      <c r="AT27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.32601612637481586</v>
+      </c>
+      <c r="AU27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.34568386861070638</v>
+      </c>
+      <c r="AV27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.35946209462760753</v>
+      </c>
+      <c r="AW27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.36848746469739424</v>
+      </c>
+      <c r="AX27" s="7">
+        <f t="shared" si="146"/>
+        <v>0.37586199938726</v>
+      </c>
+      <c r="AY27" s="7">
+        <f t="shared" ref="AY27:BB27" si="147">AY8/AY3</f>
+        <v>0.38171756545389868</v>
+      </c>
+      <c r="AZ27" s="7">
         <f t="shared" si="147"/>
-        <v>0.23072383949645953</v>
-      </c>
-      <c r="AM27" s="7">
+        <v>0.38622356296041682</v>
+      </c>
+      <c r="BA27" s="7">
         <f t="shared" si="147"/>
-        <v>9.8603744994047005E-2</v>
-      </c>
-      <c r="AN27" s="7">
+        <v>0.39055790341906754</v>
+      </c>
+      <c r="BB27" s="7">
         <f t="shared" si="147"/>
-        <v>0.22280116715298048</v>
-      </c>
-      <c r="AO27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.16382022471910113</v>
-      </c>
-      <c r="AP27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.18973278079451283</v>
-      </c>
-      <c r="AQ27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.26724042198778453</v>
-      </c>
-      <c r="AR27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.26260896882399309</v>
-      </c>
-      <c r="AS27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.30430864384382689</v>
-      </c>
-      <c r="AT27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.33084306501754523</v>
-      </c>
-      <c r="AU27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.34996515331990974</v>
-      </c>
-      <c r="AV27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.36336112177348934</v>
-      </c>
-      <c r="AW27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.37213609560454958</v>
-      </c>
-      <c r="AX27" s="7">
-        <f t="shared" si="147"/>
-        <v>0.37930603416878039</v>
-      </c>
-      <c r="AY27" s="7">
-        <f t="shared" ref="AY27:BB27" si="148">AY8/AY3</f>
-        <v>0.38499914576459271</v>
-      </c>
-      <c r="AZ27" s="7">
-        <f t="shared" si="148"/>
-        <v>0.38938013068784627</v>
-      </c>
-      <c r="BA27" s="7">
-        <f t="shared" si="148"/>
-        <v>0.39359422094735691</v>
-      </c>
-      <c r="BB27" s="7">
-        <f t="shared" si="148"/>
-        <v>0.3976477744350766</v>
+        <v>0.39472712614596023</v>
       </c>
       <c r="BD27" t="s">
         <v>41</v>
@@ -6087,211 +6081,211 @@
         <v>37</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28:R28" si="149">C13/C3</f>
+        <f t="shared" ref="C28:R28" si="148">C13/C3</f>
         <v>-0.22712933753943226</v>
       </c>
       <c r="D28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.26790450928381948</v>
+      </c>
+      <c r="E28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.47113163972286393</v>
+      </c>
+      <c r="F28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.12248995983935747</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="148"/>
+        <v>-9.4117647058823514E-2</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.11577181208053688</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.1426392067124333</v>
+      </c>
+      <c r="J28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.2276422764227643</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.45173267326732686</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.36477045908183642</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.20484319174275514</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.22032258064516125</v>
+      </c>
+      <c r="O28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.34857881136950897</v>
+      </c>
+      <c r="P28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.3146883946267342</v>
+      </c>
+      <c r="Q28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.15216964461024926</v>
+      </c>
+      <c r="R28" s="7">
+        <f t="shared" si="148"/>
+        <v>-0.24560478199718716</v>
+      </c>
+      <c r="S28" s="7">
+        <f t="shared" ref="S28:AD28" si="149">S13/S3</f>
+        <v>-0.28244274809160314</v>
+      </c>
+      <c r="T28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.26790450928381948</v>
-      </c>
-      <c r="E28" s="7">
+        <v>-0.2880581867388361</v>
+      </c>
+      <c r="U28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.47113163972286393</v>
-      </c>
-      <c r="F28" s="7">
+        <v>-0.5796793509754683</v>
+      </c>
+      <c r="V28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.12248995983935747</v>
-      </c>
-      <c r="G28" s="7">
+        <v>-0.52124352331606216</v>
+      </c>
+      <c r="W28" s="7">
         <f t="shared" si="149"/>
-        <v>-9.4117647058823514E-2</v>
-      </c>
-      <c r="H28" s="7">
+        <v>-0.44224019533038328</v>
+      </c>
+      <c r="X28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.11577181208053688</v>
-      </c>
-      <c r="I28" s="7">
+        <v>-0.46092831962397185</v>
+      </c>
+      <c r="Y28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.1426392067124333</v>
-      </c>
-      <c r="J28" s="7">
+        <v>-0.42077958496915296</v>
+      </c>
+      <c r="Z28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.2276422764227643</v>
-      </c>
-      <c r="K28" s="7">
+        <v>-0.47379650620082681</v>
+      </c>
+      <c r="AA28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.45173267326732686</v>
-      </c>
-      <c r="L28" s="7">
+        <v>-0.37726194933233514</v>
+      </c>
+      <c r="AB28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.36477045908183642</v>
-      </c>
-      <c r="M28" s="7">
+        <v>-0.26648013430330159</v>
+      </c>
+      <c r="AC28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.20484319174275514</v>
-      </c>
-      <c r="N28" s="7">
+        <v>-0.30337323177366698</v>
+      </c>
+      <c r="AD28" s="7">
         <f t="shared" si="149"/>
-        <v>-0.22032258064516125</v>
-      </c>
-      <c r="O28" s="7">
-        <f t="shared" si="149"/>
-        <v>-0.34857881136950897</v>
-      </c>
-      <c r="P28" s="7">
-        <f t="shared" si="149"/>
-        <v>-0.3146883946267342</v>
-      </c>
-      <c r="Q28" s="7">
-        <f t="shared" si="149"/>
-        <v>-0.15216964461024926</v>
-      </c>
-      <c r="R28" s="7">
-        <f t="shared" si="149"/>
-        <v>-0.24560478199718716</v>
-      </c>
-      <c r="S28" s="7">
-        <f t="shared" ref="S28:AD28" si="150">S13/S3</f>
-        <v>-0.28244274809160314</v>
-      </c>
-      <c r="T28" s="7">
+        <v>-0.24691358024691357</v>
+      </c>
+      <c r="AE28" s="7">
+        <f t="shared" ref="AE28:AH28" si="150">AE13/AE3</f>
+        <v>-0.24603941267387935</v>
+      </c>
+      <c r="AF28" s="7">
         <f t="shared" si="150"/>
-        <v>-0.2880581867388361</v>
-      </c>
-      <c r="U28" s="7">
+        <v>-0.29841769223651338</v>
+      </c>
+      <c r="AG28" s="7">
         <f t="shared" si="150"/>
-        <v>-0.5796793509754683</v>
-      </c>
-      <c r="V28" s="7">
+        <v>-0.21815239776404827</v>
+      </c>
+      <c r="AH28" s="7">
         <f t="shared" si="150"/>
-        <v>-0.52124352331606216</v>
-      </c>
-      <c r="W28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.44224019533038328</v>
-      </c>
-      <c r="X28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.46092831962397185</v>
-      </c>
-      <c r="Y28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.42077958496915296</v>
-      </c>
-      <c r="Z28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.47379650620082681</v>
-      </c>
-      <c r="AA28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.37726194933233514</v>
-      </c>
-      <c r="AB28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.26648013430330159</v>
-      </c>
-      <c r="AC28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.30337323177366698</v>
-      </c>
-      <c r="AD28" s="7">
-        <f t="shared" si="150"/>
-        <v>-0.24691358024691357</v>
-      </c>
-      <c r="AE28" s="7">
-        <f t="shared" ref="AE28:AH28" si="151">AE13/AE3</f>
-        <v>-0.24603941267387935</v>
-      </c>
-      <c r="AF28" s="7">
+        <v>-0.23597319802237843</v>
+      </c>
+      <c r="AK28" s="7">
+        <f t="shared" ref="AK28:AX28" si="151">AK13/AK3</f>
+        <v>-0.2695384615384615</v>
+      </c>
+      <c r="AL28" s="7">
         <f t="shared" si="151"/>
-        <v>-0.29841769223651338</v>
-      </c>
-      <c r="AG28" s="7">
+        <v>-0.15047206923682141</v>
+      </c>
+      <c r="AM28" s="7">
         <f t="shared" si="151"/>
-        <v>-0.26210044052863429</v>
-      </c>
-      <c r="AH28" s="7">
+        <v>-0.28790994696395711</v>
+      </c>
+      <c r="AN28" s="7">
         <f t="shared" si="151"/>
-        <v>-0.23297474129150209</v>
-      </c>
-      <c r="AK28" s="7">
-        <f t="shared" ref="AK28:AX28" si="152">AK13/AK3</f>
-        <v>-0.2695384615384615</v>
-      </c>
-      <c r="AL28" s="7">
+        <v>-0.25791996665277195</v>
+      </c>
+      <c r="AO28" s="7">
+        <f t="shared" si="151"/>
+        <v>-0.41523595505617983</v>
+      </c>
+      <c r="AP28" s="7">
+        <f t="shared" si="151"/>
+        <v>-0.44977136324664169</v>
+      </c>
+      <c r="AQ28" s="7">
+        <f t="shared" si="151"/>
+        <v>-0.29516935036091063</v>
+      </c>
+      <c r="AR28" s="7">
+        <f t="shared" si="151"/>
+        <v>-0.24701978604563102</v>
+      </c>
+      <c r="AS28" s="7">
+        <f t="shared" si="151"/>
+        <v>-0.12779096557335898</v>
+      </c>
+      <c r="AT28" s="7">
+        <f t="shared" si="151"/>
+        <v>-5.2116150353586438E-2</v>
+      </c>
+      <c r="AU28" s="7">
+        <f t="shared" si="151"/>
+        <v>3.0197573041559327E-3</v>
+      </c>
+      <c r="AV28" s="7">
+        <f t="shared" si="151"/>
+        <v>4.2174220755591872E-2</v>
+      </c>
+      <c r="AW28" s="7">
+        <f t="shared" si="151"/>
+        <v>7.0104094051817903E-2</v>
+      </c>
+      <c r="AX28" s="7">
+        <f t="shared" si="151"/>
+        <v>9.0727028483962191E-2</v>
+      </c>
+      <c r="AY28" s="7">
+        <f t="shared" ref="AY28:BB28" si="152">AY13/AY3</f>
+        <v>0.10701987381223026</v>
+      </c>
+      <c r="AZ28" s="7">
         <f t="shared" si="152"/>
-        <v>-0.15047206923682141</v>
-      </c>
-      <c r="AM28" s="7">
+        <v>0.11945047594337756</v>
+      </c>
+      <c r="BA28" s="7">
         <f t="shared" si="152"/>
-        <v>-0.28790994696395711</v>
-      </c>
-      <c r="AN28" s="7">
+        <v>0.13142568296775467</v>
+      </c>
+      <c r="BB28" s="7">
         <f t="shared" si="152"/>
-        <v>-0.25791996665277195</v>
-      </c>
-      <c r="AO28" s="7">
-        <f t="shared" si="152"/>
-        <v>-0.41523595505617983</v>
-      </c>
-      <c r="AP28" s="7">
-        <f t="shared" si="152"/>
-        <v>-0.44977136324664169</v>
-      </c>
-      <c r="AQ28" s="7">
-        <f t="shared" si="152"/>
-        <v>-0.29516935036091063</v>
-      </c>
-      <c r="AR28" s="7">
-        <f t="shared" si="152"/>
-        <v>-0.2592972608125112</v>
-      </c>
-      <c r="AS28" s="7">
-        <f t="shared" si="152"/>
-        <v>-0.15162605258203868</v>
-      </c>
-      <c r="AT28" s="7">
-        <f t="shared" si="152"/>
-        <v>-7.306925887262769E-2</v>
-      </c>
-      <c r="AU28" s="7">
-        <f t="shared" si="152"/>
-        <v>-1.577772016529818E-2</v>
-      </c>
-      <c r="AV28" s="7">
-        <f t="shared" si="152"/>
-        <v>2.4956205351940118E-2</v>
-      </c>
-      <c r="AW28" s="7">
-        <f t="shared" si="152"/>
-        <v>5.4092116118641766E-2</v>
-      </c>
-      <c r="AX28" s="7">
-        <f t="shared" si="152"/>
-        <v>7.5523843899563042E-2</v>
-      </c>
-      <c r="AY28" s="7">
-        <f t="shared" ref="AY28:BB28" si="153">AY13/AY3</f>
-        <v>9.2448107308072888E-2</v>
-      </c>
-      <c r="AZ28" s="7">
-        <f t="shared" si="153"/>
-        <v>0.10535056003610177</v>
-      </c>
-      <c r="BA28" s="7">
-        <f t="shared" si="153"/>
-        <v>0.11778202137702877</v>
-      </c>
-      <c r="BB28" s="7">
-        <f t="shared" si="153"/>
-        <v>0.12975984727069825</v>
+        <v>0.14296232465206496</v>
       </c>
       <c r="BD28" t="s">
         <v>42</v>
       </c>
       <c r="BE28" s="5">
         <f>NPV(BE27,AR19:FK19)</f>
-        <v>12322.354963311001</v>
+        <v>15254.245708414473</v>
       </c>
     </row>
     <row r="29" spans="2:167" x14ac:dyDescent="0.3">
@@ -6303,184 +6297,184 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7">
-        <f t="shared" ref="G29:G30" si="154">G9/C9-1</f>
+        <f t="shared" ref="G29:G30" si="153">G9/C9-1</f>
         <v>0.56521739130434789</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" ref="H29:H30" si="155">H9/D9-1</f>
+        <f t="shared" ref="H29:H30" si="154">H9/D9-1</f>
         <v>0.51219512195121975</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" ref="I29:I30" si="156">I9/E9-1</f>
+        <f t="shared" ref="I29:I30" si="155">I9/E9-1</f>
         <v>-0.22005571030640669</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" ref="J29:J30" si="157">J9/F9-1</f>
+        <f t="shared" ref="J29:J30" si="156">J9/F9-1</f>
         <v>0.55714285714285738</v>
       </c>
       <c r="K29" s="7">
-        <f t="shared" ref="K29:K30" si="158">K9/G9-1</f>
+        <f t="shared" ref="K29:K30" si="157">K9/G9-1</f>
         <v>1.2870370370370368</v>
       </c>
       <c r="L29" s="7">
-        <f t="shared" ref="L29:L30" si="159">L9/H9-1</f>
+        <f t="shared" ref="L29:L30" si="158">L9/H9-1</f>
         <v>0.62096774193548399</v>
       </c>
       <c r="M29" s="7">
-        <f t="shared" ref="M29:M30" si="160">M9/I9-1</f>
+        <f t="shared" ref="M29:M30" si="159">M9/I9-1</f>
         <v>0.84642857142857153</v>
       </c>
       <c r="N29" s="7">
-        <f t="shared" ref="N29:N30" si="161">N9/J9-1</f>
+        <f t="shared" ref="N29:N30" si="160">N9/J9-1</f>
         <v>0.83792048929663543</v>
       </c>
       <c r="O29" s="7">
-        <f t="shared" ref="O29:O30" si="162">O9/K9-1</f>
+        <f t="shared" ref="O29:O30" si="161">O9/K9-1</f>
         <v>0.95546558704453433</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" ref="P29:P30" si="163">P9/L9-1</f>
+        <f t="shared" ref="P29:P30" si="162">P9/L9-1</f>
         <v>2.1019900497512438</v>
       </c>
       <c r="Q29" s="7">
-        <f t="shared" ref="Q29:Q30" si="164">Q9/M9-1</f>
+        <f t="shared" ref="Q29:Q30" si="163">Q9/M9-1</f>
         <v>1.67311411992263</v>
       </c>
       <c r="R29" s="7">
-        <f t="shared" ref="R29:R30" si="165">R9/N9-1</f>
+        <f t="shared" ref="R29:R30" si="164">R9/N9-1</f>
         <v>1.8885191347753749</v>
       </c>
       <c r="S29" s="7">
-        <f t="shared" ref="S29:S30" si="166">S9/O9-1</f>
+        <f t="shared" ref="S29:S30" si="165">S9/O9-1</f>
         <v>0.84057971014492772</v>
       </c>
       <c r="T29" s="7">
-        <f t="shared" ref="T29:T30" si="167">T9/P9-1</f>
+        <f t="shared" ref="T29:T30" si="166">T9/P9-1</f>
         <v>0.69847634322373708</v>
       </c>
       <c r="U29" s="7">
-        <f t="shared" ref="U29:U30" si="168">U9/Q9-1</f>
+        <f t="shared" ref="U29:U30" si="167">U9/Q9-1</f>
         <v>0.70477568740955143</v>
       </c>
       <c r="V29" s="7">
-        <f t="shared" ref="V29:V30" si="169">V9/R9-1</f>
+        <f t="shared" ref="V29:V30" si="168">V9/R9-1</f>
         <v>0.43087557603686655</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" ref="W29:W30" si="170">W9/S9-1</f>
+        <f t="shared" ref="W29:W30" si="169">W9/S9-1</f>
         <v>0.54949381327334068</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" ref="X29:X30" si="171">X9/T9-1</f>
+        <f t="shared" ref="X29:X30" si="170">X9/T9-1</f>
         <v>0.48866855524079322</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" ref="Y29:Y30" si="172">Y9/U9-1</f>
+        <f t="shared" ref="Y29:Y30" si="171">Y9/U9-1</f>
         <v>0.36502546689303927</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" ref="Z29:Z30" si="173">Z9/V9-1</f>
+        <f t="shared" ref="Z29:Z30" si="172">Z9/V9-1</f>
         <v>0.37318840579710155</v>
       </c>
       <c r="AA29" s="7">
-        <f t="shared" ref="AA29:AA30" si="174">AA9/W9-1</f>
+        <f t="shared" ref="AA29:AA30" si="173">AA9/W9-1</f>
         <v>0.31433756805807622</v>
       </c>
       <c r="AB29" s="7">
-        <f t="shared" ref="AB29:AB30" si="175">AB9/X9-1</f>
+        <f t="shared" ref="AB29:AB30" si="174">AB9/X9-1</f>
         <v>0.14716143355534395</v>
       </c>
       <c r="AC29" s="7">
-        <f t="shared" ref="AC29:AC30" si="176">AC9/Y9-1</f>
+        <f t="shared" ref="AC29:AC30" si="175">AC9/Y9-1</f>
         <v>0.13619402985074602</v>
       </c>
       <c r="AD29" s="7">
-        <f t="shared" ref="AD29:AD30" si="177">AD9/Z9-1</f>
+        <f t="shared" ref="AD29:AD30" si="176">AD9/Z9-1</f>
         <v>4.0750513046027503E-2</v>
       </c>
       <c r="AE29" s="7">
-        <f t="shared" ref="AE29:AE30" si="178">AE9/AA9-1</f>
+        <f t="shared" ref="AE29:AE30" si="177">AE9/AA9-1</f>
         <v>3.4520850593758645E-2</v>
       </c>
       <c r="AF29" s="7">
-        <f t="shared" ref="AF29:AF30" si="179">AF9/AB9-1</f>
+        <f t="shared" ref="AF29:AF30" si="178">AF9/AB9-1</f>
         <v>6.4418025988388194E-2</v>
       </c>
       <c r="AG29" s="7">
-        <f t="shared" ref="AG29:AG30" si="180">AG9/AC9-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AG29:AG30" si="179">AG9/AC9-1</f>
+        <v>9.0038314176245304E-2</v>
       </c>
       <c r="AH29" s="7">
-        <f t="shared" ref="AH29:AH30" si="181">AH9/AD9-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AH29:AH30" si="180">AH9/AD9-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AK29" s="7"/>
       <c r="AL29" s="7">
-        <f t="shared" ref="AL29:AW29" si="182">AL9/AK9-1</f>
+        <f t="shared" ref="AL29:AW29" si="181">AL9/AK9-1</f>
         <v>0.2296211251435134</v>
       </c>
       <c r="AM29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.88048552754435105</v>
       </c>
       <c r="AN29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>1.6469712015888778</v>
       </c>
       <c r="AO29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.63871693866066392</v>
       </c>
       <c r="AP29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.43486721611721602</v>
       </c>
       <c r="AQ29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>0.15213402473075366</v>
       </c>
       <c r="AR29" s="7">
-        <f t="shared" si="182"/>
-        <v>4.9585929926603045E-2</v>
+        <f t="shared" si="181"/>
+        <v>8.1983104833125875E-2</v>
       </c>
       <c r="AS29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW29" s="7">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="7">
-        <f t="shared" ref="AX29:AX30" si="183">AX9/AW9-1</f>
+        <f t="shared" ref="AX29:AX30" si="182">AX9/AW9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="7">
-        <f t="shared" ref="AY29:AY30" si="184">AY9/AX9-1</f>
+        <f t="shared" ref="AY29:AY30" si="183">AY9/AX9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="7">
-        <f t="shared" ref="AZ29:AZ30" si="185">AZ9/AY9-1</f>
+        <f t="shared" ref="AZ29:AZ30" si="184">AZ9/AY9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="7">
-        <f t="shared" ref="BA29:BA30" si="186">BA9/AZ9-1</f>
+        <f t="shared" ref="BA29:BA30" si="185">BA9/AZ9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB29" s="7">
-        <f t="shared" ref="BB29:BB30" si="187">BB9/BA9-1</f>
+        <f t="shared" ref="BB29:BB30" si="186">BB9/BA9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD29" t="s">
@@ -6488,7 +6482,7 @@
       </c>
       <c r="BE29" s="5">
         <f>Main!D8</f>
-        <v>3746.1</v>
+        <v>4228.4000000000005</v>
       </c>
       <c r="BG29" t="s">
         <v>75</v>
@@ -6503,192 +6497,192 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7">
+        <f t="shared" si="153"/>
+        <v>0.54385964912280715</v>
+      </c>
+      <c r="H30" s="7">
         <f t="shared" si="154"/>
-        <v>0.54385964912280715</v>
-      </c>
-      <c r="H30" s="7">
+        <v>0.36111111111111116</v>
+      </c>
+      <c r="I30" s="7">
         <f t="shared" si="155"/>
-        <v>0.36111111111111116</v>
-      </c>
-      <c r="I30" s="7">
+        <v>-0.23703703703703694</v>
+      </c>
+      <c r="J30" s="7">
         <f t="shared" si="156"/>
-        <v>-0.23703703703703694</v>
-      </c>
-      <c r="J30" s="7">
+        <v>0.60493827160493829</v>
+      </c>
+      <c r="K30" s="7">
         <f t="shared" si="157"/>
-        <v>0.60493827160493829</v>
-      </c>
-      <c r="K30" s="7">
+        <v>2.4772727272727271</v>
+      </c>
+      <c r="L30" s="7">
         <f t="shared" si="158"/>
-        <v>2.4772727272727271</v>
-      </c>
-      <c r="L30" s="7">
+        <v>0.90816326530612224</v>
+      </c>
+      <c r="M30" s="7">
         <f t="shared" si="159"/>
-        <v>0.90816326530612224</v>
-      </c>
-      <c r="M30" s="7">
+        <v>0.57281553398058227</v>
+      </c>
+      <c r="N30" s="7">
         <f t="shared" si="160"/>
-        <v>0.57281553398058227</v>
-      </c>
-      <c r="N30" s="7">
+        <v>1.4461538461538455</v>
+      </c>
+      <c r="O30" s="7">
         <f t="shared" si="161"/>
-        <v>1.4461538461538455</v>
-      </c>
-      <c r="O30" s="7">
+        <v>2.0849673202614381</v>
+      </c>
+      <c r="P30" s="7">
         <f t="shared" si="162"/>
-        <v>2.0849673202614381</v>
-      </c>
-      <c r="P30" s="7">
+        <v>4.2245989304812834</v>
+      </c>
+      <c r="Q30" s="7">
         <f t="shared" si="163"/>
-        <v>4.2245989304812834</v>
-      </c>
-      <c r="Q30" s="7">
+        <v>2.1851851851851856</v>
+      </c>
+      <c r="R30" s="7">
         <f t="shared" si="164"/>
-        <v>2.1851851851851856</v>
-      </c>
-      <c r="R30" s="7">
+        <v>0.86792452830188727</v>
+      </c>
+      <c r="S30" s="7">
         <f t="shared" si="165"/>
-        <v>0.86792452830188727</v>
-      </c>
-      <c r="S30" s="7">
+        <v>-0.38771186440677974</v>
+      </c>
+      <c r="T30" s="7">
         <f t="shared" si="166"/>
-        <v>-0.38771186440677974</v>
-      </c>
-      <c r="T30" s="7">
+        <v>-0.19447287615148412</v>
+      </c>
+      <c r="U30" s="7">
         <f t="shared" si="167"/>
-        <v>-0.19447287615148412</v>
-      </c>
-      <c r="U30" s="7">
+        <v>0.57364341085271309</v>
+      </c>
+      <c r="V30" s="7">
         <f t="shared" si="168"/>
-        <v>0.57364341085271309</v>
-      </c>
-      <c r="V30" s="7">
+        <v>0.34175084175084192</v>
+      </c>
+      <c r="W30" s="7">
         <f t="shared" si="169"/>
-        <v>0.34175084175084192</v>
-      </c>
-      <c r="W30" s="7">
+        <v>0.68858131487889263</v>
+      </c>
+      <c r="X30" s="7">
         <f t="shared" si="170"/>
-        <v>0.68858131487889263</v>
-      </c>
-      <c r="X30" s="7">
+        <v>0.22236340533672183</v>
+      </c>
+      <c r="Y30" s="7">
         <f t="shared" si="171"/>
-        <v>0.22236340533672183</v>
-      </c>
-      <c r="Y30" s="7">
+        <v>0.2007389162561577</v>
+      </c>
+      <c r="Z30" s="7">
         <f t="shared" si="172"/>
-        <v>0.2007389162561577</v>
-      </c>
-      <c r="Z30" s="7">
+        <v>0.23964868255959848</v>
+      </c>
+      <c r="AA30" s="7">
         <f t="shared" si="173"/>
-        <v>0.23964868255959848</v>
-      </c>
-      <c r="AA30" s="7">
+        <v>2.049180327868827E-3</v>
+      </c>
+      <c r="AB30" s="7">
         <f t="shared" si="174"/>
-        <v>2.049180327868827E-3</v>
-      </c>
-      <c r="AB30" s="7">
+        <v>9.7713097713097552E-2</v>
+      </c>
+      <c r="AC30" s="7">
         <f t="shared" si="175"/>
-        <v>9.7713097713097552E-2</v>
-      </c>
-      <c r="AC30" s="7">
+        <v>1.2307692307692353E-2</v>
+      </c>
+      <c r="AD30" s="7">
         <f t="shared" si="176"/>
-        <v>1.2307692307692353E-2</v>
-      </c>
-      <c r="AD30" s="7">
+        <v>6.578947368421062E-2</v>
+      </c>
+      <c r="AE30" s="7">
         <f t="shared" si="177"/>
-        <v>6.578947368421062E-2</v>
-      </c>
-      <c r="AE30" s="7">
+        <v>0.21779141104294486</v>
+      </c>
+      <c r="AF30" s="7">
         <f t="shared" si="178"/>
-        <v>0.21779141104294486</v>
-      </c>
-      <c r="AF30" s="7">
+        <v>0.44128787878787867</v>
+      </c>
+      <c r="AG30" s="7">
         <f t="shared" si="179"/>
-        <v>0.44128787878787867</v>
-      </c>
-      <c r="AG30" s="7">
+        <v>0.46909827760891587</v>
+      </c>
+      <c r="AH30" s="7">
         <f t="shared" si="180"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AH30" s="7">
-        <f t="shared" si="181"/>
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="AK30" s="7"/>
       <c r="AL30" s="7">
-        <f t="shared" ref="AL30:AW30" si="188">AL10/AK10-1</f>
+        <f t="shared" ref="AL30:AW30" si="187">AL10/AK10-1</f>
         <v>0.21449275362318865</v>
       </c>
       <c r="AM30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>1.3221957040572789</v>
       </c>
       <c r="AN30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>2.1151079136690649</v>
       </c>
       <c r="AO30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>-1.8805674694820307E-2</v>
       </c>
       <c r="AP30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>0.31170141223940839</v>
       </c>
       <c r="AQ30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>4.4347603178672035E-2</v>
       </c>
       <c r="AR30" s="7">
-        <f t="shared" si="188"/>
-        <v>0.45418507609229253</v>
+        <f t="shared" si="187"/>
+        <v>0.40179430535100624</v>
       </c>
       <c r="AS30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AT30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AU30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AV30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW30" s="7">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX30" s="7">
+        <f t="shared" si="182"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AY30" s="7">
         <f t="shared" si="183"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AY30" s="7">
+      <c r="AZ30" s="7">
         <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AZ30" s="7">
+      <c r="BA30" s="7">
         <f t="shared" si="185"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA30" s="7">
+      <c r="BB30" s="7">
         <f t="shared" si="186"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB30" s="7">
-        <f t="shared" si="187"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BD30" t="s">
         <v>44</v>
       </c>
       <c r="BE30" s="5">
         <f>BE28+BE29</f>
-        <v>16068.454963311002</v>
+        <v>19482.645708414475</v>
       </c>
     </row>
     <row r="31" spans="2:167" x14ac:dyDescent="0.3">
@@ -6696,211 +6690,211 @@
         <v>38</v>
       </c>
       <c r="C31" s="7">
-        <f t="shared" ref="C31:R31" si="189">C11/C3</f>
+        <f t="shared" ref="C31:R31" si="188">C11/C3</f>
         <v>0.14826498422712936</v>
       </c>
       <c r="D31" s="7">
+        <f t="shared" si="188"/>
+        <v>0.14588859416445621</v>
+      </c>
+      <c r="E31" s="7">
+        <f t="shared" si="188"/>
+        <v>0.13048498845265591</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="188"/>
+        <v>8.9357429718875517E-2</v>
+      </c>
+      <c r="G31" s="7">
+        <f t="shared" si="188"/>
+        <v>7.601809954751132E-2</v>
+      </c>
+      <c r="H31" s="7">
+        <f t="shared" si="188"/>
+        <v>8.5570469798657706E-2</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="188"/>
+        <v>9.6872616323417232E-2</v>
+      </c>
+      <c r="J31" s="7">
+        <f t="shared" si="188"/>
+        <v>9.1463414634146339E-2</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="188"/>
+        <v>9.7153465346534656E-2</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="188"/>
+        <v>6.9361277445109781E-2</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="188"/>
+        <v>5.1210797935688765E-2</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="188"/>
+        <v>5.129032258064517E-2</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" si="188"/>
+        <v>5.1679586563307491E-2</v>
+      </c>
+      <c r="P31" s="7">
+        <f t="shared" si="188"/>
+        <v>4.1841004184100417E-2</v>
+      </c>
+      <c r="Q31" s="7">
+        <f t="shared" si="188"/>
+        <v>3.8484193991753388E-2</v>
+      </c>
+      <c r="R31" s="7">
+        <f t="shared" si="188"/>
+        <v>4.8874824191279892E-2</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" ref="S31:AD31" si="189">S11/S3</f>
+        <v>5.4179854775646991E-2</v>
+      </c>
+      <c r="T31" s="7">
         <f t="shared" si="189"/>
-        <v>0.14588859416445621</v>
-      </c>
-      <c r="E31" s="7">
+        <v>4.4824086603518262E-2</v>
+      </c>
+      <c r="U31" s="7">
         <f t="shared" si="189"/>
-        <v>0.13048498845265591</v>
-      </c>
-      <c r="F31" s="7">
+        <v>6.200502221363724E-2</v>
+      </c>
+      <c r="V31" s="7">
         <f t="shared" si="189"/>
-        <v>8.9357429718875517E-2</v>
-      </c>
-      <c r="G31" s="7">
+        <v>5.1295336787564767E-2</v>
+      </c>
+      <c r="W31" s="7">
         <f t="shared" si="189"/>
-        <v>7.601809954751132E-2</v>
-      </c>
-      <c r="H31" s="7">
+        <v>4.0897298947047155E-2</v>
+      </c>
+      <c r="X31" s="7">
         <f t="shared" si="189"/>
-        <v>8.5570469798657706E-2</v>
-      </c>
-      <c r="I31" s="7">
+        <v>4.4506462984723862E-2</v>
+      </c>
+      <c r="Y31" s="7">
         <f t="shared" si="189"/>
-        <v>9.6872616323417232E-2</v>
-      </c>
-      <c r="J31" s="7">
+        <v>5.7347167694896235E-2</v>
+      </c>
+      <c r="Z31" s="7">
         <f t="shared" si="189"/>
-        <v>9.1463414634146339E-2</v>
-      </c>
-      <c r="K31" s="7">
+        <v>6.4675290038671826E-2</v>
+      </c>
+      <c r="AA31" s="7">
         <f t="shared" si="189"/>
-        <v>9.7153465346534656E-2</v>
-      </c>
-      <c r="L31" s="7">
+        <v>4.430300761262948E-2</v>
+      </c>
+      <c r="AB31" s="7">
         <f t="shared" si="189"/>
-        <v>6.9361277445109781E-2</v>
-      </c>
-      <c r="M31" s="7">
+        <v>4.0626748740906542E-2</v>
+      </c>
+      <c r="AC31" s="7">
         <f t="shared" si="189"/>
-        <v>5.1210797935688765E-2</v>
-      </c>
-      <c r="N31" s="7">
+        <v>5.7236126224156691E-2</v>
+      </c>
+      <c r="AD31" s="7">
         <f t="shared" si="189"/>
-        <v>5.129032258064517E-2</v>
-      </c>
-      <c r="O31" s="7">
-        <f t="shared" si="189"/>
-        <v>5.1679586563307491E-2</v>
-      </c>
-      <c r="P31" s="7">
-        <f t="shared" si="189"/>
-        <v>4.1841004184100417E-2</v>
-      </c>
-      <c r="Q31" s="7">
-        <f t="shared" si="189"/>
-        <v>3.8484193991753388E-2</v>
-      </c>
-      <c r="R31" s="7">
-        <f t="shared" si="189"/>
-        <v>4.8874824191279892E-2</v>
-      </c>
-      <c r="S31" s="7">
-        <f t="shared" ref="S31:AD31" si="190">S11/S3</f>
-        <v>5.4179854775646991E-2</v>
-      </c>
-      <c r="T31" s="7">
+        <v>5.0394656952033996E-2</v>
+      </c>
+      <c r="AE31" s="7">
+        <f t="shared" ref="AE31:AH31" si="190">AE11/AE3</f>
+        <v>4.6174652241112821E-2</v>
+      </c>
+      <c r="AF31" s="7">
         <f t="shared" si="190"/>
-        <v>4.4824086603518262E-2</v>
-      </c>
-      <c r="U31" s="7">
+        <v>4.8857222170815208E-2</v>
+      </c>
+      <c r="AG31" s="7">
         <f t="shared" si="190"/>
-        <v>6.200502221363724E-2</v>
-      </c>
-      <c r="V31" s="7">
+        <v>4.9352750809061485E-2</v>
+      </c>
+      <c r="AH31" s="7">
         <f t="shared" si="190"/>
-        <v>5.1295336787564767E-2</v>
-      </c>
-      <c r="W31" s="7">
-        <f t="shared" si="190"/>
-        <v>4.0897298947047155E-2</v>
-      </c>
-      <c r="X31" s="7">
-        <f t="shared" si="190"/>
-        <v>4.4506462984723862E-2</v>
-      </c>
-      <c r="Y31" s="7">
-        <f t="shared" si="190"/>
-        <v>5.7347167694896235E-2</v>
-      </c>
-      <c r="Z31" s="7">
-        <f t="shared" si="190"/>
-        <v>6.4675290038671826E-2</v>
-      </c>
-      <c r="AA31" s="7">
-        <f t="shared" si="190"/>
-        <v>4.430300761262948E-2</v>
-      </c>
-      <c r="AB31" s="7">
-        <f t="shared" si="190"/>
-        <v>4.0626748740906542E-2</v>
-      </c>
-      <c r="AC31" s="7">
-        <f t="shared" si="190"/>
-        <v>5.7236126224156691E-2</v>
-      </c>
-      <c r="AD31" s="7">
-        <f t="shared" si="190"/>
-        <v>5.0394656952033996E-2</v>
-      </c>
-      <c r="AE31" s="7">
-        <f t="shared" ref="AE31:AH31" si="191">AE11/AE3</f>
-        <v>4.6174652241112821E-2</v>
-      </c>
-      <c r="AF31" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="AK31" s="7">
+        <f t="shared" ref="AK31:AX31" si="191">AK11/AK3</f>
+        <v>0.12492307692307693</v>
+      </c>
+      <c r="AL31" s="7">
         <f t="shared" si="191"/>
-        <v>4.8857222170815208E-2</v>
-      </c>
-      <c r="AG31" s="7">
+        <v>8.8119590873328088E-2</v>
+      </c>
+      <c r="AM31" s="7">
+        <f t="shared" si="191"/>
+        <v>6.3210304145470284E-2</v>
+      </c>
+      <c r="AN31" s="7">
+        <f t="shared" si="191"/>
+        <v>4.5018757815756566E-2</v>
+      </c>
+      <c r="AO31" s="7">
+        <f t="shared" si="191"/>
+        <v>5.2764044943820226E-2</v>
+      </c>
+      <c r="AP31" s="7">
+        <f t="shared" si="191"/>
+        <v>5.2336381823378103E-2</v>
+      </c>
+      <c r="AQ31" s="7">
+        <f t="shared" si="191"/>
+        <v>4.8362021099389224E-2</v>
+      </c>
+      <c r="AR31" s="7">
+        <f t="shared" si="191"/>
+        <v>4.8749737599249228E-2</v>
+      </c>
+      <c r="AS31" s="7">
+        <f t="shared" si="191"/>
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="AT31" s="7">
         <f t="shared" si="191"/>
         <v>0.05</v>
       </c>
-      <c r="AH31" s="7">
+      <c r="AU31" s="7">
         <f t="shared" si="191"/>
         <v>0.05</v>
       </c>
-      <c r="AK31" s="7">
-        <f t="shared" ref="AK31:AX31" si="192">AK11/AK3</f>
-        <v>0.12492307692307693</v>
-      </c>
-      <c r="AL31" s="7">
-        <f t="shared" si="192"/>
-        <v>8.8119590873328088E-2</v>
-      </c>
-      <c r="AM31" s="7">
-        <f t="shared" si="192"/>
-        <v>6.3210304145470284E-2</v>
-      </c>
-      <c r="AN31" s="7">
-        <f t="shared" si="192"/>
-        <v>4.5018757815756566E-2</v>
-      </c>
-      <c r="AO31" s="7">
-        <f t="shared" si="192"/>
-        <v>5.2764044943820226E-2</v>
-      </c>
-      <c r="AP31" s="7">
-        <f t="shared" si="192"/>
-        <v>5.2336381823378103E-2</v>
-      </c>
-      <c r="AQ31" s="7">
-        <f t="shared" si="192"/>
-        <v>4.8362021099389224E-2</v>
-      </c>
-      <c r="AR31" s="7">
-        <f t="shared" si="192"/>
-        <v>4.8834288042824602E-2</v>
-      </c>
-      <c r="AS31" s="7">
+      <c r="AV31" s="7">
+        <f t="shared" si="191"/>
+        <v>0.05</v>
+      </c>
+      <c r="AW31" s="7">
+        <f t="shared" si="191"/>
+        <v>0.05</v>
+      </c>
+      <c r="AX31" s="7">
+        <f t="shared" si="191"/>
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="AY31" s="7">
+        <f t="shared" ref="AY31:BB31" si="192">AY11/AY3</f>
+        <v>0.05</v>
+      </c>
+      <c r="AZ31" s="7">
         <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
-      <c r="AT31" s="7">
+      <c r="BA31" s="7">
         <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
-      <c r="AU31" s="7">
+      <c r="BB31" s="7">
         <f t="shared" si="192"/>
         <v>0.05</v>
       </c>
-      <c r="AV31" s="7">
-        <f t="shared" si="192"/>
-        <v>0.05</v>
-      </c>
-      <c r="AW31" s="7">
-        <f t="shared" si="192"/>
-        <v>0.05</v>
-      </c>
-      <c r="AX31" s="7">
-        <f t="shared" si="192"/>
-        <v>0.05</v>
-      </c>
-      <c r="AY31" s="7">
-        <f t="shared" ref="AY31:BB31" si="193">AY11/AY3</f>
-        <v>0.05</v>
-      </c>
-      <c r="AZ31" s="7">
-        <f t="shared" si="193"/>
-        <v>4.9999999999999996E-2</v>
-      </c>
-      <c r="BA31" s="7">
-        <f t="shared" si="193"/>
-        <v>0.05</v>
-      </c>
-      <c r="BB31" s="7">
-        <f t="shared" si="193"/>
-        <v>0.05</v>
-      </c>
       <c r="BD31" t="s">
         <v>45</v>
       </c>
       <c r="BE31" s="4">
         <f>BE30/AW20</f>
-        <v>24.912333276451164</v>
+        <v>27.753056564692983</v>
       </c>
     </row>
     <row r="32" spans="2:167" x14ac:dyDescent="0.3">
@@ -6908,43 +6902,43 @@
         <v>29</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32:L32" si="194">C17/C16</f>
+        <f t="shared" ref="C32:L32" si="193">C17/C16</f>
         <v>0</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="M32" s="7">
@@ -6952,159 +6946,159 @@
         <v>0</v>
       </c>
       <c r="N32" s="7">
-        <f t="shared" ref="N32:R32" si="195">N17/N16</f>
+        <f t="shared" ref="N32:R32" si="194">N17/N16</f>
         <v>0.10436137071651093</v>
       </c>
       <c r="O32" s="7">
+        <f t="shared" si="194"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="7">
+        <f t="shared" si="194"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <f t="shared" si="194"/>
+        <v>1.2771392081736919E-2</v>
+      </c>
+      <c r="R32" s="7">
+        <f t="shared" si="194"/>
+        <v>-4.771642808452623E-3</v>
+      </c>
+      <c r="S32" s="7">
+        <f t="shared" ref="S32:AD32" si="195">S17/S16</f>
+        <v>-1.852995676343421E-3</v>
+      </c>
+      <c r="T32" s="7">
         <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="P32" s="7">
+        <v>1.6750418760469021E-3</v>
+      </c>
+      <c r="U32" s="7">
         <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="7">
+        <v>-1.3262599469496023E-3</v>
+      </c>
+      <c r="V32" s="7">
         <f t="shared" si="195"/>
-        <v>1.2771392081736919E-2</v>
-      </c>
-      <c r="R32" s="7">
+        <v>-1.1103400416377517E-2</v>
+      </c>
+      <c r="W32" s="7">
         <f t="shared" si="195"/>
-        <v>-4.771642808452623E-3</v>
-      </c>
-      <c r="S32" s="7">
-        <f t="shared" ref="S32:AD32" si="196">S17/S16</f>
-        <v>-1.852995676343421E-3</v>
-      </c>
-      <c r="T32" s="7">
+        <v>-2.6012634708286872E-3</v>
+      </c>
+      <c r="X32" s="7">
+        <f t="shared" si="195"/>
+        <v>4.1987403778866337E-3</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="195"/>
+        <v>-2.5152712899748474E-3</v>
+      </c>
+      <c r="Z32" s="7">
+        <f t="shared" si="195"/>
+        <v>-9.225092250922509E-4</v>
+      </c>
+      <c r="AA32" s="7">
+        <f t="shared" si="195"/>
+        <v>-4.0620384047267344E-3</v>
+      </c>
+      <c r="AB32" s="7">
+        <f t="shared" si="195"/>
+        <v>-4.8262548262548275E-4</v>
+      </c>
+      <c r="AC32" s="7">
+        <f t="shared" si="195"/>
+        <v>-1.25E-3</v>
+      </c>
+      <c r="AD32" s="7">
+        <f t="shared" si="195"/>
+        <v>-1.1915673693858845E-2</v>
+      </c>
+      <c r="AE32" s="7">
+        <f t="shared" ref="AE32:AH32" si="196">AE17/AE16</f>
+        <v>-4.1763341067285404E-3</v>
+      </c>
+      <c r="AF32" s="7">
         <f t="shared" si="196"/>
-        <v>1.6750418760469021E-3</v>
-      </c>
-      <c r="U32" s="7">
+        <v>-3.5855145213338118E-3</v>
+      </c>
+      <c r="AG32" s="7">
         <f t="shared" si="196"/>
-        <v>-1.3262599469496023E-3</v>
-      </c>
-      <c r="V32" s="7">
+        <v>-3.1164783794312423E-3</v>
+      </c>
+      <c r="AH32" s="7">
         <f t="shared" si="196"/>
-        <v>-1.1103400416377517E-2</v>
-      </c>
-      <c r="W32" s="7">
-        <f t="shared" si="196"/>
-        <v>-2.6012634708286872E-3</v>
-      </c>
-      <c r="X32" s="7">
-        <f t="shared" si="196"/>
-        <v>4.1987403778866337E-3</v>
-      </c>
-      <c r="Y32" s="7">
-        <f t="shared" si="196"/>
-        <v>-2.5152712899748474E-3</v>
-      </c>
-      <c r="Z32" s="7">
-        <f t="shared" si="196"/>
-        <v>-9.225092250922509E-4</v>
-      </c>
-      <c r="AA32" s="7">
-        <f t="shared" si="196"/>
-        <v>-4.0620384047267344E-3</v>
-      </c>
-      <c r="AB32" s="7">
-        <f t="shared" si="196"/>
-        <v>-4.8262548262548275E-4</v>
-      </c>
-      <c r="AC32" s="7">
-        <f t="shared" si="196"/>
-        <v>-1.25E-3</v>
-      </c>
-      <c r="AD32" s="7">
-        <f t="shared" si="196"/>
-        <v>-1.1915673693858845E-2</v>
-      </c>
-      <c r="AE32" s="7">
-        <f t="shared" ref="AE32:AH32" si="197">AE17/AE16</f>
-        <v>-4.1763341067285404E-3</v>
-      </c>
-      <c r="AF32" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="AK32" s="7">
+        <f t="shared" ref="AK32:AM32" si="197">AK17/AK16</f>
+        <v>0</v>
+      </c>
+      <c r="AL32" s="7">
         <f t="shared" si="197"/>
-        <v>-3.5855145213338118E-3</v>
-      </c>
-      <c r="AG32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="7">
         <f t="shared" si="197"/>
-        <v>0.01</v>
-      </c>
-      <c r="AH32" s="7">
-        <f t="shared" si="197"/>
-        <v>0.01</v>
-      </c>
-      <c r="AK32" s="7">
-        <f t="shared" ref="AK32:AM32" si="198">AK17/AK16</f>
-        <v>0</v>
-      </c>
-      <c r="AL32" s="7">
+        <v>2.5359576078728244E-2</v>
+      </c>
+      <c r="AN32" s="7">
+        <f t="shared" ref="AN32:AW32" si="198">AN17/AN16</f>
+        <v>5.953562214725146E-4</v>
+      </c>
+      <c r="AO32" s="7">
         <f t="shared" si="198"/>
-        <v>0</v>
-      </c>
-      <c r="AM32" s="7">
+        <v>-3.8676407391491185E-3</v>
+      </c>
+      <c r="AP32" s="7">
         <f t="shared" si="198"/>
-        <v>2.5359576078728244E-2</v>
-      </c>
-      <c r="AN32" s="7">
-        <f t="shared" ref="AN32:AW32" si="199">AN17/AN16</f>
-        <v>5.953562214725146E-4</v>
-      </c>
-      <c r="AO32" s="7">
+        <v>-4.3162983425414374E-4</v>
+      </c>
+      <c r="AQ32" s="7">
+        <f t="shared" si="198"/>
+        <v>-4.3794061098055975E-3</v>
+      </c>
+      <c r="AR32" s="7">
+        <f t="shared" si="198"/>
+        <v>2.6767654335625821E-4</v>
+      </c>
+      <c r="AS32" s="7">
+        <f t="shared" si="198"/>
+        <v>0</v>
+      </c>
+      <c r="AT32" s="7">
+        <f t="shared" si="198"/>
+        <v>0</v>
+      </c>
+      <c r="AU32" s="7">
+        <f t="shared" si="198"/>
+        <v>0</v>
+      </c>
+      <c r="AV32" s="7">
+        <f t="shared" si="198"/>
+        <v>0</v>
+      </c>
+      <c r="AW32" s="7">
+        <f t="shared" si="198"/>
+        <v>0</v>
+      </c>
+      <c r="AX32" s="7">
+        <f t="shared" ref="AX32:BB32" si="199">AX17/AX16</f>
+        <v>0</v>
+      </c>
+      <c r="AY32" s="7">
         <f t="shared" si="199"/>
-        <v>-3.8676407391491185E-3</v>
-      </c>
-      <c r="AP32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="7">
         <f t="shared" si="199"/>
-        <v>-4.3162983425414374E-4</v>
-      </c>
-      <c r="AQ32" s="7">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="7">
         <f t="shared" si="199"/>
-        <v>-4.3794061098055975E-3</v>
-      </c>
-      <c r="AR32" s="7">
+        <v>0</v>
+      </c>
+      <c r="BB32" s="7">
         <f t="shared" si="199"/>
-        <v>3.1676101434354649E-3</v>
-      </c>
-      <c r="AS32" s="7">
-        <f t="shared" si="199"/>
-        <v>0</v>
-      </c>
-      <c r="AT32" s="7">
-        <f t="shared" si="199"/>
-        <v>0</v>
-      </c>
-      <c r="AU32" s="7">
-        <f t="shared" si="199"/>
-        <v>0</v>
-      </c>
-      <c r="AV32" s="7">
-        <f t="shared" si="199"/>
-        <v>0</v>
-      </c>
-      <c r="AW32" s="7">
-        <f t="shared" si="199"/>
-        <v>0</v>
-      </c>
-      <c r="AX32" s="7">
-        <f t="shared" ref="AX32:BB32" si="200">AX17/AX16</f>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="7">
-        <f t="shared" si="200"/>
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="7">
-        <f t="shared" si="200"/>
-        <v>0</v>
-      </c>
-      <c r="BA32" s="7">
-        <f t="shared" si="200"/>
-        <v>0</v>
-      </c>
-      <c r="BB32" s="7">
-        <f t="shared" si="200"/>
         <v>0</v>
       </c>
       <c r="BD32" t="s">
@@ -7112,16 +7106,219 @@
       </c>
       <c r="BE32" s="4">
         <f>Main!D3</f>
-        <v>128.47</v>
+        <v>116.53</v>
       </c>
     </row>
     <row r="33" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="7">
+        <f>C19/C3</f>
+        <v>-0.22712933753943226</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" ref="D33:AH33" si="200">D19/D3</f>
+        <v>-0.31299734748010588</v>
+      </c>
+      <c r="E33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.45727482678983844</v>
+      </c>
+      <c r="F33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.10642570281124501</v>
+      </c>
+      <c r="G33" s="7">
+        <f t="shared" si="200"/>
+        <v>-8.0542986425339358E-2</v>
+      </c>
+      <c r="H33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.10234899328859058</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.13272311212814647</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.22086720867208678</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.46039603960396053</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.37075848303393227</v>
+      </c>
+      <c r="M33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.19333068678046852</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.17967741935483866</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.34651162790697665</v>
+      </c>
+      <c r="P33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.30852235190486677</v>
+      </c>
+      <c r="Q33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.14549381504025119</v>
+      </c>
+      <c r="R33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.2521097046413503</v>
+      </c>
+      <c r="S33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.29864084900390997</v>
+      </c>
+      <c r="T33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.29854533152909313</v>
+      </c>
+      <c r="U33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.57542978559010993</v>
+      </c>
+      <c r="V33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.50051813471502582</v>
+      </c>
+      <c r="W33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.40927819319395708</v>
+      </c>
+      <c r="X33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.41495299647473566</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.38881099270891745</v>
+      </c>
+      <c r="Z33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.4319242565675423</v>
+      </c>
+      <c r="AA33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.33770123549232517</v>
+      </c>
+      <c r="AB33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.23055400111919411</v>
+      </c>
+      <c r="AC33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.26028291621327526</v>
+      </c>
+      <c r="AD33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.2219186399514268</v>
+      </c>
+      <c r="AE33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.20778593508500764</v>
+      </c>
+      <c r="AF33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.2577033404275007</v>
+      </c>
+      <c r="AG33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.18814357163871734</v>
+      </c>
+      <c r="AH33" s="7">
+        <f t="shared" si="200"/>
+        <v>-0.21115051608986043</v>
+      </c>
+      <c r="AK33" s="7">
+        <f t="shared" ref="AK33:BB33" si="201">AK19/AK3</f>
+        <v>-0.27138461538461534</v>
+      </c>
+      <c r="AL33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.1398505114083399</v>
+      </c>
+      <c r="AM33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.27394739690442682</v>
+      </c>
+      <c r="AN33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.25620050020842011</v>
+      </c>
+      <c r="AO33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.4155505617977529</v>
+      </c>
+      <c r="AP33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.41151043155187178</v>
+      </c>
+      <c r="AQ33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.25960577456968353</v>
+      </c>
+      <c r="AR33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.21435003148809015</v>
+      </c>
+      <c r="AS33" s="7">
+        <f t="shared" si="201"/>
+        <v>-0.10102958367299521</v>
+      </c>
+      <c r="AT33" s="7">
+        <f t="shared" si="201"/>
+        <v>-2.9782864301680669E-2</v>
+      </c>
+      <c r="AU33" s="7">
+        <f t="shared" si="201"/>
+        <v>2.2146295204030546E-2</v>
+      </c>
+      <c r="AV33" s="7">
+        <f t="shared" si="201"/>
+        <v>5.902774892986215E-2</v>
+      </c>
+      <c r="AW33" s="7">
+        <f t="shared" si="201"/>
+        <v>8.5410413740331328E-2</v>
+      </c>
+      <c r="AX33" s="7">
+        <f t="shared" si="201"/>
+        <v>0.10492950982091877</v>
+      </c>
+      <c r="AY33" s="7">
+        <f t="shared" si="201"/>
+        <v>0.12034670256280054</v>
+      </c>
+      <c r="AZ33" s="7">
+        <f t="shared" si="201"/>
+        <v>0.13210454048259093</v>
+      </c>
+      <c r="BA33" s="7">
+        <f t="shared" si="201"/>
+        <v>0.14343243089201391</v>
+      </c>
+      <c r="BB33" s="7">
+        <f t="shared" si="201"/>
+        <v>0.1543462393117121</v>
+      </c>
       <c r="BD33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="BE33" s="10">
         <f>BE31/BE32-1</f>
-        <v>-0.80608443001127761</v>
+        <v>-0.76183766785640628</v>
       </c>
     </row>
     <row r="34" spans="2:57" x14ac:dyDescent="0.3">
@@ -7137,11 +7334,11 @@
         <v>31</v>
       </c>
       <c r="AO35" s="9">
-        <f t="shared" ref="AO35:AP35" si="201">AO19</f>
+        <f t="shared" ref="AO35:AP35" si="202">AO19</f>
         <v>-924.60000000000025</v>
       </c>
       <c r="AP35" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>-1151.8999999999996</v>
       </c>
       <c r="AQ35" s="9">
@@ -7149,48 +7346,48 @@
         <v>-935.1</v>
       </c>
       <c r="AR35" s="9">
-        <f t="shared" ref="AR35:BB35" si="202">AR19</f>
-        <v>-990.7532943999995</v>
+        <f t="shared" ref="AR35:BB35" si="203">AR19</f>
+        <v>-1041.5225160000002</v>
       </c>
       <c r="AS35" s="9">
-        <f t="shared" si="202"/>
-        <v>-662.29255026000021</v>
+        <f t="shared" si="203"/>
+        <v>-598.89888630000041</v>
       </c>
       <c r="AT35" s="9">
-        <f t="shared" si="202"/>
-        <v>-308.71102741379997</v>
+        <f t="shared" si="203"/>
+        <v>-208.33076672100182</v>
       </c>
       <c r="AU35" s="9">
-        <f t="shared" si="202"/>
-        <v>41.694191276759675</v>
+        <f t="shared" si="203"/>
+        <v>178.15001959259897</v>
       </c>
       <c r="AV35" s="9">
-        <f t="shared" si="202"/>
-        <v>362.66395139279012</v>
+        <f t="shared" si="203"/>
+        <v>531.81310351276693</v>
       </c>
       <c r="AW35" s="9">
-        <f t="shared" si="202"/>
-        <v>642.42508812541246</v>
+        <f t="shared" si="203"/>
+        <v>838.76468355085308</v>
       </c>
       <c r="AX35" s="9">
-        <f t="shared" si="202"/>
-        <v>882.27116344414139</v>
+        <f t="shared" si="203"/>
+        <v>1102.5815784407882</v>
       </c>
       <c r="AY35" s="9">
-        <f t="shared" si="202"/>
-        <v>1098.2870918753292</v>
+        <f t="shared" si="203"/>
+        <v>1340.4578078006627</v>
       </c>
       <c r="AZ35" s="9">
-        <f t="shared" si="202"/>
-        <v>1283.6830698904685</v>
+        <f t="shared" si="203"/>
+        <v>1544.9911540000182</v>
       </c>
       <c r="BA35" s="9">
-        <f t="shared" si="202"/>
-        <v>1479.8825831967754</v>
+        <f t="shared" si="203"/>
+        <v>1761.3469447841414</v>
       </c>
       <c r="BB35" s="9">
-        <f t="shared" si="202"/>
-        <v>1687.445724325838</v>
+        <f t="shared" si="203"/>
+        <v>1990.1366736093557</v>
       </c>
     </row>
     <row r="36" spans="2:57" x14ac:dyDescent="0.3">
@@ -7211,43 +7408,43 @@
         <v>237.72000000000003</v>
       </c>
       <c r="AS36" s="5">
-        <f t="shared" ref="AS36:BB36" si="203">AR36*1.05</f>
+        <f t="shared" ref="AS36:BB36" si="204">AR36*1.05</f>
         <v>249.60600000000005</v>
       </c>
       <c r="AT36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>262.08630000000005</v>
       </c>
       <c r="AU36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>275.19061500000009</v>
       </c>
       <c r="AV36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>288.9501457500001</v>
       </c>
       <c r="AW36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>303.39765303750011</v>
       </c>
       <c r="AX36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>318.56753568937512</v>
       </c>
       <c r="AY36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>334.49591247384387</v>
       </c>
       <c r="AZ36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>351.22070809753609</v>
       </c>
       <c r="BA36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>368.78174350241289</v>
       </c>
       <c r="BB36" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>387.22083067753357</v>
       </c>
     </row>
@@ -7285,7 +7482,7 @@
         <v>1203.7534740000001</v>
       </c>
       <c r="AW37" s="5">
-        <f t="shared" ref="AW37" si="204">AV37*0.9</f>
+        <f t="shared" ref="AW37" si="205">AV37*0.9</f>
         <v>1083.3781266000001</v>
       </c>
       <c r="AX37" s="5">
@@ -7293,19 +7490,19 @@
         <v>866.70250128000009</v>
       </c>
       <c r="AY37" s="5">
-        <f t="shared" ref="AY37:BB37" si="205">AX37*0.8</f>
+        <f t="shared" ref="AY37:BB37" si="206">AX37*0.8</f>
         <v>693.36200102400016</v>
       </c>
       <c r="AZ37" s="5">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>554.68960081920011</v>
       </c>
       <c r="BA37" s="5">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>443.75168065536013</v>
       </c>
       <c r="BB37" s="5">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>355.00134452428813</v>
       </c>
     </row>
@@ -7327,43 +7524,43 @@
         <v>121.643</v>
       </c>
       <c r="AS38" s="5">
-        <f t="shared" ref="AS38:BB38" si="206">AR38*1.03</f>
+        <f t="shared" ref="AS38:BB38" si="207">AR38*1.03</f>
         <v>125.29229000000001</v>
       </c>
       <c r="AT38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>129.0510587</v>
       </c>
       <c r="AU38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>132.922590461</v>
       </c>
       <c r="AV38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>136.91026817483001</v>
       </c>
       <c r="AW38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>141.01757622007491</v>
       </c>
       <c r="AX38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>145.24810350667715</v>
       </c>
       <c r="AY38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>149.60554661187749</v>
       </c>
       <c r="AZ38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>154.09371301023381</v>
       </c>
       <c r="BA38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>158.71652440054083</v>
       </c>
       <c r="BB38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>163.47802013255708</v>
       </c>
     </row>
@@ -7996,47 +8193,47 @@
       </c>
       <c r="AR52" s="9">
         <f>AR35+SUM(AR36:AR51)</f>
-        <v>587.56970560000036</v>
+        <v>536.80048399999964</v>
       </c>
       <c r="AS52" s="9">
-        <f t="shared" ref="AS52:BB52" si="207">AS35+SUM(AS36:AS51)</f>
-        <v>1053.4617397399998</v>
+        <f t="shared" ref="AS52:BB52" si="208">AS35+SUM(AS36:AS51)</f>
+        <v>1116.8554036999997</v>
       </c>
       <c r="AT52" s="9">
-        <f t="shared" si="207"/>
-        <v>1490.3251312862003</v>
+        <f t="shared" si="208"/>
+        <v>1590.7053919789985</v>
       </c>
       <c r="AU52" s="9">
-        <f t="shared" si="207"/>
-        <v>1787.31125673776</v>
+        <f t="shared" si="208"/>
+        <v>1923.7670850535992</v>
       </c>
       <c r="AV52" s="9">
-        <f t="shared" si="207"/>
-        <v>1992.2778393176202</v>
+        <f t="shared" si="208"/>
+        <v>2161.4269914375973</v>
       </c>
       <c r="AW52" s="9">
-        <f t="shared" si="207"/>
-        <v>2170.2184439829875</v>
+        <f t="shared" si="208"/>
+        <v>2366.5580394084282</v>
       </c>
       <c r="AX52" s="9">
-        <f t="shared" si="207"/>
-        <v>2212.7893039201936</v>
+        <f t="shared" si="208"/>
+        <v>2433.0997189168406</v>
       </c>
       <c r="AY52" s="9">
-        <f t="shared" si="207"/>
-        <v>2275.7505519850511</v>
+        <f t="shared" si="208"/>
+        <v>2517.9212679103844</v>
       </c>
       <c r="AZ52" s="9">
-        <f t="shared" si="207"/>
-        <v>2343.6870918174382</v>
+        <f t="shared" si="208"/>
+        <v>2604.9951759269879</v>
       </c>
       <c r="BA52" s="9">
-        <f t="shared" si="207"/>
-        <v>2451.1325317550891</v>
+        <f t="shared" si="208"/>
+        <v>2732.5968933424551</v>
       </c>
       <c r="BB52" s="9">
-        <f t="shared" si="207"/>
-        <v>2593.1459196602168</v>
+        <f t="shared" si="208"/>
+        <v>2895.8368689437348</v>
       </c>
     </row>
     <row r="53" spans="2:146" x14ac:dyDescent="0.3">
@@ -8058,43 +8255,43 @@
         <v>197.56</v>
       </c>
       <c r="AS53" s="5">
-        <f t="shared" ref="AS53:BB53" si="208">AR53*1.1</f>
+        <f t="shared" ref="AS53:BB53" si="209">AR53*1.1</f>
         <v>217.31600000000003</v>
       </c>
       <c r="AT53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>239.04760000000005</v>
       </c>
       <c r="AU53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>262.95236000000006</v>
       </c>
       <c r="AV53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>289.2475960000001</v>
       </c>
       <c r="AW53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>318.17235560000012</v>
       </c>
       <c r="AX53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>349.98959116000015</v>
       </c>
       <c r="AY53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>384.98855027600018</v>
       </c>
       <c r="AZ53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>423.48740530360021</v>
       </c>
       <c r="BA53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>465.83614583396024</v>
       </c>
       <c r="BB53" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>512.41976041735631</v>
       </c>
     </row>
@@ -8116,451 +8313,451 @@
       </c>
       <c r="AR54" s="9">
         <f>AR52-AR53</f>
-        <v>390.00970560000036</v>
+        <v>339.24048399999964</v>
       </c>
       <c r="AS54" s="9">
-        <f t="shared" ref="AS54:BB54" si="209">AS52-AS53</f>
-        <v>836.14573973999973</v>
+        <f t="shared" ref="AS54:BB54" si="210">AS52-AS53</f>
+        <v>899.53940369999964</v>
       </c>
       <c r="AT54" s="9">
-        <f t="shared" si="209"/>
-        <v>1251.2775312862002</v>
+        <f t="shared" si="210"/>
+        <v>1351.6577919789984</v>
       </c>
       <c r="AU54" s="9">
-        <f t="shared" si="209"/>
-        <v>1524.35889673776</v>
+        <f t="shared" si="210"/>
+        <v>1660.8147250535992</v>
       </c>
       <c r="AV54" s="9">
-        <f t="shared" si="209"/>
-        <v>1703.03024331762</v>
+        <f t="shared" si="210"/>
+        <v>1872.1793954375971</v>
       </c>
       <c r="AW54" s="9">
-        <f t="shared" si="209"/>
-        <v>1852.0460883829874</v>
+        <f t="shared" si="210"/>
+        <v>2048.385683808428</v>
       </c>
       <c r="AX54" s="9">
-        <f t="shared" si="209"/>
-        <v>1862.7997127601934</v>
+        <f t="shared" si="210"/>
+        <v>2083.1101277568405</v>
       </c>
       <c r="AY54" s="9">
-        <f t="shared" si="209"/>
-        <v>1890.7620017090508</v>
+        <f t="shared" si="210"/>
+        <v>2132.9327176343841</v>
       </c>
       <c r="AZ54" s="9">
-        <f t="shared" si="209"/>
-        <v>1920.1996865138381</v>
+        <f t="shared" si="210"/>
+        <v>2181.5077706233878</v>
       </c>
       <c r="BA54" s="9">
-        <f t="shared" si="209"/>
-        <v>1985.2963859211288</v>
+        <f t="shared" si="210"/>
+        <v>2266.7607475084951</v>
       </c>
       <c r="BB54" s="9">
-        <f t="shared" si="209"/>
-        <v>2080.7261592428604</v>
+        <f t="shared" si="210"/>
+        <v>2383.4171085263783</v>
       </c>
       <c r="BC54" s="1">
         <f>BB54*(1+$BE$26)</f>
-        <v>2059.918897650432</v>
+        <v>2359.5829374411146</v>
       </c>
       <c r="BD54" s="1">
-        <f t="shared" ref="BD54:DO54" si="210">BC54*(1+$BE$26)</f>
-        <v>2039.3197086739276</v>
+        <f t="shared" ref="BD54:DO54" si="211">BC54*(1+$BE$26)</f>
+        <v>2335.9871080667035</v>
       </c>
       <c r="BE54" s="1">
-        <f t="shared" si="210"/>
-        <v>2018.9265115871883</v>
+        <f t="shared" si="211"/>
+        <v>2312.6272369860367</v>
       </c>
       <c r="BF54" s="1">
-        <f t="shared" si="210"/>
-        <v>1998.7372464713164</v>
+        <f t="shared" si="211"/>
+        <v>2289.5009646161761</v>
       </c>
       <c r="BG54" s="1">
-        <f t="shared" si="210"/>
-        <v>1978.7498740066032</v>
+        <f t="shared" si="211"/>
+        <v>2266.6059549700144</v>
       </c>
       <c r="BH54" s="1">
-        <f t="shared" si="210"/>
-        <v>1958.9623752665373</v>
+        <f t="shared" si="211"/>
+        <v>2243.9398954203143</v>
       </c>
       <c r="BI54" s="1">
-        <f t="shared" si="210"/>
-        <v>1939.3727515138719</v>
+        <f t="shared" si="211"/>
+        <v>2221.5004964661111</v>
       </c>
       <c r="BJ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1919.9790239987331</v>
+        <f t="shared" si="211"/>
+        <v>2199.28549150145</v>
       </c>
       <c r="BK54" s="1">
-        <f t="shared" si="210"/>
-        <v>1900.7792337587457</v>
+        <f t="shared" si="211"/>
+        <v>2177.2926365864355</v>
       </c>
       <c r="BL54" s="1">
-        <f t="shared" si="210"/>
-        <v>1881.7714414211582</v>
+        <f t="shared" si="211"/>
+        <v>2155.5197102205711</v>
       </c>
       <c r="BM54" s="1">
-        <f t="shared" si="210"/>
-        <v>1862.9537270069466</v>
+        <f t="shared" si="211"/>
+        <v>2133.9645131183656</v>
       </c>
       <c r="BN54" s="1">
-        <f t="shared" si="210"/>
-        <v>1844.3241897368771</v>
+        <f t="shared" si="211"/>
+        <v>2112.6248679871819</v>
       </c>
       <c r="BO54" s="1">
-        <f t="shared" si="210"/>
-        <v>1825.8809478395083</v>
+        <f t="shared" si="211"/>
+        <v>2091.49861930731</v>
       </c>
       <c r="BP54" s="1">
-        <f t="shared" si="210"/>
-        <v>1807.6221383611132</v>
+        <f t="shared" si="211"/>
+        <v>2070.5836331142368</v>
       </c>
       <c r="BQ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1789.545916977502</v>
+        <f t="shared" si="211"/>
+        <v>2049.8777967830943</v>
       </c>
       <c r="BR54" s="1">
-        <f t="shared" si="210"/>
-        <v>1771.650457807727</v>
+        <f t="shared" si="211"/>
+        <v>2029.3790188152634</v>
       </c>
       <c r="BS54" s="1">
-        <f t="shared" si="210"/>
-        <v>1753.9339532296497</v>
+        <f t="shared" si="211"/>
+        <v>2009.0852286271108</v>
       </c>
       <c r="BT54" s="1">
-        <f t="shared" si="210"/>
-        <v>1736.3946136973532</v>
+        <f t="shared" si="211"/>
+        <v>1988.9943763408396</v>
       </c>
       <c r="BU54" s="1">
-        <f t="shared" si="210"/>
-        <v>1719.0306675603797</v>
+        <f t="shared" si="211"/>
+        <v>1969.1044325774312</v>
       </c>
       <c r="BV54" s="1">
-        <f t="shared" si="210"/>
-        <v>1701.8403608847759</v>
+        <f t="shared" si="211"/>
+        <v>1949.4133882516569</v>
       </c>
       <c r="BW54" s="1">
-        <f t="shared" si="210"/>
-        <v>1684.8219572759281</v>
+        <f t="shared" si="211"/>
+        <v>1929.9192543691404</v>
       </c>
       <c r="BX54" s="1">
-        <f t="shared" si="210"/>
-        <v>1667.9737377031688</v>
+        <f t="shared" si="211"/>
+        <v>1910.6200618254491</v>
       </c>
       <c r="BY54" s="1">
-        <f t="shared" si="210"/>
-        <v>1651.2940003261372</v>
+        <f t="shared" si="211"/>
+        <v>1891.5138612071946</v>
       </c>
       <c r="BZ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1634.7810603228759</v>
+        <f t="shared" si="211"/>
+        <v>1872.5987225951226</v>
       </c>
       <c r="CA54" s="1">
-        <f t="shared" si="210"/>
-        <v>1618.4332497196472</v>
+        <f t="shared" si="211"/>
+        <v>1853.8727353691713</v>
       </c>
       <c r="CB54" s="1">
-        <f t="shared" si="210"/>
-        <v>1602.2489172224507</v>
+        <f t="shared" si="211"/>
+        <v>1835.3340080154796</v>
       </c>
       <c r="CC54" s="1">
-        <f t="shared" si="210"/>
-        <v>1586.2264280502261</v>
+        <f t="shared" si="211"/>
+        <v>1816.9806679353248</v>
       </c>
       <c r="CD54" s="1">
-        <f t="shared" si="210"/>
-        <v>1570.3641637697237</v>
+        <f t="shared" si="211"/>
+        <v>1798.8108612559715</v>
       </c>
       <c r="CE54" s="1">
-        <f t="shared" si="210"/>
-        <v>1554.6605221320265</v>
+        <f t="shared" si="211"/>
+        <v>1780.8227526434118</v>
       </c>
       <c r="CF54" s="1">
-        <f t="shared" si="210"/>
-        <v>1539.1139169107062</v>
+        <f t="shared" si="211"/>
+        <v>1763.0145251169777</v>
       </c>
       <c r="CG54" s="1">
-        <f t="shared" si="210"/>
-        <v>1523.7227777415992</v>
+        <f t="shared" si="211"/>
+        <v>1745.3843798658079</v>
       </c>
       <c r="CH54" s="1">
-        <f t="shared" si="210"/>
-        <v>1508.4855499641833</v>
+        <f t="shared" si="211"/>
+        <v>1727.9305360671499</v>
       </c>
       <c r="CI54" s="1">
-        <f t="shared" si="210"/>
-        <v>1493.4006944645414</v>
+        <f t="shared" si="211"/>
+        <v>1710.6512307064784</v>
       </c>
       <c r="CJ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1478.4666875198959</v>
+        <f t="shared" si="211"/>
+        <v>1693.5447183994136</v>
       </c>
       <c r="CK54" s="1">
-        <f t="shared" si="210"/>
-        <v>1463.6820206446969</v>
+        <f t="shared" si="211"/>
+        <v>1676.6092712154193</v>
       </c>
       <c r="CL54" s="1">
-        <f t="shared" si="210"/>
-        <v>1449.0452004382498</v>
+        <f t="shared" si="211"/>
+        <v>1659.8431785032651</v>
       </c>
       <c r="CM54" s="1">
-        <f t="shared" si="210"/>
-        <v>1434.5547484338674</v>
+        <f t="shared" si="211"/>
+        <v>1643.2447467182324</v>
       </c>
       <c r="CN54" s="1">
-        <f t="shared" si="210"/>
-        <v>1420.2092009495286</v>
+        <f t="shared" si="211"/>
+        <v>1626.81229925105</v>
       </c>
       <c r="CO54" s="1">
-        <f t="shared" si="210"/>
-        <v>1406.0071089400333</v>
+        <f t="shared" si="211"/>
+        <v>1610.5441762585394</v>
       </c>
       <c r="CP54" s="1">
-        <f t="shared" si="210"/>
-        <v>1391.947037850633</v>
+        <f t="shared" si="211"/>
+        <v>1594.4387344959541</v>
       </c>
       <c r="CQ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1378.0275674721267</v>
+        <f t="shared" si="211"/>
+        <v>1578.4943471509946</v>
       </c>
       <c r="CR54" s="1">
-        <f t="shared" si="210"/>
-        <v>1364.2472917974055</v>
+        <f t="shared" si="211"/>
+        <v>1562.7094036794847</v>
       </c>
       <c r="CS54" s="1">
-        <f t="shared" si="210"/>
-        <v>1350.6048188794314</v>
+        <f t="shared" si="211"/>
+        <v>1547.0823096426898</v>
       </c>
       <c r="CT54" s="1">
-        <f t="shared" si="210"/>
-        <v>1337.0987706906371</v>
+        <f t="shared" si="211"/>
+        <v>1531.6114865462628</v>
       </c>
       <c r="CU54" s="1">
-        <f t="shared" si="210"/>
-        <v>1323.7277829837308</v>
+        <f t="shared" si="211"/>
+        <v>1516.2953716808001</v>
       </c>
       <c r="CV54" s="1">
-        <f t="shared" si="210"/>
-        <v>1310.4905051538935</v>
+        <f t="shared" si="211"/>
+        <v>1501.1324179639921</v>
       </c>
       <c r="CW54" s="1">
-        <f t="shared" si="210"/>
-        <v>1297.3856001023546</v>
+        <f t="shared" si="211"/>
+        <v>1486.1210937843521</v>
       </c>
       <c r="CX54" s="1">
-        <f t="shared" si="210"/>
-        <v>1284.4117441013311</v>
+        <f t="shared" si="211"/>
+        <v>1471.2598828465086</v>
       </c>
       <c r="CY54" s="1">
-        <f t="shared" si="210"/>
-        <v>1271.5676266603177</v>
+        <f t="shared" si="211"/>
+        <v>1456.5472840180435</v>
       </c>
       <c r="CZ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1258.8519503937146</v>
+        <f t="shared" si="211"/>
+        <v>1441.9818111778629</v>
       </c>
       <c r="DA54" s="1">
-        <f t="shared" si="210"/>
-        <v>1246.2634308897775</v>
+        <f t="shared" si="211"/>
+        <v>1427.5619930660844</v>
       </c>
       <c r="DB54" s="1">
-        <f t="shared" si="210"/>
-        <v>1233.8007965808797</v>
+        <f t="shared" si="211"/>
+        <v>1413.2863731354234</v>
       </c>
       <c r="DC54" s="1">
-        <f t="shared" si="210"/>
-        <v>1221.4627886150708</v>
+        <f t="shared" si="211"/>
+        <v>1399.1535094040692</v>
       </c>
       <c r="DD54" s="1">
-        <f t="shared" si="210"/>
-        <v>1209.2481607289201</v>
+        <f t="shared" si="211"/>
+        <v>1385.1619743100284</v>
       </c>
       <c r="DE54" s="1">
-        <f t="shared" si="210"/>
-        <v>1197.1556791216308</v>
+        <f t="shared" si="211"/>
+        <v>1371.310354566928</v>
       </c>
       <c r="DF54" s="1">
-        <f t="shared" si="210"/>
-        <v>1185.1841223304145</v>
+        <f t="shared" si="211"/>
+        <v>1357.5972510212587</v>
       </c>
       <c r="DG54" s="1">
-        <f t="shared" si="210"/>
-        <v>1173.3322811071105</v>
+        <f t="shared" si="211"/>
+        <v>1344.0212785110461</v>
       </c>
       <c r="DH54" s="1">
-        <f t="shared" si="210"/>
-        <v>1161.5989582960394</v>
+        <f t="shared" si="211"/>
+        <v>1330.5810657259358</v>
       </c>
       <c r="DI54" s="1">
-        <f t="shared" si="210"/>
-        <v>1149.9829687130791</v>
+        <f t="shared" si="211"/>
+        <v>1317.2752550686764</v>
       </c>
       <c r="DJ54" s="1">
-        <f t="shared" si="210"/>
-        <v>1138.4831390259483</v>
+        <f t="shared" si="211"/>
+        <v>1304.1025025179897</v>
       </c>
       <c r="DK54" s="1">
-        <f t="shared" si="210"/>
-        <v>1127.0983076356888</v>
+        <f t="shared" si="211"/>
+        <v>1291.0614774928099</v>
       </c>
       <c r="DL54" s="1">
-        <f t="shared" si="210"/>
-        <v>1115.8273245593318</v>
+        <f t="shared" si="211"/>
+        <v>1278.1508627178819</v>
       </c>
       <c r="DM54" s="1">
-        <f t="shared" si="210"/>
-        <v>1104.6690513137385</v>
+        <f t="shared" si="211"/>
+        <v>1265.3693540907029</v>
       </c>
       <c r="DN54" s="1">
-        <f t="shared" si="210"/>
-        <v>1093.622360800601</v>
+        <f t="shared" si="211"/>
+        <v>1252.715660549796</v>
       </c>
       <c r="DO54" s="1">
-        <f t="shared" si="210"/>
-        <v>1082.686137192595</v>
+        <f t="shared" si="211"/>
+        <v>1240.188503944298</v>
       </c>
       <c r="DP54" s="1">
-        <f t="shared" ref="DP54:EP54" si="211">DO54*(1+$BE$26)</f>
-        <v>1071.8592758206689</v>
+        <f t="shared" ref="DP54:EP54" si="212">DO54*(1+$BE$26)</f>
+        <v>1227.786618904855</v>
       </c>
       <c r="DQ54" s="1">
-        <f t="shared" si="211"/>
-        <v>1061.1406830624621</v>
+        <f t="shared" si="212"/>
+        <v>1215.5087527158064</v>
       </c>
       <c r="DR54" s="1">
-        <f t="shared" si="211"/>
-        <v>1050.5292762318375</v>
+        <f t="shared" si="212"/>
+        <v>1203.3536651886484</v>
       </c>
       <c r="DS54" s="1">
-        <f t="shared" si="211"/>
-        <v>1040.0239834695192</v>
+        <f t="shared" si="212"/>
+        <v>1191.3201285367618</v>
       </c>
       <c r="DT54" s="1">
-        <f t="shared" si="211"/>
-        <v>1029.623743634824</v>
+        <f t="shared" si="212"/>
+        <v>1179.4069272513941</v>
       </c>
       <c r="DU54" s="1">
-        <f t="shared" si="211"/>
-        <v>1019.3275061984757</v>
+        <f t="shared" si="212"/>
+        <v>1167.6128579788801</v>
       </c>
       <c r="DV54" s="1">
-        <f t="shared" si="211"/>
-        <v>1009.1342311364909</v>
+        <f t="shared" si="212"/>
+        <v>1155.9367293990913</v>
       </c>
       <c r="DW54" s="1">
-        <f t="shared" si="211"/>
-        <v>999.04288882512606</v>
+        <f t="shared" si="212"/>
+        <v>1144.3773621051005</v>
       </c>
       <c r="DX54" s="1">
-        <f t="shared" si="211"/>
-        <v>989.05245993687481</v>
+        <f t="shared" si="212"/>
+        <v>1132.9335884840496</v>
       </c>
       <c r="DY54" s="1">
-        <f t="shared" si="211"/>
-        <v>979.16193533750607</v>
+        <f t="shared" si="212"/>
+        <v>1121.6042525992091</v>
       </c>
       <c r="DZ54" s="1">
-        <f t="shared" si="211"/>
-        <v>969.37031598413103</v>
+        <f t="shared" si="212"/>
+        <v>1110.3882100732169</v>
       </c>
       <c r="EA54" s="1">
-        <f t="shared" si="211"/>
-        <v>959.67661282428969</v>
+        <f t="shared" si="212"/>
+        <v>1099.2843279724848</v>
       </c>
       <c r="EB54" s="1">
-        <f t="shared" si="211"/>
-        <v>950.07984669604673</v>
+        <f t="shared" si="212"/>
+        <v>1088.2914846927599</v>
       </c>
       <c r="EC54" s="1">
-        <f t="shared" si="211"/>
-        <v>940.5790482290862</v>
+        <f t="shared" si="212"/>
+        <v>1077.4085698458323</v>
       </c>
       <c r="ED54" s="1">
-        <f t="shared" si="211"/>
-        <v>931.17325774679534</v>
+        <f t="shared" si="212"/>
+        <v>1066.634484147374</v>
       </c>
       <c r="EE54" s="1">
-        <f t="shared" si="211"/>
-        <v>921.86152516932736</v>
+        <f t="shared" si="212"/>
+        <v>1055.9681393059002</v>
       </c>
       <c r="EF54" s="1">
-        <f t="shared" si="211"/>
-        <v>912.64290991763403</v>
+        <f t="shared" si="212"/>
+        <v>1045.4084579128412</v>
       </c>
       <c r="EG54" s="1">
-        <f t="shared" si="211"/>
-        <v>903.51648081845769</v>
+        <f t="shared" si="212"/>
+        <v>1034.9543733337127</v>
       </c>
       <c r="EH54" s="1">
-        <f t="shared" si="211"/>
-        <v>894.48131601027308</v>
+        <f t="shared" si="212"/>
+        <v>1024.6048296003755</v>
       </c>
       <c r="EI54" s="1">
-        <f t="shared" si="211"/>
-        <v>885.53650285017034</v>
+        <f t="shared" si="212"/>
+        <v>1014.3587813043717</v>
       </c>
       <c r="EJ54" s="1">
-        <f t="shared" si="211"/>
-        <v>876.68113782166859</v>
+        <f t="shared" si="212"/>
+        <v>1004.215193491328</v>
       </c>
       <c r="EK54" s="1">
-        <f t="shared" si="211"/>
-        <v>867.91432644345184</v>
+        <f t="shared" si="212"/>
+        <v>994.17304155641477</v>
       </c>
       <c r="EL54" s="1">
-        <f t="shared" si="211"/>
-        <v>859.23518317901733</v>
+        <f t="shared" si="212"/>
+        <v>984.23131114085061</v>
       </c>
       <c r="EM54" s="1">
-        <f t="shared" si="211"/>
-        <v>850.64283134722712</v>
+        <f t="shared" si="212"/>
+        <v>974.38899802944206</v>
       </c>
       <c r="EN54" s="1">
-        <f t="shared" si="211"/>
-        <v>842.13640303375485</v>
+        <f t="shared" si="212"/>
+        <v>964.64510804914767</v>
       </c>
       <c r="EO54" s="1">
-        <f t="shared" si="211"/>
-        <v>833.71503900341725</v>
+        <f t="shared" si="212"/>
+        <v>954.99865696865618</v>
       </c>
       <c r="EP54" s="1">
-        <f t="shared" si="211"/>
-        <v>825.37788861338311</v>
+        <f t="shared" si="212"/>
+        <v>945.44867039896963</v>
       </c>
     </row>
     <row r="56" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE56" s="5">
         <f>NPV(BE27,AR54:EP54)</f>
-        <v>23253.763191710452</v>
+        <v>26184.529468639561</v>
       </c>
     </row>
     <row r="57" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE57" s="5">
         <f>Main!D8</f>
-        <v>3746.1</v>
+        <v>4228.4000000000005</v>
       </c>
     </row>
     <row r="58" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE58" s="5">
         <f>BE56+BE57</f>
-        <v>26999.86319171045</v>
+        <v>30412.929468639562</v>
       </c>
     </row>
     <row r="59" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE59" s="4">
         <f>BE58/BB20</f>
-        <v>41.860253010403802</v>
+        <v>43.323261351338409</v>
       </c>
     </row>
     <row r="60" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE60" s="4">
         <f>Main!D3</f>
-        <v>128.47</v>
+        <v>116.53</v>
       </c>
     </row>
     <row r="61" spans="2:146" x14ac:dyDescent="0.3">
       <c r="BE61" s="10">
         <f>BE59/BE60-1</f>
-        <v>-0.67416320533662488</v>
+        <v>-0.62822224876565347</v>
       </c>
     </row>
   </sheetData>
